--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709781</v>
+        <v>127706915</v>
       </c>
       <c r="B6" t="n">
-        <v>92620</v>
+        <v>58520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>208249</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811479</v>
+        <v>811694</v>
       </c>
       <c r="R6" t="n">
-        <v>7391142</v>
+        <v>7390899</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,60 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709774</v>
+        <v>127706921</v>
       </c>
       <c r="B7" t="n">
-        <v>91591</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811658</v>
+        <v>811722</v>
       </c>
       <c r="R7" t="n">
-        <v>7390945</v>
+        <v>7390955</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127709721</v>
+        <v>127706923</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811493</v>
+        <v>811648</v>
       </c>
       <c r="R8" t="n">
-        <v>7391183</v>
+        <v>7390971</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127706915</v>
+        <v>127706928</v>
       </c>
       <c r="B9" t="n">
-        <v>58520</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811694</v>
+        <v>811509</v>
       </c>
       <c r="R9" t="n">
-        <v>7390899</v>
+        <v>7391152</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1451,48 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127706921</v>
+        <v>127709781</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>92620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811722</v>
+        <v>811479</v>
       </c>
       <c r="R10" t="n">
-        <v>7390955</v>
+        <v>7391142</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,60 +1536,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706923</v>
+        <v>127709774</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>91591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811648</v>
+        <v>811658</v>
       </c>
       <c r="R11" t="n">
-        <v>7390971</v>
+        <v>7390945</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127706928</v>
+        <v>127709721</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811509</v>
+        <v>811493</v>
       </c>
       <c r="R12" t="n">
-        <v>7391152</v>
+        <v>7391183</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1730,12 +1730,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127709692</v>
+        <v>127706933</v>
       </c>
       <c r="B54" t="n">
-        <v>79636</v>
+        <v>78424</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5793,37 +5793,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811591</v>
+        <v>811536</v>
       </c>
       <c r="R54" t="n">
-        <v>7391072</v>
+        <v>7391018</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5867,22 +5867,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709771</v>
+        <v>127706919</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>92813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5890,37 +5890,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811735</v>
+        <v>811446</v>
       </c>
       <c r="R55" t="n">
-        <v>7391006</v>
+        <v>7391045</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,22 +5964,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709792</v>
+        <v>127709717</v>
       </c>
       <c r="B56" t="n">
-        <v>92620</v>
+        <v>79042</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5987,21 +5987,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6011,10 +6011,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811619</v>
+        <v>811625</v>
       </c>
       <c r="R56" t="n">
-        <v>7391036</v>
+        <v>7390984</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6073,10 +6073,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127706933</v>
+        <v>127709702</v>
       </c>
       <c r="B57" t="n">
-        <v>78424</v>
+        <v>79636</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6084,37 +6084,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811536</v>
+        <v>811715</v>
       </c>
       <c r="R57" t="n">
-        <v>7391018</v>
+        <v>7391028</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6158,22 +6158,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127706919</v>
+        <v>127709692</v>
       </c>
       <c r="B58" t="n">
-        <v>92813</v>
+        <v>79636</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6181,37 +6181,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811446</v>
+        <v>811591</v>
       </c>
       <c r="R58" t="n">
-        <v>7391045</v>
+        <v>7391072</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6255,44 +6255,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709717</v>
+        <v>127709771</v>
       </c>
       <c r="B59" t="n">
-        <v>79042</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811625</v>
+        <v>811735</v>
       </c>
       <c r="R59" t="n">
-        <v>7390984</v>
+        <v>7391006</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6364,32 +6364,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709702</v>
+        <v>127709792</v>
       </c>
       <c r="B60" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811715</v>
+        <v>811619</v>
       </c>
       <c r="R60" t="n">
-        <v>7391028</v>
+        <v>7391036</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6778,32 +6778,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127709737</v>
+        <v>127709748</v>
       </c>
       <c r="B64" t="n">
-        <v>92813</v>
+        <v>58031</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811493</v>
+        <v>811439</v>
       </c>
       <c r="R64" t="n">
-        <v>7391027</v>
+        <v>7391070</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6875,32 +6875,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127709748</v>
+        <v>127709737</v>
       </c>
       <c r="B65" t="n">
-        <v>58031</v>
+        <v>92813</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>2079</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811439</v>
+        <v>811493</v>
       </c>
       <c r="R65" t="n">
-        <v>7391070</v>
+        <v>7391027</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7761,10 +7761,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709754</v>
+        <v>127709696</v>
       </c>
       <c r="B74" t="n">
-        <v>78776</v>
+        <v>79636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7772,21 +7772,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811518</v>
+        <v>811519</v>
       </c>
       <c r="R74" t="n">
-        <v>7391069</v>
+        <v>7391067</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7858,10 +7858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709696</v>
+        <v>127709772</v>
       </c>
       <c r="B75" t="n">
-        <v>79636</v>
+        <v>82859</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7869,21 +7869,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811519</v>
+        <v>811763</v>
       </c>
       <c r="R75" t="n">
-        <v>7391067</v>
+        <v>7390963</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709772</v>
+        <v>127709805</v>
       </c>
       <c r="B76" t="n">
-        <v>82859</v>
+        <v>78424</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811763</v>
+        <v>811635</v>
       </c>
       <c r="R76" t="n">
-        <v>7390963</v>
+        <v>7391001</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8052,10 +8052,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709805</v>
+        <v>127709762</v>
       </c>
       <c r="B77" t="n">
-        <v>78424</v>
+        <v>79018</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,21 +8063,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811635</v>
+        <v>811718</v>
       </c>
       <c r="R77" t="n">
-        <v>7391001</v>
+        <v>7390806</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8149,10 +8149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709762</v>
+        <v>127709701</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811718</v>
+        <v>811632</v>
       </c>
       <c r="R78" t="n">
-        <v>7390806</v>
+        <v>7391030</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709701</v>
+        <v>127709754</v>
       </c>
       <c r="B79" t="n">
-        <v>79636</v>
+        <v>78776</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8257,21 +8257,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811632</v>
+        <v>811518</v>
       </c>
       <c r="R79" t="n">
-        <v>7391030</v>
+        <v>7391069</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8537,10 +8537,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709738</v>
+        <v>127709755</v>
       </c>
       <c r="B82" t="n">
-        <v>92813</v>
+        <v>78776</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8548,21 +8548,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8572,10 +8572,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811577</v>
+        <v>811542</v>
       </c>
       <c r="R82" t="n">
-        <v>7391006</v>
+        <v>7391054</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8634,32 +8634,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127709755</v>
+        <v>127709760</v>
       </c>
       <c r="B83" t="n">
-        <v>78776</v>
+        <v>91491</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8669,10 +8669,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811542</v>
+        <v>811582</v>
       </c>
       <c r="R83" t="n">
-        <v>7391054</v>
+        <v>7391002</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8731,32 +8731,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709760</v>
+        <v>127709738</v>
       </c>
       <c r="B84" t="n">
-        <v>91491</v>
+        <v>92813</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8766,10 +8766,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811582</v>
+        <v>811577</v>
       </c>
       <c r="R84" t="n">
-        <v>7391002</v>
+        <v>7391006</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9895,32 +9895,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B96" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R96" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9992,49 +9992,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709799</v>
+        <v>127709783</v>
       </c>
       <c r="B97" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811707</v>
+        <v>811387</v>
       </c>
       <c r="R97" t="n">
-        <v>7390860</v>
+        <v>7391146</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10075,7 +10071,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10094,10 +10089,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709693</v>
+        <v>127709769</v>
       </c>
       <c r="B98" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10105,21 +10100,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10129,10 +10124,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811486</v>
+        <v>811672</v>
       </c>
       <c r="R98" t="n">
-        <v>7391112</v>
+        <v>7390924</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10191,7 +10186,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709783</v>
+        <v>127709795</v>
       </c>
       <c r="B99" t="n">
         <v>92620</v>
@@ -10226,10 +10221,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811387</v>
+        <v>811676</v>
       </c>
       <c r="R99" t="n">
-        <v>7391146</v>
+        <v>7391004</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10288,10 +10283,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709769</v>
+        <v>127709799</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>92614</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10299,34 +10294,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811672</v>
+        <v>811707</v>
       </c>
       <c r="R100" t="n">
-        <v>7390924</v>
+        <v>7390860</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10367,6 +10366,7 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709720</v>
+        <v>127709804</v>
       </c>
       <c r="B111" t="n">
-        <v>57658</v>
+        <v>78424</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11370,21 +11370,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11394,10 +11394,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811515</v>
+        <v>811452</v>
       </c>
       <c r="R111" t="n">
-        <v>7391165</v>
+        <v>7391056</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11456,10 +11456,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709707</v>
+        <v>127709697</v>
       </c>
       <c r="B112" t="n">
-        <v>57661</v>
+        <v>79636</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11467,42 +11467,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811874</v>
+        <v>811625</v>
       </c>
       <c r="R112" t="n">
-        <v>7390830</v>
+        <v>7390969</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11537,11 +11529,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -11559,17 +11546,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709804</v>
+        <v>127709801</v>
       </c>
       <c r="B113" t="n">
-        <v>78424</v>
+        <v>92614</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11577,21 +11564,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11601,10 +11588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811452</v>
+        <v>811615</v>
       </c>
       <c r="R113" t="n">
-        <v>7391056</v>
+        <v>7390990</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11663,32 +11650,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709697</v>
+        <v>127709726</v>
       </c>
       <c r="B114" t="n">
-        <v>79636</v>
+        <v>92624</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11698,10 +11685,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811625</v>
+        <v>811638</v>
       </c>
       <c r="R114" t="n">
-        <v>7390969</v>
+        <v>7391044</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11760,10 +11747,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709801</v>
+        <v>127709720</v>
       </c>
       <c r="B115" t="n">
-        <v>92614</v>
+        <v>57658</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11771,21 +11758,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11795,10 +11782,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811615</v>
+        <v>811515</v>
       </c>
       <c r="R115" t="n">
-        <v>7390990</v>
+        <v>7391165</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11857,45 +11844,53 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127709726</v>
+        <v>127709707</v>
       </c>
       <c r="B116" t="n">
-        <v>92624</v>
+        <v>57661</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811638</v>
+        <v>811874</v>
       </c>
       <c r="R116" t="n">
-        <v>7391044</v>
+        <v>7390830</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11930,6 +11925,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11947,7 +11947,7 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127706926</v>
+        <v>127709763</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,17 +706,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811754</v>
+        <v>811692</v>
       </c>
       <c r="R2" t="n">
-        <v>7390851</v>
+        <v>7390815</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127709734</v>
+        <v>127706926</v>
       </c>
       <c r="B3" t="n">
-        <v>79042</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811573</v>
+        <v>811754</v>
       </c>
       <c r="R3" t="n">
-        <v>7391001</v>
+        <v>7390851</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>127709784</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709763</v>
+        <v>127709734</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811692</v>
+        <v>811573</v>
       </c>
       <c r="R5" t="n">
-        <v>7390815</v>
+        <v>7391001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127706915</v>
+        <v>127709781</v>
       </c>
       <c r="B6" t="n">
-        <v>58520</v>
+        <v>92622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811694</v>
+        <v>811479</v>
       </c>
       <c r="R6" t="n">
-        <v>7390899</v>
+        <v>7391142</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1148,60 +1148,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127706921</v>
+        <v>127709774</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811722</v>
+        <v>811658</v>
       </c>
       <c r="R7" t="n">
-        <v>7390955</v>
+        <v>7390945</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127706923</v>
+        <v>127709721</v>
       </c>
       <c r="B8" t="n">
-        <v>78777</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811648</v>
+        <v>811493</v>
       </c>
       <c r="R8" t="n">
-        <v>7390971</v>
+        <v>7391183</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127706928</v>
+        <v>127706921</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811509</v>
+        <v>811722</v>
       </c>
       <c r="R9" t="n">
-        <v>7391152</v>
+        <v>7390955</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1451,48 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127709781</v>
+        <v>127706923</v>
       </c>
       <c r="B10" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811479</v>
+        <v>811648</v>
       </c>
       <c r="R10" t="n">
-        <v>7391142</v>
+        <v>7390971</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,60 +1536,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127709774</v>
+        <v>127706928</v>
       </c>
       <c r="B11" t="n">
-        <v>91591</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811658</v>
+        <v>811509</v>
       </c>
       <c r="R11" t="n">
-        <v>7390945</v>
+        <v>7391152</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127709721</v>
+        <v>127709710</v>
       </c>
       <c r="B12" t="n">
-        <v>57658</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1673,17 +1673,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811493</v>
+        <v>811505</v>
       </c>
       <c r="R12" t="n">
-        <v>7391183</v>
+        <v>7391045</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1718,6 +1726,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1735,63 +1748,55 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709710</v>
+        <v>127706915</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>58522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811505</v>
+        <v>811694</v>
       </c>
       <c r="R13" t="n">
-        <v>7391045</v>
+        <v>7390899</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1821,11 +1826,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1840,22 +1840,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127706925</v>
+        <v>127709694</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811866</v>
+        <v>811441</v>
       </c>
       <c r="R14" t="n">
-        <v>7390863</v>
+        <v>7391158</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,12 +1937,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1952,7 +1952,7 @@
         <v>127706914</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127709694</v>
+        <v>127709695</v>
       </c>
       <c r="B16" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811441</v>
+        <v>811430</v>
       </c>
       <c r="R16" t="n">
-        <v>7391158</v>
+        <v>7391046</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709695</v>
+        <v>127709699</v>
       </c>
       <c r="B17" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811430</v>
+        <v>811707</v>
       </c>
       <c r="R17" t="n">
-        <v>7391046</v>
+        <v>7390941</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709699</v>
+        <v>127706925</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811707</v>
+        <v>811866</v>
       </c>
       <c r="R18" t="n">
-        <v>7390941</v>
+        <v>7390863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
         <v>127709709</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         <v>127709800</v>
       </c>
       <c r="B20" t="n">
-        <v>92614</v>
+        <v>92616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>127709704</v>
       </c>
       <c r="B21" t="n">
-        <v>90365</v>
+        <v>90367</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>127709797</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2738,45 +2738,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709698</v>
+        <v>127709725</v>
       </c>
       <c r="B23" t="n">
-        <v>79636</v>
+        <v>92626</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811656</v>
+        <v>811692</v>
       </c>
       <c r="R23" t="n">
-        <v>7390942</v>
+        <v>7390871</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2817,6 +2820,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2835,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709731</v>
+        <v>127709698</v>
       </c>
       <c r="B24" t="n">
-        <v>79042</v>
+        <v>79638</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811484</v>
+        <v>811656</v>
       </c>
       <c r="R24" t="n">
-        <v>7391038</v>
+        <v>7390942</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2932,48 +2936,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709725</v>
+        <v>127709731</v>
       </c>
       <c r="B25" t="n">
-        <v>92624</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811692</v>
+        <v>811484</v>
       </c>
       <c r="R25" t="n">
-        <v>7390871</v>
+        <v>7391038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3014,7 +3015,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>127706927</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709758</v>
+        <v>127709722</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811621</v>
+        <v>811476</v>
       </c>
       <c r="R27" t="n">
-        <v>7390981</v>
+        <v>7391149</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709730</v>
+        <v>127709703</v>
       </c>
       <c r="B28" t="n">
-        <v>79042</v>
+        <v>79609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811452</v>
+        <v>811724</v>
       </c>
       <c r="R28" t="n">
-        <v>7391057</v>
+        <v>7390998</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3306,6 +3306,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3324,32 +3325,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709790</v>
+        <v>127709741</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3360,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811610</v>
+        <v>811489</v>
       </c>
       <c r="R29" t="n">
-        <v>7391012</v>
+        <v>7391186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,32 +3422,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709703</v>
+        <v>127709790</v>
       </c>
       <c r="B30" t="n">
-        <v>79607</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811724</v>
+        <v>811610</v>
       </c>
       <c r="R30" t="n">
-        <v>7390998</v>
+        <v>7391012</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3500,7 +3501,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3519,10 +3519,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709736</v>
+        <v>127709786</v>
       </c>
       <c r="B31" t="n">
-        <v>79042</v>
+        <v>92622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811662</v>
+        <v>811612</v>
       </c>
       <c r="R31" t="n">
-        <v>7390926</v>
+        <v>7390987</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3616,32 +3616,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709741</v>
+        <v>127709779</v>
       </c>
       <c r="B32" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3651,10 +3651,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811489</v>
+        <v>811561</v>
       </c>
       <c r="R32" t="n">
-        <v>7391186</v>
+        <v>7391108</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709786</v>
+        <v>127709796</v>
       </c>
       <c r="B33" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811612</v>
+        <v>811672</v>
       </c>
       <c r="R33" t="n">
-        <v>7390987</v>
+        <v>7391010</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709722</v>
+        <v>127709758</v>
       </c>
       <c r="B34" t="n">
-        <v>57658</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811476</v>
+        <v>811621</v>
       </c>
       <c r="R34" t="n">
-        <v>7391149</v>
+        <v>7390981</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3907,10 +3907,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127709779</v>
+        <v>127709730</v>
       </c>
       <c r="B35" t="n">
-        <v>92620</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3918,21 +3918,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3942,10 +3942,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811561</v>
+        <v>811452</v>
       </c>
       <c r="R35" t="n">
-        <v>7391108</v>
+        <v>7391057</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4004,10 +4004,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127709796</v>
+        <v>127709736</v>
       </c>
       <c r="B36" t="n">
-        <v>92620</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,21 +4015,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811672</v>
+        <v>811662</v>
       </c>
       <c r="R36" t="n">
-        <v>7391010</v>
+        <v>7390926</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709768</v>
+        <v>127709756</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811776</v>
+        <v>811538</v>
       </c>
       <c r="R37" t="n">
-        <v>7390918</v>
+        <v>7391022</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709780</v>
+        <v>127709768</v>
       </c>
       <c r="B38" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811475</v>
+        <v>811776</v>
       </c>
       <c r="R38" t="n">
-        <v>7391196</v>
+        <v>7390918</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4298,7 +4298,7 @@
         <v>127709766</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709756</v>
+        <v>127709708</v>
       </c>
       <c r="B40" t="n">
-        <v>78776</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,34 +4403,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811538</v>
+        <v>811580</v>
       </c>
       <c r="R40" t="n">
-        <v>7391022</v>
+        <v>7391090</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4465,6 +4473,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4482,60 +4495,52 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709708</v>
+        <v>127709780</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>92622</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811580</v>
+        <v>811475</v>
       </c>
       <c r="R41" t="n">
-        <v>7391090</v>
+        <v>7391196</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4570,11 +4575,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4592,55 +4592,55 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127706917</v>
+        <v>127709735</v>
       </c>
       <c r="B42" t="n">
-        <v>57661</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811865</v>
+        <v>811626</v>
       </c>
       <c r="R42" t="n">
-        <v>7390848</v>
+        <v>7390972</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4670,11 +4670,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4689,44 +4684,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127709735</v>
+        <v>127709752</v>
       </c>
       <c r="B43" t="n">
-        <v>79042</v>
+        <v>78778</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4736,10 +4731,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811626</v>
+        <v>811490</v>
       </c>
       <c r="R43" t="n">
-        <v>7390972</v>
+        <v>7391186</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4798,10 +4793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127709744</v>
+        <v>127706917</v>
       </c>
       <c r="B44" t="n">
-        <v>78777</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4809,37 +4804,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811539</v>
+        <v>811865</v>
       </c>
       <c r="R44" t="n">
-        <v>7391022</v>
+        <v>7390848</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4869,6 +4864,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4883,22 +4883,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127709752</v>
+        <v>127709712</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4906,34 +4906,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811490</v>
+        <v>811420</v>
       </c>
       <c r="R45" t="n">
-        <v>7391186</v>
+        <v>7391078</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4968,6 +4976,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -4985,17 +4998,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127709712</v>
+        <v>127709744</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>78779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5003,42 +5016,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811420</v>
+        <v>811539</v>
       </c>
       <c r="R46" t="n">
-        <v>7391078</v>
+        <v>7391022</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5073,11 +5078,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5095,17 +5095,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127706932</v>
+        <v>127709782</v>
       </c>
       <c r="B47" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5133,17 +5133,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811449</v>
+        <v>811426</v>
       </c>
       <c r="R47" t="n">
-        <v>7391067</v>
+        <v>7391161</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5187,22 +5187,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127709782</v>
+        <v>127706932</v>
       </c>
       <c r="B48" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5230,17 +5230,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811426</v>
+        <v>811449</v>
       </c>
       <c r="R48" t="n">
-        <v>7391161</v>
+        <v>7391067</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5284,12 +5284,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
         <v>127709750</v>
       </c>
       <c r="B49" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5393,32 +5393,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127709740</v>
+        <v>127709793</v>
       </c>
       <c r="B50" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811709</v>
+        <v>811612</v>
       </c>
       <c r="R50" t="n">
-        <v>7391020</v>
+        <v>7391041</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5472,7 +5472,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5494,7 +5493,7 @@
         <v>127709749</v>
       </c>
       <c r="B51" t="n">
-        <v>80993</v>
+        <v>80995</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5591,7 +5590,7 @@
         <v>127709753</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5685,32 +5684,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127709793</v>
+        <v>127709740</v>
       </c>
       <c r="B53" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5720,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811612</v>
+        <v>811709</v>
       </c>
       <c r="R53" t="n">
-        <v>7391041</v>
+        <v>7391020</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5764,6 +5763,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5782,10 +5782,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127706933</v>
+        <v>127706919</v>
       </c>
       <c r="B54" t="n">
-        <v>78424</v>
+        <v>92815</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5793,21 +5793,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5817,10 +5817,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811536</v>
+        <v>811446</v>
       </c>
       <c r="R54" t="n">
-        <v>7391018</v>
+        <v>7391045</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -5879,48 +5879,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127706919</v>
+        <v>127709792</v>
       </c>
       <c r="B55" t="n">
-        <v>92813</v>
+        <v>92622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811446</v>
+        <v>811619</v>
       </c>
       <c r="R55" t="n">
-        <v>7391045</v>
+        <v>7391036</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5964,12 +5964,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -5979,7 +5979,7 @@
         <v>127709717</v>
       </c>
       <c r="B56" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6073,10 +6073,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709702</v>
+        <v>127706933</v>
       </c>
       <c r="B57" t="n">
-        <v>79636</v>
+        <v>78426</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6084,37 +6084,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811715</v>
+        <v>811536</v>
       </c>
       <c r="R57" t="n">
-        <v>7391028</v>
+        <v>7391018</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6158,22 +6158,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709692</v>
+        <v>127709702</v>
       </c>
       <c r="B58" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6205,10 +6205,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811591</v>
+        <v>811715</v>
       </c>
       <c r="R58" t="n">
-        <v>7391072</v>
+        <v>7391028</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6267,10 +6267,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709771</v>
+        <v>127709692</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6278,21 +6278,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6302,10 +6302,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811735</v>
+        <v>811591</v>
       </c>
       <c r="R59" t="n">
-        <v>7391006</v>
+        <v>7391072</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6364,32 +6364,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709792</v>
+        <v>127709771</v>
       </c>
       <c r="B60" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811619</v>
+        <v>811735</v>
       </c>
       <c r="R60" t="n">
-        <v>7391036</v>
+        <v>7391006</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6464,7 +6464,7 @@
         <v>127709713</v>
       </c>
       <c r="B61" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>127709711</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6681,48 +6681,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127706912</v>
+        <v>127709748</v>
       </c>
       <c r="B63" t="n">
-        <v>91252</v>
+        <v>58033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3242</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811615</v>
+        <v>811439</v>
       </c>
       <c r="R63" t="n">
-        <v>7391007</v>
+        <v>7391070</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6766,44 +6766,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127709748</v>
+        <v>127709737</v>
       </c>
       <c r="B64" t="n">
-        <v>58031</v>
+        <v>92815</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6813,10 +6813,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811439</v>
+        <v>811493</v>
       </c>
       <c r="R64" t="n">
-        <v>7391070</v>
+        <v>7391027</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -6875,10 +6875,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127709737</v>
+        <v>127706912</v>
       </c>
       <c r="B65" t="n">
-        <v>92813</v>
+        <v>91254</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6886,37 +6886,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811493</v>
+        <v>811615</v>
       </c>
       <c r="R65" t="n">
-        <v>7391027</v>
+        <v>7391007</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6960,60 +6960,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127706913</v>
+        <v>127709724</v>
       </c>
       <c r="B66" t="n">
-        <v>91295</v>
+        <v>57660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811507</v>
+        <v>811533</v>
       </c>
       <c r="R66" t="n">
-        <v>7391034</v>
+        <v>7391035</v>
       </c>
       <c r="S66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7057,12 +7057,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7072,7 +7072,7 @@
         <v>127709739</v>
       </c>
       <c r="B67" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709724</v>
+        <v>127709802</v>
       </c>
       <c r="B68" t="n">
-        <v>57658</v>
+        <v>92616</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7177,21 +7177,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7201,10 +7201,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811533</v>
+        <v>811642</v>
       </c>
       <c r="R68" t="n">
-        <v>7391035</v>
+        <v>7391000</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7263,10 +7263,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709798</v>
+        <v>127706913</v>
       </c>
       <c r="B69" t="n">
-        <v>79042</v>
+        <v>91297</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7274,37 +7274,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811676</v>
+        <v>811507</v>
       </c>
       <c r="R69" t="n">
-        <v>7390933</v>
+        <v>7391034</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7348,44 +7348,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709802</v>
+        <v>127709798</v>
       </c>
       <c r="B70" t="n">
-        <v>92614</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811642</v>
+        <v>811676</v>
       </c>
       <c r="R70" t="n">
-        <v>7391000</v>
+        <v>7390933</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7460,7 +7460,7 @@
         <v>127709803</v>
       </c>
       <c r="B71" t="n">
-        <v>78424</v>
+        <v>78426</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         <v>127709700</v>
       </c>
       <c r="B72" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>127709705</v>
       </c>
       <c r="B73" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7761,10 +7761,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709696</v>
+        <v>127709772</v>
       </c>
       <c r="B74" t="n">
-        <v>79636</v>
+        <v>82861</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7772,21 +7772,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7796,10 +7796,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811519</v>
+        <v>811763</v>
       </c>
       <c r="R74" t="n">
-        <v>7391067</v>
+        <v>7390963</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7858,10 +7858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709772</v>
+        <v>127709754</v>
       </c>
       <c r="B75" t="n">
-        <v>82859</v>
+        <v>78778</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7869,21 +7869,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811763</v>
+        <v>811518</v>
       </c>
       <c r="R75" t="n">
-        <v>7390963</v>
+        <v>7391069</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709805</v>
+        <v>127709696</v>
       </c>
       <c r="B76" t="n">
-        <v>78424</v>
+        <v>79638</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811635</v>
+        <v>811519</v>
       </c>
       <c r="R76" t="n">
-        <v>7391001</v>
+        <v>7391067</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8052,10 +8052,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709762</v>
+        <v>127709805</v>
       </c>
       <c r="B77" t="n">
-        <v>79018</v>
+        <v>78426</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,21 +8063,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811718</v>
+        <v>811635</v>
       </c>
       <c r="R77" t="n">
-        <v>7390806</v>
+        <v>7391001</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8152,7 +8152,7 @@
         <v>127709701</v>
       </c>
       <c r="B78" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709754</v>
+        <v>127709762</v>
       </c>
       <c r="B79" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8257,21 +8257,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811518</v>
+        <v>811718</v>
       </c>
       <c r="R79" t="n">
-        <v>7391069</v>
+        <v>7390806</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8343,48 +8343,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706931</v>
+        <v>127709738</v>
       </c>
       <c r="B80" t="n">
-        <v>92620</v>
+        <v>92815</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811711</v>
+        <v>811577</v>
       </c>
       <c r="R80" t="n">
-        <v>7390853</v>
+        <v>7391006</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8428,44 +8428,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127706918</v>
+        <v>127706931</v>
       </c>
       <c r="B81" t="n">
-        <v>91626</v>
+        <v>92622</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8475,10 +8475,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811451</v>
+        <v>811711</v>
       </c>
       <c r="R81" t="n">
-        <v>7391161</v>
+        <v>7390853</v>
       </c>
       <c r="S81" t="n">
         <v>1</v>
@@ -8537,10 +8537,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709755</v>
+        <v>127706918</v>
       </c>
       <c r="B82" t="n">
-        <v>78776</v>
+        <v>91628</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8548,37 +8548,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811542</v>
+        <v>811451</v>
       </c>
       <c r="R82" t="n">
-        <v>7391054</v>
+        <v>7391161</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8622,12 +8622,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8637,7 +8637,7 @@
         <v>127709760</v>
       </c>
       <c r="B83" t="n">
-        <v>91491</v>
+        <v>91493</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8731,10 +8731,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709738</v>
+        <v>127709755</v>
       </c>
       <c r="B84" t="n">
-        <v>92813</v>
+        <v>78778</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8742,21 +8742,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8766,10 +8766,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811577</v>
+        <v>811542</v>
       </c>
       <c r="R84" t="n">
-        <v>7391006</v>
+        <v>7391054</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8831,7 +8831,7 @@
         <v>127706929</v>
       </c>
       <c r="B85" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8928,7 +8928,7 @@
         <v>127709789</v>
       </c>
       <c r="B86" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>127709788</v>
       </c>
       <c r="B87" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         <v>127709757</v>
       </c>
       <c r="B88" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9219,7 +9219,7 @@
         <v>127709759</v>
       </c>
       <c r="B89" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>127706916</v>
       </c>
       <c r="B90" t="n">
-        <v>90365</v>
+        <v>90367</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9410,48 +9410,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127706922</v>
+        <v>127709777</v>
       </c>
       <c r="B91" t="n">
-        <v>78777</v>
+        <v>92622</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811556</v>
+        <v>811696</v>
       </c>
       <c r="R91" t="n">
-        <v>7391103</v>
+        <v>7390929</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9495,12 +9495,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9510,7 +9510,7 @@
         <v>127709728</v>
       </c>
       <c r="B92" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9604,32 +9604,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709777</v>
+        <v>127709775</v>
       </c>
       <c r="B93" t="n">
-        <v>92620</v>
+        <v>78687</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811696</v>
+        <v>811544</v>
       </c>
       <c r="R93" t="n">
-        <v>7390929</v>
+        <v>7391011</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9704,7 +9704,7 @@
         <v>127709742</v>
       </c>
       <c r="B94" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9798,10 +9798,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127709775</v>
+        <v>127706922</v>
       </c>
       <c r="B95" t="n">
-        <v>78685</v>
+        <v>78779</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9809,37 +9809,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811544</v>
+        <v>811556</v>
       </c>
       <c r="R95" t="n">
-        <v>7391011</v>
+        <v>7391103</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9883,44 +9883,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709693</v>
+        <v>127709795</v>
       </c>
       <c r="B96" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811486</v>
+        <v>811676</v>
       </c>
       <c r="R96" t="n">
-        <v>7391112</v>
+        <v>7391004</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9992,45 +9992,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709783</v>
+        <v>127709799</v>
       </c>
       <c r="B97" t="n">
-        <v>92620</v>
+        <v>92616</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811387</v>
+        <v>811707</v>
       </c>
       <c r="R97" t="n">
-        <v>7391146</v>
+        <v>7390860</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10071,6 +10075,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10089,32 +10094,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709769</v>
+        <v>127709783</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10124,10 +10129,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811672</v>
+        <v>811387</v>
       </c>
       <c r="R98" t="n">
-        <v>7390924</v>
+        <v>7391146</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10186,32 +10191,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709795</v>
+        <v>127709769</v>
       </c>
       <c r="B99" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10221,10 +10226,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811676</v>
+        <v>811672</v>
       </c>
       <c r="R99" t="n">
-        <v>7391004</v>
+        <v>7390924</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10283,10 +10288,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709799</v>
+        <v>127709693</v>
       </c>
       <c r="B100" t="n">
-        <v>92614</v>
+        <v>79638</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10294,38 +10299,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811707</v>
+        <v>811486</v>
       </c>
       <c r="R100" t="n">
-        <v>7390860</v>
+        <v>7391112</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10366,7 +10367,6 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -10385,48 +10385,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127706920</v>
+        <v>127709733</v>
       </c>
       <c r="B101" t="n">
-        <v>92813</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811552</v>
+        <v>811530</v>
       </c>
       <c r="R101" t="n">
-        <v>7391002</v>
+        <v>7391016</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10470,22 +10470,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127706924</v>
+        <v>127709729</v>
       </c>
       <c r="B102" t="n">
-        <v>58031</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10493,37 +10493,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811422</v>
+        <v>811434</v>
       </c>
       <c r="R102" t="n">
-        <v>7391139</v>
+        <v>7391048</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10567,44 +10567,44 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709785</v>
+        <v>127709770</v>
       </c>
       <c r="B103" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10614,10 +10614,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811504</v>
+        <v>811608</v>
       </c>
       <c r="R103" t="n">
-        <v>7391047</v>
+        <v>7391004</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10676,32 +10676,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127709733</v>
+        <v>127709764</v>
       </c>
       <c r="B104" t="n">
-        <v>79042</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10711,10 +10711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811530</v>
+        <v>811498</v>
       </c>
       <c r="R104" t="n">
-        <v>7391016</v>
+        <v>7391103</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10773,10 +10773,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709747</v>
+        <v>127706924</v>
       </c>
       <c r="B105" t="n">
-        <v>57765</v>
+        <v>58033</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10784,16 +10784,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10804,17 +10804,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811653</v>
+        <v>811422</v>
       </c>
       <c r="R105" t="n">
-        <v>7390948</v>
+        <v>7391139</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10858,22 +10858,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709787</v>
+        <v>127709785</v>
       </c>
       <c r="B106" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10905,10 +10905,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811677</v>
+        <v>811504</v>
       </c>
       <c r="R106" t="n">
-        <v>7390878</v>
+        <v>7391047</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10967,10 +10967,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709770</v>
+        <v>127706920</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>92815</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10978,37 +10978,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811608</v>
+        <v>811552</v>
       </c>
       <c r="R107" t="n">
-        <v>7391004</v>
+        <v>7391002</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11052,57 +11052,60 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709729</v>
+        <v>127709727</v>
       </c>
       <c r="B108" t="n">
-        <v>79042</v>
+        <v>92626</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6434</v>
+        <v>4365</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811434</v>
+        <v>811545</v>
       </c>
       <c r="R108" t="n">
-        <v>7391048</v>
+        <v>7391008</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11143,6 +11146,7 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
+      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11161,32 +11165,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709764</v>
+        <v>127709787</v>
       </c>
       <c r="B109" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11196,10 +11200,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811498</v>
+        <v>811677</v>
       </c>
       <c r="R109" t="n">
-        <v>7391103</v>
+        <v>7390878</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11258,48 +11262,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709727</v>
+        <v>127709747</v>
       </c>
       <c r="B110" t="n">
-        <v>92624</v>
+        <v>57767</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4365</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811545</v>
+        <v>811653</v>
       </c>
       <c r="R110" t="n">
-        <v>7391008</v>
+        <v>7390948</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11340,7 +11341,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11359,10 +11359,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709804</v>
+        <v>127709801</v>
       </c>
       <c r="B111" t="n">
-        <v>78424</v>
+        <v>92616</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11370,21 +11370,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11394,10 +11394,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811452</v>
+        <v>811615</v>
       </c>
       <c r="R111" t="n">
-        <v>7391056</v>
+        <v>7390990</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11456,32 +11456,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709697</v>
+        <v>127709726</v>
       </c>
       <c r="B112" t="n">
-        <v>79636</v>
+        <v>92626</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11491,10 +11491,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811625</v>
+        <v>811638</v>
       </c>
       <c r="R112" t="n">
-        <v>7390969</v>
+        <v>7391044</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709801</v>
+        <v>127709804</v>
       </c>
       <c r="B113" t="n">
-        <v>92614</v>
+        <v>78426</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811615</v>
+        <v>811452</v>
       </c>
       <c r="R113" t="n">
-        <v>7390990</v>
+        <v>7391056</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11650,32 +11650,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709726</v>
+        <v>127709697</v>
       </c>
       <c r="B114" t="n">
-        <v>92624</v>
+        <v>79638</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811638</v>
+        <v>811625</v>
       </c>
       <c r="R114" t="n">
-        <v>7391044</v>
+        <v>7390969</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11750,7 +11750,7 @@
         <v>127709720</v>
       </c>
       <c r="B115" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>127709707</v>
       </c>
       <c r="B116" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11954,10 +11954,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709743</v>
+        <v>127709776</v>
       </c>
       <c r="B117" t="n">
-        <v>78777</v>
+        <v>78687</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11965,21 +11965,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11989,10 +11989,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811385</v>
+        <v>811646</v>
       </c>
       <c r="R117" t="n">
-        <v>7391163</v>
+        <v>7390963</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12051,10 +12051,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709778</v>
+        <v>127709732</v>
       </c>
       <c r="B118" t="n">
-        <v>92620</v>
+        <v>79044</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12062,21 +12062,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12086,10 +12086,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811683</v>
+        <v>811523</v>
       </c>
       <c r="R118" t="n">
-        <v>7390938</v>
+        <v>7391024</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,10 +12148,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709723</v>
+        <v>127709765</v>
       </c>
       <c r="B119" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12159,21 +12159,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12183,10 +12183,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811411</v>
+        <v>811478</v>
       </c>
       <c r="R119" t="n">
-        <v>7391165</v>
+        <v>7391172</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,32 +12245,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709732</v>
+        <v>127709723</v>
       </c>
       <c r="B120" t="n">
-        <v>79042</v>
+        <v>57660</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811523</v>
+        <v>811411</v>
       </c>
       <c r="R120" t="n">
-        <v>7391024</v>
+        <v>7391165</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12342,32 +12342,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709776</v>
+        <v>127709778</v>
       </c>
       <c r="B121" t="n">
-        <v>78685</v>
+        <v>92622</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12377,10 +12377,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811646</v>
+        <v>811683</v>
       </c>
       <c r="R121" t="n">
-        <v>7390963</v>
+        <v>7390938</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12439,32 +12439,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709765</v>
+        <v>127709791</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811478</v>
+        <v>811605</v>
       </c>
       <c r="R122" t="n">
-        <v>7391172</v>
+        <v>7391024</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12536,32 +12536,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127709791</v>
+        <v>127709743</v>
       </c>
       <c r="B123" t="n">
-        <v>92620</v>
+        <v>78779</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12571,10 +12571,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811605</v>
+        <v>811385</v>
       </c>
       <c r="R123" t="n">
-        <v>7391024</v>
+        <v>7391163</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127709763</v>
+        <v>127709784</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811692</v>
+        <v>811414</v>
       </c>
       <c r="R2" t="n">
-        <v>7390815</v>
+        <v>7391125</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709784</v>
+        <v>127709763</v>
       </c>
       <c r="B4" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811414</v>
+        <v>811692</v>
       </c>
       <c r="R4" t="n">
-        <v>7391125</v>
+        <v>7390815</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709781</v>
+        <v>127709774</v>
       </c>
       <c r="B6" t="n">
-        <v>92622</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811479</v>
+        <v>811658</v>
       </c>
       <c r="R6" t="n">
-        <v>7391142</v>
+        <v>7390945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709774</v>
+        <v>127709781</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811658</v>
+        <v>811479</v>
       </c>
       <c r="R7" t="n">
-        <v>7390945</v>
+        <v>7391142</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127709721</v>
+        <v>127709710</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1285,17 +1285,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811493</v>
+        <v>811505</v>
       </c>
       <c r="R8" t="n">
-        <v>7391183</v>
+        <v>7391045</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1330,6 +1338,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1347,39 +1360,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127706921</v>
+        <v>127706915</v>
       </c>
       <c r="B9" t="n">
-        <v>78779</v>
+        <v>58522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811722</v>
+        <v>811694</v>
       </c>
       <c r="R9" t="n">
-        <v>7390955</v>
+        <v>7390899</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1451,7 +1464,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127706923</v>
+        <v>127706921</v>
       </c>
       <c r="B10" t="n">
         <v>78779</v>
@@ -1486,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811648</v>
+        <v>811722</v>
       </c>
       <c r="R10" t="n">
-        <v>7390971</v>
+        <v>7390955</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1548,10 +1561,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706928</v>
+        <v>127706923</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1572,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811509</v>
+        <v>811648</v>
       </c>
       <c r="R11" t="n">
-        <v>7391152</v>
+        <v>7390971</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1645,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127709710</v>
+        <v>127706928</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,45 +1669,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811505</v>
+        <v>811509</v>
       </c>
       <c r="R12" t="n">
-        <v>7391045</v>
+        <v>7391152</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1724,11 +1729,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,60 +1743,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127706915</v>
+        <v>127709721</v>
       </c>
       <c r="B13" t="n">
-        <v>58522</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208249</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811694</v>
+        <v>811493</v>
       </c>
       <c r="R13" t="n">
-        <v>7390899</v>
+        <v>7391183</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1840,12 +1840,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709800</v>
+        <v>127709704</v>
       </c>
       <c r="B20" t="n">
-        <v>92616</v>
+        <v>90367</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811725</v>
+        <v>811693</v>
       </c>
       <c r="R20" t="n">
-        <v>7390826</v>
+        <v>7390866</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709704</v>
+        <v>127709800</v>
       </c>
       <c r="B21" t="n">
-        <v>90367</v>
+        <v>92616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811693</v>
+        <v>811725</v>
       </c>
       <c r="R21" t="n">
-        <v>7390866</v>
+        <v>7390826</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3033,48 +3033,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127706927</v>
+        <v>127709790</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811760</v>
+        <v>811610</v>
       </c>
       <c r="R26" t="n">
-        <v>7390859</v>
+        <v>7391012</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3118,44 +3118,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709722</v>
+        <v>127709786</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>92622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811476</v>
+        <v>811612</v>
       </c>
       <c r="R27" t="n">
-        <v>7391149</v>
+        <v>7390987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709703</v>
+        <v>127709779</v>
       </c>
       <c r="B28" t="n">
-        <v>79609</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811724</v>
+        <v>811561</v>
       </c>
       <c r="R28" t="n">
-        <v>7390998</v>
+        <v>7391108</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3306,7 +3306,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3325,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709741</v>
+        <v>127709796</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3360,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811489</v>
+        <v>811672</v>
       </c>
       <c r="R29" t="n">
-        <v>7391186</v>
+        <v>7391010</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3422,48 +3421,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709790</v>
+        <v>127706927</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811610</v>
+        <v>811760</v>
       </c>
       <c r="R30" t="n">
-        <v>7391012</v>
+        <v>7390859</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3507,44 +3506,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709786</v>
+        <v>127709758</v>
       </c>
       <c r="B31" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3554,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811612</v>
+        <v>811621</v>
       </c>
       <c r="R31" t="n">
-        <v>7390987</v>
+        <v>7390981</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3616,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709779</v>
+        <v>127709730</v>
       </c>
       <c r="B32" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3627,21 +3626,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3651,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811561</v>
+        <v>811452</v>
       </c>
       <c r="R32" t="n">
-        <v>7391108</v>
+        <v>7391057</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3713,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709796</v>
+        <v>127709736</v>
       </c>
       <c r="B33" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3724,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3748,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811672</v>
+        <v>811662</v>
       </c>
       <c r="R33" t="n">
-        <v>7391010</v>
+        <v>7390926</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3810,10 +3809,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709758</v>
+        <v>127709722</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>57660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3821,21 +3820,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3845,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811621</v>
+        <v>811476</v>
       </c>
       <c r="R34" t="n">
-        <v>7390981</v>
+        <v>7391149</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3907,32 +3906,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127709730</v>
+        <v>127709703</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79609</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3942,10 +3941,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811452</v>
+        <v>811724</v>
       </c>
       <c r="R35" t="n">
-        <v>7391057</v>
+        <v>7390998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3986,6 +3985,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4004,32 +4004,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127709736</v>
+        <v>127709741</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>78779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811662</v>
+        <v>811489</v>
       </c>
       <c r="R36" t="n">
-        <v>7390926</v>
+        <v>7391186</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709756</v>
+        <v>127709766</v>
       </c>
       <c r="B37" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811538</v>
+        <v>811730</v>
       </c>
       <c r="R37" t="n">
-        <v>7391022</v>
+        <v>7390914</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709768</v>
+        <v>127709780</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811776</v>
+        <v>811475</v>
       </c>
       <c r="R38" t="n">
-        <v>7390918</v>
+        <v>7391196</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4295,7 +4295,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709766</v>
+        <v>127709768</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811730</v>
+        <v>811776</v>
       </c>
       <c r="R39" t="n">
-        <v>7390914</v>
+        <v>7390918</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4392,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709708</v>
+        <v>127709756</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>78778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,42 +4403,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811580</v>
+        <v>811538</v>
       </c>
       <c r="R40" t="n">
-        <v>7391090</v>
+        <v>7391022</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4473,11 +4465,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4495,52 +4482,60 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709780</v>
+        <v>127709708</v>
       </c>
       <c r="B41" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811475</v>
+        <v>811580</v>
       </c>
       <c r="R41" t="n">
-        <v>7391196</v>
+        <v>7391090</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4575,6 +4570,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127709749</v>
+        <v>127709740</v>
       </c>
       <c r="B51" t="n">
-        <v>80995</v>
+        <v>78779</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811750</v>
+        <v>811709</v>
       </c>
       <c r="R51" t="n">
-        <v>7390835</v>
+        <v>7391020</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5569,6 +5569,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5587,10 +5588,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709753</v>
+        <v>127709749</v>
       </c>
       <c r="B52" t="n">
-        <v>78778</v>
+        <v>80995</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,21 +5599,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5623,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811385</v>
+        <v>811750</v>
       </c>
       <c r="R52" t="n">
-        <v>7391163</v>
+        <v>7390835</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5684,10 +5685,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127709740</v>
+        <v>127709753</v>
       </c>
       <c r="B53" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,21 +5696,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5719,10 +5720,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811709</v>
+        <v>811385</v>
       </c>
       <c r="R53" t="n">
-        <v>7391020</v>
+        <v>7391163</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5763,7 +5764,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5879,45 +5879,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709792</v>
+        <v>127709713</v>
       </c>
       <c r="B55" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811619</v>
+        <v>811514</v>
       </c>
       <c r="R55" t="n">
-        <v>7391036</v>
+        <v>7391024</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5952,6 +5960,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5969,52 +5982,60 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709717</v>
+        <v>127709711</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57663</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811625</v>
+        <v>811535</v>
       </c>
       <c r="R56" t="n">
-        <v>7390984</v>
+        <v>7391056</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6049,6 +6070,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6066,55 +6092,55 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127706933</v>
+        <v>127709792</v>
       </c>
       <c r="B57" t="n">
-        <v>78426</v>
+        <v>92622</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811536</v>
+        <v>811619</v>
       </c>
       <c r="R57" t="n">
-        <v>7391018</v>
+        <v>7391036</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6158,22 +6184,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709702</v>
+        <v>127709771</v>
       </c>
       <c r="B58" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6181,21 +6207,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6205,10 +6231,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811715</v>
+        <v>811735</v>
       </c>
       <c r="R58" t="n">
-        <v>7391028</v>
+        <v>7391006</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6267,32 +6293,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709692</v>
+        <v>127709717</v>
       </c>
       <c r="B59" t="n">
-        <v>79638</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6302,10 +6328,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811591</v>
+        <v>811625</v>
       </c>
       <c r="R59" t="n">
-        <v>7391072</v>
+        <v>7390984</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6364,10 +6390,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709771</v>
+        <v>127706933</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>78426</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6375,37 +6401,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811735</v>
+        <v>811536</v>
       </c>
       <c r="R60" t="n">
-        <v>7391006</v>
+        <v>7391018</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6449,22 +6475,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709713</v>
+        <v>127709702</v>
       </c>
       <c r="B61" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6472,42 +6498,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811514</v>
+        <v>811715</v>
       </c>
       <c r="R61" t="n">
-        <v>7391024</v>
+        <v>7391028</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6542,11 +6560,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6564,17 +6577,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709711</v>
+        <v>127709692</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>79638</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6582,42 +6595,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811535</v>
+        <v>811591</v>
       </c>
       <c r="R62" t="n">
-        <v>7391056</v>
+        <v>7391072</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6652,11 +6657,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6674,39 +6674,39 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127709748</v>
+        <v>127709737</v>
       </c>
       <c r="B63" t="n">
-        <v>58033</v>
+        <v>92815</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811439</v>
+        <v>811493</v>
       </c>
       <c r="R63" t="n">
-        <v>7391070</v>
+        <v>7391027</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127709737</v>
+        <v>127706912</v>
       </c>
       <c r="B64" t="n">
-        <v>92815</v>
+        <v>91254</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6789,37 +6789,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811493</v>
+        <v>811615</v>
       </c>
       <c r="R64" t="n">
-        <v>7391027</v>
+        <v>7391007</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6863,60 +6863,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127706912</v>
+        <v>127709748</v>
       </c>
       <c r="B65" t="n">
-        <v>91254</v>
+        <v>58033</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3242</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811615</v>
+        <v>811439</v>
       </c>
       <c r="R65" t="n">
-        <v>7391007</v>
+        <v>7391070</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6960,22 +6960,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127709724</v>
+        <v>127709739</v>
       </c>
       <c r="B66" t="n">
-        <v>57660</v>
+        <v>92815</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811533</v>
+        <v>811603</v>
       </c>
       <c r="R66" t="n">
-        <v>7391035</v>
+        <v>7390979</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127709739</v>
+        <v>127709802</v>
       </c>
       <c r="B67" t="n">
-        <v>92815</v>
+        <v>92616</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811603</v>
+        <v>811642</v>
       </c>
       <c r="R67" t="n">
-        <v>7390979</v>
+        <v>7391000</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7166,48 +7166,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709802</v>
+        <v>127706913</v>
       </c>
       <c r="B68" t="n">
-        <v>92616</v>
+        <v>91297</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811642</v>
+        <v>811507</v>
       </c>
       <c r="R68" t="n">
-        <v>7391000</v>
+        <v>7391034</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7251,22 +7251,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127706913</v>
+        <v>127709798</v>
       </c>
       <c r="B69" t="n">
-        <v>91297</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7274,37 +7274,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811507</v>
+        <v>811676</v>
       </c>
       <c r="R69" t="n">
-        <v>7391034</v>
+        <v>7390933</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7348,44 +7348,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709798</v>
+        <v>127709803</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>78426</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7395,10 +7395,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811676</v>
+        <v>811716</v>
       </c>
       <c r="R70" t="n">
-        <v>7390933</v>
+        <v>7390831</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7457,10 +7457,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709803</v>
+        <v>127709700</v>
       </c>
       <c r="B71" t="n">
-        <v>78426</v>
+        <v>79638</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811716</v>
+        <v>811687</v>
       </c>
       <c r="R71" t="n">
-        <v>7390831</v>
+        <v>7390967</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7554,10 +7554,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709700</v>
+        <v>127709705</v>
       </c>
       <c r="B72" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7565,34 +7565,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811687</v>
+        <v>811705</v>
       </c>
       <c r="R72" t="n">
-        <v>7390967</v>
+        <v>7390855</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7627,6 +7635,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7644,17 +7657,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709705</v>
+        <v>127709724</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7662,16 +7675,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7679,25 +7692,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811705</v>
+        <v>811533</v>
       </c>
       <c r="R73" t="n">
-        <v>7390855</v>
+        <v>7391035</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7732,11 +7737,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7858,10 +7858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709754</v>
+        <v>127709762</v>
       </c>
       <c r="B75" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7869,21 +7869,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811518</v>
+        <v>811718</v>
       </c>
       <c r="R75" t="n">
-        <v>7391069</v>
+        <v>7390806</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709696</v>
+        <v>127709754</v>
       </c>
       <c r="B76" t="n">
-        <v>79638</v>
+        <v>78778</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811519</v>
+        <v>811518</v>
       </c>
       <c r="R76" t="n">
-        <v>7391067</v>
+        <v>7391069</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8052,10 +8052,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709805</v>
+        <v>127709696</v>
       </c>
       <c r="B77" t="n">
-        <v>78426</v>
+        <v>79638</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8063,21 +8063,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8087,10 +8087,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811635</v>
+        <v>811519</v>
       </c>
       <c r="R77" t="n">
-        <v>7391001</v>
+        <v>7391067</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8149,10 +8149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709701</v>
+        <v>127709805</v>
       </c>
       <c r="B78" t="n">
-        <v>79638</v>
+        <v>78426</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811632</v>
+        <v>811635</v>
       </c>
       <c r="R78" t="n">
-        <v>7391030</v>
+        <v>7391001</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709762</v>
+        <v>127709701</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8257,21 +8257,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811718</v>
+        <v>811632</v>
       </c>
       <c r="R79" t="n">
-        <v>7390806</v>
+        <v>7391030</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8343,10 +8343,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B80" t="n">
-        <v>92815</v>
+        <v>91628</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8354,37 +8354,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R80" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8428,60 +8428,60 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127706931</v>
+        <v>127709760</v>
       </c>
       <c r="B81" t="n">
-        <v>92622</v>
+        <v>91493</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811711</v>
+        <v>811582</v>
       </c>
       <c r="R81" t="n">
-        <v>7390853</v>
+        <v>7391002</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8525,22 +8525,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127706918</v>
+        <v>127709738</v>
       </c>
       <c r="B82" t="n">
-        <v>91628</v>
+        <v>92815</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8548,37 +8548,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811451</v>
+        <v>811577</v>
       </c>
       <c r="R82" t="n">
-        <v>7391161</v>
+        <v>7391006</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8622,60 +8622,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127709760</v>
+        <v>127706931</v>
       </c>
       <c r="B83" t="n">
-        <v>91493</v>
+        <v>92622</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811582</v>
+        <v>811711</v>
       </c>
       <c r="R83" t="n">
-        <v>7391002</v>
+        <v>7390853</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8719,12 +8719,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9313,48 +9313,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127706916</v>
+        <v>127709728</v>
       </c>
       <c r="B90" t="n">
-        <v>90367</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1962</v>
+        <v>6434</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811652</v>
+        <v>811385</v>
       </c>
       <c r="R90" t="n">
-        <v>7390945</v>
+        <v>7391153</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9398,44 +9398,44 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709777</v>
+        <v>127709775</v>
       </c>
       <c r="B91" t="n">
-        <v>92622</v>
+        <v>78687</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9445,10 +9445,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811696</v>
+        <v>811544</v>
       </c>
       <c r="R91" t="n">
-        <v>7390929</v>
+        <v>7391011</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9507,48 +9507,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127709728</v>
+        <v>127706916</v>
       </c>
       <c r="B92" t="n">
-        <v>79044</v>
+        <v>90367</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6434</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811385</v>
+        <v>811652</v>
       </c>
       <c r="R92" t="n">
-        <v>7391153</v>
+        <v>7390945</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9592,44 +9592,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709775</v>
+        <v>127709777</v>
       </c>
       <c r="B93" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811544</v>
+        <v>811696</v>
       </c>
       <c r="R93" t="n">
-        <v>7391011</v>
+        <v>7390929</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9895,32 +9895,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B96" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R96" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9992,49 +9992,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709799</v>
+        <v>127709795</v>
       </c>
       <c r="B97" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811707</v>
+        <v>811676</v>
       </c>
       <c r="R97" t="n">
-        <v>7390860</v>
+        <v>7391004</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10075,7 +10071,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10094,45 +10089,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709783</v>
+        <v>127709799</v>
       </c>
       <c r="B98" t="n">
-        <v>92622</v>
+        <v>92616</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811387</v>
+        <v>811707</v>
       </c>
       <c r="R98" t="n">
-        <v>7391146</v>
+        <v>7390860</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10173,6 +10172,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10191,32 +10191,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709769</v>
+        <v>127709783</v>
       </c>
       <c r="B99" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10226,10 +10226,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811672</v>
+        <v>811387</v>
       </c>
       <c r="R99" t="n">
-        <v>7390924</v>
+        <v>7391146</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10288,10 +10288,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709693</v>
+        <v>127709769</v>
       </c>
       <c r="B100" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10299,21 +10299,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811486</v>
+        <v>811672</v>
       </c>
       <c r="R100" t="n">
-        <v>7391112</v>
+        <v>7390924</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10385,10 +10385,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709733</v>
+        <v>127709785</v>
       </c>
       <c r="B101" t="n">
-        <v>79044</v>
+        <v>92622</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10396,21 +10396,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811530</v>
+        <v>811504</v>
       </c>
       <c r="R101" t="n">
-        <v>7391016</v>
+        <v>7391047</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10482,45 +10482,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709729</v>
+        <v>127709727</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>92626</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>4365</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811434</v>
+        <v>811545</v>
       </c>
       <c r="R102" t="n">
-        <v>7391048</v>
+        <v>7391008</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10561,6 +10564,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10579,32 +10583,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709770</v>
+        <v>127709787</v>
       </c>
       <c r="B103" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10614,10 +10618,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811608</v>
+        <v>811677</v>
       </c>
       <c r="R103" t="n">
-        <v>7391004</v>
+        <v>7390878</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10676,10 +10680,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127709764</v>
+        <v>127706920</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>92815</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10687,37 +10691,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811498</v>
+        <v>811552</v>
       </c>
       <c r="R104" t="n">
-        <v>7391103</v>
+        <v>7391002</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10761,60 +10765,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127706924</v>
+        <v>127709764</v>
       </c>
       <c r="B105" t="n">
-        <v>58033</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811422</v>
+        <v>811498</v>
       </c>
       <c r="R105" t="n">
-        <v>7391139</v>
+        <v>7391103</v>
       </c>
       <c r="S105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10858,44 +10862,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709785</v>
+        <v>127709770</v>
       </c>
       <c r="B106" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10905,10 +10909,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811504</v>
+        <v>811608</v>
       </c>
       <c r="R106" t="n">
-        <v>7391047</v>
+        <v>7391004</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10967,48 +10971,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127706920</v>
+        <v>127709733</v>
       </c>
       <c r="B107" t="n">
-        <v>92815</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811552</v>
+        <v>811530</v>
       </c>
       <c r="R107" t="n">
-        <v>7391002</v>
+        <v>7391016</v>
       </c>
       <c r="S107" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11052,60 +11056,57 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709727</v>
+        <v>127709729</v>
       </c>
       <c r="B108" t="n">
-        <v>92626</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811545</v>
+        <v>811434</v>
       </c>
       <c r="R108" t="n">
-        <v>7391008</v>
+        <v>7391048</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11146,7 +11147,6 @@
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
@@ -11165,10 +11165,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709787</v>
+        <v>127709747</v>
       </c>
       <c r="B109" t="n">
-        <v>92622</v>
+        <v>57767</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11176,21 +11176,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811677</v>
+        <v>811653</v>
       </c>
       <c r="R109" t="n">
-        <v>7390878</v>
+        <v>7390948</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11262,10 +11262,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709747</v>
+        <v>127706924</v>
       </c>
       <c r="B110" t="n">
-        <v>57767</v>
+        <v>58033</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11273,16 +11273,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11293,17 +11293,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811653</v>
+        <v>811422</v>
       </c>
       <c r="R110" t="n">
-        <v>7390948</v>
+        <v>7391139</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11347,12 +11347,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709804</v>
+        <v>127709720</v>
       </c>
       <c r="B113" t="n">
-        <v>78426</v>
+        <v>57660</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811452</v>
+        <v>811515</v>
       </c>
       <c r="R113" t="n">
-        <v>7391056</v>
+        <v>7391165</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709697</v>
+        <v>127709804</v>
       </c>
       <c r="B114" t="n">
-        <v>79638</v>
+        <v>78426</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11661,21 +11661,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811625</v>
+        <v>811452</v>
       </c>
       <c r="R114" t="n">
-        <v>7390969</v>
+        <v>7391056</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11747,10 +11747,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709720</v>
+        <v>127709697</v>
       </c>
       <c r="B115" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11758,21 +11758,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811515</v>
+        <v>811625</v>
       </c>
       <c r="R115" t="n">
-        <v>7391165</v>
+        <v>7390969</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12051,10 +12051,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709732</v>
+        <v>127709778</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>92622</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12062,21 +12062,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12086,10 +12086,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811523</v>
+        <v>811683</v>
       </c>
       <c r="R118" t="n">
-        <v>7391024</v>
+        <v>7390938</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12148,32 +12148,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709765</v>
+        <v>127709791</v>
       </c>
       <c r="B119" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12183,10 +12183,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811478</v>
+        <v>811605</v>
       </c>
       <c r="R119" t="n">
-        <v>7391172</v>
+        <v>7391024</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12245,10 +12245,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709723</v>
+        <v>127709765</v>
       </c>
       <c r="B120" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12256,21 +12256,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811411</v>
+        <v>811478</v>
       </c>
       <c r="R120" t="n">
-        <v>7391165</v>
+        <v>7391172</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12342,32 +12342,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709778</v>
+        <v>127709723</v>
       </c>
       <c r="B121" t="n">
-        <v>92622</v>
+        <v>57660</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12377,10 +12377,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811683</v>
+        <v>811411</v>
       </c>
       <c r="R121" t="n">
-        <v>7390938</v>
+        <v>7391165</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12439,10 +12439,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709791</v>
+        <v>127709732</v>
       </c>
       <c r="B122" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12450,21 +12450,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12474,7 +12474,7 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811605</v>
+        <v>811523</v>
       </c>
       <c r="R122" t="n">
         <v>7391024</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -3033,48 +3033,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709790</v>
+        <v>127706927</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811610</v>
+        <v>811760</v>
       </c>
       <c r="R26" t="n">
-        <v>7391012</v>
+        <v>7390859</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3118,44 +3118,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709786</v>
+        <v>127709722</v>
       </c>
       <c r="B27" t="n">
-        <v>92622</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811612</v>
+        <v>811476</v>
       </c>
       <c r="R27" t="n">
-        <v>7390987</v>
+        <v>7391149</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709779</v>
+        <v>127709790</v>
       </c>
       <c r="B28" t="n">
         <v>92622</v>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811561</v>
+        <v>811610</v>
       </c>
       <c r="R28" t="n">
-        <v>7391108</v>
+        <v>7391012</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709796</v>
+        <v>127709786</v>
       </c>
       <c r="B29" t="n">
         <v>92622</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811672</v>
+        <v>811612</v>
       </c>
       <c r="R29" t="n">
-        <v>7391010</v>
+        <v>7390987</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,48 +3421,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127706927</v>
+        <v>127709779</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811760</v>
+        <v>811561</v>
       </c>
       <c r="R30" t="n">
-        <v>7390859</v>
+        <v>7391108</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3506,44 +3506,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709758</v>
+        <v>127709796</v>
       </c>
       <c r="B31" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811621</v>
+        <v>811672</v>
       </c>
       <c r="R31" t="n">
-        <v>7390981</v>
+        <v>7391010</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3615,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709730</v>
+        <v>127709758</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>78778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811452</v>
+        <v>811621</v>
       </c>
       <c r="R32" t="n">
-        <v>7391057</v>
+        <v>7390981</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3712,7 +3712,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709736</v>
+        <v>127709730</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811662</v>
+        <v>811452</v>
       </c>
       <c r="R33" t="n">
-        <v>7390926</v>
+        <v>7391057</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3809,32 +3809,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709722</v>
+        <v>127709736</v>
       </c>
       <c r="B34" t="n">
-        <v>57660</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811476</v>
+        <v>811662</v>
       </c>
       <c r="R34" t="n">
-        <v>7391149</v>
+        <v>7390926</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4101,7 +4101,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709766</v>
+        <v>127709768</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811730</v>
+        <v>811776</v>
       </c>
       <c r="R37" t="n">
-        <v>7390914</v>
+        <v>7390918</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709780</v>
+        <v>127709766</v>
       </c>
       <c r="B38" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811475</v>
+        <v>811730</v>
       </c>
       <c r="R38" t="n">
-        <v>7391196</v>
+        <v>7390914</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709768</v>
+        <v>127709756</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811776</v>
+        <v>811538</v>
       </c>
       <c r="R39" t="n">
-        <v>7390918</v>
+        <v>7391022</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4392,32 +4392,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709756</v>
+        <v>127709780</v>
       </c>
       <c r="B40" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811538</v>
+        <v>811475</v>
       </c>
       <c r="R40" t="n">
-        <v>7391022</v>
+        <v>7391196</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -8537,48 +8537,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709738</v>
+        <v>127706931</v>
       </c>
       <c r="B82" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811577</v>
+        <v>811711</v>
       </c>
       <c r="R82" t="n">
-        <v>7391006</v>
+        <v>7390853</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8622,60 +8622,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127706931</v>
+        <v>127709755</v>
       </c>
       <c r="B83" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811711</v>
+        <v>811542</v>
       </c>
       <c r="R83" t="n">
-        <v>7390853</v>
+        <v>7391054</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8719,22 +8719,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709755</v>
+        <v>127709738</v>
       </c>
       <c r="B84" t="n">
-        <v>78778</v>
+        <v>92815</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8742,21 +8742,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8766,10 +8766,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811542</v>
+        <v>811577</v>
       </c>
       <c r="R84" t="n">
-        <v>7391054</v>
+        <v>7391006</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -8828,10 +8828,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127706929</v>
+        <v>127709757</v>
       </c>
       <c r="B85" t="n">
-        <v>82861</v>
+        <v>78778</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8839,37 +8839,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811496</v>
+        <v>811625</v>
       </c>
       <c r="R85" t="n">
-        <v>7391110</v>
+        <v>7390969</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8913,60 +8913,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709789</v>
+        <v>127706929</v>
       </c>
       <c r="B86" t="n">
-        <v>92622</v>
+        <v>82861</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811610</v>
+        <v>811496</v>
       </c>
       <c r="R86" t="n">
-        <v>7390981</v>
+        <v>7391110</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9010,19 +9010,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127709788</v>
+        <v>127709789</v>
       </c>
       <c r="B87" t="n">
         <v>92622</v>
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811667</v>
+        <v>811610</v>
       </c>
       <c r="R87" t="n">
-        <v>7390931</v>
+        <v>7390981</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9119,32 +9119,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709757</v>
+        <v>127709788</v>
       </c>
       <c r="B88" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811625</v>
+        <v>811667</v>
       </c>
       <c r="R88" t="n">
-        <v>7390969</v>
+        <v>7390931</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10385,32 +10385,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709785</v>
+        <v>127709764</v>
       </c>
       <c r="B101" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811504</v>
+        <v>811498</v>
       </c>
       <c r="R101" t="n">
-        <v>7391047</v>
+        <v>7391103</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10482,48 +10482,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709727</v>
+        <v>127709770</v>
       </c>
       <c r="B102" t="n">
-        <v>92626</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811545</v>
+        <v>811608</v>
       </c>
       <c r="R102" t="n">
-        <v>7391008</v>
+        <v>7391004</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10564,7 +10561,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10583,10 +10579,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709787</v>
+        <v>127709729</v>
       </c>
       <c r="B103" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10594,21 +10590,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10618,10 +10614,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811677</v>
+        <v>811434</v>
       </c>
       <c r="R103" t="n">
-        <v>7390878</v>
+        <v>7391048</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10680,32 +10676,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127706920</v>
+        <v>127706924</v>
       </c>
       <c r="B104" t="n">
-        <v>92815</v>
+        <v>58033</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2079</v>
+        <v>103015</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10715,10 +10711,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811552</v>
+        <v>811422</v>
       </c>
       <c r="R104" t="n">
-        <v>7391002</v>
+        <v>7391139</v>
       </c>
       <c r="S104" t="n">
         <v>1</v>
@@ -10777,10 +10773,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709764</v>
+        <v>127706920</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>92815</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10788,37 +10784,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811498</v>
+        <v>811552</v>
       </c>
       <c r="R105" t="n">
-        <v>7391103</v>
+        <v>7391002</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10862,44 +10858,44 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709770</v>
+        <v>127709785</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10909,10 +10905,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811608</v>
+        <v>811504</v>
       </c>
       <c r="R106" t="n">
-        <v>7391004</v>
+        <v>7391047</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10971,45 +10967,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709733</v>
+        <v>127709727</v>
       </c>
       <c r="B107" t="n">
-        <v>79044</v>
+        <v>92626</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6434</v>
+        <v>4365</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811530</v>
+        <v>811545</v>
       </c>
       <c r="R107" t="n">
-        <v>7391016</v>
+        <v>7391008</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11050,6 +11049,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11068,10 +11068,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709729</v>
+        <v>127709787</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>92622</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11079,21 +11079,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811434</v>
+        <v>811677</v>
       </c>
       <c r="R108" t="n">
-        <v>7391048</v>
+        <v>7390878</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11165,10 +11165,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709747</v>
+        <v>127709733</v>
       </c>
       <c r="B109" t="n">
-        <v>57767</v>
+        <v>79044</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11176,21 +11176,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103031</v>
+        <v>6434</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811653</v>
+        <v>811530</v>
       </c>
       <c r="R109" t="n">
-        <v>7390948</v>
+        <v>7391016</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11262,10 +11262,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127706924</v>
+        <v>127709747</v>
       </c>
       <c r="B110" t="n">
-        <v>58033</v>
+        <v>57767</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11273,16 +11273,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11293,17 +11293,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811422</v>
+        <v>811653</v>
       </c>
       <c r="R110" t="n">
-        <v>7391139</v>
+        <v>7390948</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11347,12 +11347,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127709784</v>
+        <v>127709734</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811414</v>
+        <v>811573</v>
       </c>
       <c r="R2" t="n">
-        <v>7391125</v>
+        <v>7391001</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127706926</v>
+        <v>127709763</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -803,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811754</v>
+        <v>811692</v>
       </c>
       <c r="R3" t="n">
-        <v>7390851</v>
+        <v>7390815</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709763</v>
+        <v>127706926</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -900,17 +900,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811692</v>
+        <v>811754</v>
       </c>
       <c r="R4" t="n">
-        <v>7390815</v>
+        <v>7390851</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709734</v>
+        <v>127709784</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>92622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811573</v>
+        <v>811414</v>
       </c>
       <c r="R5" t="n">
-        <v>7391001</v>
+        <v>7391125</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1160,45 +1160,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709781</v>
+        <v>127709710</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811479</v>
+        <v>811505</v>
       </c>
       <c r="R7" t="n">
-        <v>7391142</v>
+        <v>7391045</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1233,6 +1241,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1250,17 +1263,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127709710</v>
+        <v>127706921</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,45 +1281,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811505</v>
+        <v>811722</v>
       </c>
       <c r="R8" t="n">
-        <v>7391045</v>
+        <v>7390955</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1336,11 +1341,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1355,44 +1355,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127706915</v>
+        <v>127706923</v>
       </c>
       <c r="B9" t="n">
-        <v>58522</v>
+        <v>78779</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208249</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811694</v>
+        <v>811648</v>
       </c>
       <c r="R9" t="n">
-        <v>7390899</v>
+        <v>7390971</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1464,48 +1464,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127706921</v>
+        <v>127709781</v>
       </c>
       <c r="B10" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811722</v>
+        <v>811479</v>
       </c>
       <c r="R10" t="n">
-        <v>7390955</v>
+        <v>7391142</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,22 +1549,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706923</v>
+        <v>127706928</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,21 +1572,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811648</v>
+        <v>811509</v>
       </c>
       <c r="R11" t="n">
-        <v>7390971</v>
+        <v>7391152</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127706928</v>
+        <v>127709721</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,37 +1669,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811509</v>
+        <v>811493</v>
       </c>
       <c r="R12" t="n">
-        <v>7391152</v>
+        <v>7391183</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1743,60 +1743,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709721</v>
+        <v>127706915</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>58522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811493</v>
+        <v>811694</v>
       </c>
       <c r="R13" t="n">
-        <v>7391183</v>
+        <v>7390899</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1840,22 +1840,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709694</v>
+        <v>127706925</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811441</v>
+        <v>811866</v>
       </c>
       <c r="R14" t="n">
-        <v>7391158</v>
+        <v>7390863</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,19 +1937,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127706914</v>
+        <v>127709694</v>
       </c>
       <c r="B15" t="n">
         <v>79638</v>
@@ -1980,17 +1980,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811645</v>
+        <v>811441</v>
       </c>
       <c r="R15" t="n">
-        <v>7390971</v>
+        <v>7391158</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,19 +2034,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127709695</v>
+        <v>127706914</v>
       </c>
       <c r="B16" t="n">
         <v>79638</v>
@@ -2077,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811430</v>
+        <v>811645</v>
       </c>
       <c r="R16" t="n">
-        <v>7391046</v>
+        <v>7390971</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709699</v>
+        <v>127709695</v>
       </c>
       <c r="B17" t="n">
         <v>79638</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811707</v>
+        <v>811430</v>
       </c>
       <c r="R17" t="n">
-        <v>7390941</v>
+        <v>7391046</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127706925</v>
+        <v>127709699</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811866</v>
+        <v>811707</v>
       </c>
       <c r="R18" t="n">
-        <v>7390863</v>
+        <v>7390941</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2447,32 +2447,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709704</v>
+        <v>127709731</v>
       </c>
       <c r="B20" t="n">
-        <v>90367</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811693</v>
+        <v>811484</v>
       </c>
       <c r="R20" t="n">
-        <v>7390866</v>
+        <v>7391038</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709800</v>
+        <v>127709698</v>
       </c>
       <c r="B21" t="n">
-        <v>92616</v>
+        <v>79638</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811725</v>
+        <v>811656</v>
       </c>
       <c r="R21" t="n">
-        <v>7390826</v>
+        <v>7390942</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709797</v>
+        <v>127709800</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>92616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811577</v>
+        <v>811725</v>
       </c>
       <c r="R22" t="n">
-        <v>7391006</v>
+        <v>7390826</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,48 +2738,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709725</v>
+        <v>127709797</v>
       </c>
       <c r="B23" t="n">
-        <v>92626</v>
+        <v>92622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811692</v>
+        <v>811577</v>
       </c>
       <c r="R23" t="n">
-        <v>7390871</v>
+        <v>7391006</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2820,7 +2817,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2839,45 +2835,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709698</v>
+        <v>127709725</v>
       </c>
       <c r="B24" t="n">
-        <v>79638</v>
+        <v>92626</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811656</v>
+        <v>811692</v>
       </c>
       <c r="R24" t="n">
-        <v>7390942</v>
+        <v>7390871</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2918,6 +2917,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709731</v>
+        <v>127709704</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>90367</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>1962</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811484</v>
+        <v>811693</v>
       </c>
       <c r="R25" t="n">
-        <v>7391038</v>
+        <v>7390866</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3033,48 +3033,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127706927</v>
+        <v>127709790</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811760</v>
+        <v>811610</v>
       </c>
       <c r="R26" t="n">
-        <v>7390859</v>
+        <v>7391012</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3118,44 +3118,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709722</v>
+        <v>127709786</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>92622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811476</v>
+        <v>811612</v>
       </c>
       <c r="R27" t="n">
-        <v>7391149</v>
+        <v>7390987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709790</v>
+        <v>127709779</v>
       </c>
       <c r="B28" t="n">
         <v>92622</v>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811610</v>
+        <v>811561</v>
       </c>
       <c r="R28" t="n">
-        <v>7391012</v>
+        <v>7391108</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709786</v>
+        <v>127709796</v>
       </c>
       <c r="B29" t="n">
         <v>92622</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811612</v>
+        <v>811672</v>
       </c>
       <c r="R29" t="n">
-        <v>7390987</v>
+        <v>7391010</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709779</v>
+        <v>127709730</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811561</v>
+        <v>811452</v>
       </c>
       <c r="R30" t="n">
-        <v>7391108</v>
+        <v>7391057</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709796</v>
+        <v>127709736</v>
       </c>
       <c r="B31" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811672</v>
+        <v>811662</v>
       </c>
       <c r="R31" t="n">
-        <v>7391010</v>
+        <v>7390926</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709758</v>
+        <v>127706927</v>
       </c>
       <c r="B32" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,37 +3626,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811621</v>
+        <v>811760</v>
       </c>
       <c r="R32" t="n">
-        <v>7390981</v>
+        <v>7390859</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3700,44 +3700,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709730</v>
+        <v>127709758</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>78778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811452</v>
+        <v>811621</v>
       </c>
       <c r="R33" t="n">
-        <v>7391057</v>
+        <v>7390981</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3809,32 +3809,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709736</v>
+        <v>127709722</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811662</v>
+        <v>811476</v>
       </c>
       <c r="R34" t="n">
-        <v>7390926</v>
+        <v>7391149</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709756</v>
+        <v>127709708</v>
       </c>
       <c r="B39" t="n">
-        <v>78778</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,34 +4306,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811538</v>
+        <v>811580</v>
       </c>
       <c r="R39" t="n">
-        <v>7391022</v>
+        <v>7391090</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4368,6 +4376,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4385,7 +4398,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4489,10 +4502,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709708</v>
+        <v>127709756</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>78778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4500,42 +4513,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811580</v>
+        <v>811538</v>
       </c>
       <c r="R41" t="n">
-        <v>7391090</v>
+        <v>7391022</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4570,11 +4575,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4592,39 +4592,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127709735</v>
+        <v>127709752</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>78778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811626</v>
+        <v>811490</v>
       </c>
       <c r="R42" t="n">
-        <v>7390972</v>
+        <v>7391186</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4696,10 +4696,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127709752</v>
+        <v>127706917</v>
       </c>
       <c r="B43" t="n">
-        <v>78778</v>
+        <v>57663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,37 +4707,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811490</v>
+        <v>811865</v>
       </c>
       <c r="R43" t="n">
-        <v>7391186</v>
+        <v>7390848</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4767,6 +4767,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4781,19 +4786,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127706917</v>
+        <v>127709712</v>
       </c>
       <c r="B44" t="n">
         <v>57663</v>
@@ -4821,20 +4826,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811865</v>
+        <v>811420</v>
       </c>
       <c r="R44" t="n">
-        <v>7390848</v>
+        <v>7391078</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4868,7 +4881,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4883,65 +4896,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127709712</v>
+        <v>127709735</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811420</v>
+        <v>811626</v>
       </c>
       <c r="R45" t="n">
-        <v>7391078</v>
+        <v>7390972</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -4976,11 +4981,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5393,32 +5393,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127709793</v>
+        <v>127709749</v>
       </c>
       <c r="B50" t="n">
-        <v>92622</v>
+        <v>80995</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811612</v>
+        <v>811750</v>
       </c>
       <c r="R50" t="n">
-        <v>7391041</v>
+        <v>7390835</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5490,32 +5490,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127709740</v>
+        <v>127709793</v>
       </c>
       <c r="B51" t="n">
-        <v>78779</v>
+        <v>92622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811709</v>
+        <v>811612</v>
       </c>
       <c r="R51" t="n">
-        <v>7391020</v>
+        <v>7391041</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5569,7 +5569,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5588,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709749</v>
+        <v>127709753</v>
       </c>
       <c r="B52" t="n">
-        <v>80995</v>
+        <v>78778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5599,21 +5598,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5623,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811750</v>
+        <v>811385</v>
       </c>
       <c r="R52" t="n">
-        <v>7390835</v>
+        <v>7391163</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5685,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127709753</v>
+        <v>127709740</v>
       </c>
       <c r="B53" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5696,21 +5695,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5720,10 +5719,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811385</v>
+        <v>811709</v>
       </c>
       <c r="R53" t="n">
-        <v>7391163</v>
+        <v>7391020</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -5764,6 +5763,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5879,53 +5879,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709713</v>
+        <v>127709717</v>
       </c>
       <c r="B55" t="n">
-        <v>57663</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811514</v>
+        <v>811625</v>
       </c>
       <c r="R55" t="n">
-        <v>7391024</v>
+        <v>7390984</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5960,11 +5952,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5982,17 +5969,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709711</v>
+        <v>127706933</v>
       </c>
       <c r="B56" t="n">
-        <v>57663</v>
+        <v>78426</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6000,45 +5987,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811535</v>
+        <v>811536</v>
       </c>
       <c r="R56" t="n">
-        <v>7391056</v>
+        <v>7391018</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6068,11 +6047,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6087,44 +6061,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709792</v>
+        <v>127709771</v>
       </c>
       <c r="B57" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6134,10 +6108,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811619</v>
+        <v>811735</v>
       </c>
       <c r="R57" t="n">
-        <v>7391036</v>
+        <v>7391006</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6196,32 +6170,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709771</v>
+        <v>127709792</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6231,10 +6205,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811735</v>
+        <v>811619</v>
       </c>
       <c r="R58" t="n">
-        <v>7391006</v>
+        <v>7391036</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6293,32 +6267,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709717</v>
+        <v>127709702</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79638</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6328,10 +6302,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811625</v>
+        <v>811715</v>
       </c>
       <c r="R59" t="n">
-        <v>7390984</v>
+        <v>7391028</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6390,10 +6364,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127706933</v>
+        <v>127709692</v>
       </c>
       <c r="B60" t="n">
-        <v>78426</v>
+        <v>79638</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6401,37 +6375,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811536</v>
+        <v>811591</v>
       </c>
       <c r="R60" t="n">
-        <v>7391018</v>
+        <v>7391072</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6475,22 +6449,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709702</v>
+        <v>127709713</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6498,34 +6472,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811715</v>
+        <v>811514</v>
       </c>
       <c r="R61" t="n">
-        <v>7391028</v>
+        <v>7391024</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6560,6 +6542,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6577,17 +6564,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709692</v>
+        <v>127709711</v>
       </c>
       <c r="B62" t="n">
-        <v>79638</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6595,34 +6582,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811591</v>
+        <v>811535</v>
       </c>
       <c r="R62" t="n">
-        <v>7391072</v>
+        <v>7391056</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6657,6 +6652,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6674,39 +6674,39 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127709737</v>
+        <v>127709748</v>
       </c>
       <c r="B63" t="n">
-        <v>92815</v>
+        <v>58033</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811493</v>
+        <v>811439</v>
       </c>
       <c r="R63" t="n">
-        <v>7391027</v>
+        <v>7391070</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -6778,10 +6778,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127706912</v>
+        <v>127709737</v>
       </c>
       <c r="B64" t="n">
-        <v>91254</v>
+        <v>92815</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6789,37 +6789,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811615</v>
+        <v>811493</v>
       </c>
       <c r="R64" t="n">
-        <v>7391007</v>
+        <v>7391027</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6863,60 +6863,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127709748</v>
+        <v>127706912</v>
       </c>
       <c r="B65" t="n">
-        <v>58033</v>
+        <v>91254</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>3242</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811439</v>
+        <v>811615</v>
       </c>
       <c r="R65" t="n">
-        <v>7391070</v>
+        <v>7391007</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6960,22 +6960,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127709739</v>
+        <v>127709802</v>
       </c>
       <c r="B66" t="n">
-        <v>92815</v>
+        <v>92616</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6983,21 +6983,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7007,10 +7007,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811603</v>
+        <v>811642</v>
       </c>
       <c r="R66" t="n">
-        <v>7390979</v>
+        <v>7391000</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127709802</v>
+        <v>127709803</v>
       </c>
       <c r="B67" t="n">
-        <v>92616</v>
+        <v>78426</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7104,10 +7104,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811642</v>
+        <v>811716</v>
       </c>
       <c r="R67" t="n">
-        <v>7391000</v>
+        <v>7390831</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7166,48 +7166,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127706913</v>
+        <v>127709700</v>
       </c>
       <c r="B68" t="n">
-        <v>91297</v>
+        <v>79638</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811507</v>
+        <v>811687</v>
       </c>
       <c r="R68" t="n">
-        <v>7391034</v>
+        <v>7390967</v>
       </c>
       <c r="S68" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7251,44 +7251,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709798</v>
+        <v>127709739</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>92815</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7298,10 +7298,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811676</v>
+        <v>811603</v>
       </c>
       <c r="R69" t="n">
-        <v>7390933</v>
+        <v>7390979</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7360,48 +7360,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709803</v>
+        <v>127706913</v>
       </c>
       <c r="B70" t="n">
-        <v>78426</v>
+        <v>91297</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811716</v>
+        <v>811507</v>
       </c>
       <c r="R70" t="n">
-        <v>7390831</v>
+        <v>7391034</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7445,44 +7445,44 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709700</v>
+        <v>127709798</v>
       </c>
       <c r="B71" t="n">
-        <v>79638</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811687</v>
+        <v>811676</v>
       </c>
       <c r="R71" t="n">
-        <v>7390967</v>
+        <v>7390933</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7554,10 +7554,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709705</v>
+        <v>127709724</v>
       </c>
       <c r="B72" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7565,16 +7565,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7582,25 +7582,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811705</v>
+        <v>811533</v>
       </c>
       <c r="R72" t="n">
-        <v>7390855</v>
+        <v>7391035</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7635,11 +7627,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7657,17 +7644,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709724</v>
+        <v>127709705</v>
       </c>
       <c r="B73" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7675,16 +7662,16 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7692,17 +7679,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811533</v>
+        <v>811705</v>
       </c>
       <c r="R73" t="n">
-        <v>7391035</v>
+        <v>7390855</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7737,6 +7732,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7858,10 +7858,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709762</v>
+        <v>127709805</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>78426</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7869,21 +7869,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7893,10 +7893,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811718</v>
+        <v>811635</v>
       </c>
       <c r="R75" t="n">
-        <v>7390806</v>
+        <v>7391001</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7955,10 +7955,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709754</v>
+        <v>127709762</v>
       </c>
       <c r="B76" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7966,21 +7966,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7990,10 +7990,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811518</v>
+        <v>811718</v>
       </c>
       <c r="R76" t="n">
-        <v>7391069</v>
+        <v>7390806</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8149,10 +8149,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709805</v>
+        <v>127709701</v>
       </c>
       <c r="B78" t="n">
-        <v>78426</v>
+        <v>79638</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8160,21 +8160,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8184,10 +8184,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811635</v>
+        <v>811632</v>
       </c>
       <c r="R78" t="n">
-        <v>7391001</v>
+        <v>7391030</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8246,10 +8246,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709701</v>
+        <v>127709754</v>
       </c>
       <c r="B79" t="n">
-        <v>79638</v>
+        <v>78778</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8257,21 +8257,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8281,10 +8281,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811632</v>
+        <v>811518</v>
       </c>
       <c r="R79" t="n">
-        <v>7391030</v>
+        <v>7391069</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8343,10 +8343,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706918</v>
+        <v>127709738</v>
       </c>
       <c r="B80" t="n">
-        <v>91628</v>
+        <v>92815</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8354,37 +8354,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811451</v>
+        <v>811577</v>
       </c>
       <c r="R80" t="n">
-        <v>7391161</v>
+        <v>7391006</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8428,12 +8428,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8537,48 +8537,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127706931</v>
+        <v>127709755</v>
       </c>
       <c r="B82" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811711</v>
+        <v>811542</v>
       </c>
       <c r="R82" t="n">
-        <v>7390853</v>
+        <v>7391054</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8622,22 +8622,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127709755</v>
+        <v>127706918</v>
       </c>
       <c r="B83" t="n">
-        <v>78778</v>
+        <v>91628</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8645,37 +8645,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811542</v>
+        <v>811451</v>
       </c>
       <c r="R83" t="n">
-        <v>7391054</v>
+        <v>7391161</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8719,60 +8719,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709738</v>
+        <v>127706931</v>
       </c>
       <c r="B84" t="n">
-        <v>92815</v>
+        <v>92622</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811577</v>
+        <v>811711</v>
       </c>
       <c r="R84" t="n">
-        <v>7391006</v>
+        <v>7390853</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8816,22 +8816,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127709757</v>
+        <v>127706929</v>
       </c>
       <c r="B85" t="n">
-        <v>78778</v>
+        <v>82861</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8839,37 +8839,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811625</v>
+        <v>811496</v>
       </c>
       <c r="R85" t="n">
-        <v>7390969</v>
+        <v>7391110</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8913,60 +8913,60 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127706929</v>
+        <v>127709789</v>
       </c>
       <c r="B86" t="n">
-        <v>82861</v>
+        <v>92622</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811496</v>
+        <v>811610</v>
       </c>
       <c r="R86" t="n">
-        <v>7391110</v>
+        <v>7390981</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9010,19 +9010,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127709789</v>
+        <v>127709788</v>
       </c>
       <c r="B87" t="n">
         <v>92622</v>
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811610</v>
+        <v>811667</v>
       </c>
       <c r="R87" t="n">
-        <v>7390981</v>
+        <v>7390931</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9119,32 +9119,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709788</v>
+        <v>127709757</v>
       </c>
       <c r="B88" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9154,10 +9154,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811667</v>
+        <v>811625</v>
       </c>
       <c r="R88" t="n">
-        <v>7390931</v>
+        <v>7390969</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9313,32 +9313,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127709728</v>
+        <v>127709775</v>
       </c>
       <c r="B90" t="n">
-        <v>79044</v>
+        <v>78687</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9348,10 +9348,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811385</v>
+        <v>811544</v>
       </c>
       <c r="R90" t="n">
-        <v>7391153</v>
+        <v>7391011</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9410,32 +9410,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709775</v>
+        <v>127709777</v>
       </c>
       <c r="B91" t="n">
-        <v>78687</v>
+        <v>92622</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9445,10 +9445,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811544</v>
+        <v>811696</v>
       </c>
       <c r="R91" t="n">
-        <v>7391011</v>
+        <v>7390929</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9604,10 +9604,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709777</v>
+        <v>127709728</v>
       </c>
       <c r="B93" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9615,21 +9615,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811696</v>
+        <v>811385</v>
       </c>
       <c r="R93" t="n">
-        <v>7390929</v>
+        <v>7391153</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9895,10 +9895,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709693</v>
+        <v>127709769</v>
       </c>
       <c r="B96" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9906,21 +9906,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9930,10 +9930,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811486</v>
+        <v>811672</v>
       </c>
       <c r="R96" t="n">
-        <v>7391112</v>
+        <v>7390924</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9992,32 +9992,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B97" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10027,10 +10027,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R97" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10089,49 +10089,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709799</v>
+        <v>127709795</v>
       </c>
       <c r="B98" t="n">
-        <v>92616</v>
+        <v>92622</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811707</v>
+        <v>811676</v>
       </c>
       <c r="R98" t="n">
-        <v>7390860</v>
+        <v>7391004</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10172,7 +10168,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10191,45 +10186,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709783</v>
+        <v>127709799</v>
       </c>
       <c r="B99" t="n">
-        <v>92622</v>
+        <v>92616</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811387</v>
+        <v>811707</v>
       </c>
       <c r="R99" t="n">
-        <v>7391146</v>
+        <v>7390860</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10270,6 +10269,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10288,32 +10288,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709769</v>
+        <v>127709783</v>
       </c>
       <c r="B100" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811672</v>
+        <v>811387</v>
       </c>
       <c r="R100" t="n">
-        <v>7390924</v>
+        <v>7391146</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10385,32 +10385,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709764</v>
+        <v>127709747</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>57767</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10420,10 +10420,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811498</v>
+        <v>811653</v>
       </c>
       <c r="R101" t="n">
-        <v>7391103</v>
+        <v>7390948</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10482,32 +10482,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709770</v>
+        <v>127709785</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811608</v>
+        <v>811504</v>
       </c>
       <c r="R102" t="n">
-        <v>7391004</v>
+        <v>7391047</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10579,45 +10579,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709729</v>
+        <v>127709727</v>
       </c>
       <c r="B103" t="n">
-        <v>79044</v>
+        <v>92626</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>4365</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811434</v>
+        <v>811545</v>
       </c>
       <c r="R103" t="n">
-        <v>7391048</v>
+        <v>7391008</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10658,6 +10661,7 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -10676,10 +10680,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127706924</v>
+        <v>127709787</v>
       </c>
       <c r="B104" t="n">
-        <v>58033</v>
+        <v>92622</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10687,37 +10691,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811422</v>
+        <v>811677</v>
       </c>
       <c r="R104" t="n">
-        <v>7391139</v>
+        <v>7390878</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10761,12 +10765,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -10870,10 +10874,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709785</v>
+        <v>127709733</v>
       </c>
       <c r="B106" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10881,21 +10885,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10905,10 +10909,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811504</v>
+        <v>811530</v>
       </c>
       <c r="R106" t="n">
-        <v>7391047</v>
+        <v>7391016</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10967,48 +10971,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709727</v>
+        <v>127709770</v>
       </c>
       <c r="B107" t="n">
-        <v>92626</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811545</v>
+        <v>811608</v>
       </c>
       <c r="R107" t="n">
-        <v>7391008</v>
+        <v>7391004</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11049,7 +11050,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11068,10 +11068,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709787</v>
+        <v>127709729</v>
       </c>
       <c r="B108" t="n">
-        <v>92622</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11079,21 +11079,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11103,10 +11103,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811677</v>
+        <v>811434</v>
       </c>
       <c r="R108" t="n">
-        <v>7390878</v>
+        <v>7391048</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11165,32 +11165,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709733</v>
+        <v>127709764</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811530</v>
+        <v>811498</v>
       </c>
       <c r="R109" t="n">
-        <v>7391016</v>
+        <v>7391103</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11262,10 +11262,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709747</v>
+        <v>127706924</v>
       </c>
       <c r="B110" t="n">
-        <v>57767</v>
+        <v>58033</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11273,16 +11273,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11293,17 +11293,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811653</v>
+        <v>811422</v>
       </c>
       <c r="R110" t="n">
-        <v>7390948</v>
+        <v>7391139</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11347,12 +11347,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11553,10 +11553,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709720</v>
+        <v>127709804</v>
       </c>
       <c r="B113" t="n">
-        <v>57660</v>
+        <v>78426</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11564,21 +11564,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11588,10 +11588,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811515</v>
+        <v>811452</v>
       </c>
       <c r="R113" t="n">
-        <v>7391165</v>
+        <v>7391056</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11650,10 +11650,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709804</v>
+        <v>127709697</v>
       </c>
       <c r="B114" t="n">
-        <v>78426</v>
+        <v>79638</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11661,21 +11661,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11685,10 +11685,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811452</v>
+        <v>811625</v>
       </c>
       <c r="R114" t="n">
-        <v>7391056</v>
+        <v>7390969</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11747,10 +11747,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709697</v>
+        <v>127709720</v>
       </c>
       <c r="B115" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11758,21 +11758,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11782,10 +11782,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811625</v>
+        <v>811515</v>
       </c>
       <c r="R115" t="n">
-        <v>7390969</v>
+        <v>7391165</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -12245,32 +12245,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709765</v>
+        <v>127709732</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>79044</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12280,10 +12280,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811478</v>
+        <v>811523</v>
       </c>
       <c r="R120" t="n">
-        <v>7391172</v>
+        <v>7391024</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12342,10 +12342,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709723</v>
+        <v>127709765</v>
       </c>
       <c r="B121" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12353,21 +12353,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12377,10 +12377,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811411</v>
+        <v>811478</v>
       </c>
       <c r="R121" t="n">
-        <v>7391165</v>
+        <v>7391172</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12439,32 +12439,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709732</v>
+        <v>127709723</v>
       </c>
       <c r="B122" t="n">
-        <v>79044</v>
+        <v>57660</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12474,10 +12474,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811523</v>
+        <v>811411</v>
       </c>
       <c r="R122" t="n">
-        <v>7391024</v>
+        <v>7391165</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY203"/>
+  <dimension ref="A1:AY209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>127709763</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127706926</v>
+        <v>127709734</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811754</v>
+        <v>811573</v>
       </c>
       <c r="R3" t="n">
-        <v>7390851</v>
+        <v>7391001</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,60 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709784</v>
+        <v>127706926</v>
       </c>
       <c r="B4" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811414</v>
+        <v>811754</v>
       </c>
       <c r="R4" t="n">
-        <v>7391125</v>
+        <v>7390851</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709734</v>
+        <v>127709784</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>92631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811573</v>
+        <v>811414</v>
       </c>
       <c r="R5" t="n">
-        <v>7391001</v>
+        <v>7391125</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709781</v>
+        <v>127709774</v>
       </c>
       <c r="B6" t="n">
-        <v>92628</v>
+        <v>91602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811479</v>
+        <v>811658</v>
       </c>
       <c r="R6" t="n">
-        <v>7391142</v>
+        <v>7390945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709710</v>
+        <v>127706928</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,45 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811505</v>
+        <v>811509</v>
       </c>
       <c r="R7" t="n">
-        <v>7391045</v>
+        <v>7391152</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1239,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1258,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1273,7 +1260,7 @@
         <v>127706921</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1357,7 @@
         <v>127706923</v>
       </c>
       <c r="B9" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1464,45 +1451,53 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127709774</v>
+        <v>127709710</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>65</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811658</v>
+        <v>811505</v>
       </c>
       <c r="R10" t="n">
-        <v>7390945</v>
+        <v>7391045</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1537,6 +1532,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1554,55 +1554,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706928</v>
+        <v>127709781</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811509</v>
+        <v>811479</v>
       </c>
       <c r="R11" t="n">
-        <v>7391152</v>
+        <v>7391142</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,12 +1646,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1661,7 +1661,7 @@
         <v>127709721</v>
       </c>
       <c r="B12" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127706915</v>
       </c>
       <c r="B13" t="n">
-        <v>58522</v>
+        <v>58525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>127706925</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127709694</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>127706914</v>
       </c>
       <c r="B16" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>127709695</v>
       </c>
       <c r="B17" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>127709699</v>
       </c>
       <c r="B18" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         <v>127709709</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,45 +2447,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709698</v>
+        <v>127709725</v>
       </c>
       <c r="B20" t="n">
-        <v>79638</v>
+        <v>92635</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811656</v>
+        <v>811692</v>
       </c>
       <c r="R20" t="n">
-        <v>7390942</v>
+        <v>7390871</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2526,6 +2529,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2544,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709731</v>
+        <v>127709797</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,21 +2559,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811484</v>
+        <v>811577</v>
       </c>
       <c r="R21" t="n">
-        <v>7391038</v>
+        <v>7391006</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709704</v>
+        <v>127709800</v>
       </c>
       <c r="B22" t="n">
-        <v>90373</v>
+        <v>92625</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,21 +2656,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811693</v>
+        <v>811725</v>
       </c>
       <c r="R22" t="n">
-        <v>7390866</v>
+        <v>7390826</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709800</v>
+        <v>127709704</v>
       </c>
       <c r="B23" t="n">
-        <v>92622</v>
+        <v>90376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2749,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2773,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811725</v>
+        <v>811693</v>
       </c>
       <c r="R23" t="n">
-        <v>7390826</v>
+        <v>7390866</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2835,32 +2839,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709797</v>
+        <v>127709698</v>
       </c>
       <c r="B24" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2870,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811577</v>
+        <v>811656</v>
       </c>
       <c r="R24" t="n">
-        <v>7391006</v>
+        <v>7390942</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2932,48 +2936,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709725</v>
+        <v>127709731</v>
       </c>
       <c r="B25" t="n">
-        <v>92632</v>
+        <v>79047</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811692</v>
+        <v>811484</v>
       </c>
       <c r="R25" t="n">
-        <v>7390871</v>
+        <v>7391038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3014,7 +3015,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127706927</v>
+        <v>127709758</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,37 +3044,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811760</v>
+        <v>811621</v>
       </c>
       <c r="R26" t="n">
-        <v>7390859</v>
+        <v>7390981</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3118,22 +3118,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709790</v>
+        <v>127709730</v>
       </c>
       <c r="B27" t="n">
-        <v>92628</v>
+        <v>79047</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811610</v>
+        <v>811452</v>
       </c>
       <c r="R27" t="n">
-        <v>7391012</v>
+        <v>7391057</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709786</v>
+        <v>127709736</v>
       </c>
       <c r="B28" t="n">
-        <v>92628</v>
+        <v>79047</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811612</v>
+        <v>811662</v>
       </c>
       <c r="R28" t="n">
-        <v>7390987</v>
+        <v>7390926</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,48 +3324,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709779</v>
+        <v>127706927</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811561</v>
+        <v>811760</v>
       </c>
       <c r="R29" t="n">
-        <v>7391108</v>
+        <v>7390859</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3409,22 +3409,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709796</v>
+        <v>127709786</v>
       </c>
       <c r="B30" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811672</v>
+        <v>811612</v>
       </c>
       <c r="R30" t="n">
-        <v>7391010</v>
+        <v>7390987</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709758</v>
+        <v>127709796</v>
       </c>
       <c r="B31" t="n">
-        <v>78778</v>
+        <v>92631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811621</v>
+        <v>811672</v>
       </c>
       <c r="R31" t="n">
-        <v>7390981</v>
+        <v>7391010</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709730</v>
+        <v>127709790</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>92631</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811452</v>
+        <v>811610</v>
       </c>
       <c r="R32" t="n">
-        <v>7391057</v>
+        <v>7391012</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709736</v>
+        <v>127709779</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>92631</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811662</v>
+        <v>811561</v>
       </c>
       <c r="R33" t="n">
-        <v>7390926</v>
+        <v>7391108</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3812,7 +3812,7 @@
         <v>127709722</v>
       </c>
       <c r="B34" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>127709703</v>
       </c>
       <c r="B35" t="n">
-        <v>79609</v>
+        <v>79612</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127709741</v>
       </c>
       <c r="B36" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709768</v>
+        <v>127709756</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>78781</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811776</v>
+        <v>811538</v>
       </c>
       <c r="R37" t="n">
-        <v>7390918</v>
+        <v>7391022</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709766</v>
+        <v>127709708</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,34 +4209,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811730</v>
+        <v>811580</v>
       </c>
       <c r="R38" t="n">
-        <v>7390914</v>
+        <v>7391090</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4271,6 +4279,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4288,39 +4301,39 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709780</v>
+        <v>127709768</v>
       </c>
       <c r="B39" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4343,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811475</v>
+        <v>811776</v>
       </c>
       <c r="R39" t="n">
-        <v>7391196</v>
+        <v>7390918</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4392,10 +4405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709756</v>
+        <v>127709766</v>
       </c>
       <c r="B40" t="n">
-        <v>78778</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,21 +4416,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811538</v>
+        <v>811730</v>
       </c>
       <c r="R40" t="n">
-        <v>7391022</v>
+        <v>7390914</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4489,53 +4502,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709708</v>
+        <v>127709780</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811580</v>
+        <v>811475</v>
       </c>
       <c r="R41" t="n">
-        <v>7391090</v>
+        <v>7391196</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4570,11 +4575,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4592,39 +4592,39 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127709744</v>
+        <v>127709735</v>
       </c>
       <c r="B42" t="n">
-        <v>78779</v>
+        <v>79047</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811539</v>
+        <v>811626</v>
       </c>
       <c r="R42" t="n">
-        <v>7391022</v>
+        <v>7390972</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -4696,32 +4696,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127709735</v>
+        <v>127709752</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>78781</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811626</v>
+        <v>811490</v>
       </c>
       <c r="R43" t="n">
-        <v>7390972</v>
+        <v>7391186</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127709752</v>
+        <v>127706917</v>
       </c>
       <c r="B44" t="n">
-        <v>78778</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4804,37 +4804,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811490</v>
+        <v>811865</v>
       </c>
       <c r="R44" t="n">
-        <v>7391186</v>
+        <v>7390848</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4864,6 +4864,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4878,22 +4883,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127706917</v>
+        <v>127709712</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4918,20 +4923,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811865</v>
+        <v>811420</v>
       </c>
       <c r="R45" t="n">
-        <v>7390848</v>
+        <v>7391078</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4965,7 +4978,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>ringhack</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4980,22 +4993,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127709712</v>
+        <v>127709744</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>78782</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5003,42 +5016,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811420</v>
+        <v>811539</v>
       </c>
       <c r="R46" t="n">
-        <v>7391078</v>
+        <v>7391022</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5073,11 +5078,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5105,7 +5105,7 @@
         <v>127709782</v>
       </c>
       <c r="B47" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>127706932</v>
       </c>
       <c r="B48" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>127709750</v>
       </c>
       <c r="B49" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>127709749</v>
       </c>
       <c r="B50" t="n">
-        <v>80995</v>
+        <v>80998</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5490,48 +5490,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127824748</v>
+        <v>127709793</v>
       </c>
       <c r="B51" t="n">
-        <v>78779</v>
+        <v>92631</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Fatikvarre, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811709</v>
+        <v>811612</v>
       </c>
       <c r="R51" t="n">
-        <v>7391020</v>
+        <v>7391041</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5587,32 +5587,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709793</v>
+        <v>127709753</v>
       </c>
       <c r="B52" t="n">
-        <v>92628</v>
+        <v>78781</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811612</v>
+        <v>811385</v>
       </c>
       <c r="R52" t="n">
-        <v>7391041</v>
+        <v>7391163</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127709753</v>
+        <v>127824748</v>
       </c>
       <c r="B53" t="n">
-        <v>78778</v>
+        <v>78782</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,37 +5695,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811385</v>
+        <v>811709</v>
       </c>
       <c r="R53" t="n">
-        <v>7391163</v>
+        <v>7391020</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>127706919</v>
       </c>
       <c r="B54" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5878,32 +5878,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709771</v>
+        <v>127709792</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811735</v>
+        <v>811619</v>
       </c>
       <c r="R55" t="n">
-        <v>7391006</v>
+        <v>7391036</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5975,53 +5975,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709713</v>
+        <v>127709717</v>
       </c>
       <c r="B56" t="n">
-        <v>57663</v>
+        <v>79047</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811514</v>
+        <v>811625</v>
       </c>
       <c r="R56" t="n">
-        <v>7391024</v>
+        <v>7390984</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6056,11 +6048,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6078,17 +6065,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709711</v>
+        <v>127706933</v>
       </c>
       <c r="B57" t="n">
-        <v>57663</v>
+        <v>78429</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6096,45 +6083,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811535</v>
+        <v>811536</v>
       </c>
       <c r="R57" t="n">
-        <v>7391056</v>
+        <v>7391018</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6164,11 +6143,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6183,44 +6157,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709792</v>
+        <v>127709702</v>
       </c>
       <c r="B58" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6230,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811619</v>
+        <v>811715</v>
       </c>
       <c r="R58" t="n">
-        <v>7391036</v>
+        <v>7391028</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6292,32 +6266,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709717</v>
+        <v>127709692</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79641</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6327,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811625</v>
+        <v>811591</v>
       </c>
       <c r="R59" t="n">
-        <v>7390984</v>
+        <v>7391072</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6389,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127706933</v>
+        <v>127709771</v>
       </c>
       <c r="B60" t="n">
-        <v>78426</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6400,37 +6374,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811536</v>
+        <v>811735</v>
       </c>
       <c r="R60" t="n">
-        <v>7391018</v>
+        <v>7391006</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6474,22 +6448,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709702</v>
+        <v>127709713</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>57666</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6497,34 +6471,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811715</v>
+        <v>811514</v>
       </c>
       <c r="R61" t="n">
-        <v>7391028</v>
+        <v>7391024</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6559,6 +6541,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6576,17 +6563,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709692</v>
+        <v>127709711</v>
       </c>
       <c r="B62" t="n">
-        <v>79638</v>
+        <v>57666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6594,34 +6581,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811591</v>
+        <v>811535</v>
       </c>
       <c r="R62" t="n">
-        <v>7391072</v>
+        <v>7391056</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6656,6 +6651,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6683,7 +6683,7 @@
         <v>127709737</v>
       </c>
       <c r="B63" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>127706912</v>
       </c>
       <c r="B64" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>127709748</v>
       </c>
       <c r="B65" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127709802</v>
+        <v>127709739</v>
       </c>
       <c r="B66" t="n">
-        <v>92622</v>
+        <v>92824</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6982,21 +6982,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811642</v>
+        <v>811603</v>
       </c>
       <c r="R66" t="n">
-        <v>7391000</v>
+        <v>7390979</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7071,7 +7071,7 @@
         <v>127706913</v>
       </c>
       <c r="B67" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7165,32 +7165,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709798</v>
+        <v>127709802</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>92625</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811676</v>
+        <v>811642</v>
       </c>
       <c r="R68" t="n">
-        <v>7390933</v>
+        <v>7391000</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7262,32 +7262,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709803</v>
+        <v>127709798</v>
       </c>
       <c r="B69" t="n">
-        <v>78426</v>
+        <v>79047</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811716</v>
+        <v>811676</v>
       </c>
       <c r="R69" t="n">
-        <v>7390831</v>
+        <v>7390933</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709700</v>
+        <v>127709803</v>
       </c>
       <c r="B70" t="n">
-        <v>79638</v>
+        <v>78429</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811687</v>
+        <v>811716</v>
       </c>
       <c r="R70" t="n">
-        <v>7390967</v>
+        <v>7390831</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7456,10 +7456,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709724</v>
+        <v>127709700</v>
       </c>
       <c r="B71" t="n">
-        <v>57660</v>
+        <v>79641</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7467,21 +7467,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7491,10 +7491,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811533</v>
+        <v>811687</v>
       </c>
       <c r="R71" t="n">
-        <v>7391035</v>
+        <v>7390967</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7553,7 +7553,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709705</v>
+        <v>127709724</v>
       </c>
       <c r="B72" t="n">
         <v>57663</v>
@@ -7564,16 +7564,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7581,25 +7581,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811705</v>
+        <v>811533</v>
       </c>
       <c r="R72" t="n">
-        <v>7390855</v>
+        <v>7391035</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -7634,11 +7626,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -7656,17 +7643,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709739</v>
+        <v>127709705</v>
       </c>
       <c r="B73" t="n">
-        <v>92821</v>
+        <v>57666</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7674,34 +7661,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811603</v>
+        <v>811705</v>
       </c>
       <c r="R73" t="n">
-        <v>7390979</v>
+        <v>7390855</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7736,6 +7731,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7753,17 +7753,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709754</v>
+        <v>127709772</v>
       </c>
       <c r="B74" t="n">
-        <v>78778</v>
+        <v>82864</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811518</v>
+        <v>811763</v>
       </c>
       <c r="R74" t="n">
-        <v>7391069</v>
+        <v>7390963</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709696</v>
+        <v>127709762</v>
       </c>
       <c r="B75" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7868,21 +7868,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811519</v>
+        <v>811718</v>
       </c>
       <c r="R75" t="n">
-        <v>7391067</v>
+        <v>7390806</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709805</v>
+        <v>127709754</v>
       </c>
       <c r="B76" t="n">
-        <v>78426</v>
+        <v>78781</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811635</v>
+        <v>811518</v>
       </c>
       <c r="R76" t="n">
-        <v>7391001</v>
+        <v>7391069</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709701</v>
+        <v>127709696</v>
       </c>
       <c r="B77" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811632</v>
+        <v>811519</v>
       </c>
       <c r="R77" t="n">
-        <v>7391030</v>
+        <v>7391067</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709772</v>
+        <v>127709805</v>
       </c>
       <c r="B78" t="n">
-        <v>82861</v>
+        <v>78429</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811763</v>
+        <v>811635</v>
       </c>
       <c r="R78" t="n">
-        <v>7390963</v>
+        <v>7391001</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709762</v>
+        <v>127709701</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811718</v>
+        <v>811632</v>
       </c>
       <c r="R79" t="n">
-        <v>7390806</v>
+        <v>7391030</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706918</v>
+        <v>127709738</v>
       </c>
       <c r="B80" t="n">
-        <v>91634</v>
+        <v>92824</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811451</v>
+        <v>811577</v>
       </c>
       <c r="R80" t="n">
-        <v>7391161</v>
+        <v>7391006</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,22 +8427,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B81" t="n">
-        <v>92821</v>
+        <v>91637</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8450,37 +8450,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R81" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8524,12 +8524,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8539,7 +8539,7 @@
         <v>127709760</v>
       </c>
       <c r="B82" t="n">
-        <v>91499</v>
+        <v>91502</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>127706931</v>
       </c>
       <c r="B83" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>127709755</v>
       </c>
       <c r="B84" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>127706929</v>
       </c>
       <c r="B85" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8924,10 +8924,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709789</v>
+        <v>127709788</v>
       </c>
       <c r="B86" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811610</v>
+        <v>811667</v>
       </c>
       <c r="R86" t="n">
-        <v>7390981</v>
+        <v>7390931</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9021,10 +9021,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127709788</v>
+        <v>127709789</v>
       </c>
       <c r="B87" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9056,10 +9056,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811667</v>
+        <v>811610</v>
       </c>
       <c r="R87" t="n">
-        <v>7390931</v>
+        <v>7390981</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9121,7 +9121,7 @@
         <v>127709757</v>
       </c>
       <c r="B88" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>127709759</v>
       </c>
       <c r="B89" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>127706916</v>
       </c>
       <c r="B90" t="n">
-        <v>90373</v>
+        <v>90376</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709775</v>
+        <v>127709742</v>
       </c>
       <c r="B91" t="n">
-        <v>78687</v>
+        <v>78782</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9420,21 +9420,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811544</v>
+        <v>811466</v>
       </c>
       <c r="R91" t="n">
-        <v>7391011</v>
+        <v>7391161</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9506,48 +9506,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127709777</v>
+        <v>127706922</v>
       </c>
       <c r="B92" t="n">
-        <v>92628</v>
+        <v>78782</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811696</v>
+        <v>811556</v>
       </c>
       <c r="R92" t="n">
-        <v>7390929</v>
+        <v>7391103</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,44 +9591,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709728</v>
+        <v>127709775</v>
       </c>
       <c r="B93" t="n">
-        <v>79044</v>
+        <v>78690</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811385</v>
+        <v>811544</v>
       </c>
       <c r="R93" t="n">
-        <v>7391153</v>
+        <v>7391011</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9700,32 +9700,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127709742</v>
+        <v>127709777</v>
       </c>
       <c r="B94" t="n">
-        <v>78779</v>
+        <v>92631</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811466</v>
+        <v>811696</v>
       </c>
       <c r="R94" t="n">
-        <v>7391161</v>
+        <v>7390929</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9797,48 +9797,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127706922</v>
+        <v>127709728</v>
       </c>
       <c r="B95" t="n">
-        <v>78779</v>
+        <v>79047</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811556</v>
+        <v>811385</v>
       </c>
       <c r="R95" t="n">
-        <v>7391103</v>
+        <v>7391153</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9882,12 +9882,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -9897,7 +9897,7 @@
         <v>127709769</v>
       </c>
       <c r="B96" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>127709795</v>
       </c>
       <c r="B97" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10088,49 +10088,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709799</v>
+        <v>127709783</v>
       </c>
       <c r="B98" t="n">
-        <v>92622</v>
+        <v>92631</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811707</v>
+        <v>811387</v>
       </c>
       <c r="R98" t="n">
-        <v>7390860</v>
+        <v>7391146</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10171,7 +10167,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10190,45 +10185,49 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709783</v>
+        <v>127709799</v>
       </c>
       <c r="B99" t="n">
-        <v>92628</v>
+        <v>92625</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811387</v>
+        <v>811707</v>
       </c>
       <c r="R99" t="n">
-        <v>7391146</v>
+        <v>7390860</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10269,6 +10268,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>127709693</v>
       </c>
       <c r="B100" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,10 +10384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709770</v>
+        <v>127706920</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>92824</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10395,37 +10395,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811608</v>
+        <v>811552</v>
       </c>
       <c r="R101" t="n">
-        <v>7391004</v>
+        <v>7391002</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,44 +10469,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709764</v>
+        <v>127709785</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811498</v>
+        <v>811504</v>
       </c>
       <c r="R102" t="n">
-        <v>7391103</v>
+        <v>7391047</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10578,10 +10578,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709747</v>
+        <v>127709729</v>
       </c>
       <c r="B103" t="n">
-        <v>57767</v>
+        <v>79047</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103031</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811653</v>
+        <v>811434</v>
       </c>
       <c r="R103" t="n">
-        <v>7390948</v>
+        <v>7391048</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10675,10 +10675,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127706920</v>
+        <v>127709770</v>
       </c>
       <c r="B104" t="n">
-        <v>92821</v>
+        <v>79023</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10686,37 +10686,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811552</v>
+        <v>811608</v>
       </c>
       <c r="R104" t="n">
-        <v>7391002</v>
+        <v>7391004</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10760,44 +10760,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709785</v>
+        <v>127709764</v>
       </c>
       <c r="B105" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811504</v>
+        <v>811498</v>
       </c>
       <c r="R105" t="n">
-        <v>7391047</v>
+        <v>7391103</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10869,48 +10869,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709727</v>
+        <v>127709787</v>
       </c>
       <c r="B106" t="n">
-        <v>92632</v>
+        <v>92631</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811545</v>
+        <v>811677</v>
       </c>
       <c r="R106" t="n">
-        <v>7391008</v>
+        <v>7390878</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10951,7 +10948,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10970,45 +10966,48 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709787</v>
+        <v>127709727</v>
       </c>
       <c r="B107" t="n">
-        <v>92628</v>
+        <v>92635</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811677</v>
+        <v>811545</v>
       </c>
       <c r="R107" t="n">
-        <v>7390878</v>
+        <v>7391008</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11049,6 +11048,7 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
+      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>127709733</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709729</v>
+        <v>127706924</v>
       </c>
       <c r="B109" t="n">
-        <v>79044</v>
+        <v>58036</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11175,37 +11175,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811434</v>
+        <v>811422</v>
       </c>
       <c r="R109" t="n">
-        <v>7391048</v>
+        <v>7391139</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11249,22 +11249,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127706924</v>
+        <v>127709747</v>
       </c>
       <c r="B110" t="n">
-        <v>58033</v>
+        <v>57770</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11272,16 +11272,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11292,17 +11292,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811422</v>
+        <v>811653</v>
       </c>
       <c r="R110" t="n">
-        <v>7391139</v>
+        <v>7390948</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11346,22 +11346,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709804</v>
+        <v>127709801</v>
       </c>
       <c r="B111" t="n">
-        <v>78426</v>
+        <v>92625</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811452</v>
+        <v>811615</v>
       </c>
       <c r="R111" t="n">
-        <v>7391056</v>
+        <v>7390990</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,32 +11455,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709697</v>
+        <v>127709726</v>
       </c>
       <c r="B112" t="n">
-        <v>79638</v>
+        <v>92635</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811625</v>
+        <v>811638</v>
       </c>
       <c r="R112" t="n">
-        <v>7390969</v>
+        <v>7391044</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11555,7 +11555,7 @@
         <v>127709720</v>
       </c>
       <c r="B113" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709707</v>
+        <v>127709804</v>
       </c>
       <c r="B114" t="n">
-        <v>57663</v>
+        <v>78429</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,42 +11660,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811874</v>
+        <v>811452</v>
       </c>
       <c r="R114" t="n">
-        <v>7390830</v>
+        <v>7391056</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11730,11 +11722,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -11752,17 +11739,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709801</v>
+        <v>127709697</v>
       </c>
       <c r="B115" t="n">
-        <v>92622</v>
+        <v>79641</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11770,21 +11757,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11794,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811615</v>
+        <v>811625</v>
       </c>
       <c r="R115" t="n">
-        <v>7390990</v>
+        <v>7390969</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11856,45 +11843,53 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127709726</v>
+        <v>127709707</v>
       </c>
       <c r="B116" t="n">
-        <v>92632</v>
+        <v>57666</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4365</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811638</v>
+        <v>811874</v>
       </c>
       <c r="R116" t="n">
-        <v>7391044</v>
+        <v>7390830</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11929,6 +11924,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11946,39 +11946,39 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709765</v>
+        <v>127709791</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811478</v>
+        <v>811605</v>
       </c>
       <c r="R117" t="n">
-        <v>7391172</v>
+        <v>7391024</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12053,7 +12053,7 @@
         <v>127709732</v>
       </c>
       <c r="B118" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12147,10 +12147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709776</v>
+        <v>127709743</v>
       </c>
       <c r="B119" t="n">
-        <v>78687</v>
+        <v>78782</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12158,21 +12158,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811646</v>
+        <v>811385</v>
       </c>
       <c r="R119" t="n">
-        <v>7390963</v>
+        <v>7391163</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,32 +12244,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709778</v>
+        <v>127709765</v>
       </c>
       <c r="B120" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811683</v>
+        <v>811478</v>
       </c>
       <c r="R120" t="n">
-        <v>7390938</v>
+        <v>7391172</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,10 +12341,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709791</v>
+        <v>127709778</v>
       </c>
       <c r="B121" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811605</v>
+        <v>811683</v>
       </c>
       <c r="R121" t="n">
-        <v>7391024</v>
+        <v>7390938</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12438,10 +12438,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709723</v>
+        <v>127709776</v>
       </c>
       <c r="B122" t="n">
-        <v>57660</v>
+        <v>78690</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811411</v>
+        <v>811646</v>
       </c>
       <c r="R122" t="n">
-        <v>7391165</v>
+        <v>7390963</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12535,10 +12535,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127709743</v>
+        <v>127709723</v>
       </c>
       <c r="B123" t="n">
-        <v>78779</v>
+        <v>57663</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12546,21 +12546,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811385</v>
+        <v>811411</v>
       </c>
       <c r="R123" t="n">
-        <v>7391163</v>
+        <v>7391165</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127824695</v>
+        <v>127824768</v>
       </c>
       <c r="B124" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>811985</v>
+        <v>811739</v>
       </c>
       <c r="R124" t="n">
-        <v>7391147</v>
+        <v>7390831</v>
       </c>
       <c r="S124" t="n">
         <v>1</v>
@@ -12729,10 +12729,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127824776</v>
+        <v>127824695</v>
       </c>
       <c r="B125" t="n">
-        <v>82861</v>
+        <v>91341</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12740,21 +12740,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12764,10 +12764,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>811943</v>
+        <v>811985</v>
       </c>
       <c r="R125" t="n">
-        <v>7390852</v>
+        <v>7391147</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -12826,10 +12826,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127824701</v>
+        <v>127824776</v>
       </c>
       <c r="B126" t="n">
-        <v>91338</v>
+        <v>82864</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12837,21 +12837,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>811868</v>
+        <v>811943</v>
       </c>
       <c r="R126" t="n">
-        <v>7390994</v>
+        <v>7390852</v>
       </c>
       <c r="S126" t="n">
         <v>1</v>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127824768</v>
+        <v>127824701</v>
       </c>
       <c r="B127" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12934,21 +12934,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12958,10 +12958,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811739</v>
+        <v>811868</v>
       </c>
       <c r="R127" t="n">
-        <v>7390831</v>
+        <v>7390994</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13023,7 +13023,7 @@
         <v>127824716</v>
       </c>
       <c r="B128" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13117,32 +13117,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127824758</v>
+        <v>127824751</v>
       </c>
       <c r="B129" t="n">
-        <v>79020</v>
+        <v>57770</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811955</v>
+        <v>812037</v>
       </c>
       <c r="R129" t="n">
-        <v>7391105</v>
+        <v>7391151</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -13214,10 +13214,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824762</v>
+        <v>127824758</v>
       </c>
       <c r="B130" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811855</v>
+        <v>811955</v>
       </c>
       <c r="R130" t="n">
-        <v>7390961</v>
+        <v>7391105</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,10 +13311,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824735</v>
+        <v>127824762</v>
       </c>
       <c r="B131" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13322,21 +13322,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811831</v>
+        <v>811855</v>
       </c>
       <c r="R131" t="n">
-        <v>7390950</v>
+        <v>7390961</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127824721</v>
+        <v>127824735</v>
       </c>
       <c r="B132" t="n">
         <v>57663</v>
@@ -13419,16 +13419,16 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -13443,10 +13443,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>811786</v>
+        <v>811831</v>
       </c>
       <c r="R132" t="n">
-        <v>7390835</v>
+        <v>7390950</v>
       </c>
       <c r="S132" t="n">
         <v>1</v>
@@ -13505,10 +13505,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>127824719</v>
+        <v>127824721</v>
       </c>
       <c r="B133" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13540,10 +13540,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>811824</v>
+        <v>811786</v>
       </c>
       <c r="R133" t="n">
-        <v>7390745</v>
+        <v>7390835</v>
       </c>
       <c r="S133" t="n">
         <v>1</v>
@@ -13602,27 +13602,27 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>127824751</v>
+        <v>127824719</v>
       </c>
       <c r="B134" t="n">
-        <v>57767</v>
+        <v>57666</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -13637,10 +13637,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>812037</v>
+        <v>811824</v>
       </c>
       <c r="R134" t="n">
-        <v>7391151</v>
+        <v>7390745</v>
       </c>
       <c r="S134" t="n">
         <v>1</v>
@@ -13702,7 +13702,7 @@
         <v>127824698</v>
       </c>
       <c r="B135" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>127824699</v>
       </c>
       <c r="B136" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>127824696</v>
       </c>
       <c r="B137" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13990,32 +13990,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824715</v>
+        <v>127824782</v>
       </c>
       <c r="B138" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811979</v>
+        <v>811902</v>
       </c>
       <c r="R138" t="n">
-        <v>7391101</v>
+        <v>7390765</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14087,32 +14087,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127824703</v>
+        <v>127824747</v>
       </c>
       <c r="B139" t="n">
-        <v>91338</v>
+        <v>79047</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6434</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14122,10 +14122,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811762</v>
+        <v>811803</v>
       </c>
       <c r="R139" t="n">
-        <v>7390826</v>
+        <v>7390886</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -14184,32 +14184,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824753</v>
+        <v>127824739</v>
       </c>
       <c r="B140" t="n">
-        <v>80995</v>
+        <v>79047</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>6434</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811752</v>
+        <v>811874</v>
       </c>
       <c r="R140" t="n">
-        <v>7390828</v>
+        <v>7391049</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824775</v>
+        <v>127824703</v>
       </c>
       <c r="B141" t="n">
-        <v>82861</v>
+        <v>91341</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811886</v>
+        <v>811762</v>
       </c>
       <c r="R141" t="n">
-        <v>7390941</v>
+        <v>7390826</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14378,32 +14378,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127824782</v>
+        <v>127824753</v>
       </c>
       <c r="B142" t="n">
-        <v>92628</v>
+        <v>80998</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14413,10 +14413,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811902</v>
+        <v>811752</v>
       </c>
       <c r="R142" t="n">
-        <v>7390765</v>
+        <v>7390828</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -14475,32 +14475,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127824747</v>
+        <v>127824775</v>
       </c>
       <c r="B143" t="n">
-        <v>79044</v>
+        <v>82864</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811803</v>
+        <v>811886</v>
       </c>
       <c r="R143" t="n">
-        <v>7390886</v>
+        <v>7390941</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -14572,32 +14572,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127824739</v>
+        <v>127824733</v>
       </c>
       <c r="B144" t="n">
-        <v>79044</v>
+        <v>92657</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6434</v>
+        <v>5448</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811874</v>
+        <v>811899</v>
       </c>
       <c r="R144" t="n">
-        <v>7391049</v>
+        <v>7390756</v>
       </c>
       <c r="S144" t="n">
         <v>1</v>
@@ -14669,10 +14669,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127824694</v>
+        <v>127824766</v>
       </c>
       <c r="B145" t="n">
-        <v>79609</v>
+        <v>79023</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811716</v>
+        <v>811921</v>
       </c>
       <c r="R145" t="n">
-        <v>7390763</v>
+        <v>7390838</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -14769,7 +14769,7 @@
         <v>127824690</v>
       </c>
       <c r="B146" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824733</v>
+        <v>127824717</v>
       </c>
       <c r="B147" t="n">
-        <v>92654</v>
+        <v>57666</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14874,21 +14874,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5448</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811899</v>
+        <v>811898</v>
       </c>
       <c r="R147" t="n">
-        <v>7390756</v>
+        <v>7390821</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -14960,32 +14960,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127824784</v>
+        <v>127824712</v>
       </c>
       <c r="B148" t="n">
-        <v>92628</v>
+        <v>57666</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811827</v>
+        <v>812079</v>
       </c>
       <c r="R148" t="n">
-        <v>7390741</v>
+        <v>7391319</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15057,10 +15057,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824766</v>
+        <v>127824725</v>
       </c>
       <c r="B149" t="n">
-        <v>79020</v>
+        <v>57826</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15068,21 +15068,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811921</v>
+        <v>811800</v>
       </c>
       <c r="R149" t="n">
-        <v>7390838</v>
+        <v>7390892</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15157,7 +15157,7 @@
         <v>127824697</v>
       </c>
       <c r="B150" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15251,32 +15251,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127824717</v>
+        <v>127824784</v>
       </c>
       <c r="B151" t="n">
-        <v>57663</v>
+        <v>92631</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811898</v>
+        <v>811827</v>
       </c>
       <c r="R151" t="n">
-        <v>7390821</v>
+        <v>7390741</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -15348,10 +15348,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127824712</v>
+        <v>127824694</v>
       </c>
       <c r="B152" t="n">
-        <v>57663</v>
+        <v>79612</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15359,21 +15359,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15383,10 +15383,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>812079</v>
+        <v>811716</v>
       </c>
       <c r="R152" t="n">
-        <v>7391319</v>
+        <v>7390763</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -15445,32 +15445,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127824725</v>
+        <v>127824783</v>
       </c>
       <c r="B153" t="n">
-        <v>57823</v>
+        <v>92631</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>811800</v>
+        <v>811895</v>
       </c>
       <c r="R153" t="n">
-        <v>7390892</v>
+        <v>7390780</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -15545,7 +15545,7 @@
         <v>127824688</v>
       </c>
       <c r="B154" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>127824777</v>
       </c>
       <c r="B155" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -15736,32 +15736,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127824783</v>
+        <v>127824692</v>
       </c>
       <c r="B156" t="n">
-        <v>92628</v>
+        <v>79641</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15771,7 +15771,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811895</v>
+        <v>811721</v>
       </c>
       <c r="R156" t="n">
         <v>7390780</v>
@@ -15833,32 +15833,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127824692</v>
+        <v>127824741</v>
       </c>
       <c r="B157" t="n">
-        <v>79638</v>
+        <v>79047</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -15868,10 +15868,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>811721</v>
+        <v>812137</v>
       </c>
       <c r="R157" t="n">
-        <v>7390780</v>
+        <v>7391383</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -15930,10 +15930,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127824741</v>
+        <v>127824722</v>
       </c>
       <c r="B158" t="n">
-        <v>79044</v>
+        <v>56858</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15941,34 +15941,38 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6434</v>
+        <v>100138</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>812137</v>
+        <v>811902</v>
       </c>
       <c r="R158" t="n">
-        <v>7391383</v>
+        <v>7390779</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -16001,6 +16005,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Hittad död under tall där någon ätit den antagligen duvhök.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16027,49 +16036,45 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824722</v>
+        <v>127824691</v>
       </c>
       <c r="B159" t="n">
-        <v>56855</v>
+        <v>79641</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811902</v>
+        <v>811718</v>
       </c>
       <c r="R159" t="n">
-        <v>7390779</v>
+        <v>7390758</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16102,11 +16107,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Hittad död under tall där någon ätit den antagligen duvhök.</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16133,10 +16133,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824691</v>
+        <v>127824769</v>
       </c>
       <c r="B160" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811718</v>
+        <v>811795</v>
       </c>
       <c r="R160" t="n">
-        <v>7390758</v>
+        <v>7390892</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16230,32 +16230,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824734</v>
+        <v>127824709</v>
       </c>
       <c r="B161" t="n">
-        <v>80152</v>
+        <v>57666</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>812156</v>
+        <v>812041</v>
       </c>
       <c r="R161" t="n">
-        <v>7391361</v>
+        <v>7391278</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16327,32 +16327,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824709</v>
+        <v>127824734</v>
       </c>
       <c r="B162" t="n">
-        <v>57663</v>
+        <v>80155</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>812041</v>
+        <v>812156</v>
       </c>
       <c r="R162" t="n">
-        <v>7391278</v>
+        <v>7391361</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16424,10 +16424,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127824769</v>
+        <v>127824755</v>
       </c>
       <c r="B163" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16459,10 +16459,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811795</v>
+        <v>812164</v>
       </c>
       <c r="R163" t="n">
-        <v>7390892</v>
+        <v>7391415</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -16521,10 +16521,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127824755</v>
+        <v>127824724</v>
       </c>
       <c r="B164" t="n">
-        <v>79020</v>
+        <v>57826</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16532,34 +16532,38 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>812164</v>
+        <v>811806</v>
       </c>
       <c r="R164" t="n">
-        <v>7391415</v>
+        <v>7390821</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
@@ -16618,10 +16622,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127824724</v>
+        <v>127824761</v>
       </c>
       <c r="B165" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16629,38 +16633,34 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811806</v>
+        <v>811845</v>
       </c>
       <c r="R165" t="n">
-        <v>7390821</v>
+        <v>7390977</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -16719,10 +16719,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127824700</v>
+        <v>127824760</v>
       </c>
       <c r="B166" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16730,21 +16730,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16754,10 +16754,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811899</v>
+        <v>811882</v>
       </c>
       <c r="R166" t="n">
-        <v>7390998</v>
+        <v>7390983</v>
       </c>
       <c r="S166" t="n">
         <v>1</v>
@@ -16816,10 +16816,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127824761</v>
+        <v>127824700</v>
       </c>
       <c r="B167" t="n">
-        <v>79020</v>
+        <v>91341</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16827,21 +16827,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16851,10 +16851,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>811845</v>
+        <v>811899</v>
       </c>
       <c r="R167" t="n">
-        <v>7390977</v>
+        <v>7390998</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -16913,10 +16913,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127824760</v>
+        <v>127824718</v>
       </c>
       <c r="B168" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -16924,21 +16924,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811882</v>
+        <v>811915</v>
       </c>
       <c r="R168" t="n">
-        <v>7390983</v>
+        <v>7390765</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -17010,10 +17010,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127824718</v>
+        <v>127824693</v>
       </c>
       <c r="B169" t="n">
-        <v>57663</v>
+        <v>79612</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17021,21 +17021,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811915</v>
+        <v>811874</v>
       </c>
       <c r="R169" t="n">
-        <v>7390765</v>
+        <v>7391049</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -17107,32 +17107,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127824710</v>
+        <v>127824738</v>
       </c>
       <c r="B170" t="n">
-        <v>57663</v>
+        <v>79047</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>812092</v>
+        <v>811854</v>
       </c>
       <c r="R170" t="n">
-        <v>7391361</v>
+        <v>7391042</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -17204,32 +17204,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824693</v>
+        <v>127824746</v>
       </c>
       <c r="B171" t="n">
-        <v>79609</v>
+        <v>79047</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811874</v>
+        <v>811759</v>
       </c>
       <c r="R171" t="n">
-        <v>7391049</v>
+        <v>7390733</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17304,7 +17304,7 @@
         <v>127824687</v>
       </c>
       <c r="B172" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>127824780</v>
       </c>
       <c r="B173" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17495,32 +17495,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824738</v>
+        <v>127824689</v>
       </c>
       <c r="B174" t="n">
-        <v>79044</v>
+        <v>79641</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811854</v>
+        <v>811755</v>
       </c>
       <c r="R174" t="n">
-        <v>7391042</v>
+        <v>7390737</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -17592,32 +17592,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127824746</v>
+        <v>127824767</v>
       </c>
       <c r="B175" t="n">
-        <v>79044</v>
+        <v>79023</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>811759</v>
+        <v>811966</v>
       </c>
       <c r="R175" t="n">
-        <v>7390733</v>
+        <v>7390830</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -17689,32 +17689,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127824689</v>
+        <v>127824781</v>
       </c>
       <c r="B176" t="n">
-        <v>79638</v>
+        <v>92631</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -17724,10 +17724,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811755</v>
+        <v>811927</v>
       </c>
       <c r="R176" t="n">
-        <v>7390737</v>
+        <v>7390809</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -17786,10 +17786,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127824767</v>
+        <v>127824765</v>
       </c>
       <c r="B177" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17821,10 +17821,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>811966</v>
+        <v>811918</v>
       </c>
       <c r="R177" t="n">
-        <v>7390830</v>
+        <v>7390852</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>
@@ -17883,32 +17883,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127824781</v>
+        <v>127824759</v>
       </c>
       <c r="B178" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -17918,10 +17918,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>811927</v>
+        <v>811950</v>
       </c>
       <c r="R178" t="n">
-        <v>7390809</v>
+        <v>7391109</v>
       </c>
       <c r="S178" t="n">
         <v>1</v>
@@ -17983,7 +17983,7 @@
         <v>127824778</v>
       </c>
       <c r="B179" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>127824772</v>
       </c>
       <c r="B180" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18174,10 +18174,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127824765</v>
+        <v>127824714</v>
       </c>
       <c r="B181" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18185,21 +18185,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18209,10 +18209,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>811918</v>
+        <v>811990</v>
       </c>
       <c r="R181" t="n">
-        <v>7390852</v>
+        <v>7391109</v>
       </c>
       <c r="S181" t="n">
         <v>1</v>
@@ -18271,32 +18271,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127824759</v>
+        <v>127824740</v>
       </c>
       <c r="B182" t="n">
-        <v>79020</v>
+        <v>79047</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18306,10 +18306,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>811950</v>
+        <v>812040</v>
       </c>
       <c r="R182" t="n">
-        <v>7391109</v>
+        <v>7391193</v>
       </c>
       <c r="S182" t="n">
         <v>1</v>
@@ -18368,32 +18368,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>127824714</v>
+        <v>127824743</v>
       </c>
       <c r="B183" t="n">
-        <v>57663</v>
+        <v>79047</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -18403,10 +18403,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>811990</v>
+        <v>811966</v>
       </c>
       <c r="R183" t="n">
-        <v>7391109</v>
+        <v>7390830</v>
       </c>
       <c r="S183" t="n">
         <v>1</v>
@@ -18465,10 +18465,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127824740</v>
+        <v>127824752</v>
       </c>
       <c r="B184" t="n">
-        <v>79044</v>
+        <v>58036</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18476,21 +18476,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>812040</v>
+        <v>812063</v>
       </c>
       <c r="R184" t="n">
-        <v>7391193</v>
+        <v>7391237</v>
       </c>
       <c r="S184" t="n">
         <v>1</v>
@@ -18562,32 +18562,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127824743</v>
+        <v>127824749</v>
       </c>
       <c r="B185" t="n">
-        <v>79044</v>
+        <v>78782</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18597,10 +18597,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>811966</v>
+        <v>812058</v>
       </c>
       <c r="R185" t="n">
-        <v>7390830</v>
+        <v>7391223</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -18659,10 +18659,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127824752</v>
+        <v>127824744</v>
       </c>
       <c r="B186" t="n">
-        <v>58033</v>
+        <v>79047</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18670,21 +18670,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>812063</v>
+        <v>811924</v>
       </c>
       <c r="R186" t="n">
-        <v>7391237</v>
+        <v>7390803</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -18756,32 +18756,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127824749</v>
+        <v>127824737</v>
       </c>
       <c r="B187" t="n">
-        <v>78779</v>
+        <v>79047</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18791,10 +18791,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>812058</v>
+        <v>811841</v>
       </c>
       <c r="R187" t="n">
-        <v>7391223</v>
+        <v>7391026</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -18853,32 +18853,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127824744</v>
+        <v>127824771</v>
       </c>
       <c r="B188" t="n">
-        <v>79044</v>
+        <v>79023</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18888,10 +18888,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>811924</v>
+        <v>811806</v>
       </c>
       <c r="R188" t="n">
-        <v>7390803</v>
+        <v>7390862</v>
       </c>
       <c r="S188" t="n">
         <v>1</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127824737</v>
+        <v>127824742</v>
       </c>
       <c r="B189" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18985,10 +18985,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811841</v>
+        <v>811875</v>
       </c>
       <c r="R189" t="n">
-        <v>7391026</v>
+        <v>7390951</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -19047,10 +19047,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127824771</v>
+        <v>127824763</v>
       </c>
       <c r="B190" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>811806</v>
+        <v>811853</v>
       </c>
       <c r="R190" t="n">
-        <v>7390862</v>
+        <v>7390925</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -19144,10 +19144,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127824742</v>
+        <v>127824750</v>
       </c>
       <c r="B191" t="n">
-        <v>79044</v>
+        <v>80162</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19155,21 +19155,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6434</v>
+        <v>6464</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811875</v>
+        <v>811976</v>
       </c>
       <c r="R191" t="n">
-        <v>7390951</v>
+        <v>7390803</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -19241,7 +19241,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824720</v>
+        <v>127824736</v>
       </c>
       <c r="B192" t="n">
         <v>57663</v>
@@ -19252,16 +19252,16 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811728</v>
+        <v>811803</v>
       </c>
       <c r="R192" t="n">
-        <v>7390781</v>
+        <v>7390857</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -19338,32 +19338,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127824750</v>
+        <v>127824686</v>
       </c>
       <c r="B193" t="n">
-        <v>80159</v>
+        <v>79641</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19373,10 +19373,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>811976</v>
+        <v>811854</v>
       </c>
       <c r="R193" t="n">
-        <v>7390803</v>
+        <v>7391042</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -19435,10 +19435,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127824763</v>
+        <v>127824764</v>
       </c>
       <c r="B194" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19470,10 +19470,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>811853</v>
+        <v>811871</v>
       </c>
       <c r="R194" t="n">
-        <v>7390925</v>
+        <v>7390883</v>
       </c>
       <c r="S194" t="n">
         <v>1</v>
@@ -19532,10 +19532,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127824686</v>
+        <v>127824702</v>
       </c>
       <c r="B195" t="n">
-        <v>79638</v>
+        <v>91341</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19543,21 +19543,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>811854</v>
+        <v>811926</v>
       </c>
       <c r="R195" t="n">
-        <v>7391042</v>
+        <v>7390831</v>
       </c>
       <c r="S195" t="n">
         <v>1</v>
@@ -19629,10 +19629,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>127824702</v>
+        <v>127824774</v>
       </c>
       <c r="B196" t="n">
-        <v>91338</v>
+        <v>82864</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19640,21 +19640,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -19664,10 +19664,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>811926</v>
+        <v>811971</v>
       </c>
       <c r="R196" t="n">
-        <v>7390831</v>
+        <v>7391094</v>
       </c>
       <c r="S196" t="n">
         <v>1</v>
@@ -19726,10 +19726,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>127824736</v>
+        <v>127824773</v>
       </c>
       <c r="B197" t="n">
-        <v>57660</v>
+        <v>82864</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19737,21 +19737,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -19761,10 +19761,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>811803</v>
+        <v>811989</v>
       </c>
       <c r="R197" t="n">
-        <v>7390857</v>
+        <v>7391103</v>
       </c>
       <c r="S197" t="n">
         <v>1</v>
@@ -19823,10 +19823,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127824764</v>
+        <v>127824711</v>
       </c>
       <c r="B198" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19834,21 +19834,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -19858,10 +19858,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>811871</v>
+        <v>812170</v>
       </c>
       <c r="R198" t="n">
-        <v>7390883</v>
+        <v>7391394</v>
       </c>
       <c r="S198" t="n">
         <v>1</v>
@@ -19920,10 +19920,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127824774</v>
+        <v>127824770</v>
       </c>
       <c r="B199" t="n">
-        <v>82861</v>
+        <v>79023</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -19931,21 +19931,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -19955,10 +19955,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>811971</v>
+        <v>811800</v>
       </c>
       <c r="R199" t="n">
-        <v>7391094</v>
+        <v>7390865</v>
       </c>
       <c r="S199" t="n">
         <v>1</v>
@@ -20017,32 +20017,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127824773</v>
+        <v>127824745</v>
       </c>
       <c r="B200" t="n">
-        <v>82861</v>
+        <v>79047</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>811989</v>
+        <v>811913</v>
       </c>
       <c r="R200" t="n">
-        <v>7391103</v>
+        <v>7390816</v>
       </c>
       <c r="S200" t="n">
         <v>1</v>
@@ -20114,10 +20114,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>127824770</v>
+        <v>127824715</v>
       </c>
       <c r="B201" t="n">
-        <v>79020</v>
+        <v>57672</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -20125,34 +20125,38 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>811800</v>
+        <v>811979</v>
       </c>
       <c r="R201" t="n">
-        <v>7390865</v>
+        <v>7391101</v>
       </c>
       <c r="S201" t="n">
         <v>1</v>
@@ -20185,6 +20189,11 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Avbarkad klenare gran. Minst två år sedan spåren uppkom.</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -20211,32 +20220,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>127824745</v>
+        <v>127824786</v>
       </c>
       <c r="B202" t="n">
-        <v>79044</v>
+        <v>57672</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -20246,10 +20255,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>811913</v>
+        <v>811846</v>
       </c>
       <c r="R202" t="n">
-        <v>7390816</v>
+        <v>7390996</v>
       </c>
       <c r="S202" t="n">
         <v>1</v>
@@ -20282,6 +20291,11 @@
       <c r="AA202" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Klen avbarkad gran troligen 2 år gamla spår.</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -20308,10 +20322,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>127824711</v>
+        <v>127824706</v>
       </c>
       <c r="B203" t="n">
-        <v>57663</v>
+        <v>57672</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -20343,10 +20357,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>812170</v>
+        <v>812033</v>
       </c>
       <c r="R203" t="n">
-        <v>7391394</v>
+        <v>7391147</v>
       </c>
       <c r="S203" t="n">
         <v>1</v>
@@ -20381,6 +20395,11 @@
           <t>2025-08-25</t>
         </is>
       </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Ringhack på tal. Äldre utan kåda.</t>
+        </is>
+      </c>
       <c r="AD203" t="b">
         <v>0</v>
       </c>
@@ -20402,6 +20421,643 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>127824708</v>
+      </c>
+      <c r="B204" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Fatikvarre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>811856</v>
+      </c>
+      <c r="R204" t="n">
+        <v>7390890</v>
+      </c>
+      <c r="S204" t="n">
+        <v>1</v>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W204" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y204" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Färskt ringhack med kåda som runnit  nedför stammen. På tall.</t>
+        </is>
+      </c>
+      <c r="AD204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG204" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT204" t="inlineStr"/>
+      <c r="AW204" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX204" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>127824710</v>
+      </c>
+      <c r="B205" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr"/>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Fatikvarre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>812092</v>
+      </c>
+      <c r="R205" t="n">
+        <v>7391361</v>
+      </c>
+      <c r="S205" t="n">
+        <v>1</v>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W205" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y205" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG205" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT205" t="inlineStr"/>
+      <c r="AW205" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX205" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>127709716</v>
+      </c>
+      <c r="B206" t="n">
+        <v>91510</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Fatikvarre norra, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>811605</v>
+      </c>
+      <c r="R206" t="n">
+        <v>7391055</v>
+      </c>
+      <c r="S206" t="n">
+        <v>5</v>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W206" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y206" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>På gammal silverlåga.</t>
+        </is>
+      </c>
+      <c r="AD206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF206" t="inlineStr"/>
+      <c r="AG206" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT206" t="inlineStr"/>
+      <c r="AW206" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX206" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>127824705</v>
+      </c>
+      <c r="B207" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Fatikvarre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>811845</v>
+      </c>
+      <c r="R207" t="n">
+        <v>7390736</v>
+      </c>
+      <c r="S207" t="n">
+        <v>1</v>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W207" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y207" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG207" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT207" t="inlineStr"/>
+      <c r="AW207" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX207" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>127824720</v>
+      </c>
+      <c r="B208" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Fatikvarre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>811728</v>
+      </c>
+      <c r="R208" t="n">
+        <v>7390781</v>
+      </c>
+      <c r="S208" t="n">
+        <v>1</v>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W208" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y208" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gammal  tall.</t>
+        </is>
+      </c>
+      <c r="AD208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG208" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT208" t="inlineStr"/>
+      <c r="AW208" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX208" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>127824707</v>
+      </c>
+      <c r="B209" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr"/>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Fatikvarre, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>811901</v>
+      </c>
+      <c r="R209" t="n">
+        <v>7391007</v>
+      </c>
+      <c r="S209" t="n">
+        <v>1</v>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W209" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y209" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran.</t>
+        </is>
+      </c>
+      <c r="AD209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG209" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT209" t="inlineStr"/>
+      <c r="AW209" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX209" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY209" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127709763</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127709734</v>
+        <v>127706926</v>
       </c>
       <c r="B3" t="n">
-        <v>79047</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811573</v>
+        <v>811754</v>
       </c>
       <c r="R3" t="n">
-        <v>7391001</v>
+        <v>7390851</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,60 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127706926</v>
+        <v>127709734</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79053</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811754</v>
+        <v>811573</v>
       </c>
       <c r="R4" t="n">
-        <v>7390851</v>
+        <v>7391001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>127709784</v>
       </c>
       <c r="B5" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127709774</v>
       </c>
       <c r="B6" t="n">
-        <v>91602</v>
+        <v>91610</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127706928</v>
+        <v>127709781</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811509</v>
+        <v>811479</v>
       </c>
       <c r="R7" t="n">
-        <v>7391152</v>
+        <v>7391142</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127706921</v>
+        <v>127706928</v>
       </c>
       <c r="B8" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811722</v>
+        <v>811509</v>
       </c>
       <c r="R8" t="n">
-        <v>7390955</v>
+        <v>7391152</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1354,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127706923</v>
+        <v>127706915</v>
       </c>
       <c r="B9" t="n">
-        <v>78782</v>
+        <v>58531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811648</v>
+        <v>811694</v>
       </c>
       <c r="R9" t="n">
-        <v>7390971</v>
+        <v>7390899</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127709710</v>
+        <v>127709721</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1479,25 +1479,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811505</v>
+        <v>811493</v>
       </c>
       <c r="R10" t="n">
-        <v>7391045</v>
+        <v>7391183</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1532,11 +1524,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1554,55 +1541,55 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127709781</v>
+        <v>127706921</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811479</v>
+        <v>811722</v>
       </c>
       <c r="R11" t="n">
-        <v>7391142</v>
+        <v>7390955</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127709721</v>
+        <v>127706923</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,37 +1656,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811493</v>
+        <v>811648</v>
       </c>
       <c r="R12" t="n">
-        <v>7391183</v>
+        <v>7390971</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1743,60 +1730,68 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127706915</v>
+        <v>127709710</v>
       </c>
       <c r="B13" t="n">
-        <v>58525</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811694</v>
+        <v>811505</v>
       </c>
       <c r="R13" t="n">
-        <v>7390899</v>
+        <v>7391045</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1826,6 +1821,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1840,22 +1840,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127706925</v>
+        <v>127706914</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811866</v>
+        <v>811645</v>
       </c>
       <c r="R14" t="n">
-        <v>7390863</v>
+        <v>7390971</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1949,10 +1949,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127709694</v>
+        <v>127709699</v>
       </c>
       <c r="B15" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811441</v>
+        <v>811707</v>
       </c>
       <c r="R15" t="n">
-        <v>7391158</v>
+        <v>7390941</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127706914</v>
+        <v>127709695</v>
       </c>
       <c r="B16" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2077,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811645</v>
+        <v>811430</v>
       </c>
       <c r="R16" t="n">
-        <v>7390971</v>
+        <v>7391046</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,22 +2131,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709695</v>
+        <v>127709694</v>
       </c>
       <c r="B17" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811430</v>
+        <v>811441</v>
       </c>
       <c r="R17" t="n">
-        <v>7391046</v>
+        <v>7391158</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709699</v>
+        <v>127706925</v>
       </c>
       <c r="B18" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811707</v>
+        <v>811866</v>
       </c>
       <c r="R18" t="n">
-        <v>7390941</v>
+        <v>7390863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2340,7 +2340,7 @@
         <v>127709709</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2447,48 +2447,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709725</v>
+        <v>127709800</v>
       </c>
       <c r="B20" t="n">
-        <v>92635</v>
+        <v>92633</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811692</v>
+        <v>811725</v>
       </c>
       <c r="R20" t="n">
-        <v>7390871</v>
+        <v>7390826</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2529,7 +2526,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2551,7 +2547,7 @@
         <v>127709797</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,45 +2641,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709800</v>
+        <v>127709725</v>
       </c>
       <c r="B22" t="n">
-        <v>92625</v>
+        <v>92643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811725</v>
+        <v>811692</v>
       </c>
       <c r="R22" t="n">
-        <v>7390826</v>
+        <v>7390871</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2724,6 +2723,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709704</v>
+        <v>127709731</v>
       </c>
       <c r="B23" t="n">
-        <v>90376</v>
+        <v>79053</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1962</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811693</v>
+        <v>811484</v>
       </c>
       <c r="R23" t="n">
-        <v>7390866</v>
+        <v>7391038</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709698</v>
+        <v>127709704</v>
       </c>
       <c r="B24" t="n">
-        <v>79641</v>
+        <v>90384</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811656</v>
+        <v>811693</v>
       </c>
       <c r="R24" t="n">
-        <v>7390942</v>
+        <v>7390866</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709731</v>
+        <v>127709698</v>
       </c>
       <c r="B25" t="n">
-        <v>79047</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811484</v>
+        <v>811656</v>
       </c>
       <c r="R25" t="n">
-        <v>7391038</v>
+        <v>7390942</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709758</v>
+        <v>127709790</v>
       </c>
       <c r="B26" t="n">
-        <v>78781</v>
+        <v>92639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811621</v>
+        <v>811610</v>
       </c>
       <c r="R26" t="n">
-        <v>7390981</v>
+        <v>7391012</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709730</v>
+        <v>127709786</v>
       </c>
       <c r="B27" t="n">
-        <v>79047</v>
+        <v>92639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811452</v>
+        <v>811612</v>
       </c>
       <c r="R27" t="n">
-        <v>7391057</v>
+        <v>7390987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709736</v>
+        <v>127709779</v>
       </c>
       <c r="B28" t="n">
-        <v>79047</v>
+        <v>92639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811662</v>
+        <v>811561</v>
       </c>
       <c r="R28" t="n">
-        <v>7390926</v>
+        <v>7391108</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,48 +3324,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127706927</v>
+        <v>127709796</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811760</v>
+        <v>811672</v>
       </c>
       <c r="R29" t="n">
-        <v>7390859</v>
+        <v>7391010</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3409,60 +3409,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709786</v>
+        <v>127706927</v>
       </c>
       <c r="B30" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811612</v>
+        <v>811760</v>
       </c>
       <c r="R30" t="n">
-        <v>7390987</v>
+        <v>7390859</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3506,44 +3506,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709796</v>
+        <v>127709758</v>
       </c>
       <c r="B31" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811672</v>
+        <v>811621</v>
       </c>
       <c r="R31" t="n">
-        <v>7391010</v>
+        <v>7390981</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709790</v>
+        <v>127709730</v>
       </c>
       <c r="B32" t="n">
-        <v>92631</v>
+        <v>79053</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811610</v>
+        <v>811452</v>
       </c>
       <c r="R32" t="n">
-        <v>7391012</v>
+        <v>7391057</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709779</v>
+        <v>127709736</v>
       </c>
       <c r="B33" t="n">
-        <v>92631</v>
+        <v>79053</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811561</v>
+        <v>811662</v>
       </c>
       <c r="R33" t="n">
-        <v>7391108</v>
+        <v>7390926</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3812,7 +3812,7 @@
         <v>127709722</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>127709703</v>
       </c>
       <c r="B35" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>127709741</v>
       </c>
       <c r="B36" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709756</v>
+        <v>127709768</v>
       </c>
       <c r="B37" t="n">
-        <v>78781</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4112,21 +4112,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811538</v>
+        <v>811776</v>
       </c>
       <c r="R37" t="n">
-        <v>7391022</v>
+        <v>7390918</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709708</v>
+        <v>127709766</v>
       </c>
       <c r="B38" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,42 +4209,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811580</v>
+        <v>811730</v>
       </c>
       <c r="R38" t="n">
-        <v>7391090</v>
+        <v>7390914</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4279,11 +4271,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4301,17 +4288,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709768</v>
+        <v>127709708</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,34 +4306,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811776</v>
+        <v>811580</v>
       </c>
       <c r="R39" t="n">
-        <v>7390918</v>
+        <v>7391090</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4381,6 +4376,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -4398,39 +4398,39 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709766</v>
+        <v>127709780</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811730</v>
+        <v>811475</v>
       </c>
       <c r="R40" t="n">
-        <v>7390914</v>
+        <v>7391196</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4502,32 +4502,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709780</v>
+        <v>127709756</v>
       </c>
       <c r="B41" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811475</v>
+        <v>811538</v>
       </c>
       <c r="R41" t="n">
-        <v>7391196</v>
+        <v>7391022</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4602,7 +4602,7 @@
         <v>127709735</v>
       </c>
       <c r="B42" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>127709752</v>
       </c>
       <c r="B43" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4796,7 +4796,7 @@
         <v>127706917</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>127709712</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>127709744</v>
       </c>
       <c r="B46" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>127709782</v>
       </c>
       <c r="B47" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>127706932</v>
       </c>
       <c r="B48" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>127709750</v>
       </c>
       <c r="B49" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5393,32 +5393,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127709749</v>
+        <v>127709793</v>
       </c>
       <c r="B50" t="n">
-        <v>80998</v>
+        <v>92639</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811750</v>
+        <v>811612</v>
       </c>
       <c r="R50" t="n">
-        <v>7390835</v>
+        <v>7391041</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5490,32 +5490,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127709793</v>
+        <v>127709749</v>
       </c>
       <c r="B51" t="n">
-        <v>92631</v>
+        <v>81004</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811612</v>
+        <v>811750</v>
       </c>
       <c r="R51" t="n">
-        <v>7391041</v>
+        <v>7390835</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709753</v>
+        <v>127824748</v>
       </c>
       <c r="B52" t="n">
-        <v>78781</v>
+        <v>78788</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,37 +5598,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811385</v>
+        <v>811709</v>
       </c>
       <c r="R52" t="n">
-        <v>7391163</v>
+        <v>7391020</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127824748</v>
+        <v>127709753</v>
       </c>
       <c r="B53" t="n">
-        <v>78782</v>
+        <v>78787</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,37 +5695,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fatikvarre, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811709</v>
+        <v>811385</v>
       </c>
       <c r="R53" t="n">
-        <v>7391020</v>
+        <v>7391163</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>127706919</v>
       </c>
       <c r="B54" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5881,7 +5881,7 @@
         <v>127709792</v>
       </c>
       <c r="B55" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5975,32 +5975,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709717</v>
+        <v>127709771</v>
       </c>
       <c r="B56" t="n">
-        <v>79047</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811625</v>
+        <v>811735</v>
       </c>
       <c r="R56" t="n">
-        <v>7390984</v>
+        <v>7391006</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6072,48 +6072,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127706933</v>
+        <v>127709717</v>
       </c>
       <c r="B57" t="n">
-        <v>78429</v>
+        <v>79053</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811536</v>
+        <v>811625</v>
       </c>
       <c r="R57" t="n">
-        <v>7391018</v>
+        <v>7390984</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6157,22 +6157,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709702</v>
+        <v>127709692</v>
       </c>
       <c r="B58" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811715</v>
+        <v>811591</v>
       </c>
       <c r="R58" t="n">
-        <v>7391028</v>
+        <v>7391072</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709692</v>
+        <v>127709702</v>
       </c>
       <c r="B59" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6301,10 +6301,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811591</v>
+        <v>811715</v>
       </c>
       <c r="R59" t="n">
-        <v>7391072</v>
+        <v>7391028</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6363,10 +6363,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709771</v>
+        <v>127709713</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,34 +6374,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811735</v>
+        <v>811514</v>
       </c>
       <c r="R60" t="n">
-        <v>7391006</v>
+        <v>7391024</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6436,6 +6444,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6453,17 +6466,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709713</v>
+        <v>127709711</v>
       </c>
       <c r="B61" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6503,10 +6516,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811514</v>
+        <v>811535</v>
       </c>
       <c r="R61" t="n">
-        <v>7391024</v>
+        <v>7391056</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6543,7 +6556,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6570,10 +6583,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709711</v>
+        <v>127706933</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>78435</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6581,45 +6594,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811535</v>
+        <v>811536</v>
       </c>
       <c r="R62" t="n">
-        <v>7391056</v>
+        <v>7391018</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6649,11 +6654,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6668,12 +6668,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6683,7 +6683,7 @@
         <v>127709737</v>
       </c>
       <c r="B63" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>127706912</v>
       </c>
       <c r="B64" t="n">
-        <v>91263</v>
+        <v>91271</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>127709748</v>
       </c>
       <c r="B65" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>127709739</v>
       </c>
       <c r="B66" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127706913</v>
+        <v>127709798</v>
       </c>
       <c r="B67" t="n">
-        <v>91306</v>
+        <v>79053</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7079,37 +7079,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811507</v>
+        <v>811676</v>
       </c>
       <c r="R67" t="n">
-        <v>7391034</v>
+        <v>7390933</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7153,22 +7153,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709802</v>
+        <v>127709803</v>
       </c>
       <c r="B68" t="n">
-        <v>92625</v>
+        <v>78435</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7176,21 +7176,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811642</v>
+        <v>811716</v>
       </c>
       <c r="R68" t="n">
-        <v>7391000</v>
+        <v>7390831</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7262,32 +7262,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709798</v>
+        <v>127709724</v>
       </c>
       <c r="B69" t="n">
-        <v>79047</v>
+        <v>57669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7297,10 +7297,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811676</v>
+        <v>811533</v>
       </c>
       <c r="R69" t="n">
-        <v>7390933</v>
+        <v>7391035</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709803</v>
+        <v>127709705</v>
       </c>
       <c r="B70" t="n">
-        <v>78429</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7370,34 +7370,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811716</v>
+        <v>811705</v>
       </c>
       <c r="R70" t="n">
-        <v>7390831</v>
+        <v>7390855</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7432,6 +7440,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7449,17 +7462,17 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709700</v>
+        <v>127709802</v>
       </c>
       <c r="B71" t="n">
-        <v>79641</v>
+        <v>92633</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7467,21 +7480,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7491,10 +7504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811687</v>
+        <v>811642</v>
       </c>
       <c r="R71" t="n">
-        <v>7390967</v>
+        <v>7391000</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7553,48 +7566,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709724</v>
+        <v>127706913</v>
       </c>
       <c r="B72" t="n">
-        <v>57663</v>
+        <v>91314</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811533</v>
+        <v>811507</v>
       </c>
       <c r="R72" t="n">
-        <v>7391035</v>
+        <v>7391034</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7638,22 +7651,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709705</v>
+        <v>127709700</v>
       </c>
       <c r="B73" t="n">
-        <v>57666</v>
+        <v>79647</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7661,42 +7674,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811705</v>
+        <v>811687</v>
       </c>
       <c r="R73" t="n">
-        <v>7390855</v>
+        <v>7390967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7731,11 +7736,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7753,7 +7753,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -7763,7 +7763,7 @@
         <v>127709772</v>
       </c>
       <c r="B74" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>127709762</v>
       </c>
       <c r="B75" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709754</v>
+        <v>127709696</v>
       </c>
       <c r="B76" t="n">
-        <v>78781</v>
+        <v>79647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811518</v>
+        <v>811519</v>
       </c>
       <c r="R76" t="n">
-        <v>7391069</v>
+        <v>7391067</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709696</v>
+        <v>127709754</v>
       </c>
       <c r="B77" t="n">
-        <v>79641</v>
+        <v>78787</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811519</v>
+        <v>811518</v>
       </c>
       <c r="R77" t="n">
-        <v>7391067</v>
+        <v>7391069</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709805</v>
+        <v>127709701</v>
       </c>
       <c r="B78" t="n">
-        <v>78429</v>
+        <v>79647</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811635</v>
+        <v>811632</v>
       </c>
       <c r="R78" t="n">
-        <v>7391001</v>
+        <v>7391030</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709701</v>
+        <v>127709805</v>
       </c>
       <c r="B79" t="n">
-        <v>79641</v>
+        <v>78435</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811632</v>
+        <v>811635</v>
       </c>
       <c r="R79" t="n">
-        <v>7391030</v>
+        <v>7391001</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8342,32 +8342,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127709738</v>
+        <v>127709760</v>
       </c>
       <c r="B80" t="n">
-        <v>92824</v>
+        <v>91510</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>1503</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811577</v>
+        <v>811582</v>
       </c>
       <c r="R80" t="n">
-        <v>7391006</v>
+        <v>7391002</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8439,10 +8439,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127706918</v>
+        <v>127709738</v>
       </c>
       <c r="B81" t="n">
-        <v>91637</v>
+        <v>92832</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8450,37 +8450,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811451</v>
+        <v>811577</v>
       </c>
       <c r="R81" t="n">
-        <v>7391161</v>
+        <v>7391006</v>
       </c>
       <c r="S81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8524,60 +8524,60 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709760</v>
+        <v>127706918</v>
       </c>
       <c r="B82" t="n">
-        <v>91502</v>
+        <v>91645</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1503</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811582</v>
+        <v>811451</v>
       </c>
       <c r="R82" t="n">
-        <v>7391002</v>
+        <v>7391161</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
         <v>127706931</v>
       </c>
       <c r="B83" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8733,7 +8733,7 @@
         <v>127709755</v>
       </c>
       <c r="B84" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8827,10 +8827,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127706929</v>
+        <v>127709757</v>
       </c>
       <c r="B85" t="n">
-        <v>82864</v>
+        <v>78787</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8838,37 +8838,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811496</v>
+        <v>811625</v>
       </c>
       <c r="R85" t="n">
-        <v>7391110</v>
+        <v>7390969</v>
       </c>
       <c r="S85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8912,44 +8912,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709788</v>
+        <v>127709759</v>
       </c>
       <c r="B86" t="n">
-        <v>92631</v>
+        <v>78787</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811667</v>
+        <v>811715</v>
       </c>
       <c r="R86" t="n">
-        <v>7390931</v>
+        <v>7391028</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9021,48 +9021,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127709789</v>
+        <v>127706929</v>
       </c>
       <c r="B87" t="n">
-        <v>92631</v>
+        <v>82870</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811610</v>
+        <v>811496</v>
       </c>
       <c r="R87" t="n">
-        <v>7390981</v>
+        <v>7391110</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9106,44 +9106,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709757</v>
+        <v>127709789</v>
       </c>
       <c r="B88" t="n">
-        <v>78781</v>
+        <v>92639</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811625</v>
+        <v>811610</v>
       </c>
       <c r="R88" t="n">
-        <v>7390969</v>
+        <v>7390981</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9215,32 +9215,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127709759</v>
+        <v>127709788</v>
       </c>
       <c r="B89" t="n">
-        <v>78781</v>
+        <v>92639</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811715</v>
+        <v>811667</v>
       </c>
       <c r="R89" t="n">
-        <v>7391028</v>
+        <v>7390931</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9315,7 +9315,7 @@
         <v>127706916</v>
       </c>
       <c r="B90" t="n">
-        <v>90376</v>
+        <v>90384</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9409,32 +9409,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709742</v>
+        <v>127709728</v>
       </c>
       <c r="B91" t="n">
-        <v>78782</v>
+        <v>79053</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811466</v>
+        <v>811385</v>
       </c>
       <c r="R91" t="n">
-        <v>7391161</v>
+        <v>7391153</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9506,48 +9506,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127706922</v>
+        <v>127709777</v>
       </c>
       <c r="B92" t="n">
-        <v>78782</v>
+        <v>92639</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811556</v>
+        <v>811696</v>
       </c>
       <c r="R92" t="n">
-        <v>7391103</v>
+        <v>7390929</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,12 +9591,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9606,7 +9606,7 @@
         <v>127709775</v>
       </c>
       <c r="B93" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9700,32 +9700,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127709777</v>
+        <v>127709742</v>
       </c>
       <c r="B94" t="n">
-        <v>92631</v>
+        <v>78788</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811696</v>
+        <v>811466</v>
       </c>
       <c r="R94" t="n">
-        <v>7390929</v>
+        <v>7391161</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9797,48 +9797,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127709728</v>
+        <v>127706922</v>
       </c>
       <c r="B95" t="n">
-        <v>79047</v>
+        <v>78788</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811385</v>
+        <v>811556</v>
       </c>
       <c r="R95" t="n">
-        <v>7391153</v>
+        <v>7391103</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9882,44 +9882,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709769</v>
+        <v>127709783</v>
       </c>
       <c r="B96" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811672</v>
+        <v>811387</v>
       </c>
       <c r="R96" t="n">
-        <v>7390924</v>
+        <v>7391146</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,32 +9991,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B97" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10026,10 +10026,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R97" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10088,10 +10088,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709783</v>
+        <v>127709795</v>
       </c>
       <c r="B98" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10123,10 +10123,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811387</v>
+        <v>811676</v>
       </c>
       <c r="R98" t="n">
-        <v>7391146</v>
+        <v>7391004</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10188,7 +10188,7 @@
         <v>127709799</v>
       </c>
       <c r="B99" t="n">
-        <v>92625</v>
+        <v>92633</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10287,10 +10287,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709693</v>
+        <v>127709769</v>
       </c>
       <c r="B100" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10298,21 +10298,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811486</v>
+        <v>811672</v>
       </c>
       <c r="R100" t="n">
-        <v>7391112</v>
+        <v>7390924</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10384,48 +10384,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127706920</v>
+        <v>127709747</v>
       </c>
       <c r="B101" t="n">
-        <v>92824</v>
+        <v>57776</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2079</v>
+        <v>103031</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811552</v>
+        <v>811653</v>
       </c>
       <c r="R101" t="n">
-        <v>7391002</v>
+        <v>7390948</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,60 +10469,60 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709785</v>
+        <v>127706920</v>
       </c>
       <c r="B102" t="n">
-        <v>92631</v>
+        <v>92832</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811504</v>
+        <v>811552</v>
       </c>
       <c r="R102" t="n">
-        <v>7391047</v>
+        <v>7391002</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10566,22 +10566,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709729</v>
+        <v>127709787</v>
       </c>
       <c r="B103" t="n">
-        <v>79047</v>
+        <v>92639</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10589,21 +10589,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10613,10 +10613,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811434</v>
+        <v>811677</v>
       </c>
       <c r="R103" t="n">
-        <v>7391048</v>
+        <v>7390878</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10675,32 +10675,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127709770</v>
+        <v>127709785</v>
       </c>
       <c r="B104" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811608</v>
+        <v>811504</v>
       </c>
       <c r="R104" t="n">
-        <v>7391004</v>
+        <v>7391047</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10772,45 +10772,48 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709764</v>
+        <v>127709727</v>
       </c>
       <c r="B105" t="n">
-        <v>79023</v>
+        <v>92643</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811498</v>
+        <v>811545</v>
       </c>
       <c r="R105" t="n">
-        <v>7391103</v>
+        <v>7391008</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10851,6 +10854,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10869,32 +10873,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709787</v>
+        <v>127709770</v>
       </c>
       <c r="B106" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10904,10 +10908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811677</v>
+        <v>811608</v>
       </c>
       <c r="R106" t="n">
-        <v>7390878</v>
+        <v>7391004</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10966,48 +10970,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709727</v>
+        <v>127709764</v>
       </c>
       <c r="B107" t="n">
-        <v>92635</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4365</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811545</v>
+        <v>811498</v>
       </c>
       <c r="R107" t="n">
-        <v>7391008</v>
+        <v>7391103</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11048,7 +11049,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -11070,7 +11070,7 @@
         <v>127709733</v>
       </c>
       <c r="B108" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127706924</v>
+        <v>127709729</v>
       </c>
       <c r="B109" t="n">
-        <v>58036</v>
+        <v>79053</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11175,37 +11175,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811422</v>
+        <v>811434</v>
       </c>
       <c r="R109" t="n">
-        <v>7391139</v>
+        <v>7391048</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11249,22 +11249,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709747</v>
+        <v>127706924</v>
       </c>
       <c r="B110" t="n">
-        <v>57770</v>
+        <v>58042</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11272,16 +11272,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11292,17 +11292,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811653</v>
+        <v>811422</v>
       </c>
       <c r="R110" t="n">
-        <v>7390948</v>
+        <v>7391139</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11346,22 +11346,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709801</v>
+        <v>127709804</v>
       </c>
       <c r="B111" t="n">
-        <v>92625</v>
+        <v>78435</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811615</v>
+        <v>811452</v>
       </c>
       <c r="R111" t="n">
-        <v>7390990</v>
+        <v>7391056</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,32 +11455,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709726</v>
+        <v>127709801</v>
       </c>
       <c r="B112" t="n">
-        <v>92635</v>
+        <v>92633</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811638</v>
+        <v>811615</v>
       </c>
       <c r="R112" t="n">
-        <v>7391044</v>
+        <v>7390990</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,32 +11552,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709720</v>
+        <v>127709726</v>
       </c>
       <c r="B113" t="n">
-        <v>57663</v>
+        <v>92643</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>4365</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811515</v>
+        <v>811638</v>
       </c>
       <c r="R113" t="n">
-        <v>7391165</v>
+        <v>7391044</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709804</v>
+        <v>127709697</v>
       </c>
       <c r="B114" t="n">
-        <v>78429</v>
+        <v>79647</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811452</v>
+        <v>811625</v>
       </c>
       <c r="R114" t="n">
-        <v>7391056</v>
+        <v>7390969</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709697</v>
+        <v>127709720</v>
       </c>
       <c r="B115" t="n">
-        <v>79641</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11757,21 +11757,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811625</v>
+        <v>811515</v>
       </c>
       <c r="R115" t="n">
-        <v>7390969</v>
+        <v>7391165</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11846,7 +11846,7 @@
         <v>127709707</v>
       </c>
       <c r="B116" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11953,10 +11953,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709791</v>
+        <v>127709778</v>
       </c>
       <c r="B117" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811605</v>
+        <v>811683</v>
       </c>
       <c r="R117" t="n">
-        <v>7391024</v>
+        <v>7390938</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709732</v>
+        <v>127709776</v>
       </c>
       <c r="B118" t="n">
-        <v>79047</v>
+        <v>78696</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811523</v>
+        <v>811646</v>
       </c>
       <c r="R118" t="n">
-        <v>7391024</v>
+        <v>7390963</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709743</v>
+        <v>127709791</v>
       </c>
       <c r="B119" t="n">
-        <v>78782</v>
+        <v>92639</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811385</v>
+        <v>811605</v>
       </c>
       <c r="R119" t="n">
-        <v>7391163</v>
+        <v>7391024</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12247,7 +12247,7 @@
         <v>127709765</v>
       </c>
       <c r="B120" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12341,10 +12341,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709778</v>
+        <v>127709732</v>
       </c>
       <c r="B121" t="n">
-        <v>92631</v>
+        <v>79053</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12352,21 +12352,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811683</v>
+        <v>811523</v>
       </c>
       <c r="R121" t="n">
-        <v>7390938</v>
+        <v>7391024</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12438,10 +12438,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709776</v>
+        <v>127709723</v>
       </c>
       <c r="B122" t="n">
-        <v>78690</v>
+        <v>57669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811646</v>
+        <v>811411</v>
       </c>
       <c r="R122" t="n">
-        <v>7390963</v>
+        <v>7391165</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12535,10 +12535,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127709723</v>
+        <v>127709743</v>
       </c>
       <c r="B123" t="n">
-        <v>57663</v>
+        <v>78788</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12546,21 +12546,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811411</v>
+        <v>811385</v>
       </c>
       <c r="R123" t="n">
-        <v>7391165</v>
+        <v>7391163</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12635,7 +12635,7 @@
         <v>127824768</v>
       </c>
       <c r="B124" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12729,10 +12729,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127824695</v>
+        <v>127824716</v>
       </c>
       <c r="B125" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12740,21 +12740,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12764,10 +12764,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>811985</v>
+        <v>811960</v>
       </c>
       <c r="R125" t="n">
-        <v>7391147</v>
+        <v>7390804</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -12826,10 +12826,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127824776</v>
+        <v>127824695</v>
       </c>
       <c r="B126" t="n">
-        <v>82864</v>
+        <v>91349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12837,21 +12837,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>811943</v>
+        <v>811985</v>
       </c>
       <c r="R126" t="n">
-        <v>7390852</v>
+        <v>7391147</v>
       </c>
       <c r="S126" t="n">
         <v>1</v>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127824701</v>
+        <v>127824776</v>
       </c>
       <c r="B127" t="n">
-        <v>91341</v>
+        <v>82870</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12934,21 +12934,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12958,10 +12958,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811868</v>
+        <v>811943</v>
       </c>
       <c r="R127" t="n">
-        <v>7390994</v>
+        <v>7390852</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13020,10 +13020,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127824716</v>
+        <v>127824701</v>
       </c>
       <c r="B128" t="n">
-        <v>57666</v>
+        <v>91349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13031,21 +13031,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13055,10 +13055,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811960</v>
+        <v>811868</v>
       </c>
       <c r="R128" t="n">
-        <v>7390804</v>
+        <v>7390994</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -13117,32 +13117,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127824751</v>
+        <v>127824758</v>
       </c>
       <c r="B129" t="n">
-        <v>57770</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>812037</v>
+        <v>811955</v>
       </c>
       <c r="R129" t="n">
-        <v>7391151</v>
+        <v>7391105</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -13214,10 +13214,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824758</v>
+        <v>127824762</v>
       </c>
       <c r="B130" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811955</v>
+        <v>811855</v>
       </c>
       <c r="R130" t="n">
-        <v>7391105</v>
+        <v>7390961</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,32 +13311,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824762</v>
+        <v>127824751</v>
       </c>
       <c r="B131" t="n">
-        <v>79023</v>
+        <v>57776</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811855</v>
+        <v>812037</v>
       </c>
       <c r="R131" t="n">
-        <v>7390961</v>
+        <v>7391151</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -13411,7 +13411,7 @@
         <v>127824735</v>
       </c>
       <c r="B132" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>127824721</v>
       </c>
       <c r="B133" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>127824719</v>
       </c>
       <c r="B134" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>127824698</v>
       </c>
       <c r="B135" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>127824699</v>
       </c>
       <c r="B136" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>127824696</v>
       </c>
       <c r="B137" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13990,10 +13990,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824782</v>
+        <v>127824739</v>
       </c>
       <c r="B138" t="n">
-        <v>92631</v>
+        <v>79053</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14001,21 +14001,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811902</v>
+        <v>811874</v>
       </c>
       <c r="R138" t="n">
-        <v>7390765</v>
+        <v>7391049</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14090,7 +14090,7 @@
         <v>127824747</v>
       </c>
       <c r="B139" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -14184,32 +14184,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824739</v>
+        <v>127824703</v>
       </c>
       <c r="B140" t="n">
-        <v>79047</v>
+        <v>91349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6434</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811874</v>
+        <v>811762</v>
       </c>
       <c r="R140" t="n">
-        <v>7391049</v>
+        <v>7390826</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824703</v>
+        <v>127824753</v>
       </c>
       <c r="B141" t="n">
-        <v>91341</v>
+        <v>81004</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811762</v>
+        <v>811752</v>
       </c>
       <c r="R141" t="n">
-        <v>7390826</v>
+        <v>7390828</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14378,10 +14378,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127824753</v>
+        <v>127824775</v>
       </c>
       <c r="B142" t="n">
-        <v>80998</v>
+        <v>82870</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14389,21 +14389,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14413,10 +14413,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811752</v>
+        <v>811886</v>
       </c>
       <c r="R142" t="n">
-        <v>7390828</v>
+        <v>7390941</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -14475,32 +14475,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127824775</v>
+        <v>127824782</v>
       </c>
       <c r="B143" t="n">
-        <v>82864</v>
+        <v>92639</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811886</v>
+        <v>811902</v>
       </c>
       <c r="R143" t="n">
-        <v>7390941</v>
+        <v>7390765</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -14572,10 +14572,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127824733</v>
+        <v>127824697</v>
       </c>
       <c r="B144" t="n">
-        <v>92657</v>
+        <v>91349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14583,21 +14583,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5448</v>
+        <v>1202</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811899</v>
+        <v>812064</v>
       </c>
       <c r="R144" t="n">
-        <v>7390756</v>
+        <v>7391153</v>
       </c>
       <c r="S144" t="n">
         <v>1</v>
@@ -14669,32 +14669,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127824766</v>
+        <v>127824784</v>
       </c>
       <c r="B145" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811921</v>
+        <v>811827</v>
       </c>
       <c r="R145" t="n">
-        <v>7390838</v>
+        <v>7390741</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824690</v>
+        <v>127824725</v>
       </c>
       <c r="B146" t="n">
-        <v>79641</v>
+        <v>57832</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811721</v>
+        <v>811800</v>
       </c>
       <c r="R146" t="n">
-        <v>7390757</v>
+        <v>7390892</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824717</v>
+        <v>127824733</v>
       </c>
       <c r="B147" t="n">
-        <v>57666</v>
+        <v>92665</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14874,21 +14874,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811898</v>
+        <v>811899</v>
       </c>
       <c r="R147" t="n">
-        <v>7390821</v>
+        <v>7390756</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -14960,10 +14960,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127824712</v>
+        <v>127824766</v>
       </c>
       <c r="B148" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -14971,21 +14971,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>812079</v>
+        <v>811921</v>
       </c>
       <c r="R148" t="n">
-        <v>7391319</v>
+        <v>7390838</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15057,10 +15057,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824725</v>
+        <v>127824690</v>
       </c>
       <c r="B149" t="n">
-        <v>57826</v>
+        <v>79647</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15068,21 +15068,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811800</v>
+        <v>811721</v>
       </c>
       <c r="R149" t="n">
-        <v>7390892</v>
+        <v>7390757</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824697</v>
+        <v>127824717</v>
       </c>
       <c r="B150" t="n">
-        <v>91341</v>
+        <v>57672</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>812064</v>
+        <v>811898</v>
       </c>
       <c r="R150" t="n">
-        <v>7391153</v>
+        <v>7390821</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -15251,32 +15251,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127824784</v>
+        <v>127824712</v>
       </c>
       <c r="B151" t="n">
-        <v>92631</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15286,10 +15286,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811827</v>
+        <v>812079</v>
       </c>
       <c r="R151" t="n">
-        <v>7390741</v>
+        <v>7391319</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -15351,7 +15351,7 @@
         <v>127824694</v>
       </c>
       <c r="B152" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -15445,32 +15445,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127824783</v>
+        <v>127824777</v>
       </c>
       <c r="B153" t="n">
-        <v>92631</v>
+        <v>82870</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15480,10 +15480,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>811895</v>
+        <v>811935</v>
       </c>
       <c r="R153" t="n">
-        <v>7390780</v>
+        <v>7390835</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -15545,7 +15545,7 @@
         <v>127824688</v>
       </c>
       <c r="B154" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15639,32 +15639,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127824777</v>
+        <v>127824783</v>
       </c>
       <c r="B155" t="n">
-        <v>82864</v>
+        <v>92639</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>811935</v>
+        <v>811895</v>
       </c>
       <c r="R155" t="n">
-        <v>7390835</v>
+        <v>7390780</v>
       </c>
       <c r="S155" t="n">
         <v>1</v>
@@ -15739,7 +15739,7 @@
         <v>127824692</v>
       </c>
       <c r="B156" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>127824741</v>
       </c>
       <c r="B157" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>127824722</v>
       </c>
       <c r="B158" t="n">
-        <v>56858</v>
+        <v>56864</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16036,10 +16036,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824691</v>
+        <v>127824769</v>
       </c>
       <c r="B159" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16047,21 +16047,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16071,10 +16071,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811718</v>
+        <v>811795</v>
       </c>
       <c r="R159" t="n">
-        <v>7390758</v>
+        <v>7390892</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16133,10 +16133,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824769</v>
+        <v>127824691</v>
       </c>
       <c r="B160" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811795</v>
+        <v>811718</v>
       </c>
       <c r="R160" t="n">
-        <v>7390892</v>
+        <v>7390758</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16230,32 +16230,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824709</v>
+        <v>127824734</v>
       </c>
       <c r="B161" t="n">
-        <v>57666</v>
+        <v>80161</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16265,10 +16265,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>812041</v>
+        <v>812156</v>
       </c>
       <c r="R161" t="n">
-        <v>7391278</v>
+        <v>7391361</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16327,32 +16327,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824734</v>
+        <v>127824709</v>
       </c>
       <c r="B162" t="n">
-        <v>80155</v>
+        <v>57672</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16362,10 +16362,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>812156</v>
+        <v>812041</v>
       </c>
       <c r="R162" t="n">
-        <v>7391361</v>
+        <v>7391278</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16427,7 +16427,7 @@
         <v>127824755</v>
       </c>
       <c r="B163" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16524,7 +16524,7 @@
         <v>127824724</v>
       </c>
       <c r="B164" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16622,10 +16622,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127824761</v>
+        <v>127824700</v>
       </c>
       <c r="B165" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -16633,21 +16633,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811845</v>
+        <v>811899</v>
       </c>
       <c r="R165" t="n">
-        <v>7390977</v>
+        <v>7390998</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -16719,10 +16719,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127824760</v>
+        <v>127824761</v>
       </c>
       <c r="B166" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -16754,10 +16754,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811882</v>
+        <v>811845</v>
       </c>
       <c r="R166" t="n">
-        <v>7390983</v>
+        <v>7390977</v>
       </c>
       <c r="S166" t="n">
         <v>1</v>
@@ -16816,10 +16816,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127824700</v>
+        <v>127824760</v>
       </c>
       <c r="B167" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -16827,21 +16827,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16851,10 +16851,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>811899</v>
+        <v>811882</v>
       </c>
       <c r="R167" t="n">
-        <v>7390998</v>
+        <v>7390983</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -16916,7 +16916,7 @@
         <v>127824718</v>
       </c>
       <c r="B168" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>127824693</v>
       </c>
       <c r="B169" t="n">
-        <v>79612</v>
+        <v>79618</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17107,32 +17107,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127824738</v>
+        <v>127824780</v>
       </c>
       <c r="B170" t="n">
-        <v>79047</v>
+        <v>91610</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6434</v>
+        <v>65</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811854</v>
+        <v>812039</v>
       </c>
       <c r="R170" t="n">
-        <v>7391042</v>
+        <v>7391269</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -17204,32 +17204,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824746</v>
+        <v>127824687</v>
       </c>
       <c r="B171" t="n">
-        <v>79047</v>
+        <v>79647</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811759</v>
+        <v>811873</v>
       </c>
       <c r="R171" t="n">
-        <v>7390733</v>
+        <v>7391047</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,32 +17301,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824687</v>
+        <v>127824738</v>
       </c>
       <c r="B172" t="n">
-        <v>79641</v>
+        <v>79053</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811873</v>
+        <v>811854</v>
       </c>
       <c r="R172" t="n">
-        <v>7391047</v>
+        <v>7391042</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,32 +17398,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824780</v>
+        <v>127824746</v>
       </c>
       <c r="B173" t="n">
-        <v>91602</v>
+        <v>79053</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>65</v>
+        <v>6434</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>812039</v>
+        <v>811759</v>
       </c>
       <c r="R173" t="n">
-        <v>7391269</v>
+        <v>7390733</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -17495,32 +17495,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824689</v>
+        <v>127824781</v>
       </c>
       <c r="B174" t="n">
-        <v>79641</v>
+        <v>92639</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811755</v>
+        <v>811927</v>
       </c>
       <c r="R174" t="n">
-        <v>7390737</v>
+        <v>7390809</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -17595,7 +17595,7 @@
         <v>127824767</v>
       </c>
       <c r="B175" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17689,32 +17689,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127824781</v>
+        <v>127824689</v>
       </c>
       <c r="B176" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -17724,10 +17724,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811927</v>
+        <v>811755</v>
       </c>
       <c r="R176" t="n">
-        <v>7390809</v>
+        <v>7390737</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -17786,10 +17786,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B177" t="n">
-        <v>79023</v>
+        <v>82870</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17797,21 +17797,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17821,10 +17821,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R177" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>
@@ -17883,10 +17883,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>127824759</v>
+        <v>127824772</v>
       </c>
       <c r="B178" t="n">
-        <v>79023</v>
+        <v>82870</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -17894,21 +17894,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -17918,10 +17918,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>811950</v>
+        <v>812010</v>
       </c>
       <c r="R178" t="n">
-        <v>7391109</v>
+        <v>7391123</v>
       </c>
       <c r="S178" t="n">
         <v>1</v>
@@ -17980,10 +17980,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127824778</v>
+        <v>127824714</v>
       </c>
       <c r="B179" t="n">
-        <v>82864</v>
+        <v>57672</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -17991,21 +17991,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>811927</v>
+        <v>811990</v>
       </c>
       <c r="R179" t="n">
-        <v>7390802</v>
+        <v>7391109</v>
       </c>
       <c r="S179" t="n">
         <v>1</v>
@@ -18077,10 +18077,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127824772</v>
+        <v>127824765</v>
       </c>
       <c r="B180" t="n">
-        <v>82864</v>
+        <v>79029</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18088,21 +18088,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18112,10 +18112,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>812010</v>
+        <v>811918</v>
       </c>
       <c r="R180" t="n">
-        <v>7391123</v>
+        <v>7390852</v>
       </c>
       <c r="S180" t="n">
         <v>1</v>
@@ -18174,10 +18174,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>127824714</v>
+        <v>127824759</v>
       </c>
       <c r="B181" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18185,21 +18185,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18209,7 +18209,7 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>811990</v>
+        <v>811950</v>
       </c>
       <c r="R181" t="n">
         <v>7391109</v>
@@ -18271,10 +18271,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127824740</v>
+        <v>127824752</v>
       </c>
       <c r="B182" t="n">
-        <v>79047</v>
+        <v>58042</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18282,21 +18282,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -18306,10 +18306,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>812040</v>
+        <v>812063</v>
       </c>
       <c r="R182" t="n">
-        <v>7391193</v>
+        <v>7391237</v>
       </c>
       <c r="S182" t="n">
         <v>1</v>
@@ -18371,7 +18371,7 @@
         <v>127824743</v>
       </c>
       <c r="B183" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -18465,10 +18465,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>127824752</v>
+        <v>127824740</v>
       </c>
       <c r="B184" t="n">
-        <v>58036</v>
+        <v>79053</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -18476,21 +18476,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -18500,10 +18500,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>812063</v>
+        <v>812040</v>
       </c>
       <c r="R184" t="n">
-        <v>7391237</v>
+        <v>7391193</v>
       </c>
       <c r="S184" t="n">
         <v>1</v>
@@ -18565,7 +18565,7 @@
         <v>127824749</v>
       </c>
       <c r="B185" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18659,32 +18659,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127824744</v>
+        <v>127824771</v>
       </c>
       <c r="B186" t="n">
-        <v>79047</v>
+        <v>79029</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811924</v>
+        <v>811806</v>
       </c>
       <c r="R186" t="n">
-        <v>7390803</v>
+        <v>7390862</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -18759,7 +18759,7 @@
         <v>127824737</v>
       </c>
       <c r="B187" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18853,32 +18853,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127824771</v>
+        <v>127824742</v>
       </c>
       <c r="B188" t="n">
-        <v>79023</v>
+        <v>79053</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18888,10 +18888,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>811806</v>
+        <v>811875</v>
       </c>
       <c r="R188" t="n">
-        <v>7390862</v>
+        <v>7390951</v>
       </c>
       <c r="S188" t="n">
         <v>1</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127824742</v>
+        <v>127824744</v>
       </c>
       <c r="B189" t="n">
-        <v>79047</v>
+        <v>79053</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18985,10 +18985,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811875</v>
+        <v>811924</v>
       </c>
       <c r="R189" t="n">
-        <v>7390951</v>
+        <v>7390803</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -19050,7 +19050,7 @@
         <v>127824763</v>
       </c>
       <c r="B190" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>127824750</v>
       </c>
       <c r="B191" t="n">
-        <v>80162</v>
+        <v>80168</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19241,10 +19241,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824736</v>
+        <v>127824764</v>
       </c>
       <c r="B192" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19252,21 +19252,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811803</v>
+        <v>811871</v>
       </c>
       <c r="R192" t="n">
-        <v>7390857</v>
+        <v>7390883</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -19341,7 +19341,7 @@
         <v>127824686</v>
       </c>
       <c r="B193" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -19435,10 +19435,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>127824764</v>
+        <v>127824702</v>
       </c>
       <c r="B194" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -19446,21 +19446,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -19470,10 +19470,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>811871</v>
+        <v>811926</v>
       </c>
       <c r="R194" t="n">
-        <v>7390883</v>
+        <v>7390831</v>
       </c>
       <c r="S194" t="n">
         <v>1</v>
@@ -19532,10 +19532,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>127824702</v>
+        <v>127824736</v>
       </c>
       <c r="B195" t="n">
-        <v>91341</v>
+        <v>57669</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -19543,21 +19543,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -19567,10 +19567,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>811926</v>
+        <v>811803</v>
       </c>
       <c r="R195" t="n">
-        <v>7390831</v>
+        <v>7390857</v>
       </c>
       <c r="S195" t="n">
         <v>1</v>
@@ -19632,7 +19632,7 @@
         <v>127824774</v>
       </c>
       <c r="B196" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>127824773</v>
       </c>
       <c r="B197" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -19823,10 +19823,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>127824711</v>
+        <v>127824770</v>
       </c>
       <c r="B198" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -19834,21 +19834,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -19858,10 +19858,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>812170</v>
+        <v>811800</v>
       </c>
       <c r="R198" t="n">
-        <v>7391394</v>
+        <v>7390865</v>
       </c>
       <c r="S198" t="n">
         <v>1</v>
@@ -19920,32 +19920,32 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>127824770</v>
+        <v>127824745</v>
       </c>
       <c r="B199" t="n">
-        <v>79023</v>
+        <v>79053</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -19955,10 +19955,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>811800</v>
+        <v>811913</v>
       </c>
       <c r="R199" t="n">
-        <v>7390865</v>
+        <v>7390816</v>
       </c>
       <c r="S199" t="n">
         <v>1</v>
@@ -20017,32 +20017,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>127824745</v>
+        <v>127824711</v>
       </c>
       <c r="B200" t="n">
-        <v>79047</v>
+        <v>57672</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20052,10 +20052,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>811913</v>
+        <v>812170</v>
       </c>
       <c r="R200" t="n">
-        <v>7390816</v>
+        <v>7391394</v>
       </c>
       <c r="S200" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127706926</v>
+        <v>127709763</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -803,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811754</v>
+        <v>811692</v>
       </c>
       <c r="R3" t="n">
-        <v>7390851</v>
+        <v>7390815</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709763</v>
+        <v>127706926</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -997,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811692</v>
+        <v>811754</v>
       </c>
       <c r="R5" t="n">
-        <v>7390815</v>
+        <v>7390851</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,44 +1051,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709781</v>
+        <v>127709774</v>
       </c>
       <c r="B6" t="n">
-        <v>92640</v>
+        <v>91611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811479</v>
+        <v>811658</v>
       </c>
       <c r="R6" t="n">
-        <v>7391142</v>
+        <v>7390945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127706928</v>
+        <v>127709721</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811509</v>
+        <v>811493</v>
       </c>
       <c r="R7" t="n">
-        <v>7391152</v>
+        <v>7391183</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127709710</v>
+        <v>127706928</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,45 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811505</v>
+        <v>811509</v>
       </c>
       <c r="R8" t="n">
-        <v>7391045</v>
+        <v>7391152</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1336,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1355,60 +1342,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127709774</v>
+        <v>127706921</v>
       </c>
       <c r="B9" t="n">
-        <v>91611</v>
+        <v>78788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811658</v>
+        <v>811722</v>
       </c>
       <c r="R9" t="n">
-        <v>7390945</v>
+        <v>7390955</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127709721</v>
+        <v>127706923</v>
       </c>
       <c r="B10" t="n">
-        <v>57669</v>
+        <v>78788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1475,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811493</v>
+        <v>811648</v>
       </c>
       <c r="R10" t="n">
-        <v>7391183</v>
+        <v>7390971</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706915</v>
+        <v>127709781</v>
       </c>
       <c r="B11" t="n">
-        <v>58531</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1572,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811694</v>
+        <v>811479</v>
       </c>
       <c r="R11" t="n">
-        <v>7390899</v>
+        <v>7391142</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127706921</v>
+        <v>127709710</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,37 +1656,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811722</v>
+        <v>811505</v>
       </c>
       <c r="R12" t="n">
-        <v>7390955</v>
+        <v>7391045</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1729,6 +1724,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,44 +1743,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127706923</v>
+        <v>127706915</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>58531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811648</v>
+        <v>811694</v>
       </c>
       <c r="R13" t="n">
-        <v>7390971</v>
+        <v>7390899</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709709</v>
+        <v>127709694</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,42 +1863,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811419</v>
+        <v>811441</v>
       </c>
       <c r="R14" t="n">
-        <v>7391124</v>
+        <v>7391158</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1933,11 +1925,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -1955,17 +1942,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127706925</v>
+        <v>127709695</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,37 +1960,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811866</v>
+        <v>811430</v>
       </c>
       <c r="R15" t="n">
-        <v>7390863</v>
+        <v>7391046</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2047,19 +2034,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127709694</v>
+        <v>127706914</v>
       </c>
       <c r="B16" t="n">
         <v>79647</v>
@@ -2090,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811441</v>
+        <v>811645</v>
       </c>
       <c r="R16" t="n">
-        <v>7391158</v>
+        <v>7390971</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2144,19 +2131,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127706914</v>
+        <v>127709699</v>
       </c>
       <c r="B17" t="n">
         <v>79647</v>
@@ -2187,17 +2174,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811645</v>
+        <v>811707</v>
       </c>
       <c r="R17" t="n">
-        <v>7390971</v>
+        <v>7390941</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2241,22 +2228,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709695</v>
+        <v>127706925</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2264,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811430</v>
+        <v>811866</v>
       </c>
       <c r="R18" t="n">
-        <v>7391046</v>
+        <v>7390863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2338,22 +2325,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127709699</v>
+        <v>127709709</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2361,34 +2348,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811707</v>
+        <v>811419</v>
       </c>
       <c r="R19" t="n">
-        <v>7390941</v>
+        <v>7391124</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2423,6 +2418,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2440,39 +2440,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709800</v>
+        <v>127709731</v>
       </c>
       <c r="B20" t="n">
-        <v>92634</v>
+        <v>79053</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811725</v>
+        <v>811484</v>
       </c>
       <c r="R20" t="n">
-        <v>7390826</v>
+        <v>7391038</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709797</v>
+        <v>127709698</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811577</v>
+        <v>811656</v>
       </c>
       <c r="R21" t="n">
-        <v>7391006</v>
+        <v>7390942</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,48 +2641,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709725</v>
+        <v>127709704</v>
       </c>
       <c r="B22" t="n">
-        <v>92644</v>
+        <v>90385</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811692</v>
+        <v>811693</v>
       </c>
       <c r="R22" t="n">
-        <v>7390871</v>
+        <v>7390866</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2723,7 +2720,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2742,10 +2738,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709698</v>
+        <v>127709800</v>
       </c>
       <c r="B23" t="n">
-        <v>79647</v>
+        <v>92634</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2749,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811656</v>
+        <v>811725</v>
       </c>
       <c r="R23" t="n">
-        <v>7390942</v>
+        <v>7390826</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2839,10 +2835,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709731</v>
+        <v>127709797</v>
       </c>
       <c r="B24" t="n">
-        <v>79053</v>
+        <v>92640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2846,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2870,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811484</v>
+        <v>811577</v>
       </c>
       <c r="R24" t="n">
-        <v>7391038</v>
+        <v>7391006</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2936,45 +2932,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709704</v>
+        <v>127709725</v>
       </c>
       <c r="B25" t="n">
-        <v>90385</v>
+        <v>92644</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811693</v>
+        <v>811692</v>
       </c>
       <c r="R25" t="n">
-        <v>7390866</v>
+        <v>7390871</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3015,6 +3014,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709741</v>
+        <v>127709722</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>57669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811489</v>
+        <v>811476</v>
       </c>
       <c r="R26" t="n">
-        <v>7391186</v>
+        <v>7391149</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709722</v>
+        <v>127709790</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>92640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811476</v>
+        <v>811610</v>
       </c>
       <c r="R27" t="n">
-        <v>7391149</v>
+        <v>7391012</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,7 +3227,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709790</v>
+        <v>127709786</v>
       </c>
       <c r="B28" t="n">
         <v>92640</v>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811610</v>
+        <v>811612</v>
       </c>
       <c r="R28" t="n">
-        <v>7391012</v>
+        <v>7390987</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709786</v>
+        <v>127709779</v>
       </c>
       <c r="B29" t="n">
         <v>92640</v>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811612</v>
+        <v>811561</v>
       </c>
       <c r="R29" t="n">
-        <v>7390987</v>
+        <v>7391108</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,7 +3421,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709779</v>
+        <v>127709796</v>
       </c>
       <c r="B30" t="n">
         <v>92640</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811561</v>
+        <v>811672</v>
       </c>
       <c r="R30" t="n">
-        <v>7391108</v>
+        <v>7391010</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3518,48 +3518,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709796</v>
+        <v>127706927</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811672</v>
+        <v>811760</v>
       </c>
       <c r="R31" t="n">
-        <v>7391010</v>
+        <v>7390859</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3603,22 +3603,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709758</v>
+        <v>127709741</v>
       </c>
       <c r="B32" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811621</v>
+        <v>811489</v>
       </c>
       <c r="R32" t="n">
-        <v>7390981</v>
+        <v>7391186</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3712,32 +3712,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709730</v>
+        <v>127709758</v>
       </c>
       <c r="B33" t="n">
-        <v>79053</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811452</v>
+        <v>811621</v>
       </c>
       <c r="R33" t="n">
-        <v>7391057</v>
+        <v>7390981</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709736</v>
+        <v>127709730</v>
       </c>
       <c r="B34" t="n">
         <v>79053</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811662</v>
+        <v>811452</v>
       </c>
       <c r="R34" t="n">
-        <v>7390926</v>
+        <v>7391057</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3906,48 +3906,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127706927</v>
+        <v>127709736</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811760</v>
+        <v>811662</v>
       </c>
       <c r="R35" t="n">
-        <v>7390859</v>
+        <v>7390926</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3991,12 +3991,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709780</v>
+        <v>127709768</v>
       </c>
       <c r="B37" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811475</v>
+        <v>811776</v>
       </c>
       <c r="R37" t="n">
-        <v>7391196</v>
+        <v>7390918</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709756</v>
+        <v>127709766</v>
       </c>
       <c r="B38" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,21 +4209,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811538</v>
+        <v>811730</v>
       </c>
       <c r="R38" t="n">
-        <v>7391022</v>
+        <v>7390914</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709768</v>
+        <v>127709756</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811776</v>
+        <v>811538</v>
       </c>
       <c r="R39" t="n">
-        <v>7390918</v>
+        <v>7391022</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4392,32 +4392,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709766</v>
+        <v>127709780</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811730</v>
+        <v>811475</v>
       </c>
       <c r="R40" t="n">
-        <v>7390914</v>
+        <v>7391196</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4793,10 +4793,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127706917</v>
+        <v>127709744</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4804,37 +4804,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811865</v>
+        <v>811539</v>
       </c>
       <c r="R44" t="n">
-        <v>7390848</v>
+        <v>7391022</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4864,11 +4864,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4883,19 +4878,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127709712</v>
+        <v>127706917</v>
       </c>
       <c r="B45" t="n">
         <v>57672</v>
@@ -4923,28 +4918,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811420</v>
+        <v>811865</v>
       </c>
       <c r="R45" t="n">
-        <v>7391078</v>
+        <v>7390848</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4978,7 +4965,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4993,22 +4980,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127709744</v>
+        <v>127709712</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5016,34 +5003,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811539</v>
+        <v>811420</v>
       </c>
       <c r="R46" t="n">
-        <v>7391022</v>
+        <v>7391078</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5078,6 +5073,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5095,39 +5095,39 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127709782</v>
+        <v>127709750</v>
       </c>
       <c r="B47" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811426</v>
+        <v>811591</v>
       </c>
       <c r="R47" t="n">
-        <v>7391161</v>
+        <v>7391072</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5199,7 +5199,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127706932</v>
+        <v>127709782</v>
       </c>
       <c r="B48" t="n">
         <v>92640</v>
@@ -5230,17 +5230,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811449</v>
+        <v>811426</v>
       </c>
       <c r="R48" t="n">
-        <v>7391067</v>
+        <v>7391161</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5284,60 +5284,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127709750</v>
+        <v>127706932</v>
       </c>
       <c r="B49" t="n">
-        <v>78787</v>
+        <v>92640</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811591</v>
+        <v>811449</v>
       </c>
       <c r="R49" t="n">
-        <v>7391072</v>
+        <v>7391067</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5381,22 +5381,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127824748</v>
+        <v>127709753</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,37 +5404,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fatikvarre, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811709</v>
+        <v>811385</v>
       </c>
       <c r="R50" t="n">
-        <v>7391020</v>
+        <v>7391163</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5684,10 +5684,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127709753</v>
+        <v>127824748</v>
       </c>
       <c r="B53" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5695,37 +5695,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811385</v>
+        <v>811709</v>
       </c>
       <c r="R53" t="n">
-        <v>7391163</v>
+        <v>7391020</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5878,45 +5878,53 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709717</v>
+        <v>127709713</v>
       </c>
       <c r="B55" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811625</v>
+        <v>811514</v>
       </c>
       <c r="R55" t="n">
-        <v>7390984</v>
+        <v>7391024</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5951,6 +5959,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5968,17 +5981,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127706933</v>
+        <v>127709711</v>
       </c>
       <c r="B56" t="n">
-        <v>78435</v>
+        <v>57672</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,37 +5999,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811536</v>
+        <v>811535</v>
       </c>
       <c r="R56" t="n">
-        <v>7391018</v>
+        <v>7391056</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6046,6 +6067,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6060,22 +6086,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709702</v>
+        <v>127706919</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>92833</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6083,37 +6109,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811715</v>
+        <v>811446</v>
       </c>
       <c r="R57" t="n">
-        <v>7391028</v>
+        <v>7391045</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6157,44 +6183,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709692</v>
+        <v>127709717</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6230,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811591</v>
+        <v>811625</v>
       </c>
       <c r="R58" t="n">
-        <v>7391072</v>
+        <v>7390984</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6266,10 +6292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709771</v>
+        <v>127706933</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>78435</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,37 +6303,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811735</v>
+        <v>811536</v>
       </c>
       <c r="R59" t="n">
-        <v>7391006</v>
+        <v>7391018</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6351,22 +6377,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127706919</v>
+        <v>127709702</v>
       </c>
       <c r="B60" t="n">
-        <v>92833</v>
+        <v>79647</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,37 +6400,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811446</v>
+        <v>811715</v>
       </c>
       <c r="R60" t="n">
-        <v>7391045</v>
+        <v>7391028</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6448,22 +6474,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709713</v>
+        <v>127709692</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6471,42 +6497,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811514</v>
+        <v>811591</v>
       </c>
       <c r="R61" t="n">
-        <v>7391024</v>
+        <v>7391072</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6541,11 +6559,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6563,17 +6576,17 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709711</v>
+        <v>127709771</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6581,42 +6594,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811535</v>
+        <v>811735</v>
       </c>
       <c r="R62" t="n">
-        <v>7391056</v>
+        <v>7391006</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6651,11 +6656,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6777,48 +6777,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127709748</v>
+        <v>127706912</v>
       </c>
       <c r="B64" t="n">
-        <v>58042</v>
+        <v>91272</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>3242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811439</v>
+        <v>811615</v>
       </c>
       <c r="R64" t="n">
-        <v>7391070</v>
+        <v>7391007</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6862,60 +6862,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127706912</v>
+        <v>127709748</v>
       </c>
       <c r="B65" t="n">
-        <v>91272</v>
+        <v>58042</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3242</v>
+        <v>103015</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811615</v>
+        <v>811439</v>
       </c>
       <c r="R65" t="n">
-        <v>7391007</v>
+        <v>7391070</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6959,12 +6959,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7068,10 +7068,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127709802</v>
+        <v>127709724</v>
       </c>
       <c r="B67" t="n">
-        <v>92634</v>
+        <v>57669</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7079,21 +7079,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811642</v>
+        <v>811533</v>
       </c>
       <c r="R67" t="n">
-        <v>7391000</v>
+        <v>7391035</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7456,48 +7456,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127706913</v>
+        <v>127709802</v>
       </c>
       <c r="B71" t="n">
-        <v>91315</v>
+        <v>92634</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811507</v>
+        <v>811642</v>
       </c>
       <c r="R71" t="n">
-        <v>7391034</v>
+        <v>7391000</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7541,60 +7541,60 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709724</v>
+        <v>127706913</v>
       </c>
       <c r="B72" t="n">
-        <v>57669</v>
+        <v>91315</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811533</v>
+        <v>811507</v>
       </c>
       <c r="R72" t="n">
-        <v>7391035</v>
+        <v>7391034</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7638,12 +7638,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7760,10 +7760,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709754</v>
+        <v>127709772</v>
       </c>
       <c r="B74" t="n">
-        <v>78787</v>
+        <v>82870</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811518</v>
+        <v>811763</v>
       </c>
       <c r="R74" t="n">
-        <v>7391069</v>
+        <v>7390963</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709696</v>
+        <v>127709754</v>
       </c>
       <c r="B75" t="n">
-        <v>79647</v>
+        <v>78787</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7868,21 +7868,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811519</v>
+        <v>811518</v>
       </c>
       <c r="R75" t="n">
-        <v>7391067</v>
+        <v>7391069</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709805</v>
+        <v>127709696</v>
       </c>
       <c r="B76" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811635</v>
+        <v>811519</v>
       </c>
       <c r="R76" t="n">
-        <v>7391001</v>
+        <v>7391067</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709701</v>
+        <v>127709805</v>
       </c>
       <c r="B77" t="n">
-        <v>79647</v>
+        <v>78435</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811632</v>
+        <v>811635</v>
       </c>
       <c r="R77" t="n">
-        <v>7391030</v>
+        <v>7391001</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709772</v>
+        <v>127709762</v>
       </c>
       <c r="B78" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811763</v>
+        <v>811718</v>
       </c>
       <c r="R78" t="n">
-        <v>7390963</v>
+        <v>7390806</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709762</v>
+        <v>127709701</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811718</v>
+        <v>811632</v>
       </c>
       <c r="R79" t="n">
-        <v>7390806</v>
+        <v>7391030</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8342,48 +8342,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706931</v>
+        <v>127709738</v>
       </c>
       <c r="B80" t="n">
-        <v>92640</v>
+        <v>92833</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811711</v>
+        <v>811577</v>
       </c>
       <c r="R80" t="n">
-        <v>7390853</v>
+        <v>7391006</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,44 +8427,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709755</v>
+        <v>127709760</v>
       </c>
       <c r="B81" t="n">
-        <v>78787</v>
+        <v>91511</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811542</v>
+        <v>811582</v>
       </c>
       <c r="R81" t="n">
-        <v>7391054</v>
+        <v>7391002</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709738</v>
+        <v>127709755</v>
       </c>
       <c r="B82" t="n">
-        <v>92833</v>
+        <v>78787</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8547,21 +8547,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811577</v>
+        <v>811542</v>
       </c>
       <c r="R82" t="n">
-        <v>7391006</v>
+        <v>7391054</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8633,32 +8633,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127706918</v>
+        <v>127706931</v>
       </c>
       <c r="B83" t="n">
-        <v>91646</v>
+        <v>92640</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811451</v>
+        <v>811711</v>
       </c>
       <c r="R83" t="n">
-        <v>7391161</v>
+        <v>7390853</v>
       </c>
       <c r="S83" t="n">
         <v>1</v>
@@ -8730,48 +8730,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709760</v>
+        <v>127706918</v>
       </c>
       <c r="B84" t="n">
-        <v>91511</v>
+        <v>91646</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1503</v>
+        <v>658</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811582</v>
+        <v>811451</v>
       </c>
       <c r="R84" t="n">
-        <v>7391002</v>
+        <v>7391161</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8815,12 +8815,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8924,10 +8924,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709759</v>
+        <v>127706929</v>
       </c>
       <c r="B86" t="n">
-        <v>78787</v>
+        <v>82870</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8935,37 +8935,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811715</v>
+        <v>811496</v>
       </c>
       <c r="R86" t="n">
-        <v>7391028</v>
+        <v>7391110</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9009,44 +9009,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127709789</v>
+        <v>127709759</v>
       </c>
       <c r="B87" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9056,10 +9056,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811610</v>
+        <v>811715</v>
       </c>
       <c r="R87" t="n">
-        <v>7390981</v>
+        <v>7391028</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9118,7 +9118,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709788</v>
+        <v>127709789</v>
       </c>
       <c r="B88" t="n">
         <v>92640</v>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811667</v>
+        <v>811610</v>
       </c>
       <c r="R88" t="n">
-        <v>7390931</v>
+        <v>7390981</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9215,48 +9215,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127706929</v>
+        <v>127709788</v>
       </c>
       <c r="B89" t="n">
-        <v>82870</v>
+        <v>92640</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811496</v>
+        <v>811667</v>
       </c>
       <c r="R89" t="n">
-        <v>7391110</v>
+        <v>7390931</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9300,12 +9300,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9409,32 +9409,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709742</v>
+        <v>127709777</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>92640</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811466</v>
+        <v>811696</v>
       </c>
       <c r="R91" t="n">
-        <v>7391161</v>
+        <v>7390929</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9506,10 +9506,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127706922</v>
+        <v>127709775</v>
       </c>
       <c r="B92" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9517,37 +9517,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811556</v>
+        <v>811544</v>
       </c>
       <c r="R92" t="n">
-        <v>7391103</v>
+        <v>7391011</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,22 +9591,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709777</v>
+        <v>127709728</v>
       </c>
       <c r="B93" t="n">
-        <v>92640</v>
+        <v>79053</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811696</v>
+        <v>811385</v>
       </c>
       <c r="R93" t="n">
-        <v>7390929</v>
+        <v>7391153</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9700,32 +9700,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127709728</v>
+        <v>127709742</v>
       </c>
       <c r="B94" t="n">
-        <v>79053</v>
+        <v>78788</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811385</v>
+        <v>811466</v>
       </c>
       <c r="R94" t="n">
-        <v>7391153</v>
+        <v>7391161</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9797,10 +9797,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127709775</v>
+        <v>127706922</v>
       </c>
       <c r="B95" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9808,37 +9808,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811544</v>
+        <v>811556</v>
       </c>
       <c r="R95" t="n">
-        <v>7391011</v>
+        <v>7391103</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9882,44 +9882,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B96" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R96" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709799</v>
+        <v>127709769</v>
       </c>
       <c r="B97" t="n">
-        <v>92634</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10002,38 +10002,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811707</v>
+        <v>811672</v>
       </c>
       <c r="R97" t="n">
-        <v>7390860</v>
+        <v>7390924</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10074,7 +10070,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10093,7 +10088,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709783</v>
+        <v>127709795</v>
       </c>
       <c r="B98" t="n">
         <v>92640</v>
@@ -10128,10 +10123,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811387</v>
+        <v>811676</v>
       </c>
       <c r="R98" t="n">
-        <v>7391146</v>
+        <v>7391004</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10190,10 +10185,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709693</v>
+        <v>127709799</v>
       </c>
       <c r="B99" t="n">
-        <v>79647</v>
+        <v>92634</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10201,34 +10196,38 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811486</v>
+        <v>811707</v>
       </c>
       <c r="R99" t="n">
-        <v>7391112</v>
+        <v>7390860</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10269,6 +10268,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10287,32 +10287,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709769</v>
+        <v>127709783</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811672</v>
+        <v>811387</v>
       </c>
       <c r="R100" t="n">
-        <v>7390924</v>
+        <v>7391146</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10384,10 +10384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709770</v>
+        <v>127706920</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>92833</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10395,37 +10395,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811608</v>
+        <v>811552</v>
       </c>
       <c r="R101" t="n">
-        <v>7391004</v>
+        <v>7391002</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,44 +10469,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709764</v>
+        <v>127709733</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811498</v>
+        <v>811530</v>
       </c>
       <c r="R102" t="n">
-        <v>7391103</v>
+        <v>7391016</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10578,48 +10578,48 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127706920</v>
+        <v>127709729</v>
       </c>
       <c r="B103" t="n">
-        <v>92833</v>
+        <v>79053</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811552</v>
+        <v>811434</v>
       </c>
       <c r="R103" t="n">
-        <v>7391002</v>
+        <v>7391048</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10663,22 +10663,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127706924</v>
+        <v>127709785</v>
       </c>
       <c r="B104" t="n">
-        <v>58042</v>
+        <v>92640</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10686,37 +10686,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811422</v>
+        <v>811504</v>
       </c>
       <c r="R104" t="n">
-        <v>7391139</v>
+        <v>7391047</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10760,57 +10760,60 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709785</v>
+        <v>127709727</v>
       </c>
       <c r="B105" t="n">
-        <v>92640</v>
+        <v>92644</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811504</v>
+        <v>811545</v>
       </c>
       <c r="R105" t="n">
-        <v>7391047</v>
+        <v>7391008</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10851,6 +10854,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10869,48 +10873,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709727</v>
+        <v>127709787</v>
       </c>
       <c r="B106" t="n">
-        <v>92644</v>
+        <v>92640</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811545</v>
+        <v>811677</v>
       </c>
       <c r="R106" t="n">
-        <v>7391008</v>
+        <v>7390878</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10951,7 +10952,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10970,10 +10970,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709787</v>
+        <v>127709747</v>
       </c>
       <c r="B107" t="n">
-        <v>92640</v>
+        <v>57776</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10981,21 +10981,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>103031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811677</v>
+        <v>811653</v>
       </c>
       <c r="R107" t="n">
-        <v>7390878</v>
+        <v>7390948</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709733</v>
+        <v>127706924</v>
       </c>
       <c r="B108" t="n">
-        <v>79053</v>
+        <v>58042</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,37 +11078,37 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811530</v>
+        <v>811422</v>
       </c>
       <c r="R108" t="n">
-        <v>7391016</v>
+        <v>7391139</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11152,44 +11152,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709729</v>
+        <v>127709770</v>
       </c>
       <c r="B109" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811434</v>
+        <v>811608</v>
       </c>
       <c r="R109" t="n">
-        <v>7391048</v>
+        <v>7391004</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11261,32 +11261,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709747</v>
+        <v>127709764</v>
       </c>
       <c r="B110" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811653</v>
+        <v>811498</v>
       </c>
       <c r="R110" t="n">
-        <v>7390948</v>
+        <v>7391103</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709707</v>
+        <v>127709804</v>
       </c>
       <c r="B112" t="n">
-        <v>57672</v>
+        <v>78435</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,42 +11466,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811874</v>
+        <v>811452</v>
       </c>
       <c r="R112" t="n">
-        <v>7390830</v>
+        <v>7391056</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11536,11 +11528,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -11558,17 +11545,17 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709801</v>
+        <v>127709697</v>
       </c>
       <c r="B113" t="n">
-        <v>92634</v>
+        <v>79647</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11576,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11600,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811615</v>
+        <v>811625</v>
       </c>
       <c r="R113" t="n">
-        <v>7390990</v>
+        <v>7390969</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11662,32 +11649,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709726</v>
+        <v>127709801</v>
       </c>
       <c r="B114" t="n">
-        <v>92644</v>
+        <v>92634</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11697,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811638</v>
+        <v>811615</v>
       </c>
       <c r="R114" t="n">
-        <v>7391044</v>
+        <v>7390990</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11759,32 +11746,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709804</v>
+        <v>127709726</v>
       </c>
       <c r="B115" t="n">
-        <v>78435</v>
+        <v>92644</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6437</v>
+        <v>4365</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11794,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811452</v>
+        <v>811638</v>
       </c>
       <c r="R115" t="n">
-        <v>7391056</v>
+        <v>7391044</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11856,10 +11843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127709697</v>
+        <v>127709707</v>
       </c>
       <c r="B116" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11867,34 +11854,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811625</v>
+        <v>811874</v>
       </c>
       <c r="R116" t="n">
-        <v>7390969</v>
+        <v>7390830</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11929,6 +11924,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11946,17 +11946,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709776</v>
+        <v>127709723</v>
       </c>
       <c r="B117" t="n">
-        <v>78696</v>
+        <v>57669</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11964,21 +11964,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811646</v>
+        <v>811411</v>
       </c>
       <c r="R117" t="n">
-        <v>7390963</v>
+        <v>7391165</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709778</v>
+        <v>127709776</v>
       </c>
       <c r="B118" t="n">
-        <v>92640</v>
+        <v>78696</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811683</v>
+        <v>811646</v>
       </c>
       <c r="R118" t="n">
-        <v>7390938</v>
+        <v>7390963</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,10 +12147,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709791</v>
+        <v>127709732</v>
       </c>
       <c r="B119" t="n">
-        <v>92640</v>
+        <v>79053</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12158,21 +12158,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811605</v>
+        <v>811523</v>
       </c>
       <c r="R119" t="n">
         <v>7391024</v>
@@ -12341,10 +12341,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709732</v>
+        <v>127709778</v>
       </c>
       <c r="B121" t="n">
-        <v>79053</v>
+        <v>92640</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12352,21 +12352,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811523</v>
+        <v>811683</v>
       </c>
       <c r="R121" t="n">
-        <v>7391024</v>
+        <v>7390938</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12438,32 +12438,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709723</v>
+        <v>127709791</v>
       </c>
       <c r="B122" t="n">
-        <v>57669</v>
+        <v>92640</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811411</v>
+        <v>811605</v>
       </c>
       <c r="R122" t="n">
-        <v>7391165</v>
+        <v>7391024</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12632,10 +12632,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127824776</v>
+        <v>127824695</v>
       </c>
       <c r="B124" t="n">
-        <v>82870</v>
+        <v>91350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12643,21 +12643,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>811943</v>
+        <v>811985</v>
       </c>
       <c r="R124" t="n">
-        <v>7390852</v>
+        <v>7391147</v>
       </c>
       <c r="S124" t="n">
         <v>1</v>
@@ -12729,10 +12729,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>127824768</v>
+        <v>127824776</v>
       </c>
       <c r="B125" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12740,21 +12740,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12764,10 +12764,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>811739</v>
+        <v>811943</v>
       </c>
       <c r="R125" t="n">
-        <v>7390831</v>
+        <v>7390852</v>
       </c>
       <c r="S125" t="n">
         <v>1</v>
@@ -12826,7 +12826,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>127824695</v>
+        <v>127824701</v>
       </c>
       <c r="B126" t="n">
         <v>91350</v>
@@ -12861,10 +12861,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>811985</v>
+        <v>811868</v>
       </c>
       <c r="R126" t="n">
-        <v>7391147</v>
+        <v>7390994</v>
       </c>
       <c r="S126" t="n">
         <v>1</v>
@@ -12923,10 +12923,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>127824701</v>
+        <v>127824768</v>
       </c>
       <c r="B127" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12934,21 +12934,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12958,10 +12958,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811868</v>
+        <v>811739</v>
       </c>
       <c r="R127" t="n">
-        <v>7390994</v>
+        <v>7390831</v>
       </c>
       <c r="S127" t="n">
         <v>1</v>
@@ -13020,10 +13020,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127824758</v>
+        <v>127824735</v>
       </c>
       <c r="B128" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13031,21 +13031,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13055,10 +13055,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811955</v>
+        <v>811831</v>
       </c>
       <c r="R128" t="n">
-        <v>7391105</v>
+        <v>7390950</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -13117,7 +13117,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127824762</v>
+        <v>127824758</v>
       </c>
       <c r="B129" t="n">
         <v>79029</v>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811855</v>
+        <v>811955</v>
       </c>
       <c r="R129" t="n">
-        <v>7390961</v>
+        <v>7391105</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -13214,10 +13214,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824735</v>
+        <v>127824762</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13225,21 +13225,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811831</v>
+        <v>811855</v>
       </c>
       <c r="R130" t="n">
-        <v>7390950</v>
+        <v>7390961</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13699,32 +13699,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824703</v>
+        <v>127824782</v>
       </c>
       <c r="B135" t="n">
-        <v>91350</v>
+        <v>92640</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811762</v>
+        <v>811902</v>
       </c>
       <c r="R135" t="n">
-        <v>7390826</v>
+        <v>7390765</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127824753</v>
+        <v>127824703</v>
       </c>
       <c r="B136" t="n">
-        <v>81004</v>
+        <v>91350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13807,21 +13807,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811752</v>
+        <v>811762</v>
       </c>
       <c r="R136" t="n">
-        <v>7390828</v>
+        <v>7390826</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -13893,32 +13893,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127824782</v>
+        <v>127824753</v>
       </c>
       <c r="B137" t="n">
-        <v>92640</v>
+        <v>81004</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>811902</v>
+        <v>811752</v>
       </c>
       <c r="R137" t="n">
-        <v>7390765</v>
+        <v>7390828</v>
       </c>
       <c r="S137" t="n">
         <v>1</v>
@@ -14281,32 +14281,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824784</v>
+        <v>127824697</v>
       </c>
       <c r="B141" t="n">
-        <v>92640</v>
+        <v>91350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811827</v>
+        <v>812064</v>
       </c>
       <c r="R141" t="n">
-        <v>7390741</v>
+        <v>7391153</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14378,32 +14378,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127824733</v>
+        <v>127824784</v>
       </c>
       <c r="B142" t="n">
-        <v>92666</v>
+        <v>92640</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14413,10 +14413,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811899</v>
+        <v>811827</v>
       </c>
       <c r="R142" t="n">
-        <v>7390756</v>
+        <v>7390741</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127824697</v>
+        <v>127824733</v>
       </c>
       <c r="B143" t="n">
-        <v>91350</v>
+        <v>92666</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14486,21 +14486,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1202</v>
+        <v>5448</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>812064</v>
+        <v>811899</v>
       </c>
       <c r="R143" t="n">
-        <v>7391153</v>
+        <v>7390756</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -14960,32 +14960,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127824783</v>
+        <v>127824688</v>
       </c>
       <c r="B148" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811895</v>
+        <v>812058</v>
       </c>
       <c r="R148" t="n">
-        <v>7390780</v>
+        <v>7391223</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15057,32 +15057,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824777</v>
+        <v>127824783</v>
       </c>
       <c r="B149" t="n">
-        <v>82870</v>
+        <v>92640</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811935</v>
+        <v>811895</v>
       </c>
       <c r="R149" t="n">
-        <v>7390835</v>
+        <v>7390780</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824688</v>
+        <v>127824777</v>
       </c>
       <c r="B150" t="n">
-        <v>79647</v>
+        <v>82870</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>812058</v>
+        <v>811935</v>
       </c>
       <c r="R150" t="n">
-        <v>7391223</v>
+        <v>7390835</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824761</v>
+        <v>127824718</v>
       </c>
       <c r="B159" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811845</v>
+        <v>811915</v>
       </c>
       <c r="R159" t="n">
-        <v>7390977</v>
+        <v>7390765</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16137,10 +16137,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824700</v>
+        <v>127824693</v>
       </c>
       <c r="B160" t="n">
-        <v>91350</v>
+        <v>79618</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16148,21 +16148,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811899</v>
+        <v>811874</v>
       </c>
       <c r="R160" t="n">
-        <v>7390998</v>
+        <v>7391049</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16234,10 +16234,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824760</v>
+        <v>127824700</v>
       </c>
       <c r="B161" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16245,21 +16245,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16269,10 +16269,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811882</v>
+        <v>811899</v>
       </c>
       <c r="R161" t="n">
-        <v>7390983</v>
+        <v>7390998</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16331,10 +16331,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824718</v>
+        <v>127824761</v>
       </c>
       <c r="B162" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16342,21 +16342,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811915</v>
+        <v>811845</v>
       </c>
       <c r="R162" t="n">
-        <v>7390765</v>
+        <v>7390977</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16428,10 +16428,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127824693</v>
+        <v>127824760</v>
       </c>
       <c r="B163" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16439,21 +16439,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811874</v>
+        <v>811882</v>
       </c>
       <c r="R163" t="n">
-        <v>7391049</v>
+        <v>7390983</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -16525,32 +16525,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>127824738</v>
+        <v>127824780</v>
       </c>
       <c r="B164" t="n">
-        <v>79053</v>
+        <v>91611</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6434</v>
+        <v>65</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -16560,10 +16560,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>811854</v>
+        <v>812039</v>
       </c>
       <c r="R164" t="n">
-        <v>7391042</v>
+        <v>7391269</v>
       </c>
       <c r="S164" t="n">
         <v>1</v>
@@ -16622,7 +16622,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>127824746</v>
+        <v>127824738</v>
       </c>
       <c r="B165" t="n">
         <v>79053</v>
@@ -16657,10 +16657,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811759</v>
+        <v>811854</v>
       </c>
       <c r="R165" t="n">
-        <v>7390733</v>
+        <v>7391042</v>
       </c>
       <c r="S165" t="n">
         <v>1</v>
@@ -16719,32 +16719,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>127824687</v>
+        <v>127824746</v>
       </c>
       <c r="B166" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -16754,10 +16754,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811873</v>
+        <v>811759</v>
       </c>
       <c r="R166" t="n">
-        <v>7391047</v>
+        <v>7390733</v>
       </c>
       <c r="S166" t="n">
         <v>1</v>
@@ -16816,32 +16816,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>127824780</v>
+        <v>127824687</v>
       </c>
       <c r="B167" t="n">
-        <v>91611</v>
+        <v>79647</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -16851,10 +16851,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>812039</v>
+        <v>811873</v>
       </c>
       <c r="R167" t="n">
-        <v>7391269</v>
+        <v>7391047</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B171" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17215,21 +17215,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R171" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,7 +17301,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824778</v>
+        <v>127824772</v>
       </c>
       <c r="B172" t="n">
         <v>82870</v>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811927</v>
+        <v>812010</v>
       </c>
       <c r="R172" t="n">
-        <v>7390802</v>
+        <v>7391123</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824772</v>
+        <v>127824765</v>
       </c>
       <c r="B173" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>812010</v>
+        <v>811918</v>
       </c>
       <c r="R173" t="n">
-        <v>7391123</v>
+        <v>7390852</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -18562,10 +18562,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127824764</v>
+        <v>127824702</v>
       </c>
       <c r="B185" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18573,21 +18573,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18597,10 +18597,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>811871</v>
+        <v>811926</v>
       </c>
       <c r="R185" t="n">
-        <v>7390883</v>
+        <v>7390831</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -18756,10 +18756,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127824702</v>
+        <v>127824686</v>
       </c>
       <c r="B187" t="n">
-        <v>91350</v>
+        <v>79647</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18767,21 +18767,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18791,10 +18791,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>811926</v>
+        <v>811854</v>
       </c>
       <c r="R187" t="n">
-        <v>7390831</v>
+        <v>7391042</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -18853,10 +18853,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127824686</v>
+        <v>127824764</v>
       </c>
       <c r="B188" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18864,21 +18864,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18888,10 +18888,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>811854</v>
+        <v>811871</v>
       </c>
       <c r="R188" t="n">
-        <v>7391042</v>
+        <v>7390883</v>
       </c>
       <c r="S188" t="n">
         <v>1</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127824770</v>
+        <v>127824774</v>
       </c>
       <c r="B189" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18961,21 +18961,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18985,10 +18985,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811800</v>
+        <v>811971</v>
       </c>
       <c r="R189" t="n">
-        <v>7390865</v>
+        <v>7391094</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -19047,7 +19047,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127824774</v>
+        <v>127824773</v>
       </c>
       <c r="B190" t="n">
         <v>82870</v>
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>811971</v>
+        <v>811989</v>
       </c>
       <c r="R190" t="n">
-        <v>7391094</v>
+        <v>7391103</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -19144,10 +19144,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127824773</v>
+        <v>127824770</v>
       </c>
       <c r="B191" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19155,21 +19155,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811989</v>
+        <v>811800</v>
       </c>
       <c r="R191" t="n">
-        <v>7391103</v>
+        <v>7390865</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -19241,32 +19241,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824745</v>
+        <v>127824711</v>
       </c>
       <c r="B192" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811913</v>
+        <v>812170</v>
       </c>
       <c r="R192" t="n">
-        <v>7390816</v>
+        <v>7391394</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -19338,32 +19338,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127824711</v>
+        <v>127824745</v>
       </c>
       <c r="B193" t="n">
-        <v>57672</v>
+        <v>79053</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19373,10 +19373,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>812170</v>
+        <v>811913</v>
       </c>
       <c r="R193" t="n">
-        <v>7391394</v>
+        <v>7390816</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127709763</v>
+        <v>127709784</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811692</v>
+        <v>811414</v>
       </c>
       <c r="R3" t="n">
-        <v>7390815</v>
+        <v>7391125</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709784</v>
+        <v>127709763</v>
       </c>
       <c r="B4" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811414</v>
+        <v>811692</v>
       </c>
       <c r="R4" t="n">
-        <v>7391125</v>
+        <v>7390815</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1063,45 +1063,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709774</v>
+        <v>127709710</v>
       </c>
       <c r="B6" t="n">
-        <v>91611</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811658</v>
+        <v>811505</v>
       </c>
       <c r="R6" t="n">
-        <v>7390945</v>
+        <v>7391045</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1136,6 +1144,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1153,17 +1166,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709721</v>
+        <v>127706921</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>78788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1184,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811493</v>
+        <v>811722</v>
       </c>
       <c r="R7" t="n">
-        <v>7391183</v>
+        <v>7390955</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127706928</v>
+        <v>127706923</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811509</v>
+        <v>811648</v>
       </c>
       <c r="R8" t="n">
-        <v>7391152</v>
+        <v>7390971</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1354,48 +1367,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127706921</v>
+        <v>127709781</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>92641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811722</v>
+        <v>811479</v>
       </c>
       <c r="R9" t="n">
-        <v>7390955</v>
+        <v>7391142</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,44 +1452,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127706923</v>
+        <v>127706915</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>58531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811648</v>
+        <v>811694</v>
       </c>
       <c r="R10" t="n">
-        <v>7390971</v>
+        <v>7390899</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1548,32 +1561,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127709781</v>
+        <v>127709774</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>91612</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811479</v>
+        <v>811658</v>
       </c>
       <c r="R11" t="n">
-        <v>7391142</v>
+        <v>7390945</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1645,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127709710</v>
+        <v>127706928</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,45 +1669,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811505</v>
+        <v>811509</v>
       </c>
       <c r="R12" t="n">
-        <v>7391045</v>
+        <v>7391152</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1724,11 +1729,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,60 +1743,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127706915</v>
+        <v>127709721</v>
       </c>
       <c r="B13" t="n">
-        <v>58531</v>
+        <v>57669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208249</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811694</v>
+        <v>811493</v>
       </c>
       <c r="R13" t="n">
-        <v>7390899</v>
+        <v>7391183</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1840,12 +1840,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127709695</v>
+        <v>127706914</v>
       </c>
       <c r="B15" t="n">
         <v>79647</v>
@@ -1980,17 +1980,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811430</v>
+        <v>811645</v>
       </c>
       <c r="R15" t="n">
-        <v>7391046</v>
+        <v>7390971</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,22 +2034,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127706914</v>
+        <v>127706925</v>
       </c>
       <c r="B16" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811645</v>
+        <v>811866</v>
       </c>
       <c r="R16" t="n">
-        <v>7390971</v>
+        <v>7390863</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709699</v>
+        <v>127709709</v>
       </c>
       <c r="B17" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,34 +2154,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811707</v>
+        <v>811419</v>
       </c>
       <c r="R17" t="n">
-        <v>7390941</v>
+        <v>7391124</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2216,6 +2224,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2233,17 +2246,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127706925</v>
+        <v>127709695</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2264,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811866</v>
+        <v>811430</v>
       </c>
       <c r="R18" t="n">
-        <v>7390863</v>
+        <v>7391046</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,22 +2338,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127709709</v>
+        <v>127709699</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,42 +2361,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811419</v>
+        <v>811707</v>
       </c>
       <c r="R19" t="n">
-        <v>7391124</v>
+        <v>7390941</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2418,11 +2423,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2440,39 +2440,39 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709731</v>
+        <v>127709698</v>
       </c>
       <c r="B20" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811484</v>
+        <v>811656</v>
       </c>
       <c r="R20" t="n">
-        <v>7391038</v>
+        <v>7390942</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709698</v>
+        <v>127709731</v>
       </c>
       <c r="B21" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811656</v>
+        <v>811484</v>
       </c>
       <c r="R21" t="n">
-        <v>7390942</v>
+        <v>7391038</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2644,7 +2644,7 @@
         <v>127709704</v>
       </c>
       <c r="B22" t="n">
-        <v>90385</v>
+        <v>90386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
         <v>127709800</v>
       </c>
       <c r="B23" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2838,7 +2838,7 @@
         <v>127709797</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127709725</v>
       </c>
       <c r="B25" t="n">
-        <v>92644</v>
+        <v>92645</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709722</v>
+        <v>127709758</v>
       </c>
       <c r="B26" t="n">
-        <v>57669</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811476</v>
+        <v>811621</v>
       </c>
       <c r="R26" t="n">
-        <v>7391149</v>
+        <v>7390981</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709790</v>
+        <v>127709730</v>
       </c>
       <c r="B27" t="n">
-        <v>92640</v>
+        <v>79053</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811610</v>
+        <v>811452</v>
       </c>
       <c r="R27" t="n">
-        <v>7391012</v>
+        <v>7391057</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709786</v>
+        <v>127709736</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>79053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811612</v>
+        <v>811662</v>
       </c>
       <c r="R28" t="n">
-        <v>7390987</v>
+        <v>7390926</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709779</v>
+        <v>127709790</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811561</v>
+        <v>811610</v>
       </c>
       <c r="R29" t="n">
-        <v>7391108</v>
+        <v>7391012</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709796</v>
+        <v>127709786</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811672</v>
+        <v>811612</v>
       </c>
       <c r="R30" t="n">
-        <v>7391010</v>
+        <v>7390987</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3518,48 +3518,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127706927</v>
+        <v>127709779</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811760</v>
+        <v>811561</v>
       </c>
       <c r="R31" t="n">
-        <v>7390859</v>
+        <v>7391108</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3603,44 +3603,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709741</v>
+        <v>127709796</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>92641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811489</v>
+        <v>811672</v>
       </c>
       <c r="R32" t="n">
-        <v>7391186</v>
+        <v>7391010</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3712,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709758</v>
+        <v>127709722</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>57669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3723,21 +3723,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811621</v>
+        <v>811476</v>
       </c>
       <c r="R33" t="n">
-        <v>7390981</v>
+        <v>7391149</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3809,48 +3809,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709730</v>
+        <v>127706927</v>
       </c>
       <c r="B34" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811452</v>
+        <v>811760</v>
       </c>
       <c r="R34" t="n">
-        <v>7391057</v>
+        <v>7390859</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3894,44 +3894,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127709736</v>
+        <v>127709703</v>
       </c>
       <c r="B35" t="n">
-        <v>79053</v>
+        <v>79618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811662</v>
+        <v>811724</v>
       </c>
       <c r="R35" t="n">
-        <v>7390926</v>
+        <v>7390998</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3985,6 +3985,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4003,10 +4004,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127709703</v>
+        <v>127709741</v>
       </c>
       <c r="B36" t="n">
-        <v>79618</v>
+        <v>78788</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4014,21 +4015,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4038,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811724</v>
+        <v>811489</v>
       </c>
       <c r="R36" t="n">
-        <v>7390998</v>
+        <v>7391186</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4082,7 +4083,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709768</v>
+        <v>127709780</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811776</v>
+        <v>811475</v>
       </c>
       <c r="R37" t="n">
-        <v>7390918</v>
+        <v>7391196</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709766</v>
+        <v>127709708</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,34 +4209,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811730</v>
+        <v>811580</v>
       </c>
       <c r="R38" t="n">
-        <v>7390914</v>
+        <v>7391090</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4271,6 +4279,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4288,7 +4301,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4392,32 +4405,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709780</v>
+        <v>127709768</v>
       </c>
       <c r="B40" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811475</v>
+        <v>811776</v>
       </c>
       <c r="R40" t="n">
-        <v>7391196</v>
+        <v>7390918</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4489,10 +4502,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709708</v>
+        <v>127709766</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4500,42 +4513,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811580</v>
+        <v>811730</v>
       </c>
       <c r="R41" t="n">
-        <v>7391090</v>
+        <v>7390914</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4570,11 +4575,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5202,7 +5202,7 @@
         <v>127709782</v>
       </c>
       <c r="B48" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>127706932</v>
       </c>
       <c r="B49" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127709753</v>
+        <v>127824748</v>
       </c>
       <c r="B50" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5404,37 +5404,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811385</v>
+        <v>811709</v>
       </c>
       <c r="R50" t="n">
-        <v>7391163</v>
+        <v>7391020</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5490,32 +5490,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127709793</v>
+        <v>127709749</v>
       </c>
       <c r="B51" t="n">
-        <v>92640</v>
+        <v>81004</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811612</v>
+        <v>811750</v>
       </c>
       <c r="R51" t="n">
-        <v>7391041</v>
+        <v>7390835</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5587,10 +5587,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709749</v>
+        <v>127709753</v>
       </c>
       <c r="B52" t="n">
-        <v>81004</v>
+        <v>78787</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5598,21 +5598,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811750</v>
+        <v>811385</v>
       </c>
       <c r="R52" t="n">
-        <v>7390835</v>
+        <v>7391163</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5684,48 +5684,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127824748</v>
+        <v>127709793</v>
       </c>
       <c r="B53" t="n">
-        <v>78788</v>
+        <v>92641</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fatikvarre, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811709</v>
+        <v>811612</v>
       </c>
       <c r="R53" t="n">
-        <v>7391020</v>
+        <v>7391041</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127709792</v>
+        <v>127709717</v>
       </c>
       <c r="B54" t="n">
-        <v>92640</v>
+        <v>79053</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811619</v>
+        <v>811625</v>
       </c>
       <c r="R54" t="n">
-        <v>7391036</v>
+        <v>7390984</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5878,10 +5878,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709713</v>
+        <v>127706933</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>78435</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,45 +5889,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811514</v>
+        <v>811536</v>
       </c>
       <c r="R55" t="n">
-        <v>7391024</v>
+        <v>7391018</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5957,11 +5949,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5976,22 +5963,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709711</v>
+        <v>127709702</v>
       </c>
       <c r="B56" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5999,42 +5986,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811535</v>
+        <v>811715</v>
       </c>
       <c r="R56" t="n">
-        <v>7391056</v>
+        <v>7391028</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6069,11 +6048,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6091,17 +6065,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127706919</v>
+        <v>127709692</v>
       </c>
       <c r="B57" t="n">
-        <v>92833</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6109,37 +6083,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811446</v>
+        <v>811591</v>
       </c>
       <c r="R57" t="n">
-        <v>7391045</v>
+        <v>7391072</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6183,60 +6157,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709717</v>
+        <v>127706919</v>
       </c>
       <c r="B58" t="n">
-        <v>79053</v>
+        <v>92834</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811625</v>
+        <v>811446</v>
       </c>
       <c r="R58" t="n">
-        <v>7390984</v>
+        <v>7391045</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6280,22 +6254,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127706933</v>
+        <v>127709713</v>
       </c>
       <c r="B59" t="n">
-        <v>78435</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6303,37 +6277,45 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811536</v>
+        <v>811514</v>
       </c>
       <c r="R59" t="n">
-        <v>7391018</v>
+        <v>7391024</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6363,6 +6345,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6377,22 +6364,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709702</v>
+        <v>127709711</v>
       </c>
       <c r="B60" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6400,34 +6387,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811715</v>
+        <v>811535</v>
       </c>
       <c r="R60" t="n">
-        <v>7391028</v>
+        <v>7391056</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6462,6 +6457,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6479,17 +6479,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709692</v>
+        <v>127709771</v>
       </c>
       <c r="B61" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811591</v>
+        <v>811735</v>
       </c>
       <c r="R61" t="n">
-        <v>7391072</v>
+        <v>7391006</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6583,32 +6583,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709771</v>
+        <v>127709792</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811735</v>
+        <v>811619</v>
       </c>
       <c r="R62" t="n">
-        <v>7391006</v>
+        <v>7391036</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6680,10 +6680,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127709737</v>
+        <v>127706912</v>
       </c>
       <c r="B63" t="n">
-        <v>92833</v>
+        <v>91273</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6691,37 +6691,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811493</v>
+        <v>811615</v>
       </c>
       <c r="R63" t="n">
-        <v>7391027</v>
+        <v>7391007</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6765,22 +6765,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127706912</v>
+        <v>127709737</v>
       </c>
       <c r="B64" t="n">
-        <v>91272</v>
+        <v>92834</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6788,37 +6788,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811615</v>
+        <v>811493</v>
       </c>
       <c r="R64" t="n">
-        <v>7391007</v>
+        <v>7391027</v>
       </c>
       <c r="S64" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6862,12 +6862,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127709739</v>
+        <v>127709705</v>
       </c>
       <c r="B66" t="n">
-        <v>92833</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6982,34 +6982,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2079</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811603</v>
+        <v>811705</v>
       </c>
       <c r="R66" t="n">
-        <v>7390979</v>
+        <v>7390855</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7044,6 +7052,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7061,39 +7074,39 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127709724</v>
+        <v>127709798</v>
       </c>
       <c r="B67" t="n">
-        <v>57669</v>
+        <v>79053</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7103,10 +7116,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811533</v>
+        <v>811676</v>
       </c>
       <c r="R67" t="n">
-        <v>7391035</v>
+        <v>7390933</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7165,32 +7178,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709798</v>
+        <v>127709803</v>
       </c>
       <c r="B68" t="n">
-        <v>79053</v>
+        <v>78435</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>6437</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7200,10 +7213,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811676</v>
+        <v>811716</v>
       </c>
       <c r="R68" t="n">
-        <v>7390933</v>
+        <v>7390831</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7262,10 +7275,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709803</v>
+        <v>127709700</v>
       </c>
       <c r="B69" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7273,21 +7286,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7297,10 +7310,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811716</v>
+        <v>811687</v>
       </c>
       <c r="R69" t="n">
-        <v>7390831</v>
+        <v>7390967</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7359,10 +7372,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709700</v>
+        <v>127709739</v>
       </c>
       <c r="B70" t="n">
-        <v>79647</v>
+        <v>92834</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7370,21 +7383,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7394,10 +7407,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811687</v>
+        <v>811603</v>
       </c>
       <c r="R70" t="n">
-        <v>7390967</v>
+        <v>7390979</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7456,10 +7469,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709802</v>
+        <v>127709724</v>
       </c>
       <c r="B71" t="n">
-        <v>92634</v>
+        <v>57669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7467,21 +7480,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7491,10 +7504,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811642</v>
+        <v>811533</v>
       </c>
       <c r="R71" t="n">
-        <v>7391000</v>
+        <v>7391035</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7556,7 +7569,7 @@
         <v>127706913</v>
       </c>
       <c r="B72" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7650,10 +7663,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709705</v>
+        <v>127709802</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>92635</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7661,42 +7674,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811705</v>
+        <v>811642</v>
       </c>
       <c r="R73" t="n">
-        <v>7390855</v>
+        <v>7391000</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7731,11 +7736,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7753,17 +7753,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709772</v>
+        <v>127709762</v>
       </c>
       <c r="B74" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811763</v>
+        <v>811718</v>
       </c>
       <c r="R74" t="n">
-        <v>7390963</v>
+        <v>7390806</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709762</v>
+        <v>127709701</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811718</v>
+        <v>811632</v>
       </c>
       <c r="R78" t="n">
-        <v>7390806</v>
+        <v>7391030</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709701</v>
+        <v>127709772</v>
       </c>
       <c r="B79" t="n">
-        <v>79647</v>
+        <v>82870</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811632</v>
+        <v>811763</v>
       </c>
       <c r="R79" t="n">
-        <v>7391030</v>
+        <v>7390963</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B80" t="n">
-        <v>92833</v>
+        <v>91647</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R80" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,44 +8427,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709760</v>
+        <v>127709755</v>
       </c>
       <c r="B81" t="n">
-        <v>91511</v>
+        <v>78787</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811582</v>
+        <v>811542</v>
       </c>
       <c r="R81" t="n">
-        <v>7391002</v>
+        <v>7391054</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709755</v>
+        <v>127709738</v>
       </c>
       <c r="B82" t="n">
-        <v>78787</v>
+        <v>92834</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8547,21 +8547,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811542</v>
+        <v>811577</v>
       </c>
       <c r="R82" t="n">
-        <v>7391054</v>
+        <v>7391006</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -8633,48 +8633,48 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127706931</v>
+        <v>127709760</v>
       </c>
       <c r="B83" t="n">
-        <v>92640</v>
+        <v>91512</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811711</v>
+        <v>811582</v>
       </c>
       <c r="R83" t="n">
-        <v>7390853</v>
+        <v>7391002</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8718,44 +8718,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127706918</v>
+        <v>127706931</v>
       </c>
       <c r="B84" t="n">
-        <v>91646</v>
+        <v>92641</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8765,10 +8765,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811451</v>
+        <v>811711</v>
       </c>
       <c r="R84" t="n">
-        <v>7391161</v>
+        <v>7390853</v>
       </c>
       <c r="S84" t="n">
         <v>1</v>
@@ -8924,10 +8924,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127706929</v>
+        <v>127709759</v>
       </c>
       <c r="B86" t="n">
-        <v>82870</v>
+        <v>78787</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8935,37 +8935,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811496</v>
+        <v>811715</v>
       </c>
       <c r="R86" t="n">
-        <v>7391110</v>
+        <v>7391028</v>
       </c>
       <c r="S86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9009,22 +9009,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127709759</v>
+        <v>127706929</v>
       </c>
       <c r="B87" t="n">
-        <v>78787</v>
+        <v>82870</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9032,37 +9032,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811715</v>
+        <v>811496</v>
       </c>
       <c r="R87" t="n">
-        <v>7391028</v>
+        <v>7391110</v>
       </c>
       <c r="S87" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9106,12 +9106,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9121,7 +9121,7 @@
         <v>127709789</v>
       </c>
       <c r="B88" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>127709788</v>
       </c>
       <c r="B89" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9315,7 +9315,7 @@
         <v>127706916</v>
       </c>
       <c r="B90" t="n">
-        <v>90385</v>
+        <v>90386</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9409,32 +9409,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709777</v>
+        <v>127709742</v>
       </c>
       <c r="B91" t="n">
-        <v>92640</v>
+        <v>78788</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9444,10 +9444,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811696</v>
+        <v>811466</v>
       </c>
       <c r="R91" t="n">
-        <v>7390929</v>
+        <v>7391161</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -9506,10 +9506,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127709775</v>
+        <v>127706922</v>
       </c>
       <c r="B92" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9517,37 +9517,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811544</v>
+        <v>811556</v>
       </c>
       <c r="R92" t="n">
-        <v>7391011</v>
+        <v>7391103</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,44 +9591,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709728</v>
+        <v>127709775</v>
       </c>
       <c r="B93" t="n">
-        <v>79053</v>
+        <v>78696</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811385</v>
+        <v>811544</v>
       </c>
       <c r="R93" t="n">
-        <v>7391153</v>
+        <v>7391011</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9700,32 +9700,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127709742</v>
+        <v>127709728</v>
       </c>
       <c r="B94" t="n">
-        <v>78788</v>
+        <v>79053</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811466</v>
+        <v>811385</v>
       </c>
       <c r="R94" t="n">
-        <v>7391161</v>
+        <v>7391153</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9797,48 +9797,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127706922</v>
+        <v>127709777</v>
       </c>
       <c r="B95" t="n">
-        <v>78788</v>
+        <v>92641</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811556</v>
+        <v>811696</v>
       </c>
       <c r="R95" t="n">
-        <v>7391103</v>
+        <v>7390929</v>
       </c>
       <c r="S95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9882,12 +9882,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
         <v>127709795</v>
       </c>
       <c r="B98" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>127709799</v>
       </c>
       <c r="B99" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>127709783</v>
       </c>
       <c r="B100" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10384,48 +10384,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127706920</v>
+        <v>127709733</v>
       </c>
       <c r="B101" t="n">
-        <v>92833</v>
+        <v>79053</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811552</v>
+        <v>811530</v>
       </c>
       <c r="R101" t="n">
-        <v>7391002</v>
+        <v>7391016</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,44 +10469,44 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709733</v>
+        <v>127709770</v>
       </c>
       <c r="B102" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10516,10 +10516,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811530</v>
+        <v>811608</v>
       </c>
       <c r="R102" t="n">
-        <v>7391016</v>
+        <v>7391004</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10675,48 +10675,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127709785</v>
+        <v>127706920</v>
       </c>
       <c r="B104" t="n">
-        <v>92640</v>
+        <v>92834</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811504</v>
+        <v>811552</v>
       </c>
       <c r="R104" t="n">
-        <v>7391047</v>
+        <v>7391002</v>
       </c>
       <c r="S104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10760,60 +10760,57 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709727</v>
+        <v>127709785</v>
       </c>
       <c r="B105" t="n">
-        <v>92644</v>
+        <v>92641</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811545</v>
+        <v>811504</v>
       </c>
       <c r="R105" t="n">
-        <v>7391008</v>
+        <v>7391047</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10854,7 +10851,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -10873,45 +10869,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709787</v>
+        <v>127709727</v>
       </c>
       <c r="B106" t="n">
-        <v>92640</v>
+        <v>92645</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811677</v>
+        <v>811545</v>
       </c>
       <c r="R106" t="n">
-        <v>7390878</v>
+        <v>7391008</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10952,6 +10951,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10970,10 +10970,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709747</v>
+        <v>127709787</v>
       </c>
       <c r="B107" t="n">
-        <v>57776</v>
+        <v>92641</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10981,21 +10981,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811653</v>
+        <v>811677</v>
       </c>
       <c r="R107" t="n">
-        <v>7390948</v>
+        <v>7390878</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11067,48 +11067,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127706924</v>
+        <v>127709764</v>
       </c>
       <c r="B108" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811422</v>
+        <v>811498</v>
       </c>
       <c r="R108" t="n">
-        <v>7391139</v>
+        <v>7391103</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11152,60 +11152,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709770</v>
+        <v>127706924</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811608</v>
+        <v>811422</v>
       </c>
       <c r="R109" t="n">
-        <v>7391004</v>
+        <v>7391139</v>
       </c>
       <c r="S109" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11249,44 +11249,44 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709764</v>
+        <v>127709747</v>
       </c>
       <c r="B110" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811498</v>
+        <v>811653</v>
       </c>
       <c r="R110" t="n">
-        <v>7391103</v>
+        <v>7390948</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709720</v>
+        <v>127709804</v>
       </c>
       <c r="B111" t="n">
-        <v>57669</v>
+        <v>78435</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6437</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811515</v>
+        <v>811452</v>
       </c>
       <c r="R111" t="n">
-        <v>7391165</v>
+        <v>7391056</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709804</v>
+        <v>127709801</v>
       </c>
       <c r="B112" t="n">
-        <v>78435</v>
+        <v>92635</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6437</v>
+        <v>4362</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811452</v>
+        <v>811615</v>
       </c>
       <c r="R112" t="n">
-        <v>7391056</v>
+        <v>7390990</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,32 +11552,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709697</v>
+        <v>127709726</v>
       </c>
       <c r="B113" t="n">
-        <v>79647</v>
+        <v>92645</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811625</v>
+        <v>811638</v>
       </c>
       <c r="R113" t="n">
-        <v>7390969</v>
+        <v>7391044</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709801</v>
+        <v>127709697</v>
       </c>
       <c r="B114" t="n">
-        <v>92634</v>
+        <v>79647</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811615</v>
+        <v>811625</v>
       </c>
       <c r="R114" t="n">
-        <v>7390990</v>
+        <v>7390969</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11746,32 +11746,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709726</v>
+        <v>127709720</v>
       </c>
       <c r="B115" t="n">
-        <v>92644</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811638</v>
+        <v>811515</v>
       </c>
       <c r="R115" t="n">
-        <v>7391044</v>
+        <v>7391165</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11953,10 +11953,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709723</v>
+        <v>127709776</v>
       </c>
       <c r="B117" t="n">
-        <v>57669</v>
+        <v>78696</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11964,21 +11964,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811411</v>
+        <v>811646</v>
       </c>
       <c r="R117" t="n">
-        <v>7391165</v>
+        <v>7390963</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709776</v>
+        <v>127709732</v>
       </c>
       <c r="B118" t="n">
-        <v>78696</v>
+        <v>79053</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811646</v>
+        <v>811523</v>
       </c>
       <c r="R118" t="n">
-        <v>7390963</v>
+        <v>7391024</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709732</v>
+        <v>127709765</v>
       </c>
       <c r="B119" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811523</v>
+        <v>811478</v>
       </c>
       <c r="R119" t="n">
-        <v>7391024</v>
+        <v>7391172</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,32 +12244,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709765</v>
+        <v>127709778</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811478</v>
+        <v>811683</v>
       </c>
       <c r="R120" t="n">
-        <v>7391172</v>
+        <v>7390938</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,10 +12341,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709778</v>
+        <v>127709791</v>
       </c>
       <c r="B121" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811683</v>
+        <v>811605</v>
       </c>
       <c r="R121" t="n">
-        <v>7390938</v>
+        <v>7391024</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12438,32 +12438,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709791</v>
+        <v>127709743</v>
       </c>
       <c r="B122" t="n">
-        <v>92640</v>
+        <v>78788</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811605</v>
+        <v>811385</v>
       </c>
       <c r="R122" t="n">
-        <v>7391024</v>
+        <v>7391163</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12535,10 +12535,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127709743</v>
+        <v>127709723</v>
       </c>
       <c r="B123" t="n">
-        <v>78788</v>
+        <v>57669</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12546,21 +12546,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811385</v>
+        <v>811411</v>
       </c>
       <c r="R123" t="n">
-        <v>7391163</v>
+        <v>7391165</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12635,7 +12635,7 @@
         <v>127824695</v>
       </c>
       <c r="B124" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>127824701</v>
       </c>
       <c r="B126" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13117,32 +13117,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127824758</v>
+        <v>127824751</v>
       </c>
       <c r="B129" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811955</v>
+        <v>812037</v>
       </c>
       <c r="R129" t="n">
-        <v>7391105</v>
+        <v>7391151</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -13214,7 +13214,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824762</v>
+        <v>127824758</v>
       </c>
       <c r="B130" t="n">
         <v>79029</v>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811855</v>
+        <v>811955</v>
       </c>
       <c r="R130" t="n">
-        <v>7390961</v>
+        <v>7391105</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,32 +13311,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824751</v>
+        <v>127824762</v>
       </c>
       <c r="B131" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>812037</v>
+        <v>811855</v>
       </c>
       <c r="R131" t="n">
-        <v>7391151</v>
+        <v>7390961</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -13411,7 +13411,7 @@
         <v>127824698</v>
       </c>
       <c r="B132" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>127824699</v>
       </c>
       <c r="B133" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>127824696</v>
       </c>
       <c r="B134" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13699,32 +13699,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824782</v>
+        <v>127824703</v>
       </c>
       <c r="B135" t="n">
-        <v>92640</v>
+        <v>91351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811902</v>
+        <v>811762</v>
       </c>
       <c r="R135" t="n">
-        <v>7390765</v>
+        <v>7390826</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127824703</v>
+        <v>127824753</v>
       </c>
       <c r="B136" t="n">
-        <v>91350</v>
+        <v>81004</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13807,21 +13807,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811762</v>
+        <v>811752</v>
       </c>
       <c r="R136" t="n">
-        <v>7390826</v>
+        <v>7390828</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -13893,10 +13893,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127824753</v>
+        <v>127824775</v>
       </c>
       <c r="B137" t="n">
-        <v>81004</v>
+        <v>82870</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13904,21 +13904,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1049</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>811752</v>
+        <v>811886</v>
       </c>
       <c r="R137" t="n">
-        <v>7390828</v>
+        <v>7390941</v>
       </c>
       <c r="S137" t="n">
         <v>1</v>
@@ -13990,32 +13990,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824775</v>
+        <v>127824747</v>
       </c>
       <c r="B138" t="n">
-        <v>82870</v>
+        <v>79053</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811886</v>
+        <v>811803</v>
       </c>
       <c r="R138" t="n">
-        <v>7390941</v>
+        <v>7390886</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14087,7 +14087,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127824747</v>
+        <v>127824739</v>
       </c>
       <c r="B139" t="n">
         <v>79053</v>
@@ -14122,10 +14122,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811803</v>
+        <v>811874</v>
       </c>
       <c r="R139" t="n">
-        <v>7390886</v>
+        <v>7391049</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -14184,10 +14184,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824739</v>
+        <v>127824782</v>
       </c>
       <c r="B140" t="n">
-        <v>79053</v>
+        <v>92641</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14195,21 +14195,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811874</v>
+        <v>811902</v>
       </c>
       <c r="R140" t="n">
-        <v>7391049</v>
+        <v>7390765</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14284,7 +14284,7 @@
         <v>127824697</v>
       </c>
       <c r="B141" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14378,32 +14378,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127824784</v>
+        <v>127824733</v>
       </c>
       <c r="B142" t="n">
-        <v>92640</v>
+        <v>92667</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14413,10 +14413,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811827</v>
+        <v>811899</v>
       </c>
       <c r="R142" t="n">
-        <v>7390741</v>
+        <v>7390756</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127824733</v>
+        <v>127824766</v>
       </c>
       <c r="B143" t="n">
-        <v>92666</v>
+        <v>79029</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14486,21 +14486,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811899</v>
+        <v>811921</v>
       </c>
       <c r="R143" t="n">
-        <v>7390756</v>
+        <v>7390838</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -14572,10 +14572,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127824766</v>
+        <v>127824690</v>
       </c>
       <c r="B144" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14583,21 +14583,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811921</v>
+        <v>811721</v>
       </c>
       <c r="R144" t="n">
-        <v>7390838</v>
+        <v>7390757</v>
       </c>
       <c r="S144" t="n">
         <v>1</v>
@@ -14669,10 +14669,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127824690</v>
+        <v>127824725</v>
       </c>
       <c r="B145" t="n">
-        <v>79647</v>
+        <v>57832</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811721</v>
+        <v>811800</v>
       </c>
       <c r="R145" t="n">
-        <v>7390757</v>
+        <v>7390892</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824725</v>
+        <v>127824694</v>
       </c>
       <c r="B146" t="n">
-        <v>57832</v>
+        <v>79618</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811800</v>
+        <v>811716</v>
       </c>
       <c r="R146" t="n">
-        <v>7390892</v>
+        <v>7390763</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,32 +14863,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824694</v>
+        <v>127824784</v>
       </c>
       <c r="B147" t="n">
-        <v>79618</v>
+        <v>92641</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811716</v>
+        <v>811827</v>
       </c>
       <c r="R147" t="n">
-        <v>7390763</v>
+        <v>7390741</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -14960,32 +14960,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127824688</v>
+        <v>127824783</v>
       </c>
       <c r="B148" t="n">
-        <v>79647</v>
+        <v>92641</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>812058</v>
+        <v>811895</v>
       </c>
       <c r="R148" t="n">
-        <v>7391223</v>
+        <v>7390780</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15057,32 +15057,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824783</v>
+        <v>127824777</v>
       </c>
       <c r="B149" t="n">
-        <v>92640</v>
+        <v>82870</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811895</v>
+        <v>811935</v>
       </c>
       <c r="R149" t="n">
-        <v>7390780</v>
+        <v>7390835</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824777</v>
+        <v>127824688</v>
       </c>
       <c r="B150" t="n">
-        <v>82870</v>
+        <v>79647</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811935</v>
+        <v>812058</v>
       </c>
       <c r="R150" t="n">
-        <v>7390835</v>
+        <v>7391223</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824718</v>
+        <v>127824700</v>
       </c>
       <c r="B159" t="n">
-        <v>57672</v>
+        <v>91351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811915</v>
+        <v>811899</v>
       </c>
       <c r="R159" t="n">
-        <v>7390765</v>
+        <v>7390998</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16137,10 +16137,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824693</v>
+        <v>127824718</v>
       </c>
       <c r="B160" t="n">
-        <v>79618</v>
+        <v>57672</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16148,21 +16148,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811874</v>
+        <v>811915</v>
       </c>
       <c r="R160" t="n">
-        <v>7391049</v>
+        <v>7390765</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16234,10 +16234,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824700</v>
+        <v>127824761</v>
       </c>
       <c r="B161" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16245,21 +16245,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16269,10 +16269,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811899</v>
+        <v>811845</v>
       </c>
       <c r="R161" t="n">
-        <v>7390998</v>
+        <v>7390977</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16331,7 +16331,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824761</v>
+        <v>127824760</v>
       </c>
       <c r="B162" t="n">
         <v>79029</v>
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811845</v>
+        <v>811882</v>
       </c>
       <c r="R162" t="n">
-        <v>7390977</v>
+        <v>7390983</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16428,10 +16428,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127824760</v>
+        <v>127824693</v>
       </c>
       <c r="B163" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16439,21 +16439,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811882</v>
+        <v>811874</v>
       </c>
       <c r="R163" t="n">
-        <v>7390983</v>
+        <v>7391049</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -16528,7 +16528,7 @@
         <v>127824780</v>
       </c>
       <c r="B164" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>127824781</v>
       </c>
       <c r="B168" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18562,10 +18562,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127824702</v>
+        <v>127824736</v>
       </c>
       <c r="B185" t="n">
-        <v>91350</v>
+        <v>57669</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18573,21 +18573,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18597,10 +18597,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>811926</v>
+        <v>811803</v>
       </c>
       <c r="R185" t="n">
-        <v>7390831</v>
+        <v>7390857</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -18659,10 +18659,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127824736</v>
+        <v>127824702</v>
       </c>
       <c r="B186" t="n">
-        <v>57669</v>
+        <v>91351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18670,21 +18670,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811803</v>
+        <v>811926</v>
       </c>
       <c r="R186" t="n">
-        <v>7390857</v>
+        <v>7390831</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -19144,10 +19144,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127824770</v>
+        <v>127824711</v>
       </c>
       <c r="B191" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19155,21 +19155,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811800</v>
+        <v>812170</v>
       </c>
       <c r="R191" t="n">
-        <v>7390865</v>
+        <v>7391394</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -19241,10 +19241,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824711</v>
+        <v>127824770</v>
       </c>
       <c r="B192" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19252,21 +19252,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>812170</v>
+        <v>811800</v>
       </c>
       <c r="R192" t="n">
-        <v>7391394</v>
+        <v>7390865</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -19960,7 +19960,7 @@
         <v>127709716</v>
       </c>
       <c r="B199" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>128198143</v>
       </c>
       <c r="B207" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127709734</v>
+        <v>127709784</v>
       </c>
       <c r="B2" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811573</v>
+        <v>811414</v>
       </c>
       <c r="R2" t="n">
-        <v>7391001</v>
+        <v>7391125</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127709784</v>
+        <v>127709734</v>
       </c>
       <c r="B3" t="n">
-        <v>92641</v>
+        <v>79053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811414</v>
+        <v>811573</v>
       </c>
       <c r="R3" t="n">
-        <v>7391125</v>
+        <v>7391001</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -1063,53 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709710</v>
+        <v>127709774</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>91613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811505</v>
+        <v>811658</v>
       </c>
       <c r="R6" t="n">
-        <v>7391045</v>
+        <v>7390945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1144,11 +1136,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1166,55 +1153,55 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127706921</v>
+        <v>127709781</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811722</v>
+        <v>811479</v>
       </c>
       <c r="R7" t="n">
-        <v>7390955</v>
+        <v>7391142</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127706923</v>
+        <v>127706928</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811648</v>
+        <v>811509</v>
       </c>
       <c r="R8" t="n">
-        <v>7390971</v>
+        <v>7391152</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1367,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127709781</v>
+        <v>127709721</v>
       </c>
       <c r="B9" t="n">
-        <v>92641</v>
+        <v>57669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811479</v>
+        <v>811493</v>
       </c>
       <c r="R9" t="n">
-        <v>7391142</v>
+        <v>7391183</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,48 +1451,56 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127706915</v>
+        <v>127709710</v>
       </c>
       <c r="B10" t="n">
-        <v>58531</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811694</v>
+        <v>811505</v>
       </c>
       <c r="R10" t="n">
-        <v>7390899</v>
+        <v>7391045</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1535,6 +1530,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1549,60 +1549,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127709774</v>
+        <v>127706915</v>
       </c>
       <c r="B11" t="n">
-        <v>91612</v>
+        <v>58531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>65</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811658</v>
+        <v>811694</v>
       </c>
       <c r="R11" t="n">
-        <v>7390945</v>
+        <v>7390899</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1646,22 +1646,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127706928</v>
+        <v>127706921</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811509</v>
+        <v>811722</v>
       </c>
       <c r="R12" t="n">
-        <v>7391152</v>
+        <v>7390955</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127709721</v>
+        <v>127706923</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>78788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811493</v>
+        <v>811648</v>
       </c>
       <c r="R13" t="n">
-        <v>7391183</v>
+        <v>7390971</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1840,12 +1840,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127706925</v>
+        <v>127709695</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,37 +2057,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811866</v>
+        <v>811430</v>
       </c>
       <c r="R16" t="n">
-        <v>7390863</v>
+        <v>7391046</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,22 +2131,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709709</v>
+        <v>127706925</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,45 +2154,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811419</v>
+        <v>811866</v>
       </c>
       <c r="R17" t="n">
-        <v>7391124</v>
+        <v>7390863</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2222,11 +2214,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Äldre.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2241,19 +2228,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709695</v>
+        <v>127709699</v>
       </c>
       <c r="B18" t="n">
         <v>79647</v>
@@ -2288,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811430</v>
+        <v>811707</v>
       </c>
       <c r="R18" t="n">
-        <v>7391046</v>
+        <v>7390941</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2350,10 +2337,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127709699</v>
+        <v>127709709</v>
       </c>
       <c r="B19" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2361,34 +2348,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811707</v>
+        <v>811419</v>
       </c>
       <c r="R19" t="n">
-        <v>7390941</v>
+        <v>7391124</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2423,6 +2418,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Äldre.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2440,17 +2440,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127709698</v>
+        <v>127709704</v>
       </c>
       <c r="B20" t="n">
-        <v>79647</v>
+        <v>90387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2458,21 +2458,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811656</v>
+        <v>811693</v>
       </c>
       <c r="R20" t="n">
-        <v>7390942</v>
+        <v>7390866</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709731</v>
+        <v>127709698</v>
       </c>
       <c r="B21" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811484</v>
+        <v>811656</v>
       </c>
       <c r="R21" t="n">
-        <v>7391038</v>
+        <v>7390942</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,10 +2641,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709704</v>
+        <v>127709800</v>
       </c>
       <c r="B22" t="n">
-        <v>90386</v>
+        <v>92636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2652,21 +2652,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811693</v>
+        <v>811725</v>
       </c>
       <c r="R22" t="n">
-        <v>7390866</v>
+        <v>7390826</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,32 +2738,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709800</v>
+        <v>127709797</v>
       </c>
       <c r="B23" t="n">
-        <v>92635</v>
+        <v>92642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811725</v>
+        <v>811577</v>
       </c>
       <c r="R23" t="n">
-        <v>7390826</v>
+        <v>7391006</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2835,45 +2835,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709797</v>
+        <v>127709725</v>
       </c>
       <c r="B24" t="n">
-        <v>92641</v>
+        <v>92646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811577</v>
+        <v>811692</v>
       </c>
       <c r="R24" t="n">
-        <v>7391006</v>
+        <v>7390871</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2914,6 +2917,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2932,48 +2936,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709725</v>
+        <v>127709731</v>
       </c>
       <c r="B25" t="n">
-        <v>92645</v>
+        <v>79053</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811692</v>
+        <v>811484</v>
       </c>
       <c r="R25" t="n">
-        <v>7390871</v>
+        <v>7391038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3014,7 +3015,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709758</v>
+        <v>127709790</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811621</v>
+        <v>811610</v>
       </c>
       <c r="R26" t="n">
-        <v>7390981</v>
+        <v>7391012</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709730</v>
+        <v>127709786</v>
       </c>
       <c r="B27" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811452</v>
+        <v>811612</v>
       </c>
       <c r="R27" t="n">
-        <v>7391057</v>
+        <v>7390987</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709736</v>
+        <v>127709779</v>
       </c>
       <c r="B28" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811662</v>
+        <v>811561</v>
       </c>
       <c r="R28" t="n">
-        <v>7390926</v>
+        <v>7391108</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709790</v>
+        <v>127709796</v>
       </c>
       <c r="B29" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811610</v>
+        <v>811672</v>
       </c>
       <c r="R29" t="n">
-        <v>7391012</v>
+        <v>7391010</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709786</v>
+        <v>127709741</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>78788</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811612</v>
+        <v>811489</v>
       </c>
       <c r="R30" t="n">
-        <v>7390987</v>
+        <v>7391186</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709779</v>
+        <v>127709758</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>78787</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811561</v>
+        <v>811621</v>
       </c>
       <c r="R31" t="n">
-        <v>7391108</v>
+        <v>7390981</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709796</v>
+        <v>127709730</v>
       </c>
       <c r="B32" t="n">
-        <v>92641</v>
+        <v>79053</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811672</v>
+        <v>811452</v>
       </c>
       <c r="R32" t="n">
-        <v>7391010</v>
+        <v>7391057</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3712,32 +3712,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709722</v>
+        <v>127709736</v>
       </c>
       <c r="B33" t="n">
-        <v>57669</v>
+        <v>79053</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811476</v>
+        <v>811662</v>
       </c>
       <c r="R33" t="n">
-        <v>7391149</v>
+        <v>7390926</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3906,10 +3906,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127709703</v>
+        <v>127709722</v>
       </c>
       <c r="B35" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3917,21 +3917,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3941,10 +3941,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811724</v>
+        <v>811476</v>
       </c>
       <c r="R35" t="n">
-        <v>7390998</v>
+        <v>7391149</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -3985,7 +3985,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +4003,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127709741</v>
+        <v>127709703</v>
       </c>
       <c r="B36" t="n">
-        <v>78788</v>
+        <v>79618</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,21 +4014,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4039,10 +4038,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811489</v>
+        <v>811724</v>
       </c>
       <c r="R36" t="n">
-        <v>7391186</v>
+        <v>7390998</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4083,6 +4082,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4101,45 +4101,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709780</v>
+        <v>127709708</v>
       </c>
       <c r="B37" t="n">
-        <v>92641</v>
+        <v>57672</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811475</v>
+        <v>811580</v>
       </c>
       <c r="R37" t="n">
-        <v>7391196</v>
+        <v>7391090</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4174,6 +4182,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4191,60 +4204,52 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709708</v>
+        <v>127709780</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811580</v>
+        <v>811475</v>
       </c>
       <c r="R38" t="n">
-        <v>7391090</v>
+        <v>7391196</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4279,11 +4284,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4301,17 +4301,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709756</v>
+        <v>127709768</v>
       </c>
       <c r="B39" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,21 +4319,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4343,10 +4343,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811538</v>
+        <v>811776</v>
       </c>
       <c r="R39" t="n">
-        <v>7391022</v>
+        <v>7390918</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709768</v>
+        <v>127709766</v>
       </c>
       <c r="B40" t="n">
         <v>79029</v>
@@ -4440,10 +4440,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811776</v>
+        <v>811730</v>
       </c>
       <c r="R40" t="n">
-        <v>7390918</v>
+        <v>7390914</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4502,10 +4502,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709766</v>
+        <v>127709756</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4513,21 +4513,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811730</v>
+        <v>811538</v>
       </c>
       <c r="R41" t="n">
-        <v>7390914</v>
+        <v>7391022</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4599,48 +4599,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127709735</v>
+        <v>127706917</v>
       </c>
       <c r="B42" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811626</v>
+        <v>811865</v>
       </c>
       <c r="R42" t="n">
-        <v>7390972</v>
+        <v>7390848</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4670,6 +4670,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4684,22 +4689,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127709752</v>
+        <v>127709712</v>
       </c>
       <c r="B43" t="n">
-        <v>78787</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,34 +4712,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811490</v>
+        <v>811420</v>
       </c>
       <c r="R43" t="n">
-        <v>7391186</v>
+        <v>7391078</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -4769,6 +4782,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4786,7 +4804,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4890,48 +4908,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127706917</v>
+        <v>127709735</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>79053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811865</v>
+        <v>811626</v>
       </c>
       <c r="R45" t="n">
-        <v>7390848</v>
+        <v>7390972</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4961,11 +4979,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4980,22 +4993,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127709712</v>
+        <v>127709752</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5003,42 +5016,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811420</v>
+        <v>811490</v>
       </c>
       <c r="R46" t="n">
-        <v>7391078</v>
+        <v>7391186</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5073,11 +5078,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5095,39 +5095,39 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127709750</v>
+        <v>127709782</v>
       </c>
       <c r="B47" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>811591</v>
+        <v>811426</v>
       </c>
       <c r="R47" t="n">
-        <v>7391072</v>
+        <v>7391161</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127709782</v>
+        <v>127706932</v>
       </c>
       <c r="B48" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5230,17 +5230,17 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811426</v>
+        <v>811449</v>
       </c>
       <c r="R48" t="n">
-        <v>7391161</v>
+        <v>7391067</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5284,60 +5284,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127706932</v>
+        <v>127709750</v>
       </c>
       <c r="B49" t="n">
-        <v>92641</v>
+        <v>78787</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811449</v>
+        <v>811591</v>
       </c>
       <c r="R49" t="n">
-        <v>7391067</v>
+        <v>7391072</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5381,60 +5381,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127824748</v>
+        <v>127709793</v>
       </c>
       <c r="B50" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Fatikvarre, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811709</v>
+        <v>811612</v>
       </c>
       <c r="R50" t="n">
-        <v>7391020</v>
+        <v>7391041</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5684,48 +5684,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127709793</v>
+        <v>127824748</v>
       </c>
       <c r="B53" t="n">
-        <v>92641</v>
+        <v>78788</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811612</v>
+        <v>811709</v>
       </c>
       <c r="R53" t="n">
-        <v>7391041</v>
+        <v>7391020</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5781,48 +5781,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127709717</v>
+        <v>127706919</v>
       </c>
       <c r="B54" t="n">
-        <v>79053</v>
+        <v>92835</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811625</v>
+        <v>811446</v>
       </c>
       <c r="R54" t="n">
-        <v>7390984</v>
+        <v>7391045</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5866,22 +5866,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127706933</v>
+        <v>127709702</v>
       </c>
       <c r="B55" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,37 +5889,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811536</v>
+        <v>811715</v>
       </c>
       <c r="R55" t="n">
-        <v>7391018</v>
+        <v>7391028</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5963,19 +5963,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709702</v>
+        <v>127709692</v>
       </c>
       <c r="B56" t="n">
         <v>79647</v>
@@ -6010,10 +6010,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811715</v>
+        <v>811591</v>
       </c>
       <c r="R56" t="n">
-        <v>7391028</v>
+        <v>7391072</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6072,32 +6072,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709692</v>
+        <v>127709717</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6107,10 +6107,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811591</v>
+        <v>811625</v>
       </c>
       <c r="R57" t="n">
-        <v>7391072</v>
+        <v>7390984</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6169,10 +6169,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127706919</v>
+        <v>127706933</v>
       </c>
       <c r="B58" t="n">
-        <v>92834</v>
+        <v>78435</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6180,21 +6180,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811446</v>
+        <v>811536</v>
       </c>
       <c r="R58" t="n">
-        <v>7391045</v>
+        <v>7391018</v>
       </c>
       <c r="S58" t="n">
         <v>1</v>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709713</v>
+        <v>127709771</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,42 +6277,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811514</v>
+        <v>811735</v>
       </c>
       <c r="R59" t="n">
-        <v>7391024</v>
+        <v>7391006</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6347,11 +6339,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6369,14 +6356,14 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709711</v>
+        <v>127709713</v>
       </c>
       <c r="B60" t="n">
         <v>57672</v>
@@ -6419,10 +6406,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811535</v>
+        <v>811514</v>
       </c>
       <c r="R60" t="n">
-        <v>7391056</v>
+        <v>7391024</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6459,7 +6446,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6486,10 +6473,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709771</v>
+        <v>127709711</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6497,34 +6484,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811735</v>
+        <v>811535</v>
       </c>
       <c r="R61" t="n">
-        <v>7391006</v>
+        <v>7391056</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6559,6 +6554,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
         <v>127709792</v>
       </c>
       <c r="B62" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>127706912</v>
       </c>
       <c r="B63" t="n">
-        <v>91273</v>
+        <v>91274</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>127709737</v>
       </c>
       <c r="B64" t="n">
-        <v>92834</v>
+        <v>92835</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6971,10 +6971,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127709705</v>
+        <v>127709739</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6982,42 +6982,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811705</v>
+        <v>811603</v>
       </c>
       <c r="R66" t="n">
-        <v>7390855</v>
+        <v>7390979</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7052,11 +7044,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7074,17 +7061,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127709798</v>
+        <v>127706913</v>
       </c>
       <c r="B67" t="n">
-        <v>79053</v>
+        <v>91317</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7092,37 +7079,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811676</v>
+        <v>811507</v>
       </c>
       <c r="R67" t="n">
-        <v>7390933</v>
+        <v>7391034</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7166,44 +7153,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709803</v>
+        <v>127709798</v>
       </c>
       <c r="B68" t="n">
-        <v>78435</v>
+        <v>79053</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7213,10 +7200,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811716</v>
+        <v>811676</v>
       </c>
       <c r="R68" t="n">
-        <v>7390831</v>
+        <v>7390933</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7275,10 +7262,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709700</v>
+        <v>127709803</v>
       </c>
       <c r="B69" t="n">
-        <v>79647</v>
+        <v>78435</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7286,21 +7273,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7310,10 +7297,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811687</v>
+        <v>811716</v>
       </c>
       <c r="R69" t="n">
-        <v>7390967</v>
+        <v>7390831</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7372,10 +7359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709739</v>
+        <v>127709700</v>
       </c>
       <c r="B70" t="n">
-        <v>92834</v>
+        <v>79647</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7383,21 +7370,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7407,10 +7394,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811603</v>
+        <v>811687</v>
       </c>
       <c r="R70" t="n">
-        <v>7390979</v>
+        <v>7390967</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7566,48 +7553,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127706913</v>
+        <v>127709802</v>
       </c>
       <c r="B72" t="n">
-        <v>91316</v>
+        <v>92636</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811507</v>
+        <v>811642</v>
       </c>
       <c r="R72" t="n">
-        <v>7391034</v>
+        <v>7391000</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7651,22 +7638,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709802</v>
+        <v>127709705</v>
       </c>
       <c r="B73" t="n">
-        <v>92635</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7674,34 +7661,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811642</v>
+        <v>811705</v>
       </c>
       <c r="R73" t="n">
-        <v>7391000</v>
+        <v>7390855</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7736,6 +7731,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7753,17 +7753,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709762</v>
+        <v>127709754</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811718</v>
+        <v>811518</v>
       </c>
       <c r="R74" t="n">
-        <v>7390806</v>
+        <v>7391069</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127709754</v>
+        <v>127709696</v>
       </c>
       <c r="B75" t="n">
-        <v>78787</v>
+        <v>79647</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7868,21 +7868,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>811518</v>
+        <v>811519</v>
       </c>
       <c r="R75" t="n">
-        <v>7391069</v>
+        <v>7391067</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709696</v>
+        <v>127709805</v>
       </c>
       <c r="B76" t="n">
-        <v>79647</v>
+        <v>78435</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811519</v>
+        <v>811635</v>
       </c>
       <c r="R76" t="n">
-        <v>7391067</v>
+        <v>7391001</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709805</v>
+        <v>127709762</v>
       </c>
       <c r="B77" t="n">
-        <v>78435</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811635</v>
+        <v>811718</v>
       </c>
       <c r="R77" t="n">
-        <v>7391001</v>
+        <v>7390806</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8342,32 +8342,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706918</v>
+        <v>127706931</v>
       </c>
       <c r="B80" t="n">
-        <v>91647</v>
+        <v>92642</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8377,10 +8377,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811451</v>
+        <v>811711</v>
       </c>
       <c r="R80" t="n">
-        <v>7391161</v>
+        <v>7390853</v>
       </c>
       <c r="S80" t="n">
         <v>1</v>
@@ -8439,10 +8439,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709755</v>
+        <v>127709738</v>
       </c>
       <c r="B81" t="n">
-        <v>78787</v>
+        <v>92835</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8450,21 +8450,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811542</v>
+        <v>811577</v>
       </c>
       <c r="R81" t="n">
-        <v>7391054</v>
+        <v>7391006</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B82" t="n">
-        <v>92834</v>
+        <v>91648</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R82" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8621,12 +8621,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8636,7 +8636,7 @@
         <v>127709760</v>
       </c>
       <c r="B83" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8730,48 +8730,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127706931</v>
+        <v>127709755</v>
       </c>
       <c r="B84" t="n">
-        <v>92641</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811711</v>
+        <v>811542</v>
       </c>
       <c r="R84" t="n">
-        <v>7390853</v>
+        <v>7391054</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8815,44 +8815,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127709757</v>
+        <v>127709789</v>
       </c>
       <c r="B85" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811625</v>
+        <v>811610</v>
       </c>
       <c r="R85" t="n">
-        <v>7390969</v>
+        <v>7390981</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8924,32 +8924,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709759</v>
+        <v>127709788</v>
       </c>
       <c r="B86" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811715</v>
+        <v>811667</v>
       </c>
       <c r="R86" t="n">
-        <v>7391028</v>
+        <v>7390931</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9118,32 +9118,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709789</v>
+        <v>127709757</v>
       </c>
       <c r="B88" t="n">
-        <v>92641</v>
+        <v>78787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811610</v>
+        <v>811625</v>
       </c>
       <c r="R88" t="n">
-        <v>7390981</v>
+        <v>7390969</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9215,32 +9215,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127709788</v>
+        <v>127709759</v>
       </c>
       <c r="B89" t="n">
-        <v>92641</v>
+        <v>78787</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811667</v>
+        <v>811715</v>
       </c>
       <c r="R89" t="n">
-        <v>7390931</v>
+        <v>7391028</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9312,48 +9312,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127706916</v>
+        <v>127709777</v>
       </c>
       <c r="B90" t="n">
-        <v>90386</v>
+        <v>92642</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811652</v>
+        <v>811696</v>
       </c>
       <c r="R90" t="n">
-        <v>7390945</v>
+        <v>7390929</v>
       </c>
       <c r="S90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9397,22 +9397,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709742</v>
+        <v>127706916</v>
       </c>
       <c r="B91" t="n">
-        <v>78788</v>
+        <v>90387</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9420,37 +9420,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811466</v>
+        <v>811652</v>
       </c>
       <c r="R91" t="n">
-        <v>7391161</v>
+        <v>7390945</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9494,22 +9494,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127706922</v>
+        <v>127709775</v>
       </c>
       <c r="B92" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9517,37 +9517,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811556</v>
+        <v>811544</v>
       </c>
       <c r="R92" t="n">
-        <v>7391103</v>
+        <v>7391011</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,44 +9591,44 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709775</v>
+        <v>127709728</v>
       </c>
       <c r="B93" t="n">
-        <v>78696</v>
+        <v>79053</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811544</v>
+        <v>811385</v>
       </c>
       <c r="R93" t="n">
-        <v>7391011</v>
+        <v>7391153</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9700,32 +9700,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127709728</v>
+        <v>127709742</v>
       </c>
       <c r="B94" t="n">
-        <v>79053</v>
+        <v>78788</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9735,10 +9735,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>811385</v>
+        <v>811466</v>
       </c>
       <c r="R94" t="n">
-        <v>7391153</v>
+        <v>7391161</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -9797,48 +9797,48 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127709777</v>
+        <v>127706922</v>
       </c>
       <c r="B95" t="n">
-        <v>92641</v>
+        <v>78788</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>811696</v>
+        <v>811556</v>
       </c>
       <c r="R95" t="n">
-        <v>7390929</v>
+        <v>7391103</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -9882,44 +9882,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709693</v>
+        <v>127709795</v>
       </c>
       <c r="B96" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811486</v>
+        <v>811676</v>
       </c>
       <c r="R96" t="n">
-        <v>7391112</v>
+        <v>7391004</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709769</v>
+        <v>127709799</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>92636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10002,34 +10002,38 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811672</v>
+        <v>811707</v>
       </c>
       <c r="R97" t="n">
-        <v>7390924</v>
+        <v>7390860</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10070,6 +10074,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10088,10 +10093,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709795</v>
+        <v>127709783</v>
       </c>
       <c r="B98" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10123,10 +10128,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811676</v>
+        <v>811387</v>
       </c>
       <c r="R98" t="n">
-        <v>7391004</v>
+        <v>7391146</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10185,10 +10190,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709799</v>
+        <v>127709693</v>
       </c>
       <c r="B99" t="n">
-        <v>92635</v>
+        <v>79647</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10196,38 +10201,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811707</v>
+        <v>811486</v>
       </c>
       <c r="R99" t="n">
-        <v>7390860</v>
+        <v>7391112</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10268,7 +10269,6 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -10287,32 +10287,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127709783</v>
+        <v>127709769</v>
       </c>
       <c r="B100" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811387</v>
+        <v>811672</v>
       </c>
       <c r="R100" t="n">
-        <v>7391146</v>
+        <v>7390924</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -10384,10 +10384,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709733</v>
+        <v>127709785</v>
       </c>
       <c r="B101" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10395,21 +10395,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10419,10 +10419,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811530</v>
+        <v>811504</v>
       </c>
       <c r="R101" t="n">
-        <v>7391016</v>
+        <v>7391047</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -10481,45 +10481,48 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709770</v>
+        <v>127709727</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>92646</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4365</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811608</v>
+        <v>811545</v>
       </c>
       <c r="R102" t="n">
-        <v>7391004</v>
+        <v>7391008</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10560,6 +10563,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -10578,10 +10582,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709729</v>
+        <v>127709787</v>
       </c>
       <c r="B103" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10589,21 +10593,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10613,10 +10617,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811434</v>
+        <v>811677</v>
       </c>
       <c r="R103" t="n">
-        <v>7391048</v>
+        <v>7390878</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -10675,48 +10679,48 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127706920</v>
+        <v>127709733</v>
       </c>
       <c r="B104" t="n">
-        <v>92834</v>
+        <v>79053</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2079</v>
+        <v>6434</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811552</v>
+        <v>811530</v>
       </c>
       <c r="R104" t="n">
-        <v>7391002</v>
+        <v>7391016</v>
       </c>
       <c r="S104" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10760,44 +10764,44 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709785</v>
+        <v>127709770</v>
       </c>
       <c r="B105" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10807,10 +10811,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811504</v>
+        <v>811608</v>
       </c>
       <c r="R105" t="n">
-        <v>7391047</v>
+        <v>7391004</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10869,48 +10873,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709727</v>
+        <v>127709729</v>
       </c>
       <c r="B106" t="n">
-        <v>92645</v>
+        <v>79053</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811545</v>
+        <v>811434</v>
       </c>
       <c r="R106" t="n">
-        <v>7391008</v>
+        <v>7391048</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10951,7 +10952,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10970,32 +10970,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709787</v>
+        <v>127709764</v>
       </c>
       <c r="B107" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811677</v>
+        <v>811498</v>
       </c>
       <c r="R107" t="n">
-        <v>7390878</v>
+        <v>7391103</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11067,48 +11067,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709764</v>
+        <v>127706924</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811498</v>
+        <v>811422</v>
       </c>
       <c r="R108" t="n">
-        <v>7391103</v>
+        <v>7391139</v>
       </c>
       <c r="S108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11152,44 +11152,44 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127706924</v>
+        <v>127706920</v>
       </c>
       <c r="B109" t="n">
-        <v>58042</v>
+        <v>92835</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103015</v>
+        <v>2079</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811422</v>
+        <v>811552</v>
       </c>
       <c r="R109" t="n">
-        <v>7391139</v>
+        <v>7391002</v>
       </c>
       <c r="S109" t="n">
         <v>1</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709801</v>
+        <v>127709697</v>
       </c>
       <c r="B112" t="n">
-        <v>92635</v>
+        <v>79647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811615</v>
+        <v>811625</v>
       </c>
       <c r="R112" t="n">
-        <v>7390990</v>
+        <v>7390969</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,32 +11552,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709726</v>
+        <v>127709720</v>
       </c>
       <c r="B113" t="n">
-        <v>92645</v>
+        <v>57669</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4365</v>
+        <v>100049</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811638</v>
+        <v>811515</v>
       </c>
       <c r="R113" t="n">
-        <v>7391044</v>
+        <v>7391165</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709697</v>
+        <v>127709707</v>
       </c>
       <c r="B114" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,34 +11660,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811625</v>
+        <v>811874</v>
       </c>
       <c r="R114" t="n">
-        <v>7390969</v>
+        <v>7390830</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11722,6 +11730,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -11739,17 +11752,17 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709720</v>
+        <v>127709801</v>
       </c>
       <c r="B115" t="n">
-        <v>57669</v>
+        <v>92636</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11757,21 +11770,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11781,10 +11794,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811515</v>
+        <v>811615</v>
       </c>
       <c r="R115" t="n">
-        <v>7391165</v>
+        <v>7390990</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11843,53 +11856,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127709707</v>
+        <v>127709726</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>92646</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811874</v>
+        <v>811638</v>
       </c>
       <c r="R116" t="n">
-        <v>7390830</v>
+        <v>7391044</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11924,11 +11929,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11946,39 +11946,39 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709776</v>
+        <v>127709732</v>
       </c>
       <c r="B117" t="n">
-        <v>78696</v>
+        <v>79053</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811646</v>
+        <v>811523</v>
       </c>
       <c r="R117" t="n">
-        <v>7390963</v>
+        <v>7391024</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709732</v>
+        <v>127709765</v>
       </c>
       <c r="B118" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811523</v>
+        <v>811478</v>
       </c>
       <c r="R118" t="n">
-        <v>7391024</v>
+        <v>7391172</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709765</v>
+        <v>127709778</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811478</v>
+        <v>811683</v>
       </c>
       <c r="R119" t="n">
-        <v>7391172</v>
+        <v>7390938</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,10 +12244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709778</v>
+        <v>127709791</v>
       </c>
       <c r="B120" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811683</v>
+        <v>811605</v>
       </c>
       <c r="R120" t="n">
-        <v>7390938</v>
+        <v>7391024</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,32 +12341,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709791</v>
+        <v>127709776</v>
       </c>
       <c r="B121" t="n">
-        <v>92641</v>
+        <v>78696</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811605</v>
+        <v>811646</v>
       </c>
       <c r="R121" t="n">
-        <v>7391024</v>
+        <v>7390963</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -12438,10 +12438,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127709743</v>
+        <v>127709723</v>
       </c>
       <c r="B122" t="n">
-        <v>78788</v>
+        <v>57669</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12449,21 +12449,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12473,10 +12473,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811385</v>
+        <v>811411</v>
       </c>
       <c r="R122" t="n">
-        <v>7391163</v>
+        <v>7391165</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -12535,10 +12535,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127709723</v>
+        <v>127709743</v>
       </c>
       <c r="B123" t="n">
-        <v>57669</v>
+        <v>78788</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12546,21 +12546,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12570,10 +12570,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811411</v>
+        <v>811385</v>
       </c>
       <c r="R123" t="n">
-        <v>7391165</v>
+        <v>7391163</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -12635,7 +12635,7 @@
         <v>127824695</v>
       </c>
       <c r="B124" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>127824701</v>
       </c>
       <c r="B126" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13020,10 +13020,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127824735</v>
+        <v>127824758</v>
       </c>
       <c r="B128" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13031,21 +13031,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13055,10 +13055,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811831</v>
+        <v>811955</v>
       </c>
       <c r="R128" t="n">
-        <v>7390950</v>
+        <v>7391105</v>
       </c>
       <c r="S128" t="n">
         <v>1</v>
@@ -13117,32 +13117,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>127824751</v>
+        <v>127824762</v>
       </c>
       <c r="B129" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13152,10 +13152,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>812037</v>
+        <v>811855</v>
       </c>
       <c r="R129" t="n">
-        <v>7391151</v>
+        <v>7390961</v>
       </c>
       <c r="S129" t="n">
         <v>1</v>
@@ -13214,10 +13214,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824758</v>
+        <v>127824735</v>
       </c>
       <c r="B130" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13225,21 +13225,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811955</v>
+        <v>811831</v>
       </c>
       <c r="R130" t="n">
-        <v>7391105</v>
+        <v>7390950</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,32 +13311,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824762</v>
+        <v>127824751</v>
       </c>
       <c r="B131" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811855</v>
+        <v>812037</v>
       </c>
       <c r="R131" t="n">
-        <v>7390961</v>
+        <v>7391151</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -13411,7 +13411,7 @@
         <v>127824698</v>
       </c>
       <c r="B132" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13508,7 +13508,7 @@
         <v>127824699</v>
       </c>
       <c r="B133" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>127824696</v>
       </c>
       <c r="B134" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -13699,10 +13699,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824703</v>
+        <v>127824753</v>
       </c>
       <c r="B135" t="n">
-        <v>91351</v>
+        <v>81004</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -13710,21 +13710,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811762</v>
+        <v>811752</v>
       </c>
       <c r="R135" t="n">
-        <v>7390826</v>
+        <v>7390828</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13796,10 +13796,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127824753</v>
+        <v>127824703</v>
       </c>
       <c r="B136" t="n">
-        <v>81004</v>
+        <v>91352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -13807,21 +13807,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1049</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811752</v>
+        <v>811762</v>
       </c>
       <c r="R136" t="n">
-        <v>7390828</v>
+        <v>7390826</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -13990,10 +13990,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824747</v>
+        <v>127824782</v>
       </c>
       <c r="B138" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14001,21 +14001,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811803</v>
+        <v>811902</v>
       </c>
       <c r="R138" t="n">
-        <v>7390886</v>
+        <v>7390765</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14087,7 +14087,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127824739</v>
+        <v>127824747</v>
       </c>
       <c r="B139" t="n">
         <v>79053</v>
@@ -14122,10 +14122,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811874</v>
+        <v>811803</v>
       </c>
       <c r="R139" t="n">
-        <v>7391049</v>
+        <v>7390886</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -14184,10 +14184,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824782</v>
+        <v>127824739</v>
       </c>
       <c r="B140" t="n">
-        <v>92641</v>
+        <v>79053</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14195,21 +14195,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811902</v>
+        <v>811874</v>
       </c>
       <c r="R140" t="n">
-        <v>7390765</v>
+        <v>7391049</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824697</v>
+        <v>127824725</v>
       </c>
       <c r="B141" t="n">
-        <v>91351</v>
+        <v>57832</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>812064</v>
+        <v>811800</v>
       </c>
       <c r="R141" t="n">
-        <v>7391153</v>
+        <v>7390892</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14378,10 +14378,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127824733</v>
+        <v>127824694</v>
       </c>
       <c r="B142" t="n">
-        <v>92667</v>
+        <v>79618</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14389,21 +14389,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5448</v>
+        <v>229821</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14413,10 +14413,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811899</v>
+        <v>811716</v>
       </c>
       <c r="R142" t="n">
-        <v>7390756</v>
+        <v>7390763</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127824766</v>
+        <v>127824733</v>
       </c>
       <c r="B143" t="n">
-        <v>79029</v>
+        <v>92668</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14486,21 +14486,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811921</v>
+        <v>811899</v>
       </c>
       <c r="R143" t="n">
-        <v>7390838</v>
+        <v>7390756</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -14572,10 +14572,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127824690</v>
+        <v>127824766</v>
       </c>
       <c r="B144" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14583,21 +14583,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -14607,10 +14607,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811721</v>
+        <v>811921</v>
       </c>
       <c r="R144" t="n">
-        <v>7390757</v>
+        <v>7390838</v>
       </c>
       <c r="S144" t="n">
         <v>1</v>
@@ -14669,10 +14669,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127824725</v>
+        <v>127824690</v>
       </c>
       <c r="B145" t="n">
-        <v>57832</v>
+        <v>79647</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811800</v>
+        <v>811721</v>
       </c>
       <c r="R145" t="n">
-        <v>7390892</v>
+        <v>7390757</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824694</v>
+        <v>127824697</v>
       </c>
       <c r="B146" t="n">
-        <v>79618</v>
+        <v>91352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811716</v>
+        <v>812064</v>
       </c>
       <c r="R146" t="n">
-        <v>7390763</v>
+        <v>7391153</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14866,7 +14866,7 @@
         <v>127824784</v>
       </c>
       <c r="B147" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14960,32 +14960,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127824783</v>
+        <v>127824777</v>
       </c>
       <c r="B148" t="n">
-        <v>92641</v>
+        <v>82870</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811895</v>
+        <v>811935</v>
       </c>
       <c r="R148" t="n">
-        <v>7390780</v>
+        <v>7390835</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15057,32 +15057,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824777</v>
+        <v>127824783</v>
       </c>
       <c r="B149" t="n">
-        <v>82870</v>
+        <v>92642</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811935</v>
+        <v>811895</v>
       </c>
       <c r="R149" t="n">
-        <v>7390835</v>
+        <v>7390780</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15251,45 +15251,49 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127824692</v>
+        <v>127824722</v>
       </c>
       <c r="B151" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811721</v>
+        <v>811902</v>
       </c>
       <c r="R151" t="n">
-        <v>7390780</v>
+        <v>7390779</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -15322,6 +15326,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Hittad död under tall där någon ätit den antagligen duvhök.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15348,32 +15357,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127824741</v>
+        <v>127824692</v>
       </c>
       <c r="B152" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15383,10 +15392,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>812137</v>
+        <v>811721</v>
       </c>
       <c r="R152" t="n">
-        <v>7391383</v>
+        <v>7390780</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -15445,10 +15454,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127824722</v>
+        <v>127824741</v>
       </c>
       <c r="B153" t="n">
-        <v>56864</v>
+        <v>79053</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -15456,38 +15465,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>811902</v>
+        <v>812137</v>
       </c>
       <c r="R153" t="n">
-        <v>7390779</v>
+        <v>7391383</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -15520,11 +15525,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Hittad död under tall där någon ätit den antagligen duvhök.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16040,10 +16040,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824700</v>
+        <v>127824761</v>
       </c>
       <c r="B159" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811899</v>
+        <v>811845</v>
       </c>
       <c r="R159" t="n">
-        <v>7390998</v>
+        <v>7390977</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16137,10 +16137,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824718</v>
+        <v>127824760</v>
       </c>
       <c r="B160" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16148,21 +16148,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811915</v>
+        <v>811882</v>
       </c>
       <c r="R160" t="n">
-        <v>7390765</v>
+        <v>7390983</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16234,10 +16234,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824761</v>
+        <v>127824718</v>
       </c>
       <c r="B161" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16245,21 +16245,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16269,10 +16269,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811845</v>
+        <v>811915</v>
       </c>
       <c r="R161" t="n">
-        <v>7390977</v>
+        <v>7390765</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16331,10 +16331,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824760</v>
+        <v>127824693</v>
       </c>
       <c r="B162" t="n">
-        <v>79029</v>
+        <v>79618</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16342,21 +16342,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811882</v>
+        <v>811874</v>
       </c>
       <c r="R162" t="n">
-        <v>7390983</v>
+        <v>7391049</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16428,10 +16428,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127824693</v>
+        <v>127824700</v>
       </c>
       <c r="B163" t="n">
-        <v>79618</v>
+        <v>91352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16439,21 +16439,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811874</v>
+        <v>811899</v>
       </c>
       <c r="R163" t="n">
-        <v>7391049</v>
+        <v>7390998</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -16528,7 +16528,7 @@
         <v>127824780</v>
       </c>
       <c r="B164" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -16916,7 +16916,7 @@
         <v>127824781</v>
       </c>
       <c r="B168" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18662,7 +18662,7 @@
         <v>127824702</v>
       </c>
       <c r="B186" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127824774</v>
+        <v>127824770</v>
       </c>
       <c r="B189" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18961,21 +18961,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18985,10 +18985,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811971</v>
+        <v>811800</v>
       </c>
       <c r="R189" t="n">
-        <v>7391094</v>
+        <v>7390865</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -19047,32 +19047,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127824773</v>
+        <v>127824745</v>
       </c>
       <c r="B190" t="n">
-        <v>82870</v>
+        <v>79053</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>811989</v>
+        <v>811913</v>
       </c>
       <c r="R190" t="n">
-        <v>7391103</v>
+        <v>7390816</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -19144,10 +19144,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127824711</v>
+        <v>127824774</v>
       </c>
       <c r="B191" t="n">
-        <v>57672</v>
+        <v>82870</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19155,21 +19155,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>812170</v>
+        <v>811971</v>
       </c>
       <c r="R191" t="n">
-        <v>7391394</v>
+        <v>7391094</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -19241,10 +19241,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824770</v>
+        <v>127824773</v>
       </c>
       <c r="B192" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -19252,21 +19252,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811800</v>
+        <v>811989</v>
       </c>
       <c r="R192" t="n">
-        <v>7390865</v>
+        <v>7391103</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -19338,32 +19338,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>127824745</v>
+        <v>127824711</v>
       </c>
       <c r="B193" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -19373,10 +19373,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>811913</v>
+        <v>812170</v>
       </c>
       <c r="R193" t="n">
-        <v>7390816</v>
+        <v>7391394</v>
       </c>
       <c r="S193" t="n">
         <v>1</v>
@@ -19960,7 +19960,7 @@
         <v>127709716</v>
       </c>
       <c r="B199" t="n">
-        <v>91512</v>
+        <v>91513</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>128198143</v>
       </c>
       <c r="B207" t="n">
-        <v>91552</v>
+        <v>91553</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127709734</v>
+        <v>127706926</v>
       </c>
       <c r="B3" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811573</v>
+        <v>811754</v>
       </c>
       <c r="R3" t="n">
-        <v>7391001</v>
+        <v>7390851</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -966,48 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127706926</v>
+        <v>127709734</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811754</v>
+        <v>811573</v>
       </c>
       <c r="R5" t="n">
-        <v>7390851</v>
+        <v>7391001</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709781</v>
+        <v>127706928</v>
       </c>
       <c r="B7" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811479</v>
+        <v>811509</v>
       </c>
       <c r="R7" t="n">
-        <v>7391142</v>
+        <v>7391152</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127706928</v>
+        <v>127709721</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811509</v>
+        <v>811493</v>
       </c>
       <c r="R8" t="n">
-        <v>7391152</v>
+        <v>7391183</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127709721</v>
+        <v>127709781</v>
       </c>
       <c r="B9" t="n">
-        <v>57669</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811493</v>
+        <v>811479</v>
       </c>
       <c r="R9" t="n">
-        <v>7391183</v>
+        <v>7391142</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127706925</v>
+        <v>127709699</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,37 +2154,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811866</v>
+        <v>811707</v>
       </c>
       <c r="R17" t="n">
-        <v>7390863</v>
+        <v>7390941</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2228,22 +2228,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709699</v>
+        <v>127706925</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811707</v>
+        <v>811866</v>
       </c>
       <c r="R18" t="n">
-        <v>7390941</v>
+        <v>7390863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709698</v>
+        <v>127709800</v>
       </c>
       <c r="B21" t="n">
-        <v>79647</v>
+        <v>92636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2555,21 +2555,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811656</v>
+        <v>811725</v>
       </c>
       <c r="R21" t="n">
-        <v>7390942</v>
+        <v>7390826</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709800</v>
+        <v>127709797</v>
       </c>
       <c r="B22" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811725</v>
+        <v>811577</v>
       </c>
       <c r="R22" t="n">
-        <v>7390826</v>
+        <v>7391006</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,45 +2738,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709797</v>
+        <v>127709725</v>
       </c>
       <c r="B23" t="n">
-        <v>92642</v>
+        <v>92646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811577</v>
+        <v>811692</v>
       </c>
       <c r="R23" t="n">
-        <v>7391006</v>
+        <v>7390871</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2817,6 +2820,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2835,48 +2839,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709725</v>
+        <v>127709698</v>
       </c>
       <c r="B24" t="n">
-        <v>92646</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811692</v>
+        <v>811656</v>
       </c>
       <c r="R24" t="n">
-        <v>7390871</v>
+        <v>7390942</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2917,7 +2918,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3033,32 +3033,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709790</v>
+        <v>127709741</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>78788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811610</v>
+        <v>811489</v>
       </c>
       <c r="R26" t="n">
-        <v>7391012</v>
+        <v>7391186</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709786</v>
+        <v>127709703</v>
       </c>
       <c r="B27" t="n">
-        <v>92642</v>
+        <v>79618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811612</v>
+        <v>811724</v>
       </c>
       <c r="R27" t="n">
-        <v>7390987</v>
+        <v>7390998</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3209,6 +3209,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3227,7 +3228,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709779</v>
+        <v>127709790</v>
       </c>
       <c r="B28" t="n">
         <v>92642</v>
@@ -3262,10 +3263,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811561</v>
+        <v>811610</v>
       </c>
       <c r="R28" t="n">
-        <v>7391108</v>
+        <v>7391012</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,7 +3325,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709796</v>
+        <v>127709786</v>
       </c>
       <c r="B29" t="n">
         <v>92642</v>
@@ -3359,10 +3360,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811672</v>
+        <v>811612</v>
       </c>
       <c r="R29" t="n">
-        <v>7391010</v>
+        <v>7390987</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,32 +3422,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709741</v>
+        <v>127709779</v>
       </c>
       <c r="B30" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811489</v>
+        <v>811561</v>
       </c>
       <c r="R30" t="n">
-        <v>7391186</v>
+        <v>7391108</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3518,32 +3519,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709758</v>
+        <v>127709796</v>
       </c>
       <c r="B31" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3554,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811621</v>
+        <v>811672</v>
       </c>
       <c r="R31" t="n">
-        <v>7390981</v>
+        <v>7391010</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3615,48 +3616,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709730</v>
+        <v>127706927</v>
       </c>
       <c r="B32" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811452</v>
+        <v>811760</v>
       </c>
       <c r="R32" t="n">
-        <v>7391057</v>
+        <v>7390859</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3700,44 +3701,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709736</v>
+        <v>127709758</v>
       </c>
       <c r="B33" t="n">
-        <v>79053</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3747,10 +3748,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811662</v>
+        <v>811621</v>
       </c>
       <c r="R33" t="n">
-        <v>7390926</v>
+        <v>7390981</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3809,48 +3810,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127706927</v>
+        <v>127709730</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811760</v>
+        <v>811452</v>
       </c>
       <c r="R34" t="n">
-        <v>7390859</v>
+        <v>7391057</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3894,44 +3895,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127709722</v>
+        <v>127709736</v>
       </c>
       <c r="B35" t="n">
-        <v>57669</v>
+        <v>79053</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3941,10 +3942,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811476</v>
+        <v>811662</v>
       </c>
       <c r="R35" t="n">
-        <v>7391149</v>
+        <v>7390926</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4003,10 +4004,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127709703</v>
+        <v>127709722</v>
       </c>
       <c r="B36" t="n">
-        <v>79618</v>
+        <v>57669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4014,21 +4015,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4038,10 +4039,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811724</v>
+        <v>811476</v>
       </c>
       <c r="R36" t="n">
-        <v>7390998</v>
+        <v>7391149</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4082,7 +4083,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4101,10 +4101,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709708</v>
+        <v>127709768</v>
       </c>
       <c r="B37" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4112,42 +4112,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811580</v>
+        <v>811776</v>
       </c>
       <c r="R37" t="n">
-        <v>7391090</v>
+        <v>7390918</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4182,11 +4174,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4204,39 +4191,39 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709780</v>
+        <v>127709766</v>
       </c>
       <c r="B38" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4246,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811475</v>
+        <v>811730</v>
       </c>
       <c r="R38" t="n">
-        <v>7391196</v>
+        <v>7390914</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4308,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709768</v>
+        <v>127709756</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4343,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811776</v>
+        <v>811538</v>
       </c>
       <c r="R39" t="n">
-        <v>7390918</v>
+        <v>7391022</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4405,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709766</v>
+        <v>127709708</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4416,34 +4403,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811730</v>
+        <v>811580</v>
       </c>
       <c r="R40" t="n">
-        <v>7390914</v>
+        <v>7391090</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4478,6 +4473,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4495,39 +4495,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709756</v>
+        <v>127709780</v>
       </c>
       <c r="B41" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811538</v>
+        <v>811475</v>
       </c>
       <c r="R41" t="n">
-        <v>7391022</v>
+        <v>7391196</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4811,32 +4811,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127709744</v>
+        <v>127709735</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>79053</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6434</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4846,10 +4846,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811539</v>
+        <v>811626</v>
       </c>
       <c r="R44" t="n">
-        <v>7391022</v>
+        <v>7390972</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4908,32 +4908,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127709735</v>
+        <v>127709752</v>
       </c>
       <c r="B45" t="n">
-        <v>79053</v>
+        <v>78787</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6434</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811626</v>
+        <v>811490</v>
       </c>
       <c r="R45" t="n">
-        <v>7390972</v>
+        <v>7391186</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5005,10 +5005,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127709752</v>
+        <v>127709744</v>
       </c>
       <c r="B46" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5016,21 +5016,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811490</v>
+        <v>811539</v>
       </c>
       <c r="R46" t="n">
-        <v>7391186</v>
+        <v>7391022</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5781,48 +5781,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127706919</v>
+        <v>127709792</v>
       </c>
       <c r="B54" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811446</v>
+        <v>811619</v>
       </c>
       <c r="R54" t="n">
-        <v>7391045</v>
+        <v>7391036</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5866,12 +5866,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6072,48 +6072,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709717</v>
+        <v>127706919</v>
       </c>
       <c r="B57" t="n">
-        <v>79053</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6434</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811625</v>
+        <v>811446</v>
       </c>
       <c r="R57" t="n">
-        <v>7390984</v>
+        <v>7391045</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6157,60 +6157,60 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127706933</v>
+        <v>127709717</v>
       </c>
       <c r="B58" t="n">
-        <v>78435</v>
+        <v>79053</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811536</v>
+        <v>811625</v>
       </c>
       <c r="R58" t="n">
-        <v>7391018</v>
+        <v>7390984</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6254,22 +6254,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709771</v>
+        <v>127706933</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>78435</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,37 +6277,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811735</v>
+        <v>811536</v>
       </c>
       <c r="R59" t="n">
-        <v>7391006</v>
+        <v>7391018</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6351,22 +6351,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709713</v>
+        <v>127709771</v>
       </c>
       <c r="B60" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6374,42 +6374,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811514</v>
+        <v>811735</v>
       </c>
       <c r="R60" t="n">
-        <v>7391024</v>
+        <v>7391006</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6444,11 +6436,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6466,14 +6453,14 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709711</v>
+        <v>127709713</v>
       </c>
       <c r="B61" t="n">
         <v>57672</v>
@@ -6516,10 +6503,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811535</v>
+        <v>811514</v>
       </c>
       <c r="R61" t="n">
-        <v>7391056</v>
+        <v>7391024</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6556,7 +6543,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6583,45 +6570,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709792</v>
+        <v>127709711</v>
       </c>
       <c r="B62" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811619</v>
+        <v>811535</v>
       </c>
       <c r="R62" t="n">
-        <v>7391036</v>
+        <v>7391056</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6656,6 +6651,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6673,17 +6673,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127706912</v>
+        <v>127709737</v>
       </c>
       <c r="B63" t="n">
-        <v>91274</v>
+        <v>92835</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6691,37 +6691,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811615</v>
+        <v>811493</v>
       </c>
       <c r="R63" t="n">
-        <v>7391007</v>
+        <v>7391027</v>
       </c>
       <c r="S63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6765,22 +6765,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127709737</v>
+        <v>127706912</v>
       </c>
       <c r="B64" t="n">
-        <v>92835</v>
+        <v>91274</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6788,37 +6788,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811493</v>
+        <v>811615</v>
       </c>
       <c r="R64" t="n">
-        <v>7391027</v>
+        <v>7391007</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6862,12 +6862,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7068,48 +7068,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127706913</v>
+        <v>127709802</v>
       </c>
       <c r="B67" t="n">
-        <v>91317</v>
+        <v>92636</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811507</v>
+        <v>811642</v>
       </c>
       <c r="R67" t="n">
-        <v>7391034</v>
+        <v>7391000</v>
       </c>
       <c r="S67" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7153,12 +7153,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709700</v>
+        <v>127709724</v>
       </c>
       <c r="B70" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7370,21 +7370,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7394,10 +7394,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811687</v>
+        <v>811533</v>
       </c>
       <c r="R70" t="n">
-        <v>7390967</v>
+        <v>7391035</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7456,10 +7456,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709724</v>
+        <v>127709705</v>
       </c>
       <c r="B71" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7467,16 +7467,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7484,17 +7484,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811533</v>
+        <v>811705</v>
       </c>
       <c r="R71" t="n">
-        <v>7391035</v>
+        <v>7390855</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7529,6 +7537,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7546,55 +7559,55 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709802</v>
+        <v>127706913</v>
       </c>
       <c r="B72" t="n">
-        <v>92636</v>
+        <v>91317</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811642</v>
+        <v>811507</v>
       </c>
       <c r="R72" t="n">
-        <v>7391000</v>
+        <v>7391034</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7638,22 +7651,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709705</v>
+        <v>127709700</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7661,42 +7674,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811705</v>
+        <v>811687</v>
       </c>
       <c r="R73" t="n">
-        <v>7390855</v>
+        <v>7390967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -7731,11 +7736,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -7753,17 +7753,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127709754</v>
+        <v>127709772</v>
       </c>
       <c r="B74" t="n">
-        <v>78787</v>
+        <v>82870</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7771,21 +7771,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7795,10 +7795,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>811518</v>
+        <v>811763</v>
       </c>
       <c r="R74" t="n">
-        <v>7391069</v>
+        <v>7390963</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127709805</v>
+        <v>127709701</v>
       </c>
       <c r="B76" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7965,21 +7965,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>811635</v>
+        <v>811632</v>
       </c>
       <c r="R76" t="n">
-        <v>7391001</v>
+        <v>7391030</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127709762</v>
+        <v>127709754</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8086,10 +8086,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>811718</v>
+        <v>811518</v>
       </c>
       <c r="R77" t="n">
-        <v>7390806</v>
+        <v>7391069</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8148,10 +8148,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127709701</v>
+        <v>127709805</v>
       </c>
       <c r="B78" t="n">
-        <v>79647</v>
+        <v>78435</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8159,21 +8159,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>811632</v>
+        <v>811635</v>
       </c>
       <c r="R78" t="n">
-        <v>7391030</v>
+        <v>7391001</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127709772</v>
+        <v>127709762</v>
       </c>
       <c r="B79" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8256,21 +8256,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8280,10 +8280,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>811763</v>
+        <v>811718</v>
       </c>
       <c r="R79" t="n">
-        <v>7390963</v>
+        <v>7390806</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -8342,48 +8342,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706931</v>
+        <v>127709738</v>
       </c>
       <c r="B80" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811711</v>
+        <v>811577</v>
       </c>
       <c r="R80" t="n">
-        <v>7390853</v>
+        <v>7391006</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,22 +8427,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709738</v>
+        <v>127709755</v>
       </c>
       <c r="B81" t="n">
-        <v>92835</v>
+        <v>78787</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8450,21 +8450,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811577</v>
+        <v>811542</v>
       </c>
       <c r="R81" t="n">
-        <v>7391006</v>
+        <v>7391054</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8730,48 +8730,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709755</v>
+        <v>127706931</v>
       </c>
       <c r="B84" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811542</v>
+        <v>811711</v>
       </c>
       <c r="R84" t="n">
-        <v>7391054</v>
+        <v>7390853</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8815,44 +8815,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127709789</v>
+        <v>127709757</v>
       </c>
       <c r="B85" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811610</v>
+        <v>811625</v>
       </c>
       <c r="R85" t="n">
-        <v>7390981</v>
+        <v>7390969</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8924,32 +8924,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709788</v>
+        <v>127709759</v>
       </c>
       <c r="B86" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811667</v>
+        <v>811715</v>
       </c>
       <c r="R86" t="n">
-        <v>7390931</v>
+        <v>7391028</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9118,32 +9118,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709757</v>
+        <v>127709789</v>
       </c>
       <c r="B88" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811625</v>
+        <v>811610</v>
       </c>
       <c r="R88" t="n">
-        <v>7390969</v>
+        <v>7390981</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9215,32 +9215,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127709759</v>
+        <v>127709788</v>
       </c>
       <c r="B89" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811715</v>
+        <v>811667</v>
       </c>
       <c r="R89" t="n">
-        <v>7391028</v>
+        <v>7390931</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -9312,10 +9312,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127709777</v>
+        <v>127709728</v>
       </c>
       <c r="B90" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9323,21 +9323,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811696</v>
+        <v>811385</v>
       </c>
       <c r="R90" t="n">
-        <v>7390929</v>
+        <v>7391153</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127706916</v>
+        <v>127709775</v>
       </c>
       <c r="B91" t="n">
-        <v>90387</v>
+        <v>78696</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9420,37 +9420,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811652</v>
+        <v>811544</v>
       </c>
       <c r="R91" t="n">
-        <v>7390945</v>
+        <v>7391011</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9494,22 +9494,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127709775</v>
+        <v>127706916</v>
       </c>
       <c r="B92" t="n">
-        <v>78696</v>
+        <v>90387</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9517,37 +9517,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811544</v>
+        <v>811652</v>
       </c>
       <c r="R92" t="n">
-        <v>7391011</v>
+        <v>7390945</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,22 +9591,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709728</v>
+        <v>127709777</v>
       </c>
       <c r="B93" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811385</v>
+        <v>811696</v>
       </c>
       <c r="R93" t="n">
-        <v>7391153</v>
+        <v>7390929</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B96" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R96" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,49 +9991,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709799</v>
+        <v>127709795</v>
       </c>
       <c r="B97" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811707</v>
+        <v>811676</v>
       </c>
       <c r="R97" t="n">
-        <v>7390860</v>
+        <v>7391004</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10074,7 +10070,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10093,45 +10088,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709783</v>
+        <v>127709799</v>
       </c>
       <c r="B98" t="n">
-        <v>92642</v>
+        <v>92636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811387</v>
+        <v>811707</v>
       </c>
       <c r="R98" t="n">
-        <v>7391146</v>
+        <v>7390860</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10172,6 +10171,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10190,32 +10190,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709693</v>
+        <v>127709783</v>
       </c>
       <c r="B99" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811486</v>
+        <v>811387</v>
       </c>
       <c r="R99" t="n">
-        <v>7391112</v>
+        <v>7391146</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10384,48 +10384,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709785</v>
+        <v>127706920</v>
       </c>
       <c r="B101" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811504</v>
+        <v>811552</v>
       </c>
       <c r="R101" t="n">
-        <v>7391047</v>
+        <v>7391002</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,60 +10469,57 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709727</v>
+        <v>127709785</v>
       </c>
       <c r="B102" t="n">
-        <v>92646</v>
+        <v>92642</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811545</v>
+        <v>811504</v>
       </c>
       <c r="R102" t="n">
-        <v>7391008</v>
+        <v>7391047</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -10563,7 +10560,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11067,10 +11063,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127706924</v>
+        <v>127709747</v>
       </c>
       <c r="B108" t="n">
-        <v>58042</v>
+        <v>57776</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,16 +11074,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103015</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -11098,17 +11094,17 @@
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811422</v>
+        <v>811653</v>
       </c>
       <c r="R108" t="n">
-        <v>7391139</v>
+        <v>7390948</v>
       </c>
       <c r="S108" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -11152,60 +11148,63 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127706920</v>
+        <v>127709727</v>
       </c>
       <c r="B109" t="n">
-        <v>92835</v>
+        <v>92646</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2079</v>
+        <v>4365</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811552</v>
+        <v>811545</v>
       </c>
       <c r="R109" t="n">
-        <v>7391002</v>
+        <v>7391008</v>
       </c>
       <c r="S109" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -11243,28 +11242,29 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709747</v>
+        <v>127706924</v>
       </c>
       <c r="B110" t="n">
-        <v>57776</v>
+        <v>58042</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11272,16 +11272,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103031</v>
+        <v>103015</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -11292,17 +11292,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811653</v>
+        <v>811422</v>
       </c>
       <c r="R110" t="n">
-        <v>7390948</v>
+        <v>7391139</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11346,22 +11346,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709804</v>
+        <v>127709697</v>
       </c>
       <c r="B111" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811452</v>
+        <v>811625</v>
       </c>
       <c r="R111" t="n">
-        <v>7391056</v>
+        <v>7390969</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709697</v>
+        <v>127709720</v>
       </c>
       <c r="B112" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811625</v>
+        <v>811515</v>
       </c>
       <c r="R112" t="n">
-        <v>7390969</v>
+        <v>7391165</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709720</v>
+        <v>127709707</v>
       </c>
       <c r="B113" t="n">
-        <v>57669</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,16 +11563,16 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -11580,17 +11580,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811515</v>
+        <v>811874</v>
       </c>
       <c r="R113" t="n">
-        <v>7391165</v>
+        <v>7390830</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11625,6 +11633,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -11642,17 +11655,17 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709707</v>
+        <v>127709801</v>
       </c>
       <c r="B114" t="n">
-        <v>57672</v>
+        <v>92636</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,42 +11673,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811874</v>
+        <v>811615</v>
       </c>
       <c r="R114" t="n">
-        <v>7390830</v>
+        <v>7390990</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11730,11 +11735,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -11752,39 +11752,39 @@
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709801</v>
+        <v>127709726</v>
       </c>
       <c r="B115" t="n">
-        <v>92636</v>
+        <v>92646</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11794,10 +11794,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811615</v>
+        <v>811638</v>
       </c>
       <c r="R115" t="n">
-        <v>7390990</v>
+        <v>7391044</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11856,32 +11856,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127709726</v>
+        <v>127709804</v>
       </c>
       <c r="B116" t="n">
-        <v>92646</v>
+        <v>78435</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11891,10 +11891,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811638</v>
+        <v>811452</v>
       </c>
       <c r="R116" t="n">
-        <v>7391044</v>
+        <v>7391056</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709778</v>
+        <v>127709776</v>
       </c>
       <c r="B119" t="n">
-        <v>92642</v>
+        <v>78696</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811683</v>
+        <v>811646</v>
       </c>
       <c r="R119" t="n">
-        <v>7390938</v>
+        <v>7390963</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,7 +12244,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709791</v>
+        <v>127709778</v>
       </c>
       <c r="B120" t="n">
         <v>92642</v>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811605</v>
+        <v>811683</v>
       </c>
       <c r="R120" t="n">
-        <v>7391024</v>
+        <v>7390938</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,32 +12341,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709776</v>
+        <v>127709791</v>
       </c>
       <c r="B121" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811646</v>
+        <v>811605</v>
       </c>
       <c r="R121" t="n">
-        <v>7390963</v>
+        <v>7391024</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13699,32 +13699,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824753</v>
+        <v>127824782</v>
       </c>
       <c r="B135" t="n">
-        <v>81004</v>
+        <v>92642</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811752</v>
+        <v>811902</v>
       </c>
       <c r="R135" t="n">
-        <v>7390828</v>
+        <v>7390765</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13990,10 +13990,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824782</v>
+        <v>127824739</v>
       </c>
       <c r="B138" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14001,21 +14001,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811902</v>
+        <v>811874</v>
       </c>
       <c r="R138" t="n">
-        <v>7390765</v>
+        <v>7391049</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14184,32 +14184,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824739</v>
+        <v>127824753</v>
       </c>
       <c r="B140" t="n">
-        <v>79053</v>
+        <v>81004</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6434</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811874</v>
+        <v>811752</v>
       </c>
       <c r="R140" t="n">
-        <v>7391049</v>
+        <v>7390828</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14378,32 +14378,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>127824694</v>
+        <v>127824784</v>
       </c>
       <c r="B142" t="n">
-        <v>79618</v>
+        <v>92642</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -14413,10 +14413,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811716</v>
+        <v>811827</v>
       </c>
       <c r="R142" t="n">
-        <v>7390763</v>
+        <v>7390741</v>
       </c>
       <c r="S142" t="n">
         <v>1</v>
@@ -14475,10 +14475,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>127824733</v>
+        <v>127824697</v>
       </c>
       <c r="B143" t="n">
-        <v>92668</v>
+        <v>91352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -14486,21 +14486,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5448</v>
+        <v>1202</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -14510,10 +14510,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811899</v>
+        <v>812064</v>
       </c>
       <c r="R143" t="n">
-        <v>7390756</v>
+        <v>7391153</v>
       </c>
       <c r="S143" t="n">
         <v>1</v>
@@ -14669,10 +14669,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>127824690</v>
+        <v>127824733</v>
       </c>
       <c r="B145" t="n">
-        <v>79647</v>
+        <v>92668</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -14680,21 +14680,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6453</v>
+        <v>5448</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811721</v>
+        <v>811899</v>
       </c>
       <c r="R145" t="n">
-        <v>7390757</v>
+        <v>7390756</v>
       </c>
       <c r="S145" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824697</v>
+        <v>127824694</v>
       </c>
       <c r="B146" t="n">
-        <v>91352</v>
+        <v>79618</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>812064</v>
+        <v>811716</v>
       </c>
       <c r="R146" t="n">
-        <v>7391153</v>
+        <v>7390763</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,32 +14863,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824784</v>
+        <v>127824690</v>
       </c>
       <c r="B147" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811827</v>
+        <v>811721</v>
       </c>
       <c r="R147" t="n">
-        <v>7390741</v>
+        <v>7390757</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -14960,32 +14960,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>127824777</v>
+        <v>127824783</v>
       </c>
       <c r="B148" t="n">
-        <v>82870</v>
+        <v>92642</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -14995,10 +14995,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811935</v>
+        <v>811895</v>
       </c>
       <c r="R148" t="n">
-        <v>7390835</v>
+        <v>7390780</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -15057,32 +15057,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824783</v>
+        <v>127824688</v>
       </c>
       <c r="B149" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811895</v>
+        <v>812058</v>
       </c>
       <c r="R149" t="n">
-        <v>7390780</v>
+        <v>7391223</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824688</v>
+        <v>127824777</v>
       </c>
       <c r="B150" t="n">
-        <v>79647</v>
+        <v>82870</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>812058</v>
+        <v>811935</v>
       </c>
       <c r="R150" t="n">
-        <v>7391223</v>
+        <v>7390835</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -15251,10 +15251,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>127824722</v>
+        <v>127824741</v>
       </c>
       <c r="B151" t="n">
-        <v>56864</v>
+        <v>79053</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15262,38 +15262,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811902</v>
+        <v>812137</v>
       </c>
       <c r="R151" t="n">
-        <v>7390779</v>
+        <v>7391383</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -15326,11 +15322,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-25</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Hittad död under tall där någon ätit den antagligen duvhök.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15357,45 +15348,49 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>127824692</v>
+        <v>127824722</v>
       </c>
       <c r="B152" t="n">
-        <v>79647</v>
+        <v>56864</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P152" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>811721</v>
+        <v>811902</v>
       </c>
       <c r="R152" t="n">
-        <v>7390780</v>
+        <v>7390779</v>
       </c>
       <c r="S152" t="n">
         <v>1</v>
@@ -15428,6 +15423,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-25</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>Hittad död under tall där någon ätit den antagligen duvhök.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -15454,32 +15454,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>127824741</v>
+        <v>127824692</v>
       </c>
       <c r="B153" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>812137</v>
+        <v>811721</v>
       </c>
       <c r="R153" t="n">
-        <v>7391383</v>
+        <v>7390780</v>
       </c>
       <c r="S153" t="n">
         <v>1</v>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127824691</v>
+        <v>127824769</v>
       </c>
       <c r="B154" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>811718</v>
+        <v>811795</v>
       </c>
       <c r="R154" t="n">
-        <v>7390758</v>
+        <v>7390892</v>
       </c>
       <c r="S154" t="n">
         <v>1</v>
@@ -15648,32 +15648,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127824734</v>
+        <v>127824691</v>
       </c>
       <c r="B155" t="n">
-        <v>80161</v>
+        <v>79647</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>812156</v>
+        <v>811718</v>
       </c>
       <c r="R155" t="n">
-        <v>7391361</v>
+        <v>7390758</v>
       </c>
       <c r="S155" t="n">
         <v>1</v>
@@ -15745,32 +15745,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127824769</v>
+        <v>127824734</v>
       </c>
       <c r="B156" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811795</v>
+        <v>812156</v>
       </c>
       <c r="R156" t="n">
-        <v>7390892</v>
+        <v>7391361</v>
       </c>
       <c r="S156" t="n">
         <v>1</v>
@@ -16040,7 +16040,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824761</v>
+        <v>127824760</v>
       </c>
       <c r="B159" t="n">
         <v>79029</v>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811845</v>
+        <v>811882</v>
       </c>
       <c r="R159" t="n">
-        <v>7390977</v>
+        <v>7390983</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16137,7 +16137,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824760</v>
+        <v>127824761</v>
       </c>
       <c r="B160" t="n">
         <v>79029</v>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811882</v>
+        <v>811845</v>
       </c>
       <c r="R160" t="n">
-        <v>7390983</v>
+        <v>7390977</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16331,10 +16331,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824693</v>
+        <v>127824700</v>
       </c>
       <c r="B162" t="n">
-        <v>79618</v>
+        <v>91352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16342,21 +16342,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811874</v>
+        <v>811899</v>
       </c>
       <c r="R162" t="n">
-        <v>7391049</v>
+        <v>7390998</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16428,10 +16428,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>127824700</v>
+        <v>127824693</v>
       </c>
       <c r="B163" t="n">
-        <v>91352</v>
+        <v>79618</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -16439,21 +16439,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -16463,10 +16463,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811899</v>
+        <v>811874</v>
       </c>
       <c r="R163" t="n">
-        <v>7390998</v>
+        <v>7391049</v>
       </c>
       <c r="S163" t="n">
         <v>1</v>
@@ -17010,10 +17010,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127824689</v>
+        <v>127824767</v>
       </c>
       <c r="B169" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17021,21 +17021,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811755</v>
+        <v>811966</v>
       </c>
       <c r="R169" t="n">
-        <v>7390737</v>
+        <v>7390830</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -17107,10 +17107,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127824767</v>
+        <v>127824689</v>
       </c>
       <c r="B170" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17118,21 +17118,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811966</v>
+        <v>811755</v>
       </c>
       <c r="R170" t="n">
-        <v>7390830</v>
+        <v>7390737</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -17592,7 +17592,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127824740</v>
+        <v>127824743</v>
       </c>
       <c r="B175" t="n">
         <v>79053</v>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>812040</v>
+        <v>811966</v>
       </c>
       <c r="R175" t="n">
-        <v>7391193</v>
+        <v>7390830</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -17689,7 +17689,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127824743</v>
+        <v>127824740</v>
       </c>
       <c r="B176" t="n">
         <v>79053</v>
@@ -17724,10 +17724,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811966</v>
+        <v>812040</v>
       </c>
       <c r="R176" t="n">
-        <v>7390830</v>
+        <v>7391193</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -17980,7 +17980,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>127824744</v>
+        <v>127824737</v>
       </c>
       <c r="B179" t="n">
         <v>79053</v>
@@ -18015,10 +18015,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>811924</v>
+        <v>811841</v>
       </c>
       <c r="R179" t="n">
-        <v>7390803</v>
+        <v>7391026</v>
       </c>
       <c r="S179" t="n">
         <v>1</v>
@@ -18077,7 +18077,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>127824737</v>
+        <v>127824742</v>
       </c>
       <c r="B180" t="n">
         <v>79053</v>
@@ -18112,10 +18112,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>811841</v>
+        <v>811875</v>
       </c>
       <c r="R180" t="n">
-        <v>7391026</v>
+        <v>7390951</v>
       </c>
       <c r="S180" t="n">
         <v>1</v>
@@ -18271,7 +18271,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>127824742</v>
+        <v>127824744</v>
       </c>
       <c r="B182" t="n">
         <v>79053</v>
@@ -18306,10 +18306,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>811875</v>
+        <v>811924</v>
       </c>
       <c r="R182" t="n">
-        <v>7390951</v>
+        <v>7390803</v>
       </c>
       <c r="S182" t="n">
         <v>1</v>
@@ -18562,10 +18562,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>127824736</v>
+        <v>127824702</v>
       </c>
       <c r="B185" t="n">
-        <v>57669</v>
+        <v>91352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -18573,21 +18573,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -18597,10 +18597,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>811803</v>
+        <v>811926</v>
       </c>
       <c r="R185" t="n">
-        <v>7390857</v>
+        <v>7390831</v>
       </c>
       <c r="S185" t="n">
         <v>1</v>
@@ -18659,10 +18659,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>127824702</v>
+        <v>127824764</v>
       </c>
       <c r="B186" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -18670,21 +18670,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -18694,10 +18694,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811926</v>
+        <v>811871</v>
       </c>
       <c r="R186" t="n">
-        <v>7390831</v>
+        <v>7390883</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -18756,10 +18756,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>127824686</v>
+        <v>127824736</v>
       </c>
       <c r="B187" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -18767,21 +18767,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -18791,10 +18791,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>811854</v>
+        <v>811803</v>
       </c>
       <c r="R187" t="n">
-        <v>7391042</v>
+        <v>7390857</v>
       </c>
       <c r="S187" t="n">
         <v>1</v>
@@ -18853,10 +18853,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>127824764</v>
+        <v>127824686</v>
       </c>
       <c r="B188" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -18864,21 +18864,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -18888,10 +18888,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>811871</v>
+        <v>811854</v>
       </c>
       <c r="R188" t="n">
-        <v>7390883</v>
+        <v>7391042</v>
       </c>
       <c r="S188" t="n">
         <v>1</v>
@@ -20598,7 +20598,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>127824721</v>
+        <v>127824719</v>
       </c>
       <c r="B205" t="n">
         <v>57672</v>
@@ -20626,11 +20626,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I205" t="inlineStr"/>
       <c r="K205" t="inlineStr"/>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr"/>
@@ -20641,10 +20637,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>811786</v>
+        <v>811824</v>
       </c>
       <c r="R205" t="n">
-        <v>7390835</v>
+        <v>7390745</v>
       </c>
       <c r="S205" t="n">
         <v>1</v>
@@ -20681,7 +20677,7 @@
       </c>
       <c r="AC205" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Älder righack på tall</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -20708,7 +20704,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>127824719</v>
+        <v>127824721</v>
       </c>
       <c r="B206" t="n">
         <v>57672</v>
@@ -20736,7 +20732,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr"/>
@@ -20747,10 +20747,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>811824</v>
+        <v>811786</v>
       </c>
       <c r="R206" t="n">
-        <v>7390745</v>
+        <v>7390835</v>
       </c>
       <c r="S206" t="n">
         <v>1</v>
@@ -20787,7 +20787,7 @@
       </c>
       <c r="AC206" t="inlineStr">
         <is>
-          <t>Älder righack på tall</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -20911,7 +20911,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>127824717</v>
+        <v>127824712</v>
       </c>
       <c r="B208" t="n">
         <v>57672</v>
@@ -20950,10 +20950,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>811898</v>
+        <v>812079</v>
       </c>
       <c r="R208" t="n">
-        <v>7390821</v>
+        <v>7391319</v>
       </c>
       <c r="S208" t="n">
         <v>1</v>
@@ -20990,7 +20990,7 @@
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>Avbarkad klen gran från föregående vinters födosök.</t>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -21017,7 +21017,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>127824712</v>
+        <v>127824717</v>
       </c>
       <c r="B209" t="n">
         <v>57672</v>
@@ -21056,10 +21056,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>812079</v>
+        <v>811898</v>
       </c>
       <c r="R209" t="n">
-        <v>7391319</v>
+        <v>7390821</v>
       </c>
       <c r="S209" t="n">
         <v>1</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="AC209" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall.</t>
+          <t>Avbarkad klen gran från föregående vinters födosök.</t>
         </is>
       </c>
       <c r="AD209" t="b">

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709800</v>
+        <v>127709731</v>
       </c>
       <c r="B21" t="n">
-        <v>92636</v>
+        <v>79053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811725</v>
+        <v>811484</v>
       </c>
       <c r="R21" t="n">
-        <v>7390826</v>
+        <v>7391038</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709797</v>
+        <v>127709800</v>
       </c>
       <c r="B22" t="n">
-        <v>92642</v>
+        <v>92636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811577</v>
+        <v>811725</v>
       </c>
       <c r="R22" t="n">
-        <v>7391006</v>
+        <v>7390826</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,48 +2738,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709725</v>
+        <v>127709797</v>
       </c>
       <c r="B23" t="n">
-        <v>92646</v>
+        <v>92642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811692</v>
+        <v>811577</v>
       </c>
       <c r="R23" t="n">
-        <v>7390871</v>
+        <v>7391006</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2820,7 +2817,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2839,45 +2835,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709698</v>
+        <v>127709725</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>92646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811656</v>
+        <v>811692</v>
       </c>
       <c r="R24" t="n">
-        <v>7390942</v>
+        <v>7390871</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2918,6 +2917,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709731</v>
+        <v>127709698</v>
       </c>
       <c r="B25" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811484</v>
+        <v>811656</v>
       </c>
       <c r="R25" t="n">
-        <v>7391038</v>
+        <v>7390942</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709768</v>
+        <v>127709780</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811776</v>
+        <v>811475</v>
       </c>
       <c r="R37" t="n">
-        <v>7390918</v>
+        <v>7391196</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709766</v>
+        <v>127709708</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,34 +4209,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811730</v>
+        <v>811580</v>
       </c>
       <c r="R38" t="n">
-        <v>7390914</v>
+        <v>7391090</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4271,6 +4279,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4288,17 +4301,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709756</v>
+        <v>127709768</v>
       </c>
       <c r="B39" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4319,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4343,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811538</v>
+        <v>811776</v>
       </c>
       <c r="R39" t="n">
-        <v>7391022</v>
+        <v>7390918</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4392,10 +4405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709708</v>
+        <v>127709766</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,42 +4416,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811580</v>
+        <v>811730</v>
       </c>
       <c r="R40" t="n">
-        <v>7391090</v>
+        <v>7390914</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4473,11 +4478,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4495,39 +4495,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709780</v>
+        <v>127709756</v>
       </c>
       <c r="B41" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811475</v>
+        <v>811538</v>
       </c>
       <c r="R41" t="n">
-        <v>7391196</v>
+        <v>7391022</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5393,32 +5393,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127709793</v>
+        <v>127709749</v>
       </c>
       <c r="B50" t="n">
-        <v>92642</v>
+        <v>81004</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811612</v>
+        <v>811750</v>
       </c>
       <c r="R50" t="n">
-        <v>7391041</v>
+        <v>7390835</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127709749</v>
+        <v>127709753</v>
       </c>
       <c r="B51" t="n">
-        <v>81004</v>
+        <v>78787</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811750</v>
+        <v>811385</v>
       </c>
       <c r="R51" t="n">
-        <v>7390835</v>
+        <v>7391163</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5587,32 +5587,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709753</v>
+        <v>127709793</v>
       </c>
       <c r="B52" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811385</v>
+        <v>811612</v>
       </c>
       <c r="R52" t="n">
-        <v>7391163</v>
+        <v>7391041</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B80" t="n">
-        <v>92835</v>
+        <v>91648</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R80" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,44 +8427,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709755</v>
+        <v>127709760</v>
       </c>
       <c r="B81" t="n">
-        <v>78787</v>
+        <v>91513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811542</v>
+        <v>811582</v>
       </c>
       <c r="R81" t="n">
-        <v>7391054</v>
+        <v>7391002</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127706918</v>
+        <v>127709738</v>
       </c>
       <c r="B82" t="n">
-        <v>91648</v>
+        <v>92835</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811451</v>
+        <v>811577</v>
       </c>
       <c r="R82" t="n">
-        <v>7391161</v>
+        <v>7391006</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8621,60 +8621,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127709760</v>
+        <v>127706931</v>
       </c>
       <c r="B83" t="n">
-        <v>91513</v>
+        <v>92642</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811582</v>
+        <v>811711</v>
       </c>
       <c r="R83" t="n">
-        <v>7391002</v>
+        <v>7390853</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8718,60 +8718,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127706931</v>
+        <v>127709755</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811711</v>
+        <v>811542</v>
       </c>
       <c r="R84" t="n">
-        <v>7390853</v>
+        <v>7391054</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8815,12 +8815,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -13699,32 +13699,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824782</v>
+        <v>127824753</v>
       </c>
       <c r="B135" t="n">
-        <v>92642</v>
+        <v>81004</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811902</v>
+        <v>811752</v>
       </c>
       <c r="R135" t="n">
-        <v>7390765</v>
+        <v>7390828</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13796,32 +13796,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127824703</v>
+        <v>127824782</v>
       </c>
       <c r="B136" t="n">
-        <v>91352</v>
+        <v>92642</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811762</v>
+        <v>811902</v>
       </c>
       <c r="R136" t="n">
-        <v>7390826</v>
+        <v>7390765</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -13893,10 +13893,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127824775</v>
+        <v>127824703</v>
       </c>
       <c r="B137" t="n">
-        <v>82870</v>
+        <v>91352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13904,21 +13904,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>811886</v>
+        <v>811762</v>
       </c>
       <c r="R137" t="n">
-        <v>7390941</v>
+        <v>7390826</v>
       </c>
       <c r="S137" t="n">
         <v>1</v>
@@ -13990,32 +13990,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824739</v>
+        <v>127824775</v>
       </c>
       <c r="B138" t="n">
-        <v>79053</v>
+        <v>82870</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811874</v>
+        <v>811886</v>
       </c>
       <c r="R138" t="n">
-        <v>7391049</v>
+        <v>7390941</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14087,7 +14087,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127824747</v>
+        <v>127824739</v>
       </c>
       <c r="B139" t="n">
         <v>79053</v>
@@ -14122,10 +14122,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811803</v>
+        <v>811874</v>
       </c>
       <c r="R139" t="n">
-        <v>7390886</v>
+        <v>7391049</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -14184,32 +14184,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824753</v>
+        <v>127824747</v>
       </c>
       <c r="B140" t="n">
-        <v>81004</v>
+        <v>79053</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1049</v>
+        <v>6434</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811752</v>
+        <v>811803</v>
       </c>
       <c r="R140" t="n">
-        <v>7390828</v>
+        <v>7390886</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824725</v>
+        <v>127824694</v>
       </c>
       <c r="B141" t="n">
-        <v>57832</v>
+        <v>79618</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811800</v>
+        <v>811716</v>
       </c>
       <c r="R141" t="n">
-        <v>7390892</v>
+        <v>7390763</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824694</v>
+        <v>127824690</v>
       </c>
       <c r="B146" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811716</v>
+        <v>811721</v>
       </c>
       <c r="R146" t="n">
-        <v>7390763</v>
+        <v>7390757</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824690</v>
+        <v>127824725</v>
       </c>
       <c r="B147" t="n">
-        <v>79647</v>
+        <v>57832</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14874,21 +14874,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811721</v>
+        <v>811800</v>
       </c>
       <c r="R147" t="n">
-        <v>7390757</v>
+        <v>7390892</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15057,10 +15057,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824688</v>
+        <v>127824777</v>
       </c>
       <c r="B149" t="n">
-        <v>79647</v>
+        <v>82870</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15068,21 +15068,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>812058</v>
+        <v>811935</v>
       </c>
       <c r="R149" t="n">
-        <v>7391223</v>
+        <v>7390835</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824777</v>
+        <v>127824688</v>
       </c>
       <c r="B150" t="n">
-        <v>82870</v>
+        <v>79647</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811935</v>
+        <v>812058</v>
       </c>
       <c r="R150" t="n">
-        <v>7390835</v>
+        <v>7391223</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824760</v>
+        <v>127824700</v>
       </c>
       <c r="B159" t="n">
-        <v>79029</v>
+        <v>91352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811882</v>
+        <v>811899</v>
       </c>
       <c r="R159" t="n">
-        <v>7390983</v>
+        <v>7390998</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16137,7 +16137,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824761</v>
+        <v>127824760</v>
       </c>
       <c r="B160" t="n">
         <v>79029</v>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811845</v>
+        <v>811882</v>
       </c>
       <c r="R160" t="n">
-        <v>7390977</v>
+        <v>7390983</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16234,10 +16234,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824718</v>
+        <v>127824761</v>
       </c>
       <c r="B161" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16245,21 +16245,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16269,10 +16269,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811915</v>
+        <v>811845</v>
       </c>
       <c r="R161" t="n">
-        <v>7390765</v>
+        <v>7390977</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16331,10 +16331,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824700</v>
+        <v>127824718</v>
       </c>
       <c r="B162" t="n">
-        <v>91352</v>
+        <v>57672</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16342,21 +16342,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811899</v>
+        <v>811915</v>
       </c>
       <c r="R162" t="n">
-        <v>7390998</v>
+        <v>7390765</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16913,32 +16913,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127824781</v>
+        <v>127824689</v>
       </c>
       <c r="B168" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811927</v>
+        <v>811755</v>
       </c>
       <c r="R168" t="n">
-        <v>7390809</v>
+        <v>7390737</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -17010,32 +17010,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127824767</v>
+        <v>127824781</v>
       </c>
       <c r="B169" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811966</v>
+        <v>811927</v>
       </c>
       <c r="R169" t="n">
-        <v>7390830</v>
+        <v>7390809</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -17107,10 +17107,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127824689</v>
+        <v>127824767</v>
       </c>
       <c r="B170" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17118,21 +17118,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811755</v>
+        <v>811966</v>
       </c>
       <c r="R170" t="n">
-        <v>7390737</v>
+        <v>7390830</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824778</v>
+        <v>127824765</v>
       </c>
       <c r="B171" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17215,21 +17215,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811927</v>
+        <v>811918</v>
       </c>
       <c r="R171" t="n">
-        <v>7390802</v>
+        <v>7390852</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,10 +17301,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824772</v>
+        <v>127824759</v>
       </c>
       <c r="B172" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17312,21 +17312,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>812010</v>
+        <v>811950</v>
       </c>
       <c r="R172" t="n">
-        <v>7391123</v>
+        <v>7391109</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B173" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R173" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824759</v>
+        <v>127824772</v>
       </c>
       <c r="B174" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17506,21 +17506,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811950</v>
+        <v>812010</v>
       </c>
       <c r="R174" t="n">
-        <v>7391109</v>
+        <v>7391123</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127824770</v>
+        <v>127824774</v>
       </c>
       <c r="B189" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18961,21 +18961,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18985,10 +18985,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811800</v>
+        <v>811971</v>
       </c>
       <c r="R189" t="n">
-        <v>7390865</v>
+        <v>7391094</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -19047,32 +19047,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127824745</v>
+        <v>127824773</v>
       </c>
       <c r="B190" t="n">
-        <v>79053</v>
+        <v>82870</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>811913</v>
+        <v>811989</v>
       </c>
       <c r="R190" t="n">
-        <v>7390816</v>
+        <v>7391103</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -19144,10 +19144,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127824774</v>
+        <v>127824770</v>
       </c>
       <c r="B191" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19155,21 +19155,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811971</v>
+        <v>811800</v>
       </c>
       <c r="R191" t="n">
-        <v>7391094</v>
+        <v>7390865</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -19241,32 +19241,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824773</v>
+        <v>127824745</v>
       </c>
       <c r="B192" t="n">
-        <v>82870</v>
+        <v>79053</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811989</v>
+        <v>811913</v>
       </c>
       <c r="R192" t="n">
-        <v>7391103</v>
+        <v>7390816</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127709784</v>
+        <v>127706926</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811414</v>
+        <v>811754</v>
       </c>
       <c r="R2" t="n">
-        <v>7391125</v>
+        <v>7390851</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127706926</v>
+        <v>127709734</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811754</v>
+        <v>811573</v>
       </c>
       <c r="R3" t="n">
-        <v>7390851</v>
+        <v>7391001</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709763</v>
+        <v>127709784</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811692</v>
+        <v>811414</v>
       </c>
       <c r="R4" t="n">
-        <v>7390815</v>
+        <v>7391125</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709734</v>
+        <v>127709763</v>
       </c>
       <c r="B5" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811573</v>
+        <v>811692</v>
       </c>
       <c r="R5" t="n">
-        <v>7391001</v>
+        <v>7390815</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709731</v>
+        <v>127709800</v>
       </c>
       <c r="B21" t="n">
-        <v>79053</v>
+        <v>92636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811484</v>
+        <v>811725</v>
       </c>
       <c r="R21" t="n">
-        <v>7391038</v>
+        <v>7390826</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709800</v>
+        <v>127709797</v>
       </c>
       <c r="B22" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811725</v>
+        <v>811577</v>
       </c>
       <c r="R22" t="n">
-        <v>7390826</v>
+        <v>7391006</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,45 +2738,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709797</v>
+        <v>127709725</v>
       </c>
       <c r="B23" t="n">
-        <v>92642</v>
+        <v>92646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811577</v>
+        <v>811692</v>
       </c>
       <c r="R23" t="n">
-        <v>7391006</v>
+        <v>7390871</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2817,6 +2820,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2835,48 +2839,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709725</v>
+        <v>127709698</v>
       </c>
       <c r="B24" t="n">
-        <v>92646</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811692</v>
+        <v>811656</v>
       </c>
       <c r="R24" t="n">
-        <v>7390871</v>
+        <v>7390942</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2917,7 +2918,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709698</v>
+        <v>127709731</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811656</v>
+        <v>811484</v>
       </c>
       <c r="R25" t="n">
-        <v>7390942</v>
+        <v>7391038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127706918</v>
+        <v>127709738</v>
       </c>
       <c r="B80" t="n">
-        <v>91648</v>
+        <v>92835</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>658</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811451</v>
+        <v>811577</v>
       </c>
       <c r="R80" t="n">
-        <v>7391161</v>
+        <v>7391006</v>
       </c>
       <c r="S80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,44 +8427,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709760</v>
+        <v>127709755</v>
       </c>
       <c r="B81" t="n">
-        <v>91513</v>
+        <v>78787</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811582</v>
+        <v>811542</v>
       </c>
       <c r="R81" t="n">
-        <v>7391002</v>
+        <v>7391054</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8536,10 +8536,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B82" t="n">
-        <v>92835</v>
+        <v>91648</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8547,37 +8547,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R82" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8621,60 +8621,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127706931</v>
+        <v>127709760</v>
       </c>
       <c r="B83" t="n">
-        <v>92642</v>
+        <v>91513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811711</v>
+        <v>811582</v>
       </c>
       <c r="R83" t="n">
-        <v>7390853</v>
+        <v>7391002</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8718,60 +8718,60 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127709755</v>
+        <v>127706931</v>
       </c>
       <c r="B84" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811542</v>
+        <v>811711</v>
       </c>
       <c r="R84" t="n">
-        <v>7391054</v>
+        <v>7390853</v>
       </c>
       <c r="S84" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8815,12 +8815,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9312,32 +9312,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127709728</v>
+        <v>127709775</v>
       </c>
       <c r="B90" t="n">
-        <v>79053</v>
+        <v>78696</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811385</v>
+        <v>811544</v>
       </c>
       <c r="R90" t="n">
-        <v>7391153</v>
+        <v>7391011</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709775</v>
+        <v>127706916</v>
       </c>
       <c r="B91" t="n">
-        <v>78696</v>
+        <v>90387</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9420,37 +9420,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811544</v>
+        <v>811652</v>
       </c>
       <c r="R91" t="n">
-        <v>7391011</v>
+        <v>7390945</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9494,60 +9494,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127706916</v>
+        <v>127709777</v>
       </c>
       <c r="B92" t="n">
-        <v>90387</v>
+        <v>92642</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811652</v>
+        <v>811696</v>
       </c>
       <c r="R92" t="n">
-        <v>7390945</v>
+        <v>7390929</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,22 +9591,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709777</v>
+        <v>127709728</v>
       </c>
       <c r="B93" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811696</v>
+        <v>811385</v>
       </c>
       <c r="R93" t="n">
-        <v>7390929</v>
+        <v>7391153</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709693</v>
+        <v>127709795</v>
       </c>
       <c r="B96" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811486</v>
+        <v>811676</v>
       </c>
       <c r="R96" t="n">
-        <v>7391112</v>
+        <v>7391004</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,45 +9991,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709795</v>
+        <v>127709799</v>
       </c>
       <c r="B97" t="n">
-        <v>92642</v>
+        <v>92636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811676</v>
+        <v>811707</v>
       </c>
       <c r="R97" t="n">
-        <v>7391004</v>
+        <v>7390860</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10070,6 +10074,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10088,49 +10093,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709799</v>
+        <v>127709783</v>
       </c>
       <c r="B98" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811707</v>
+        <v>811387</v>
       </c>
       <c r="R98" t="n">
-        <v>7390860</v>
+        <v>7391146</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10171,7 +10172,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10190,32 +10190,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709783</v>
+        <v>127709693</v>
       </c>
       <c r="B99" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811387</v>
+        <v>811486</v>
       </c>
       <c r="R99" t="n">
-        <v>7391146</v>
+        <v>7391112</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -10384,48 +10384,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127706920</v>
+        <v>127709747</v>
       </c>
       <c r="B101" t="n">
-        <v>92835</v>
+        <v>57776</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2079</v>
+        <v>103031</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811552</v>
+        <v>811653</v>
       </c>
       <c r="R101" t="n">
-        <v>7391002</v>
+        <v>7390948</v>
       </c>
       <c r="S101" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,22 +10469,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127709785</v>
+        <v>127706924</v>
       </c>
       <c r="B102" t="n">
-        <v>92642</v>
+        <v>58042</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10492,37 +10492,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>103015</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811504</v>
+        <v>811422</v>
       </c>
       <c r="R102" t="n">
-        <v>7391047</v>
+        <v>7391139</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10566,60 +10566,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127709787</v>
+        <v>127706920</v>
       </c>
       <c r="B103" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811677</v>
+        <v>811552</v>
       </c>
       <c r="R103" t="n">
-        <v>7390878</v>
+        <v>7391002</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10663,22 +10663,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127709733</v>
+        <v>127709785</v>
       </c>
       <c r="B104" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10686,21 +10686,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811530</v>
+        <v>811504</v>
       </c>
       <c r="R104" t="n">
-        <v>7391016</v>
+        <v>7391047</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10772,32 +10772,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709770</v>
+        <v>127709787</v>
       </c>
       <c r="B105" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811608</v>
+        <v>811677</v>
       </c>
       <c r="R105" t="n">
-        <v>7391004</v>
+        <v>7390878</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10869,45 +10869,48 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709729</v>
+        <v>127709727</v>
       </c>
       <c r="B106" t="n">
-        <v>79053</v>
+        <v>92646</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6434</v>
+        <v>4365</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811434</v>
+        <v>811545</v>
       </c>
       <c r="R106" t="n">
-        <v>7391048</v>
+        <v>7391008</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10948,6 +10951,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10966,32 +10970,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709764</v>
+        <v>127709733</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11001,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811498</v>
+        <v>811530</v>
       </c>
       <c r="R107" t="n">
-        <v>7391103</v>
+        <v>7391016</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11063,32 +11067,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709747</v>
+        <v>127709770</v>
       </c>
       <c r="B108" t="n">
-        <v>57776</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11098,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811653</v>
+        <v>811608</v>
       </c>
       <c r="R108" t="n">
-        <v>7390948</v>
+        <v>7391004</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11160,48 +11164,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709727</v>
+        <v>127709729</v>
       </c>
       <c r="B109" t="n">
-        <v>92646</v>
+        <v>79053</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811545</v>
+        <v>811434</v>
       </c>
       <c r="R109" t="n">
-        <v>7391008</v>
+        <v>7391048</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11242,7 +11243,6 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11261,48 +11261,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127706924</v>
+        <v>127709764</v>
       </c>
       <c r="B110" t="n">
-        <v>58042</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811422</v>
+        <v>811498</v>
       </c>
       <c r="R110" t="n">
-        <v>7391139</v>
+        <v>7391103</v>
       </c>
       <c r="S110" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11346,22 +11346,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709697</v>
+        <v>127709720</v>
       </c>
       <c r="B111" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811625</v>
+        <v>811515</v>
       </c>
       <c r="R111" t="n">
-        <v>7390969</v>
+        <v>7391165</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709720</v>
+        <v>127709801</v>
       </c>
       <c r="B112" t="n">
-        <v>57669</v>
+        <v>92636</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811515</v>
+        <v>811615</v>
       </c>
       <c r="R112" t="n">
-        <v>7391165</v>
+        <v>7390990</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,53 +11552,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709707</v>
+        <v>127709726</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>92646</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>4365</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811874</v>
+        <v>811638</v>
       </c>
       <c r="R113" t="n">
-        <v>7390830</v>
+        <v>7391044</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11633,11 +11625,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -11655,17 +11642,17 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127709801</v>
+        <v>127709697</v>
       </c>
       <c r="B114" t="n">
-        <v>92636</v>
+        <v>79647</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11673,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11697,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811615</v>
+        <v>811625</v>
       </c>
       <c r="R114" t="n">
-        <v>7390990</v>
+        <v>7390969</v>
       </c>
       <c r="S114" t="n">
         <v>5</v>
@@ -11759,32 +11746,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709726</v>
+        <v>127709804</v>
       </c>
       <c r="B115" t="n">
-        <v>92646</v>
+        <v>78435</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11794,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811638</v>
+        <v>811452</v>
       </c>
       <c r="R115" t="n">
-        <v>7391044</v>
+        <v>7391056</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -11856,10 +11843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127709804</v>
+        <v>127709707</v>
       </c>
       <c r="B116" t="n">
-        <v>78435</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11867,34 +11854,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811452</v>
+        <v>811874</v>
       </c>
       <c r="R116" t="n">
-        <v>7391056</v>
+        <v>7390830</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -11929,6 +11924,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -11946,39 +11946,39 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709732</v>
+        <v>127709776</v>
       </c>
       <c r="B117" t="n">
-        <v>79053</v>
+        <v>78696</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811523</v>
+        <v>811646</v>
       </c>
       <c r="R117" t="n">
-        <v>7391024</v>
+        <v>7390963</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709765</v>
+        <v>127709778</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811478</v>
+        <v>811683</v>
       </c>
       <c r="R118" t="n">
-        <v>7391172</v>
+        <v>7390938</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709776</v>
+        <v>127709791</v>
       </c>
       <c r="B119" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811646</v>
+        <v>811605</v>
       </c>
       <c r="R119" t="n">
-        <v>7390963</v>
+        <v>7391024</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,10 +12244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709778</v>
+        <v>127709732</v>
       </c>
       <c r="B120" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12255,21 +12255,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811683</v>
+        <v>811523</v>
       </c>
       <c r="R120" t="n">
-        <v>7390938</v>
+        <v>7391024</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,32 +12341,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709791</v>
+        <v>127709765</v>
       </c>
       <c r="B121" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811605</v>
+        <v>811478</v>
       </c>
       <c r="R121" t="n">
-        <v>7391024</v>
+        <v>7391172</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13214,27 +13214,27 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824735</v>
+        <v>127824751</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>57776</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811831</v>
+        <v>812037</v>
       </c>
       <c r="R130" t="n">
-        <v>7390950</v>
+        <v>7391151</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,27 +13311,27 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824751</v>
+        <v>127824735</v>
       </c>
       <c r="B131" t="n">
-        <v>57776</v>
+        <v>57669</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>812037</v>
+        <v>811831</v>
       </c>
       <c r="R131" t="n">
-        <v>7391151</v>
+        <v>7390950</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127824769</v>
+        <v>127824691</v>
       </c>
       <c r="B154" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>811795</v>
+        <v>811718</v>
       </c>
       <c r="R154" t="n">
-        <v>7390892</v>
+        <v>7390758</v>
       </c>
       <c r="S154" t="n">
         <v>1</v>
@@ -15648,32 +15648,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127824691</v>
+        <v>127824734</v>
       </c>
       <c r="B155" t="n">
-        <v>79647</v>
+        <v>80161</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>811718</v>
+        <v>812156</v>
       </c>
       <c r="R155" t="n">
-        <v>7390758</v>
+        <v>7391361</v>
       </c>
       <c r="S155" t="n">
         <v>1</v>
@@ -15745,32 +15745,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127824734</v>
+        <v>127824769</v>
       </c>
       <c r="B156" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>812156</v>
+        <v>811795</v>
       </c>
       <c r="R156" t="n">
-        <v>7391361</v>
+        <v>7390892</v>
       </c>
       <c r="S156" t="n">
         <v>1</v>
@@ -16040,10 +16040,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>127824700</v>
+        <v>127824760</v>
       </c>
       <c r="B159" t="n">
-        <v>91352</v>
+        <v>79029</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16051,21 +16051,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16075,10 +16075,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811899</v>
+        <v>811882</v>
       </c>
       <c r="R159" t="n">
-        <v>7390998</v>
+        <v>7390983</v>
       </c>
       <c r="S159" t="n">
         <v>1</v>
@@ -16137,7 +16137,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>127824760</v>
+        <v>127824761</v>
       </c>
       <c r="B160" t="n">
         <v>79029</v>
@@ -16172,10 +16172,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811882</v>
+        <v>811845</v>
       </c>
       <c r="R160" t="n">
-        <v>7390983</v>
+        <v>7390977</v>
       </c>
       <c r="S160" t="n">
         <v>1</v>
@@ -16234,10 +16234,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>127824761</v>
+        <v>127824718</v>
       </c>
       <c r="B161" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16245,21 +16245,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16269,10 +16269,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811845</v>
+        <v>811915</v>
       </c>
       <c r="R161" t="n">
-        <v>7390977</v>
+        <v>7390765</v>
       </c>
       <c r="S161" t="n">
         <v>1</v>
@@ -16331,10 +16331,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>127824718</v>
+        <v>127824700</v>
       </c>
       <c r="B162" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16342,21 +16342,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16366,10 +16366,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811915</v>
+        <v>811899</v>
       </c>
       <c r="R162" t="n">
-        <v>7390765</v>
+        <v>7390998</v>
       </c>
       <c r="S162" t="n">
         <v>1</v>
@@ -16913,32 +16913,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127824689</v>
+        <v>127824781</v>
       </c>
       <c r="B168" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811755</v>
+        <v>811927</v>
       </c>
       <c r="R168" t="n">
-        <v>7390737</v>
+        <v>7390809</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -17010,32 +17010,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127824781</v>
+        <v>127824767</v>
       </c>
       <c r="B169" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811927</v>
+        <v>811966</v>
       </c>
       <c r="R169" t="n">
-        <v>7390809</v>
+        <v>7390830</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -17107,10 +17107,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127824767</v>
+        <v>127824689</v>
       </c>
       <c r="B170" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17118,21 +17118,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811966</v>
+        <v>811755</v>
       </c>
       <c r="R170" t="n">
-        <v>7390830</v>
+        <v>7390737</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B171" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17215,21 +17215,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R171" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,10 +17301,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824759</v>
+        <v>127824772</v>
       </c>
       <c r="B172" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17312,21 +17312,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811950</v>
+        <v>812010</v>
       </c>
       <c r="R172" t="n">
-        <v>7391109</v>
+        <v>7391123</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824778</v>
+        <v>127824765</v>
       </c>
       <c r="B173" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811927</v>
+        <v>811918</v>
       </c>
       <c r="R173" t="n">
-        <v>7390802</v>
+        <v>7390852</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824772</v>
+        <v>127824759</v>
       </c>
       <c r="B174" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17506,21 +17506,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>812010</v>
+        <v>811950</v>
       </c>
       <c r="R174" t="n">
-        <v>7391123</v>
+        <v>7391109</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -17592,10 +17592,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127824743</v>
+        <v>127824752</v>
       </c>
       <c r="B175" t="n">
-        <v>79053</v>
+        <v>58042</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17603,21 +17603,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>811966</v>
+        <v>812063</v>
       </c>
       <c r="R175" t="n">
-        <v>7390830</v>
+        <v>7391237</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -17689,7 +17689,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127824740</v>
+        <v>127824743</v>
       </c>
       <c r="B176" t="n">
         <v>79053</v>
@@ -17724,10 +17724,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>812040</v>
+        <v>811966</v>
       </c>
       <c r="R176" t="n">
-        <v>7391193</v>
+        <v>7390830</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -17786,10 +17786,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127824752</v>
+        <v>127824740</v>
       </c>
       <c r="B177" t="n">
-        <v>58042</v>
+        <v>79053</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17797,21 +17797,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17821,10 +17821,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>812063</v>
+        <v>812040</v>
       </c>
       <c r="R177" t="n">
-        <v>7391237</v>
+        <v>7391193</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709774</v>
+        <v>127709721</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
+        <v>57669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811658</v>
+        <v>811493</v>
       </c>
       <c r="R6" t="n">
-        <v>7390945</v>
+        <v>7391183</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127706928</v>
+        <v>127709781</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811509</v>
+        <v>811479</v>
       </c>
       <c r="R7" t="n">
-        <v>7391152</v>
+        <v>7391142</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127709721</v>
+        <v>127706928</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811493</v>
+        <v>811509</v>
       </c>
       <c r="R8" t="n">
-        <v>7391183</v>
+        <v>7391152</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127709781</v>
+        <v>127709774</v>
       </c>
       <c r="B9" t="n">
-        <v>92642</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811479</v>
+        <v>811658</v>
       </c>
       <c r="R9" t="n">
-        <v>7391142</v>
+        <v>7390945</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127709710</v>
+        <v>127706921</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,45 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811505</v>
+        <v>811722</v>
       </c>
       <c r="R10" t="n">
-        <v>7391045</v>
+        <v>7390955</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1530,11 +1522,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1549,44 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706915</v>
+        <v>127706923</v>
       </c>
       <c r="B11" t="n">
-        <v>58531</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208249</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1596,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811694</v>
+        <v>811648</v>
       </c>
       <c r="R11" t="n">
-        <v>7390899</v>
+        <v>7390971</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1658,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127706921</v>
+        <v>127709710</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,37 +1656,45 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811722</v>
+        <v>811505</v>
       </c>
       <c r="R12" t="n">
-        <v>7390955</v>
+        <v>7391045</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1729,6 +1724,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,44 +1743,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127706923</v>
+        <v>127706915</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>58531</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811648</v>
+        <v>811694</v>
       </c>
       <c r="R13" t="n">
-        <v>7390971</v>
+        <v>7390899</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709694</v>
+        <v>127706925</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811441</v>
+        <v>811866</v>
       </c>
       <c r="R14" t="n">
-        <v>7391158</v>
+        <v>7390863</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,19 +1937,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127706914</v>
+        <v>127709694</v>
       </c>
       <c r="B15" t="n">
         <v>79647</v>
@@ -1980,17 +1980,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811645</v>
+        <v>811441</v>
       </c>
       <c r="R15" t="n">
-        <v>7390971</v>
+        <v>7391158</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,19 +2034,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127709695</v>
+        <v>127706914</v>
       </c>
       <c r="B16" t="n">
         <v>79647</v>
@@ -2077,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811430</v>
+        <v>811645</v>
       </c>
       <c r="R16" t="n">
-        <v>7391046</v>
+        <v>7390971</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709699</v>
+        <v>127709695</v>
       </c>
       <c r="B17" t="n">
         <v>79647</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811707</v>
+        <v>811430</v>
       </c>
       <c r="R17" t="n">
-        <v>7390941</v>
+        <v>7391046</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127706925</v>
+        <v>127709699</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811866</v>
+        <v>811707</v>
       </c>
       <c r="R18" t="n">
-        <v>7390863</v>
+        <v>7390941</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709800</v>
+        <v>127709731</v>
       </c>
       <c r="B21" t="n">
-        <v>92636</v>
+        <v>79053</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811725</v>
+        <v>811484</v>
       </c>
       <c r="R21" t="n">
-        <v>7390826</v>
+        <v>7391038</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709797</v>
+        <v>127709800</v>
       </c>
       <c r="B22" t="n">
-        <v>92642</v>
+        <v>92636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811577</v>
+        <v>811725</v>
       </c>
       <c r="R22" t="n">
-        <v>7391006</v>
+        <v>7390826</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,48 +2738,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709725</v>
+        <v>127709797</v>
       </c>
       <c r="B23" t="n">
-        <v>92646</v>
+        <v>92642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811692</v>
+        <v>811577</v>
       </c>
       <c r="R23" t="n">
-        <v>7390871</v>
+        <v>7391006</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2820,7 +2817,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2839,45 +2835,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709698</v>
+        <v>127709725</v>
       </c>
       <c r="B24" t="n">
-        <v>79647</v>
+        <v>92646</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811656</v>
+        <v>811692</v>
       </c>
       <c r="R24" t="n">
-        <v>7390942</v>
+        <v>7390871</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2918,6 +2917,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709731</v>
+        <v>127709698</v>
       </c>
       <c r="B25" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811484</v>
+        <v>811656</v>
       </c>
       <c r="R25" t="n">
-        <v>7391038</v>
+        <v>7390942</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709780</v>
+        <v>127709768</v>
       </c>
       <c r="B37" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811475</v>
+        <v>811776</v>
       </c>
       <c r="R37" t="n">
-        <v>7391196</v>
+        <v>7390918</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709708</v>
+        <v>127709766</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,42 +4209,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811580</v>
+        <v>811730</v>
       </c>
       <c r="R38" t="n">
-        <v>7391090</v>
+        <v>7390914</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4279,11 +4271,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4301,17 +4288,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709768</v>
+        <v>127709756</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4319,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4343,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811776</v>
+        <v>811538</v>
       </c>
       <c r="R39" t="n">
-        <v>7390918</v>
+        <v>7391022</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4405,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709766</v>
+        <v>127709708</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4416,34 +4403,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811730</v>
+        <v>811580</v>
       </c>
       <c r="R40" t="n">
-        <v>7390914</v>
+        <v>7391090</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4478,6 +4473,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4495,39 +4495,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709756</v>
+        <v>127709780</v>
       </c>
       <c r="B41" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811538</v>
+        <v>811475</v>
       </c>
       <c r="R41" t="n">
-        <v>7391022</v>
+        <v>7391196</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5781,45 +5781,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127709792</v>
+        <v>127709713</v>
       </c>
       <c r="B54" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811619</v>
+        <v>811514</v>
       </c>
       <c r="R54" t="n">
-        <v>7391036</v>
+        <v>7391024</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5854,6 +5862,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5871,17 +5884,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709702</v>
+        <v>127709711</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,34 +5902,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811715</v>
+        <v>811535</v>
       </c>
       <c r="R55" t="n">
-        <v>7391028</v>
+        <v>7391056</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5951,6 +5972,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5968,17 +5994,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709692</v>
+        <v>127706919</v>
       </c>
       <c r="B56" t="n">
-        <v>79647</v>
+        <v>92835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,37 +6012,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811591</v>
+        <v>811446</v>
       </c>
       <c r="R56" t="n">
-        <v>7391072</v>
+        <v>7391045</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6060,60 +6086,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127706919</v>
+        <v>127709792</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811446</v>
+        <v>811619</v>
       </c>
       <c r="R57" t="n">
-        <v>7391045</v>
+        <v>7391036</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6157,44 +6183,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709717</v>
+        <v>127709702</v>
       </c>
       <c r="B58" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6230,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811625</v>
+        <v>811715</v>
       </c>
       <c r="R58" t="n">
-        <v>7390984</v>
+        <v>7391028</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6266,10 +6292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127706933</v>
+        <v>127709692</v>
       </c>
       <c r="B59" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,37 +6303,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811536</v>
+        <v>811591</v>
       </c>
       <c r="R59" t="n">
-        <v>7391018</v>
+        <v>7391072</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6351,44 +6377,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709771</v>
+        <v>127709717</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6424,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811735</v>
+        <v>811625</v>
       </c>
       <c r="R60" t="n">
-        <v>7391006</v>
+        <v>7390984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6460,10 +6486,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709713</v>
+        <v>127706933</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>78435</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6471,45 +6497,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811514</v>
+        <v>811536</v>
       </c>
       <c r="R61" t="n">
-        <v>7391024</v>
+        <v>7391018</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6539,11 +6557,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6558,22 +6571,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709711</v>
+        <v>127709771</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6581,42 +6594,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811535</v>
+        <v>811735</v>
       </c>
       <c r="R62" t="n">
-        <v>7391056</v>
+        <v>7391006</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6651,11 +6656,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7165,45 +7165,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709798</v>
+        <v>127709705</v>
       </c>
       <c r="B68" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811676</v>
+        <v>811705</v>
       </c>
       <c r="R68" t="n">
-        <v>7390933</v>
+        <v>7390855</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7238,6 +7246,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7255,55 +7268,55 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709803</v>
+        <v>127706913</v>
       </c>
       <c r="B69" t="n">
-        <v>78435</v>
+        <v>91317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811716</v>
+        <v>811507</v>
       </c>
       <c r="R69" t="n">
-        <v>7390831</v>
+        <v>7391034</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7347,22 +7360,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709724</v>
+        <v>127709700</v>
       </c>
       <c r="B70" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7370,21 +7383,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7394,10 +7407,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811533</v>
+        <v>811687</v>
       </c>
       <c r="R70" t="n">
-        <v>7391035</v>
+        <v>7390967</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7456,53 +7469,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709705</v>
+        <v>127709798</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>79053</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811705</v>
+        <v>811676</v>
       </c>
       <c r="R71" t="n">
-        <v>7390855</v>
+        <v>7390933</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7537,11 +7542,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7559,55 +7559,55 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127706913</v>
+        <v>127709803</v>
       </c>
       <c r="B72" t="n">
-        <v>91317</v>
+        <v>78435</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811507</v>
+        <v>811716</v>
       </c>
       <c r="R72" t="n">
-        <v>7391034</v>
+        <v>7390831</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7651,22 +7651,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709700</v>
+        <v>127709724</v>
       </c>
       <c r="B73" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7674,21 +7674,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811687</v>
+        <v>811533</v>
       </c>
       <c r="R73" t="n">
-        <v>7390967</v>
+        <v>7391035</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8342,10 +8342,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127709738</v>
+        <v>127706918</v>
       </c>
       <c r="B80" t="n">
-        <v>92835</v>
+        <v>91648</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8353,37 +8353,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>658</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>811577</v>
+        <v>811451</v>
       </c>
       <c r="R80" t="n">
-        <v>7391006</v>
+        <v>7391161</v>
       </c>
       <c r="S80" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -8427,44 +8427,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127709755</v>
+        <v>127709760</v>
       </c>
       <c r="B81" t="n">
-        <v>78787</v>
+        <v>91513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8474,10 +8474,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>811542</v>
+        <v>811582</v>
       </c>
       <c r="R81" t="n">
-        <v>7391054</v>
+        <v>7391002</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -8536,32 +8536,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127706918</v>
+        <v>127706931</v>
       </c>
       <c r="B82" t="n">
-        <v>91648</v>
+        <v>92642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>658</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811451</v>
+        <v>811711</v>
       </c>
       <c r="R82" t="n">
-        <v>7391161</v>
+        <v>7390853</v>
       </c>
       <c r="S82" t="n">
         <v>1</v>
@@ -8633,32 +8633,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127709760</v>
+        <v>127709738</v>
       </c>
       <c r="B83" t="n">
-        <v>91513</v>
+        <v>92835</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1503</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8668,10 +8668,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811582</v>
+        <v>811577</v>
       </c>
       <c r="R83" t="n">
-        <v>7391002</v>
+        <v>7391006</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -8730,48 +8730,48 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127706931</v>
+        <v>127709755</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>811711</v>
+        <v>811542</v>
       </c>
       <c r="R84" t="n">
-        <v>7390853</v>
+        <v>7391054</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8815,12 +8815,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9312,32 +9312,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127709775</v>
+        <v>127709728</v>
       </c>
       <c r="B90" t="n">
-        <v>78696</v>
+        <v>79053</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811544</v>
+        <v>811385</v>
       </c>
       <c r="R90" t="n">
-        <v>7391011</v>
+        <v>7391153</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127706916</v>
+        <v>127709775</v>
       </c>
       <c r="B91" t="n">
-        <v>90387</v>
+        <v>78696</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9420,37 +9420,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811652</v>
+        <v>811544</v>
       </c>
       <c r="R91" t="n">
-        <v>7390945</v>
+        <v>7391011</v>
       </c>
       <c r="S91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9494,60 +9494,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127709777</v>
+        <v>127706916</v>
       </c>
       <c r="B92" t="n">
-        <v>92642</v>
+        <v>90387</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811696</v>
+        <v>811652</v>
       </c>
       <c r="R92" t="n">
-        <v>7390929</v>
+        <v>7390945</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,22 +9591,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709728</v>
+        <v>127709777</v>
       </c>
       <c r="B93" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811385</v>
+        <v>811696</v>
       </c>
       <c r="R93" t="n">
-        <v>7391153</v>
+        <v>7390929</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -10384,48 +10384,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127709747</v>
+        <v>127706920</v>
       </c>
       <c r="B101" t="n">
-        <v>57776</v>
+        <v>92835</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103031</v>
+        <v>2079</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811653</v>
+        <v>811552</v>
       </c>
       <c r="R101" t="n">
-        <v>7390948</v>
+        <v>7391002</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10469,22 +10469,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127706924</v>
+        <v>127709785</v>
       </c>
       <c r="B102" t="n">
-        <v>58042</v>
+        <v>92642</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10492,37 +10492,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103015</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811422</v>
+        <v>811504</v>
       </c>
       <c r="R102" t="n">
-        <v>7391139</v>
+        <v>7391047</v>
       </c>
       <c r="S102" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10566,60 +10566,60 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127706920</v>
+        <v>127709787</v>
       </c>
       <c r="B103" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811552</v>
+        <v>811677</v>
       </c>
       <c r="R103" t="n">
-        <v>7391002</v>
+        <v>7390878</v>
       </c>
       <c r="S103" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10663,22 +10663,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127709785</v>
+        <v>127709733</v>
       </c>
       <c r="B104" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10686,21 +10686,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10710,10 +10710,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811504</v>
+        <v>811530</v>
       </c>
       <c r="R104" t="n">
-        <v>7391047</v>
+        <v>7391016</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -10772,32 +10772,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127709787</v>
+        <v>127709770</v>
       </c>
       <c r="B105" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10807,10 +10807,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811677</v>
+        <v>811608</v>
       </c>
       <c r="R105" t="n">
-        <v>7390878</v>
+        <v>7391004</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -10869,48 +10869,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127709727</v>
+        <v>127709729</v>
       </c>
       <c r="B106" t="n">
-        <v>92646</v>
+        <v>79053</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4365</v>
+        <v>6434</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811545</v>
+        <v>811434</v>
       </c>
       <c r="R106" t="n">
-        <v>7391008</v>
+        <v>7391048</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -10951,7 +10948,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -10970,32 +10966,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127709733</v>
+        <v>127709764</v>
       </c>
       <c r="B107" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11005,10 +11001,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811530</v>
+        <v>811498</v>
       </c>
       <c r="R107" t="n">
-        <v>7391016</v>
+        <v>7391103</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -11067,32 +11063,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127709770</v>
+        <v>127709747</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>57776</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11098,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811608</v>
+        <v>811653</v>
       </c>
       <c r="R108" t="n">
-        <v>7391004</v>
+        <v>7390948</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -11164,45 +11160,48 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127709729</v>
+        <v>127709727</v>
       </c>
       <c r="B109" t="n">
-        <v>79053</v>
+        <v>92646</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6434</v>
+        <v>4365</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811434</v>
+        <v>811545</v>
       </c>
       <c r="R109" t="n">
-        <v>7391048</v>
+        <v>7391008</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -11243,6 +11242,7 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
@@ -11261,48 +11261,48 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127709764</v>
+        <v>127706924</v>
       </c>
       <c r="B110" t="n">
-        <v>79029</v>
+        <v>58042</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811498</v>
+        <v>811422</v>
       </c>
       <c r="R110" t="n">
-        <v>7391103</v>
+        <v>7391139</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -11346,12 +11346,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -11953,32 +11953,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709776</v>
+        <v>127709732</v>
       </c>
       <c r="B117" t="n">
-        <v>78696</v>
+        <v>79053</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>6434</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811646</v>
+        <v>811523</v>
       </c>
       <c r="R117" t="n">
-        <v>7390963</v>
+        <v>7391024</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709778</v>
+        <v>127709765</v>
       </c>
       <c r="B118" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811683</v>
+        <v>811478</v>
       </c>
       <c r="R118" t="n">
-        <v>7390938</v>
+        <v>7391172</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709791</v>
+        <v>127709776</v>
       </c>
       <c r="B119" t="n">
-        <v>92642</v>
+        <v>78696</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811605</v>
+        <v>811646</v>
       </c>
       <c r="R119" t="n">
-        <v>7391024</v>
+        <v>7390963</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,10 +12244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709732</v>
+        <v>127709778</v>
       </c>
       <c r="B120" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12255,21 +12255,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811523</v>
+        <v>811683</v>
       </c>
       <c r="R120" t="n">
-        <v>7391024</v>
+        <v>7390938</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,32 +12341,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709765</v>
+        <v>127709791</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811478</v>
+        <v>811605</v>
       </c>
       <c r="R121" t="n">
-        <v>7391172</v>
+        <v>7391024</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13214,27 +13214,27 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824751</v>
+        <v>127824735</v>
       </c>
       <c r="B130" t="n">
-        <v>57776</v>
+        <v>57669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>812037</v>
+        <v>811831</v>
       </c>
       <c r="R130" t="n">
-        <v>7391151</v>
+        <v>7390950</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,27 +13311,27 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824735</v>
+        <v>127824751</v>
       </c>
       <c r="B131" t="n">
-        <v>57669</v>
+        <v>57776</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811831</v>
+        <v>812037</v>
       </c>
       <c r="R131" t="n">
-        <v>7390950</v>
+        <v>7391151</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824694</v>
+        <v>127824725</v>
       </c>
       <c r="B141" t="n">
-        <v>79618</v>
+        <v>57832</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811716</v>
+        <v>811800</v>
       </c>
       <c r="R141" t="n">
-        <v>7390763</v>
+        <v>7390892</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824690</v>
+        <v>127824694</v>
       </c>
       <c r="B146" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811721</v>
+        <v>811716</v>
       </c>
       <c r="R146" t="n">
-        <v>7390757</v>
+        <v>7390763</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824725</v>
+        <v>127824690</v>
       </c>
       <c r="B147" t="n">
-        <v>57832</v>
+        <v>79647</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14874,21 +14874,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811800</v>
+        <v>811721</v>
       </c>
       <c r="R147" t="n">
-        <v>7390892</v>
+        <v>7390757</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15057,10 +15057,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824777</v>
+        <v>127824688</v>
       </c>
       <c r="B149" t="n">
-        <v>82870</v>
+        <v>79647</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15068,21 +15068,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811935</v>
+        <v>812058</v>
       </c>
       <c r="R149" t="n">
-        <v>7390835</v>
+        <v>7391223</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824688</v>
+        <v>127824777</v>
       </c>
       <c r="B150" t="n">
-        <v>79647</v>
+        <v>82870</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>812058</v>
+        <v>811935</v>
       </c>
       <c r="R150" t="n">
-        <v>7391223</v>
+        <v>7390835</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -15842,10 +15842,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127824755</v>
+        <v>127824724</v>
       </c>
       <c r="B157" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15853,34 +15853,38 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>812164</v>
+        <v>811806</v>
       </c>
       <c r="R157" t="n">
-        <v>7391415</v>
+        <v>7390821</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -15939,10 +15943,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127824724</v>
+        <v>127824755</v>
       </c>
       <c r="B158" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15950,38 +15954,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>811806</v>
+        <v>812164</v>
       </c>
       <c r="R158" t="n">
-        <v>7390821</v>
+        <v>7391415</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824778</v>
+        <v>127824765</v>
       </c>
       <c r="B171" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17215,21 +17215,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811927</v>
+        <v>811918</v>
       </c>
       <c r="R171" t="n">
-        <v>7390802</v>
+        <v>7390852</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,10 +17301,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824772</v>
+        <v>127824759</v>
       </c>
       <c r="B172" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17312,21 +17312,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>812010</v>
+        <v>811950</v>
       </c>
       <c r="R172" t="n">
-        <v>7391123</v>
+        <v>7391109</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B173" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R173" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824759</v>
+        <v>127824772</v>
       </c>
       <c r="B174" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17506,21 +17506,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811950</v>
+        <v>812010</v>
       </c>
       <c r="R174" t="n">
-        <v>7391109</v>
+        <v>7391123</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127706926</v>
+        <v>127709784</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811754</v>
+        <v>811414</v>
       </c>
       <c r="R2" t="n">
-        <v>7390851</v>
+        <v>7391125</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127709734</v>
+        <v>127706926</v>
       </c>
       <c r="B3" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811573</v>
+        <v>811754</v>
       </c>
       <c r="R3" t="n">
-        <v>7391001</v>
+        <v>7390851</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709784</v>
+        <v>127709763</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811414</v>
+        <v>811692</v>
       </c>
       <c r="R4" t="n">
-        <v>7391125</v>
+        <v>7390815</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709763</v>
+        <v>127709734</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811692</v>
+        <v>811573</v>
       </c>
       <c r="R5" t="n">
-        <v>7390815</v>
+        <v>7391001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127706925</v>
+        <v>127709694</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811866</v>
+        <v>811441</v>
       </c>
       <c r="R14" t="n">
-        <v>7390863</v>
+        <v>7391158</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,19 +1937,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127709694</v>
+        <v>127706914</v>
       </c>
       <c r="B15" t="n">
         <v>79647</v>
@@ -1980,17 +1980,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811441</v>
+        <v>811645</v>
       </c>
       <c r="R15" t="n">
-        <v>7391158</v>
+        <v>7390971</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,19 +2034,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127706914</v>
+        <v>127709695</v>
       </c>
       <c r="B16" t="n">
         <v>79647</v>
@@ -2077,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811645</v>
+        <v>811430</v>
       </c>
       <c r="R16" t="n">
-        <v>7390971</v>
+        <v>7391046</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709695</v>
+        <v>127709699</v>
       </c>
       <c r="B17" t="n">
         <v>79647</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811430</v>
+        <v>811707</v>
       </c>
       <c r="R17" t="n">
-        <v>7391046</v>
+        <v>7390941</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709699</v>
+        <v>127706925</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811707</v>
+        <v>811866</v>
       </c>
       <c r="R18" t="n">
-        <v>7390941</v>
+        <v>7390863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2544,32 +2544,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127709731</v>
+        <v>127709800</v>
       </c>
       <c r="B21" t="n">
-        <v>79053</v>
+        <v>92636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811484</v>
+        <v>811725</v>
       </c>
       <c r="R21" t="n">
-        <v>7391038</v>
+        <v>7390826</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2641,32 +2641,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127709800</v>
+        <v>127709797</v>
       </c>
       <c r="B22" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811725</v>
+        <v>811577</v>
       </c>
       <c r="R22" t="n">
-        <v>7390826</v>
+        <v>7391006</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2738,45 +2738,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127709797</v>
+        <v>127709725</v>
       </c>
       <c r="B23" t="n">
-        <v>92642</v>
+        <v>92646</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811577</v>
+        <v>811692</v>
       </c>
       <c r="R23" t="n">
-        <v>7391006</v>
+        <v>7390871</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2817,6 +2820,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2835,48 +2839,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127709725</v>
+        <v>127709698</v>
       </c>
       <c r="B24" t="n">
-        <v>92646</v>
+        <v>79647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811692</v>
+        <v>811656</v>
       </c>
       <c r="R24" t="n">
-        <v>7390871</v>
+        <v>7390942</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2917,7 +2918,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2936,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127709698</v>
+        <v>127709731</v>
       </c>
       <c r="B25" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811656</v>
+        <v>811484</v>
       </c>
       <c r="R25" t="n">
-        <v>7390942</v>
+        <v>7391038</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709741</v>
+        <v>127709758</v>
       </c>
       <c r="B26" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811489</v>
+        <v>811621</v>
       </c>
       <c r="R26" t="n">
-        <v>7391186</v>
+        <v>7390981</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709703</v>
+        <v>127709730</v>
       </c>
       <c r="B27" t="n">
-        <v>79618</v>
+        <v>79053</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>6434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811724</v>
+        <v>811452</v>
       </c>
       <c r="R27" t="n">
-        <v>7390998</v>
+        <v>7391057</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3209,7 +3209,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3228,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709790</v>
+        <v>127709736</v>
       </c>
       <c r="B28" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3239,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3263,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811610</v>
+        <v>811662</v>
       </c>
       <c r="R28" t="n">
-        <v>7391012</v>
+        <v>7390926</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3325,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709786</v>
+        <v>127709741</v>
       </c>
       <c r="B29" t="n">
-        <v>92642</v>
+        <v>78788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3360,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811612</v>
+        <v>811489</v>
       </c>
       <c r="R29" t="n">
-        <v>7390987</v>
+        <v>7391186</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3422,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709779</v>
+        <v>127709703</v>
       </c>
       <c r="B30" t="n">
-        <v>92642</v>
+        <v>79618</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3457,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811561</v>
+        <v>811724</v>
       </c>
       <c r="R30" t="n">
-        <v>7391108</v>
+        <v>7390998</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3501,6 +3500,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709796</v>
+        <v>127709790</v>
       </c>
       <c r="B31" t="n">
         <v>92642</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811672</v>
+        <v>811610</v>
       </c>
       <c r="R31" t="n">
-        <v>7391010</v>
+        <v>7391012</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3616,48 +3616,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127706927</v>
+        <v>127709786</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811760</v>
+        <v>811612</v>
       </c>
       <c r="R32" t="n">
-        <v>7390859</v>
+        <v>7390987</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,44 +3701,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709758</v>
+        <v>127709779</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811621</v>
+        <v>811561</v>
       </c>
       <c r="R33" t="n">
-        <v>7390981</v>
+        <v>7391108</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709730</v>
+        <v>127709796</v>
       </c>
       <c r="B34" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811452</v>
+        <v>811672</v>
       </c>
       <c r="R34" t="n">
-        <v>7391057</v>
+        <v>7391010</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3907,48 +3907,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127709736</v>
+        <v>127706927</v>
       </c>
       <c r="B35" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811662</v>
+        <v>811760</v>
       </c>
       <c r="R35" t="n">
-        <v>7390926</v>
+        <v>7390859</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3992,12 +3992,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4101,32 +4101,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127709768</v>
+        <v>127709780</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4136,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811776</v>
+        <v>811475</v>
       </c>
       <c r="R37" t="n">
-        <v>7390918</v>
+        <v>7391196</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4198,10 +4198,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127709766</v>
+        <v>127709708</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4209,34 +4209,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811730</v>
+        <v>811580</v>
       </c>
       <c r="R38" t="n">
-        <v>7390914</v>
+        <v>7391090</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4271,6 +4279,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4288,17 +4301,17 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127709756</v>
+        <v>127709768</v>
       </c>
       <c r="B39" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4319,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4343,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811538</v>
+        <v>811776</v>
       </c>
       <c r="R39" t="n">
-        <v>7391022</v>
+        <v>7390918</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4392,10 +4405,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127709708</v>
+        <v>127709766</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,42 +4416,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811580</v>
+        <v>811730</v>
       </c>
       <c r="R40" t="n">
-        <v>7391090</v>
+        <v>7390914</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4473,11 +4478,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4495,39 +4495,39 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127709780</v>
+        <v>127709756</v>
       </c>
       <c r="B41" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4537,10 +4537,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811475</v>
+        <v>811538</v>
       </c>
       <c r="R41" t="n">
-        <v>7391196</v>
+        <v>7391022</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5393,32 +5393,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127709749</v>
+        <v>127709793</v>
       </c>
       <c r="B50" t="n">
-        <v>81004</v>
+        <v>92642</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811750</v>
+        <v>811612</v>
       </c>
       <c r="R50" t="n">
-        <v>7390835</v>
+        <v>7391041</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5490,10 +5490,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127709753</v>
+        <v>127709749</v>
       </c>
       <c r="B51" t="n">
-        <v>78787</v>
+        <v>81004</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5501,21 +5501,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811385</v>
+        <v>811750</v>
       </c>
       <c r="R51" t="n">
-        <v>7391163</v>
+        <v>7390835</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5587,32 +5587,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127709793</v>
+        <v>127709753</v>
       </c>
       <c r="B52" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5622,10 +5622,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811612</v>
+        <v>811385</v>
       </c>
       <c r="R52" t="n">
-        <v>7391041</v>
+        <v>7391163</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -5781,53 +5781,45 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127709713</v>
+        <v>127709792</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811514</v>
+        <v>811619</v>
       </c>
       <c r="R54" t="n">
-        <v>7391024</v>
+        <v>7391036</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5862,11 +5854,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5884,17 +5871,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709711</v>
+        <v>127709702</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5902,42 +5889,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811535</v>
+        <v>811715</v>
       </c>
       <c r="R55" t="n">
-        <v>7391056</v>
+        <v>7391028</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5972,11 +5951,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5994,17 +5968,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127706919</v>
+        <v>127709692</v>
       </c>
       <c r="B56" t="n">
-        <v>92835</v>
+        <v>79647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6012,37 +5986,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811446</v>
+        <v>811591</v>
       </c>
       <c r="R56" t="n">
-        <v>7391045</v>
+        <v>7391072</v>
       </c>
       <c r="S56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6086,60 +6060,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127709792</v>
+        <v>127706919</v>
       </c>
       <c r="B57" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811619</v>
+        <v>811446</v>
       </c>
       <c r="R57" t="n">
-        <v>7391036</v>
+        <v>7391045</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6183,44 +6157,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709702</v>
+        <v>127709717</v>
       </c>
       <c r="B58" t="n">
-        <v>79647</v>
+        <v>79053</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6230,10 +6204,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811715</v>
+        <v>811625</v>
       </c>
       <c r="R58" t="n">
-        <v>7391028</v>
+        <v>7390984</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6292,10 +6266,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127709692</v>
+        <v>127706933</v>
       </c>
       <c r="B59" t="n">
-        <v>79647</v>
+        <v>78435</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6303,37 +6277,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811591</v>
+        <v>811536</v>
       </c>
       <c r="R59" t="n">
-        <v>7391072</v>
+        <v>7391018</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6377,44 +6351,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709717</v>
+        <v>127709771</v>
       </c>
       <c r="B60" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6424,10 +6398,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811625</v>
+        <v>811735</v>
       </c>
       <c r="R60" t="n">
-        <v>7390984</v>
+        <v>7391006</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6486,10 +6460,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127706933</v>
+        <v>127709713</v>
       </c>
       <c r="B61" t="n">
-        <v>78435</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6497,37 +6471,45 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811536</v>
+        <v>811514</v>
       </c>
       <c r="R61" t="n">
-        <v>7391018</v>
+        <v>7391024</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6557,6 +6539,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6571,22 +6558,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709771</v>
+        <v>127709711</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6594,34 +6581,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811735</v>
+        <v>811535</v>
       </c>
       <c r="R62" t="n">
-        <v>7391006</v>
+        <v>7391056</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6656,6 +6651,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7165,53 +7165,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709705</v>
+        <v>127709798</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>79053</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811705</v>
+        <v>811676</v>
       </c>
       <c r="R68" t="n">
-        <v>7390855</v>
+        <v>7390933</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7246,11 +7238,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7268,55 +7255,55 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127706913</v>
+        <v>127709803</v>
       </c>
       <c r="B69" t="n">
-        <v>91317</v>
+        <v>78435</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811507</v>
+        <v>811716</v>
       </c>
       <c r="R69" t="n">
-        <v>7391034</v>
+        <v>7390831</v>
       </c>
       <c r="S69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7360,22 +7347,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709700</v>
+        <v>127709724</v>
       </c>
       <c r="B70" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7383,21 +7370,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7407,10 +7394,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811687</v>
+        <v>811533</v>
       </c>
       <c r="R70" t="n">
-        <v>7390967</v>
+        <v>7391035</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7469,45 +7456,53 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709798</v>
+        <v>127709705</v>
       </c>
       <c r="B71" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811676</v>
+        <v>811705</v>
       </c>
       <c r="R71" t="n">
-        <v>7390933</v>
+        <v>7390855</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7542,6 +7537,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7559,55 +7559,55 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127709803</v>
+        <v>127706913</v>
       </c>
       <c r="B72" t="n">
-        <v>78435</v>
+        <v>91317</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811716</v>
+        <v>811507</v>
       </c>
       <c r="R72" t="n">
-        <v>7390831</v>
+        <v>7391034</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7651,22 +7651,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709724</v>
+        <v>127709700</v>
       </c>
       <c r="B73" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7674,21 +7674,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811533</v>
+        <v>811687</v>
       </c>
       <c r="R73" t="n">
-        <v>7391035</v>
+        <v>7390967</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8536,48 +8536,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127706931</v>
+        <v>127709738</v>
       </c>
       <c r="B82" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811711</v>
+        <v>811577</v>
       </c>
       <c r="R82" t="n">
-        <v>7390853</v>
+        <v>7391006</v>
       </c>
       <c r="S82" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8621,60 +8621,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127709738</v>
+        <v>127706931</v>
       </c>
       <c r="B83" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811577</v>
+        <v>811711</v>
       </c>
       <c r="R83" t="n">
-        <v>7391006</v>
+        <v>7390853</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8718,12 +8718,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8827,32 +8827,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127709757</v>
+        <v>127709789</v>
       </c>
       <c r="B85" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8862,10 +8862,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>811625</v>
+        <v>811610</v>
       </c>
       <c r="R85" t="n">
-        <v>7390969</v>
+        <v>7390981</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -8924,32 +8924,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127709759</v>
+        <v>127709788</v>
       </c>
       <c r="B86" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8959,10 +8959,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>811715</v>
+        <v>811667</v>
       </c>
       <c r="R86" t="n">
-        <v>7391028</v>
+        <v>7390931</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9021,10 +9021,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127706929</v>
+        <v>127709757</v>
       </c>
       <c r="B87" t="n">
-        <v>82870</v>
+        <v>78787</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9032,37 +9032,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>811496</v>
+        <v>811625</v>
       </c>
       <c r="R87" t="n">
-        <v>7391110</v>
+        <v>7390969</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9106,44 +9106,44 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127709789</v>
+        <v>127709759</v>
       </c>
       <c r="B88" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9153,10 +9153,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>811610</v>
+        <v>811715</v>
       </c>
       <c r="R88" t="n">
-        <v>7390981</v>
+        <v>7391028</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -9215,48 +9215,48 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127709788</v>
+        <v>127706929</v>
       </c>
       <c r="B89" t="n">
-        <v>92642</v>
+        <v>82870</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>811667</v>
+        <v>811496</v>
       </c>
       <c r="R89" t="n">
-        <v>7390931</v>
+        <v>7391110</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9300,44 +9300,44 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127709728</v>
+        <v>127709775</v>
       </c>
       <c r="B90" t="n">
-        <v>79053</v>
+        <v>78696</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9347,10 +9347,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>811385</v>
+        <v>811544</v>
       </c>
       <c r="R90" t="n">
-        <v>7391153</v>
+        <v>7391011</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -9409,10 +9409,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127709775</v>
+        <v>127706916</v>
       </c>
       <c r="B91" t="n">
-        <v>78696</v>
+        <v>90387</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9420,37 +9420,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>811544</v>
+        <v>811652</v>
       </c>
       <c r="R91" t="n">
-        <v>7391011</v>
+        <v>7390945</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -9494,60 +9494,60 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127706916</v>
+        <v>127709777</v>
       </c>
       <c r="B92" t="n">
-        <v>90387</v>
+        <v>92642</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>811652</v>
+        <v>811696</v>
       </c>
       <c r="R92" t="n">
-        <v>7390945</v>
+        <v>7390929</v>
       </c>
       <c r="S92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -9591,22 +9591,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127709777</v>
+        <v>127709728</v>
       </c>
       <c r="B93" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9614,21 +9614,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>811696</v>
+        <v>811385</v>
       </c>
       <c r="R93" t="n">
-        <v>7390929</v>
+        <v>7391153</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709795</v>
+        <v>127709693</v>
       </c>
       <c r="B96" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811676</v>
+        <v>811486</v>
       </c>
       <c r="R96" t="n">
-        <v>7391004</v>
+        <v>7391112</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,49 +9991,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709799</v>
+        <v>127709795</v>
       </c>
       <c r="B97" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811707</v>
+        <v>811676</v>
       </c>
       <c r="R97" t="n">
-        <v>7390860</v>
+        <v>7391004</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10074,7 +10070,6 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10093,45 +10088,49 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709783</v>
+        <v>127709799</v>
       </c>
       <c r="B98" t="n">
-        <v>92642</v>
+        <v>92636</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811387</v>
+        <v>811707</v>
       </c>
       <c r="R98" t="n">
-        <v>7391146</v>
+        <v>7390860</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10172,6 +10171,7 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10190,32 +10190,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709693</v>
+        <v>127709783</v>
       </c>
       <c r="B99" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811486</v>
+        <v>811387</v>
       </c>
       <c r="R99" t="n">
-        <v>7391112</v>
+        <v>7391146</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11953,32 +11953,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127709732</v>
+        <v>127709776</v>
       </c>
       <c r="B117" t="n">
-        <v>79053</v>
+        <v>78696</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6434</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11988,10 +11988,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811523</v>
+        <v>811646</v>
       </c>
       <c r="R117" t="n">
-        <v>7391024</v>
+        <v>7390963</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -12050,32 +12050,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127709765</v>
+        <v>127709778</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12085,10 +12085,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811478</v>
+        <v>811683</v>
       </c>
       <c r="R118" t="n">
-        <v>7391172</v>
+        <v>7390938</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -12147,32 +12147,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127709776</v>
+        <v>127709791</v>
       </c>
       <c r="B119" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12182,10 +12182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811646</v>
+        <v>811605</v>
       </c>
       <c r="R119" t="n">
-        <v>7390963</v>
+        <v>7391024</v>
       </c>
       <c r="S119" t="n">
         <v>5</v>
@@ -12244,10 +12244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127709778</v>
+        <v>127709732</v>
       </c>
       <c r="B120" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12255,21 +12255,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811683</v>
+        <v>811523</v>
       </c>
       <c r="R120" t="n">
-        <v>7390938</v>
+        <v>7391024</v>
       </c>
       <c r="S120" t="n">
         <v>5</v>
@@ -12341,32 +12341,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127709791</v>
+        <v>127709765</v>
       </c>
       <c r="B121" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12376,10 +12376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811605</v>
+        <v>811478</v>
       </c>
       <c r="R121" t="n">
-        <v>7391024</v>
+        <v>7391172</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -13214,27 +13214,27 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824735</v>
+        <v>127824751</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>57776</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811831</v>
+        <v>812037</v>
       </c>
       <c r="R130" t="n">
-        <v>7390950</v>
+        <v>7391151</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,27 +13311,27 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824751</v>
+        <v>127824735</v>
       </c>
       <c r="B131" t="n">
-        <v>57776</v>
+        <v>57669</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>812037</v>
+        <v>811831</v>
       </c>
       <c r="R131" t="n">
-        <v>7391151</v>
+        <v>7390950</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -13699,32 +13699,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824753</v>
+        <v>127824782</v>
       </c>
       <c r="B135" t="n">
-        <v>81004</v>
+        <v>92642</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1049</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811752</v>
+        <v>811902</v>
       </c>
       <c r="R135" t="n">
-        <v>7390828</v>
+        <v>7390765</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13796,32 +13796,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127824782</v>
+        <v>127824703</v>
       </c>
       <c r="B136" t="n">
-        <v>92642</v>
+        <v>91352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811902</v>
+        <v>811762</v>
       </c>
       <c r="R136" t="n">
-        <v>7390765</v>
+        <v>7390826</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -13893,10 +13893,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127824703</v>
+        <v>127824775</v>
       </c>
       <c r="B137" t="n">
-        <v>91352</v>
+        <v>82870</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13904,21 +13904,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>811762</v>
+        <v>811886</v>
       </c>
       <c r="R137" t="n">
-        <v>7390826</v>
+        <v>7390941</v>
       </c>
       <c r="S137" t="n">
         <v>1</v>
@@ -13990,32 +13990,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>127824775</v>
+        <v>127824739</v>
       </c>
       <c r="B138" t="n">
-        <v>82870</v>
+        <v>79053</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14025,10 +14025,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811886</v>
+        <v>811874</v>
       </c>
       <c r="R138" t="n">
-        <v>7390941</v>
+        <v>7391049</v>
       </c>
       <c r="S138" t="n">
         <v>1</v>
@@ -14087,7 +14087,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>127824739</v>
+        <v>127824747</v>
       </c>
       <c r="B139" t="n">
         <v>79053</v>
@@ -14122,10 +14122,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811874</v>
+        <v>811803</v>
       </c>
       <c r="R139" t="n">
-        <v>7391049</v>
+        <v>7390886</v>
       </c>
       <c r="S139" t="n">
         <v>1</v>
@@ -14184,32 +14184,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>127824747</v>
+        <v>127824753</v>
       </c>
       <c r="B140" t="n">
-        <v>79053</v>
+        <v>81004</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6434</v>
+        <v>1049</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14219,10 +14219,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811803</v>
+        <v>811752</v>
       </c>
       <c r="R140" t="n">
-        <v>7390886</v>
+        <v>7390828</v>
       </c>
       <c r="S140" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824725</v>
+        <v>127824694</v>
       </c>
       <c r="B141" t="n">
-        <v>57832</v>
+        <v>79618</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811800</v>
+        <v>811716</v>
       </c>
       <c r="R141" t="n">
-        <v>7390892</v>
+        <v>7390763</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824694</v>
+        <v>127824690</v>
       </c>
       <c r="B146" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811716</v>
+        <v>811721</v>
       </c>
       <c r="R146" t="n">
-        <v>7390763</v>
+        <v>7390757</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824690</v>
+        <v>127824725</v>
       </c>
       <c r="B147" t="n">
-        <v>79647</v>
+        <v>57832</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14874,21 +14874,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811721</v>
+        <v>811800</v>
       </c>
       <c r="R147" t="n">
-        <v>7390757</v>
+        <v>7390892</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15551,10 +15551,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>127824691</v>
+        <v>127824769</v>
       </c>
       <c r="B154" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -15562,21 +15562,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -15586,10 +15586,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>811718</v>
+        <v>811795</v>
       </c>
       <c r="R154" t="n">
-        <v>7390758</v>
+        <v>7390892</v>
       </c>
       <c r="S154" t="n">
         <v>1</v>
@@ -15648,32 +15648,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>127824734</v>
+        <v>127824691</v>
       </c>
       <c r="B155" t="n">
-        <v>80161</v>
+        <v>79647</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -15683,10 +15683,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>812156</v>
+        <v>811718</v>
       </c>
       <c r="R155" t="n">
-        <v>7391361</v>
+        <v>7390758</v>
       </c>
       <c r="S155" t="n">
         <v>1</v>
@@ -15745,32 +15745,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>127824769</v>
+        <v>127824734</v>
       </c>
       <c r="B156" t="n">
-        <v>79029</v>
+        <v>80161</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811795</v>
+        <v>812156</v>
       </c>
       <c r="R156" t="n">
-        <v>7390892</v>
+        <v>7391361</v>
       </c>
       <c r="S156" t="n">
         <v>1</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B171" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17215,21 +17215,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R171" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,10 +17301,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824759</v>
+        <v>127824772</v>
       </c>
       <c r="B172" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17312,21 +17312,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811950</v>
+        <v>812010</v>
       </c>
       <c r="R172" t="n">
-        <v>7391109</v>
+        <v>7391123</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824778</v>
+        <v>127824765</v>
       </c>
       <c r="B173" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811927</v>
+        <v>811918</v>
       </c>
       <c r="R173" t="n">
-        <v>7390802</v>
+        <v>7390852</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824772</v>
+        <v>127824759</v>
       </c>
       <c r="B174" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17506,21 +17506,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>812010</v>
+        <v>811950</v>
       </c>
       <c r="R174" t="n">
-        <v>7391123</v>
+        <v>7391109</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127709784</v>
+        <v>127706926</v>
       </c>
       <c r="B2" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811414</v>
+        <v>811754</v>
       </c>
       <c r="R2" t="n">
-        <v>7391125</v>
+        <v>7390851</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,60 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127706926</v>
+        <v>127709734</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811754</v>
+        <v>811573</v>
       </c>
       <c r="R3" t="n">
-        <v>7390851</v>
+        <v>7391001</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,44 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127709763</v>
+        <v>127709784</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811692</v>
+        <v>811414</v>
       </c>
       <c r="R4" t="n">
-        <v>7390815</v>
+        <v>7391125</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127709734</v>
+        <v>127709763</v>
       </c>
       <c r="B5" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811573</v>
+        <v>811692</v>
       </c>
       <c r="R5" t="n">
-        <v>7391001</v>
+        <v>7390815</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127709721</v>
+        <v>127709774</v>
       </c>
       <c r="B6" t="n">
-        <v>57669</v>
+        <v>91613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811493</v>
+        <v>811658</v>
       </c>
       <c r="R6" t="n">
-        <v>7391183</v>
+        <v>7390945</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1160,48 +1160,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127709781</v>
+        <v>127706928</v>
       </c>
       <c r="B7" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811479</v>
+        <v>811509</v>
       </c>
       <c r="R7" t="n">
-        <v>7391142</v>
+        <v>7391152</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127706928</v>
+        <v>127709721</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811509</v>
+        <v>811493</v>
       </c>
       <c r="R8" t="n">
-        <v>7391152</v>
+        <v>7391183</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1342,44 +1342,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127709774</v>
+        <v>127709781</v>
       </c>
       <c r="B9" t="n">
-        <v>91613</v>
+        <v>92642</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811658</v>
+        <v>811479</v>
       </c>
       <c r="R9" t="n">
-        <v>7390945</v>
+        <v>7391142</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127706921</v>
+        <v>127709710</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811722</v>
+        <v>811505</v>
       </c>
       <c r="R10" t="n">
-        <v>7390955</v>
+        <v>7391045</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1522,6 +1530,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1536,44 +1549,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127706923</v>
+        <v>127706915</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>58531</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>208249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1596,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811648</v>
+        <v>811694</v>
       </c>
       <c r="R11" t="n">
-        <v>7390971</v>
+        <v>7390899</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1645,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127709710</v>
+        <v>127706921</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,45 +1669,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811505</v>
+        <v>811722</v>
       </c>
       <c r="R12" t="n">
-        <v>7391045</v>
+        <v>7390955</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1724,11 +1729,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,44 +1743,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127706915</v>
+        <v>127706923</v>
       </c>
       <c r="B13" t="n">
-        <v>58531</v>
+        <v>78788</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>208249</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811694</v>
+        <v>811648</v>
       </c>
       <c r="R13" t="n">
-        <v>7390899</v>
+        <v>7390971</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127709694</v>
+        <v>127706925</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811441</v>
+        <v>811866</v>
       </c>
       <c r="R14" t="n">
-        <v>7391158</v>
+        <v>7390863</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,19 +1937,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127706914</v>
+        <v>127709694</v>
       </c>
       <c r="B15" t="n">
         <v>79647</v>
@@ -1980,17 +1980,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811645</v>
+        <v>811441</v>
       </c>
       <c r="R15" t="n">
-        <v>7390971</v>
+        <v>7391158</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,19 +2034,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127709695</v>
+        <v>127706914</v>
       </c>
       <c r="B16" t="n">
         <v>79647</v>
@@ -2077,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811430</v>
+        <v>811645</v>
       </c>
       <c r="R16" t="n">
-        <v>7391046</v>
+        <v>7390971</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709699</v>
+        <v>127709695</v>
       </c>
       <c r="B17" t="n">
         <v>79647</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811707</v>
+        <v>811430</v>
       </c>
       <c r="R17" t="n">
-        <v>7390941</v>
+        <v>7391046</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127706925</v>
+        <v>127709699</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811866</v>
+        <v>811707</v>
       </c>
       <c r="R18" t="n">
-        <v>7390863</v>
+        <v>7390941</v>
       </c>
       <c r="S18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -4599,10 +4599,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127706917</v>
+        <v>127709744</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>78788</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4610,37 +4610,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>811865</v>
+        <v>811539</v>
       </c>
       <c r="R42" t="n">
-        <v>7390848</v>
+        <v>7391022</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4670,11 +4670,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4689,19 +4684,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127709712</v>
+        <v>127706917</v>
       </c>
       <c r="B43" t="n">
         <v>57672</v>
@@ -4729,28 +4724,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811420</v>
+        <v>811865</v>
       </c>
       <c r="R43" t="n">
-        <v>7391078</v>
+        <v>7390848</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4784,7 +4771,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack.</t>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4799,57 +4786,65 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127709735</v>
+        <v>127709712</v>
       </c>
       <c r="B44" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811626</v>
+        <v>811420</v>
       </c>
       <c r="R44" t="n">
-        <v>7390972</v>
+        <v>7391078</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -4884,6 +4879,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -4901,39 +4901,39 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127709752</v>
+        <v>127709735</v>
       </c>
       <c r="B45" t="n">
-        <v>78787</v>
+        <v>79053</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6434</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811490</v>
+        <v>811626</v>
       </c>
       <c r="R45" t="n">
-        <v>7391186</v>
+        <v>7390972</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5005,10 +5005,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127709744</v>
+        <v>127709752</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5016,21 +5016,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5040,10 +5040,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811539</v>
+        <v>811490</v>
       </c>
       <c r="R46" t="n">
-        <v>7391022</v>
+        <v>7391186</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5781,45 +5781,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127709792</v>
+        <v>127709713</v>
       </c>
       <c r="B54" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811619</v>
+        <v>811514</v>
       </c>
       <c r="R54" t="n">
-        <v>7391036</v>
+        <v>7391024</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -5854,6 +5862,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Äldre ringhack.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5871,17 +5884,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127709702</v>
+        <v>127709711</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>57672</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5889,34 +5902,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811715</v>
+        <v>811535</v>
       </c>
       <c r="R55" t="n">
-        <v>7391028</v>
+        <v>7391056</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -5951,6 +5972,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5968,17 +5994,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127709692</v>
+        <v>127706919</v>
       </c>
       <c r="B56" t="n">
-        <v>79647</v>
+        <v>92835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5986,37 +6012,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811591</v>
+        <v>811446</v>
       </c>
       <c r="R56" t="n">
-        <v>7391072</v>
+        <v>7391045</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6060,60 +6086,60 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127706919</v>
+        <v>127709792</v>
       </c>
       <c r="B57" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811446</v>
+        <v>811619</v>
       </c>
       <c r="R57" t="n">
-        <v>7391045</v>
+        <v>7391036</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6157,44 +6183,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127709717</v>
+        <v>127709702</v>
       </c>
       <c r="B58" t="n">
-        <v>79053</v>
+        <v>79647</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6434</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6204,10 +6230,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811625</v>
+        <v>811715</v>
       </c>
       <c r="R58" t="n">
-        <v>7390984</v>
+        <v>7391028</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6266,10 +6292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127706933</v>
+        <v>127709692</v>
       </c>
       <c r="B59" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6277,37 +6303,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811536</v>
+        <v>811591</v>
       </c>
       <c r="R59" t="n">
-        <v>7391018</v>
+        <v>7391072</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6351,44 +6377,44 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127709771</v>
+        <v>127709717</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6398,10 +6424,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811735</v>
+        <v>811625</v>
       </c>
       <c r="R60" t="n">
-        <v>7391006</v>
+        <v>7390984</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6460,10 +6486,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127709713</v>
+        <v>127706933</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>78435</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6471,45 +6497,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6437</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811514</v>
+        <v>811536</v>
       </c>
       <c r="R61" t="n">
-        <v>7391024</v>
+        <v>7391018</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6539,11 +6557,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6558,22 +6571,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127709711</v>
+        <v>127709771</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6581,42 +6594,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811535</v>
+        <v>811735</v>
       </c>
       <c r="R62" t="n">
-        <v>7391056</v>
+        <v>7391006</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -6651,11 +6656,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7165,45 +7165,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127709798</v>
+        <v>127709705</v>
       </c>
       <c r="B68" t="n">
-        <v>79053</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811676</v>
+        <v>811705</v>
       </c>
       <c r="R68" t="n">
-        <v>7390933</v>
+        <v>7390855</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7238,6 +7246,11 @@
           <t>2025-08-20</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7255,55 +7268,55 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Marie Karlsson, Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127709803</v>
+        <v>127706913</v>
       </c>
       <c r="B69" t="n">
-        <v>78435</v>
+        <v>91317</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>811716</v>
+        <v>811507</v>
       </c>
       <c r="R69" t="n">
-        <v>7390831</v>
+        <v>7391034</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7347,22 +7360,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127709724</v>
+        <v>127709700</v>
       </c>
       <c r="B70" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7370,21 +7383,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7394,10 +7407,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>811533</v>
+        <v>811687</v>
       </c>
       <c r="R70" t="n">
-        <v>7391035</v>
+        <v>7390967</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -7456,53 +7469,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127709705</v>
+        <v>127709798</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>79053</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>811705</v>
+        <v>811676</v>
       </c>
       <c r="R71" t="n">
-        <v>7390855</v>
+        <v>7390933</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -7537,11 +7542,6 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -7559,55 +7559,55 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marie Karlsson, Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127706913</v>
+        <v>127709803</v>
       </c>
       <c r="B72" t="n">
-        <v>91317</v>
+        <v>78435</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5447</v>
+        <v>6437</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>811507</v>
+        <v>811716</v>
       </c>
       <c r="R72" t="n">
-        <v>7391034</v>
+        <v>7390831</v>
       </c>
       <c r="S72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7651,22 +7651,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127709700</v>
+        <v>127709724</v>
       </c>
       <c r="B73" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7674,21 +7674,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7698,10 +7698,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>811687</v>
+        <v>811533</v>
       </c>
       <c r="R73" t="n">
-        <v>7390967</v>
+        <v>7391035</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8536,48 +8536,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127709738</v>
+        <v>127706931</v>
       </c>
       <c r="B82" t="n">
-        <v>92835</v>
+        <v>92642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>811577</v>
+        <v>811711</v>
       </c>
       <c r="R82" t="n">
-        <v>7391006</v>
+        <v>7390853</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8621,60 +8621,60 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127706931</v>
+        <v>127709738</v>
       </c>
       <c r="B83" t="n">
-        <v>92642</v>
+        <v>92835</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>811711</v>
+        <v>811577</v>
       </c>
       <c r="R83" t="n">
-        <v>7390853</v>
+        <v>7391006</v>
       </c>
       <c r="S83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8718,12 +8718,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127709720</v>
+        <v>127709801</v>
       </c>
       <c r="B111" t="n">
-        <v>57669</v>
+        <v>92636</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811515</v>
+        <v>811615</v>
       </c>
       <c r="R111" t="n">
-        <v>7391165</v>
+        <v>7390990</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -11455,32 +11455,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127709801</v>
+        <v>127709726</v>
       </c>
       <c r="B112" t="n">
-        <v>92636</v>
+        <v>92646</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811615</v>
+        <v>811638</v>
       </c>
       <c r="R112" t="n">
-        <v>7390990</v>
+        <v>7391044</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -11552,32 +11552,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127709726</v>
+        <v>127709804</v>
       </c>
       <c r="B113" t="n">
-        <v>92646</v>
+        <v>78435</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4365</v>
+        <v>6437</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811638</v>
+        <v>811452</v>
       </c>
       <c r="R113" t="n">
-        <v>7391044</v>
+        <v>7391056</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127709804</v>
+        <v>127709720</v>
       </c>
       <c r="B115" t="n">
-        <v>78435</v>
+        <v>57669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11757,21 +11757,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6437</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811452</v>
+        <v>811515</v>
       </c>
       <c r="R115" t="n">
-        <v>7391056</v>
+        <v>7391165</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -13214,27 +13214,27 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824751</v>
+        <v>127824735</v>
       </c>
       <c r="B130" t="n">
-        <v>57776</v>
+        <v>57669</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>812037</v>
+        <v>811831</v>
       </c>
       <c r="R130" t="n">
-        <v>7391151</v>
+        <v>7390950</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,27 +13311,27 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824735</v>
+        <v>127824751</v>
       </c>
       <c r="B131" t="n">
-        <v>57669</v>
+        <v>57776</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811831</v>
+        <v>812037</v>
       </c>
       <c r="R131" t="n">
-        <v>7390950</v>
+        <v>7391151</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -14281,10 +14281,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>127824694</v>
+        <v>127824725</v>
       </c>
       <c r="B141" t="n">
-        <v>79618</v>
+        <v>57832</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14292,21 +14292,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>103021</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14316,10 +14316,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811716</v>
+        <v>811800</v>
       </c>
       <c r="R141" t="n">
-        <v>7390763</v>
+        <v>7390892</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -14766,10 +14766,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>127824690</v>
+        <v>127824694</v>
       </c>
       <c r="B146" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -14777,21 +14777,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -14801,10 +14801,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811721</v>
+        <v>811716</v>
       </c>
       <c r="R146" t="n">
-        <v>7390757</v>
+        <v>7390763</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -14863,10 +14863,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>127824725</v>
+        <v>127824690</v>
       </c>
       <c r="B147" t="n">
-        <v>57832</v>
+        <v>79647</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -14874,21 +14874,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -14898,10 +14898,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811800</v>
+        <v>811721</v>
       </c>
       <c r="R147" t="n">
-        <v>7390892</v>
+        <v>7390757</v>
       </c>
       <c r="S147" t="n">
         <v>1</v>
@@ -15057,10 +15057,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>127824688</v>
+        <v>127824777</v>
       </c>
       <c r="B149" t="n">
-        <v>79647</v>
+        <v>82870</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15068,21 +15068,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15092,10 +15092,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>812058</v>
+        <v>811935</v>
       </c>
       <c r="R149" t="n">
-        <v>7391223</v>
+        <v>7390835</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -15154,10 +15154,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>127824777</v>
+        <v>127824688</v>
       </c>
       <c r="B150" t="n">
-        <v>82870</v>
+        <v>79647</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15165,21 +15165,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15189,10 +15189,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811935</v>
+        <v>812058</v>
       </c>
       <c r="R150" t="n">
-        <v>7390835</v>
+        <v>7391223</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -15842,10 +15842,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>127824724</v>
+        <v>127824755</v>
       </c>
       <c r="B157" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -15853,38 +15853,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>811806</v>
+        <v>812164</v>
       </c>
       <c r="R157" t="n">
-        <v>7390821</v>
+        <v>7391415</v>
       </c>
       <c r="S157" t="n">
         <v>1</v>
@@ -15943,10 +15939,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>127824755</v>
+        <v>127824724</v>
       </c>
       <c r="B158" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -15954,34 +15950,38 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P158" t="inlineStr">
         <is>
           <t>Fatikvarre, Lu lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>812164</v>
+        <v>811806</v>
       </c>
       <c r="R158" t="n">
-        <v>7391415</v>
+        <v>7390821</v>
       </c>
       <c r="S158" t="n">
         <v>1</v>
@@ -16913,32 +16913,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>127824781</v>
+        <v>127824689</v>
       </c>
       <c r="B168" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -16948,10 +16948,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811927</v>
+        <v>811755</v>
       </c>
       <c r="R168" t="n">
-        <v>7390809</v>
+        <v>7390737</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -17010,32 +17010,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>127824767</v>
+        <v>127824781</v>
       </c>
       <c r="B169" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17045,10 +17045,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811966</v>
+        <v>811927</v>
       </c>
       <c r="R169" t="n">
-        <v>7390830</v>
+        <v>7390809</v>
       </c>
       <c r="S169" t="n">
         <v>1</v>
@@ -17107,10 +17107,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>127824689</v>
+        <v>127824767</v>
       </c>
       <c r="B170" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17118,21 +17118,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17142,10 +17142,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811755</v>
+        <v>811966</v>
       </c>
       <c r="R170" t="n">
-        <v>7390737</v>
+        <v>7390830</v>
       </c>
       <c r="S170" t="n">
         <v>1</v>
@@ -17204,10 +17204,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>127824778</v>
+        <v>127824765</v>
       </c>
       <c r="B171" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17215,21 +17215,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17239,10 +17239,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811927</v>
+        <v>811918</v>
       </c>
       <c r="R171" t="n">
-        <v>7390802</v>
+        <v>7390852</v>
       </c>
       <c r="S171" t="n">
         <v>1</v>
@@ -17301,10 +17301,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>127824772</v>
+        <v>127824759</v>
       </c>
       <c r="B172" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17312,21 +17312,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17336,10 +17336,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>812010</v>
+        <v>811950</v>
       </c>
       <c r="R172" t="n">
-        <v>7391123</v>
+        <v>7391109</v>
       </c>
       <c r="S172" t="n">
         <v>1</v>
@@ -17398,10 +17398,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>127824765</v>
+        <v>127824778</v>
       </c>
       <c r="B173" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -17409,21 +17409,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -17433,10 +17433,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811918</v>
+        <v>811927</v>
       </c>
       <c r="R173" t="n">
-        <v>7390852</v>
+        <v>7390802</v>
       </c>
       <c r="S173" t="n">
         <v>1</v>
@@ -17495,10 +17495,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>127824759</v>
+        <v>127824772</v>
       </c>
       <c r="B174" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -17506,21 +17506,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -17530,10 +17530,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811950</v>
+        <v>812010</v>
       </c>
       <c r="R174" t="n">
-        <v>7391109</v>
+        <v>7391123</v>
       </c>
       <c r="S174" t="n">
         <v>1</v>
@@ -17592,10 +17592,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>127824752</v>
+        <v>127824743</v>
       </c>
       <c r="B175" t="n">
-        <v>58042</v>
+        <v>79053</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -17603,21 +17603,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103015</v>
+        <v>6434</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -17627,10 +17627,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>812063</v>
+        <v>811966</v>
       </c>
       <c r="R175" t="n">
-        <v>7391237</v>
+        <v>7390830</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -17689,7 +17689,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>127824743</v>
+        <v>127824740</v>
       </c>
       <c r="B176" t="n">
         <v>79053</v>
@@ -17724,10 +17724,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811966</v>
+        <v>812040</v>
       </c>
       <c r="R176" t="n">
-        <v>7390830</v>
+        <v>7391193</v>
       </c>
       <c r="S176" t="n">
         <v>1</v>
@@ -17786,10 +17786,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>127824740</v>
+        <v>127824752</v>
       </c>
       <c r="B177" t="n">
-        <v>79053</v>
+        <v>58042</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17797,21 +17797,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6434</v>
+        <v>103015</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -17821,10 +17821,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>812040</v>
+        <v>812063</v>
       </c>
       <c r="R177" t="n">
-        <v>7391193</v>
+        <v>7391237</v>
       </c>
       <c r="S177" t="n">
         <v>1</v>
@@ -18950,10 +18950,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>127824774</v>
+        <v>127824770</v>
       </c>
       <c r="B189" t="n">
-        <v>82870</v>
+        <v>79029</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -18961,21 +18961,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -18985,10 +18985,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811971</v>
+        <v>811800</v>
       </c>
       <c r="R189" t="n">
-        <v>7391094</v>
+        <v>7390865</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -19047,32 +19047,32 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>127824773</v>
+        <v>127824745</v>
       </c>
       <c r="B190" t="n">
-        <v>82870</v>
+        <v>79053</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1312</v>
+        <v>6434</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19082,10 +19082,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>811989</v>
+        <v>811913</v>
       </c>
       <c r="R190" t="n">
-        <v>7391103</v>
+        <v>7390816</v>
       </c>
       <c r="S190" t="n">
         <v>1</v>
@@ -19144,10 +19144,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>127824770</v>
+        <v>127824774</v>
       </c>
       <c r="B191" t="n">
-        <v>79029</v>
+        <v>82870</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -19155,21 +19155,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -19179,10 +19179,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811800</v>
+        <v>811971</v>
       </c>
       <c r="R191" t="n">
-        <v>7390865</v>
+        <v>7391094</v>
       </c>
       <c r="S191" t="n">
         <v>1</v>
@@ -19241,32 +19241,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>127824745</v>
+        <v>127824773</v>
       </c>
       <c r="B192" t="n">
-        <v>79053</v>
+        <v>82870</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6434</v>
+        <v>1312</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811913</v>
+        <v>811989</v>
       </c>
       <c r="R192" t="n">
-        <v>7390816</v>
+        <v>7391103</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>

--- a/artfynd/A 31333-2025 artfynd.xlsx
+++ b/artfynd/A 31333-2025 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127706925</v>
+        <v>127709694</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811866</v>
+        <v>811441</v>
       </c>
       <c r="R14" t="n">
-        <v>7390863</v>
+        <v>7391158</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1937,19 +1937,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127709694</v>
+        <v>127706914</v>
       </c>
       <c r="B15" t="n">
         <v>79647</v>
@@ -1980,17 +1980,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811441</v>
+        <v>811645</v>
       </c>
       <c r="R15" t="n">
-        <v>7391158</v>
+        <v>7390971</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2034,19 +2034,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127706914</v>
+        <v>127709695</v>
       </c>
       <c r="B16" t="n">
         <v>79647</v>
@@ -2077,17 +2077,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811645</v>
+        <v>811430</v>
       </c>
       <c r="R16" t="n">
-        <v>7390971</v>
+        <v>7391046</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2131,19 +2131,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127709695</v>
+        <v>127709699</v>
       </c>
       <c r="B17" t="n">
         <v>79647</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811430</v>
+        <v>811707</v>
       </c>
       <c r="R17" t="n">
-        <v>7391046</v>
+        <v>7390941</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127709699</v>
+        <v>127706925</v>
       </c>
       <c r="B18" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,37 +2251,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811707</v>
+        <v>811866</v>
       </c>
       <c r="R18" t="n">
-        <v>7390941</v>
+        <v>7390863</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127709758</v>
+        <v>127709741</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811621</v>
+        <v>811489</v>
       </c>
       <c r="R26" t="n">
-        <v>7390981</v>
+        <v>7391186</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3130,32 +3130,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127709730</v>
+        <v>127709703</v>
       </c>
       <c r="B27" t="n">
-        <v>79053</v>
+        <v>79618</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6434</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811452</v>
+        <v>811724</v>
       </c>
       <c r="R27" t="n">
-        <v>7391057</v>
+        <v>7390998</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3209,6 +3209,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3227,10 +3228,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127709736</v>
+        <v>127709790</v>
       </c>
       <c r="B28" t="n">
-        <v>79053</v>
+        <v>92642</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3239,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3263,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811662</v>
+        <v>811610</v>
       </c>
       <c r="R28" t="n">
-        <v>7390926</v>
+        <v>7391012</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3324,32 +3325,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127709741</v>
+        <v>127709786</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3360,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811489</v>
+        <v>811612</v>
       </c>
       <c r="R29" t="n">
-        <v>7391186</v>
+        <v>7390987</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3421,32 +3422,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127709703</v>
+        <v>127709779</v>
       </c>
       <c r="B30" t="n">
-        <v>79618</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3457,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811724</v>
+        <v>811561</v>
       </c>
       <c r="R30" t="n">
-        <v>7390998</v>
+        <v>7391108</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3500,7 +3501,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127709790</v>
+        <v>127709796</v>
       </c>
       <c r="B31" t="n">
         <v>92642</v>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811610</v>
+        <v>811672</v>
       </c>
       <c r="R31" t="n">
-        <v>7391012</v>
+        <v>7391010</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3616,48 +3616,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127709786</v>
+        <v>127706927</v>
       </c>
       <c r="B32" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Fatikvarre norra, Lu lm</t>
+          <t>Fatikberget, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811612</v>
+        <v>811760</v>
       </c>
       <c r="R32" t="n">
-        <v>7390987</v>
+        <v>7390859</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3701,44 +3701,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Cecilia Goldkuhl, Marie Karlsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127709779</v>
+        <v>127709758</v>
       </c>
       <c r="B33" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811561</v>
+        <v>811621</v>
       </c>
       <c r="R33" t="n">
-        <v>7391108</v>
+        <v>7390981</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127709796</v>
+        <v>127709730</v>
       </c>
       <c r="B34" t="n">
-        <v>92642</v>
+        <v>79053</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3821,21 +3821,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811672</v>
+        <v>811452</v>
       </c>
       <c r="R34" t="n">
-        <v>7391010</v>
+        <v>7391057</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3907,48 +3907,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127706927</v>
+        <v>127709736</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Fatikberget, Lu lm</t>
+          <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811760</v>
+        <v>811662</v>
       </c>
       <c r="R35" t="n">
-        <v>7390859</v>
+        <v>7390926</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3992,12 +3992,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Marie Karlsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -9894,32 +9894,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127709693</v>
+        <v>127709795</v>
       </c>
       <c r="B96" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9929,10 +9929,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811486</v>
+        <v>811676</v>
       </c>
       <c r="R96" t="n">
-        <v>7391112</v>
+        <v>7391004</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -9991,45 +9991,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127709795</v>
+        <v>127709799</v>
       </c>
       <c r="B97" t="n">
-        <v>92642</v>
+        <v>92636</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811676</v>
+        <v>811707</v>
       </c>
       <c r="R97" t="n">
-        <v>7391004</v>
+        <v>7390860</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10070,6 +10074,7 @@
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -10088,49 +10093,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127709799</v>
+        <v>127709783</v>
       </c>
       <c r="B98" t="n">
-        <v>92636</v>
+        <v>92642</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Fatikvarre norra, Lu lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811707</v>
+        <v>811387</v>
       </c>
       <c r="R98" t="n">
-        <v>7390860</v>
+        <v>7391146</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -10171,7 +10172,6 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -10190,32 +10190,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127709783</v>
+        <v>127709693</v>
       </c>
       <c r="B99" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10225,10 +10225,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811387</v>
+        <v>811486</v>
       </c>
       <c r="R99" t="n">
-        <v>7391146</v>
+        <v>7391112</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -13214,27 +13214,27 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>127824735</v>
+        <v>127824751</v>
       </c>
       <c r="B130" t="n">
-        <v>57669</v>
+        <v>57776</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100049</v>
+        <v>103031</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -13249,10 +13249,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811831</v>
+        <v>812037</v>
       </c>
       <c r="R130" t="n">
-        <v>7390950</v>
+        <v>7391151</v>
       </c>
       <c r="S130" t="n">
         <v>1</v>
@@ -13311,27 +13311,27 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>127824751</v>
+        <v>127824735</v>
       </c>
       <c r="B131" t="n">
-        <v>57776</v>
+        <v>57669</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -13346,10 +13346,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>812037</v>
+        <v>811831</v>
       </c>
       <c r="R131" t="n">
-        <v>7391151</v>
+        <v>7390950</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -13699,32 +13699,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>127824782</v>
+        <v>127824753</v>
       </c>
       <c r="B135" t="n">
-        <v>92642</v>
+        <v>81004</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>1049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811902</v>
+        <v>811752</v>
       </c>
       <c r="R135" t="n">
-        <v>7390765</v>
+        <v>7390828</v>
       </c>
       <c r="S135" t="n">
         <v>1</v>
@@ -13796,32 +13796,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>127824703</v>
+        <v>127824782</v>
       </c>
       <c r="B136" t="n">
-        <v>91352</v>
+        <v>92642</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -13831,10 +13831,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811762</v>
+        <v>811902</v>
       </c>
       <c r="R136" t="n">
-        <v>7390826</v>
+        <v>7390765</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -13893,10 +13893,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>127824775</v>
+        <v>127824703</v>
       </c>
       <c r="B137" t="n">
-        <v>82870</v>
+        <v>91352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -13904,21 +13904,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </